--- a/傷病手当金算定表_v2.xlsx
+++ b/傷病手当金算定表_v2.xlsx
@@ -19,6 +19,12 @@
     <definedName name="CLAIM_TO">'入力'!$C$70</definedName>
     <definedName name="EMP_ID">'入力'!$C$4</definedName>
     <definedName name="EMP_NAME">'入力'!$C$5</definedName>
+    <definedName name="P_START">'入力'!$J$5</definedName>
+    <definedName name="P_LEGAL_END">'入力'!$J$6</definedName>
+    <definedName name="P_ADD_START">'入力'!$J$7</definedName>
+    <definedName name="P_ADD_END">'入力'!$J$8</definedName>
+    <definedName name="P_FINAL">'入力'!$J$9</definedName>
+    <definedName name="EXT_DAYS">'入力'!$D$55</definedName>
     <definedName name="DAILY_RATE">'入力'!$J$10</definedName>
     <definedName name="CALC_TABLE">'算定表'!$A$6:$O$53</definedName>
     <definedName name="SET_PREFIX">'設定'!$B$3</definedName>
@@ -40,11 +46,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0;0"/>
     <numFmt numFmtId="165" formatCode="yyyy/m"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="yyyy/m/d"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="169" formatCode="0&quot;日&quot;"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -288,7 +296,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -423,19 +431,32 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -844,7 +865,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>使い方 ／ 入力（黄色セルのみ入力） ／ 月別集計（基幹入力用） ／ 算定表（結果。印刷用） ／ カレンダーマスタ ／ 請求シート雛形（マクロが複写。書式・文言を直せる） ／ 設定（マクロのメッセージ・シート名）</t>
+          <t>使い方 ／ 入力（黄色セルのみ入力） ／ 月別集計（基幹入力用） ／ 算定表（結果。印刷用） ／ カレンダーマスタ（開始月を入れると自動作成） ／ 請求シート雛形（マクロが複写。書式・文言を直せる） ／ 設定（マクロのメッセージ・シート名）</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2025,15 @@
     <row r="55">
       <c r="A55" s="62" t="inlineStr">
         <is>
-          <t>延長なし</t>
+          <t>基準・合計</t>
         </is>
       </c>
       <c r="B55" s="28" t="n"/>
       <c r="C55" s="28" t="n"/>
-      <c r="D55" s="28" t="n"/>
+      <c r="D55" s="48">
+        <f>SUMIFS(D56:D65,E56:E65,"法定")+SUMIFS(D56:D65,E56:E65,"附加")</f>
+        <v/>
+      </c>
       <c r="E55" s="28" t="n"/>
       <c r="F55" s="15">
         <f>DATE(YEAR($J$5)+1,MONTH($J$5)+6,DAY($J$5)-1)</f>
@@ -2547,6 +2571,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="14">
+        <f>"支給開始日：" &amp; TEXT(入力!J5,"yyyy/m/d") &amp; "　　法定給付の末日：" &amp; TEXT(入力!J6,"yyyy/m/d") &amp; "　　附加給付：" &amp; IF(入力!J9&gt;入力!J6,TEXT(入力!J7,"yyyy/m/d") &amp; "～" &amp; TEXT(入力!J8,"yyyy/m/d"),"なし") &amp; "　　算定の最終日：" &amp; TEXT(入力!J9,"yyyy/m/d")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14">
+        <f>"傷病手当日額（支給開始月で固定）：" &amp; TEXT(入力!J10,"#,##0") &amp; "円" &amp; IF(入力!D55&gt;0,"　　出勤による延長：" &amp; 入力!D55 &amp; "日","")</f>
+        <v/>
+      </c>
+    </row>
     <row r="5" ht="34" customHeight="1" s="39">
       <c r="A5" s="18" t="inlineStr">
         <is>
@@ -4424,7 +4460,7 @@
         <v/>
       </c>
       <c r="H6" s="52">
-        <f>IF(F6="","",IFERROR(VLOOKUP(DATE(B6,C6,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B6,C6,1),EOMONTH(F6,0))))</f>
+        <f>IF(F6="","",IFERROR(VLOOKUP(DATE(B6,C6,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B6,C6,1),EOMONTH(F6,0))))</f>
         <v/>
       </c>
       <c r="I6" s="33">
@@ -4498,7 +4534,7 @@
         <v/>
       </c>
       <c r="H7" s="52">
-        <f>IF(F7="","",IFERROR(VLOOKUP(DATE(B7,C7,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B7,C7,1),EOMONTH(F7,0))))</f>
+        <f>IF(F7="","",IFERROR(VLOOKUP(DATE(B7,C7,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B7,C7,1),EOMONTH(F7,0))))</f>
         <v/>
       </c>
       <c r="I7" s="33">
@@ -4572,7 +4608,7 @@
         <v/>
       </c>
       <c r="H8" s="52">
-        <f>IF(F8="","",IFERROR(VLOOKUP(DATE(B8,C8,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B8,C8,1),EOMONTH(F8,0))))</f>
+        <f>IF(F8="","",IFERROR(VLOOKUP(DATE(B8,C8,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B8,C8,1),EOMONTH(F8,0))))</f>
         <v/>
       </c>
       <c r="I8" s="33">
@@ -4646,7 +4682,7 @@
         <v/>
       </c>
       <c r="H9" s="52">
-        <f>IF(F9="","",IFERROR(VLOOKUP(DATE(B9,C9,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B9,C9,1),EOMONTH(F9,0))))</f>
+        <f>IF(F9="","",IFERROR(VLOOKUP(DATE(B9,C9,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B9,C9,1),EOMONTH(F9,0))))</f>
         <v/>
       </c>
       <c r="I9" s="33">
@@ -4720,7 +4756,7 @@
         <v/>
       </c>
       <c r="H10" s="52">
-        <f>IF(F10="","",IFERROR(VLOOKUP(DATE(B10,C10,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B10,C10,1),EOMONTH(F10,0))))</f>
+        <f>IF(F10="","",IFERROR(VLOOKUP(DATE(B10,C10,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B10,C10,1),EOMONTH(F10,0))))</f>
         <v/>
       </c>
       <c r="I10" s="33">
@@ -4794,7 +4830,7 @@
         <v/>
       </c>
       <c r="H11" s="52">
-        <f>IF(F11="","",IFERROR(VLOOKUP(DATE(B11,C11,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B11,C11,1),EOMONTH(F11,0))))</f>
+        <f>IF(F11="","",IFERROR(VLOOKUP(DATE(B11,C11,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B11,C11,1),EOMONTH(F11,0))))</f>
         <v/>
       </c>
       <c r="I11" s="33">
@@ -4868,7 +4904,7 @@
         <v/>
       </c>
       <c r="H12" s="52">
-        <f>IF(F12="","",IFERROR(VLOOKUP(DATE(B12,C12,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B12,C12,1),EOMONTH(F12,0))))</f>
+        <f>IF(F12="","",IFERROR(VLOOKUP(DATE(B12,C12,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B12,C12,1),EOMONTH(F12,0))))</f>
         <v/>
       </c>
       <c r="I12" s="33">
@@ -4942,7 +4978,7 @@
         <v/>
       </c>
       <c r="H13" s="52">
-        <f>IF(F13="","",IFERROR(VLOOKUP(DATE(B13,C13,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B13,C13,1),EOMONTH(F13,0))))</f>
+        <f>IF(F13="","",IFERROR(VLOOKUP(DATE(B13,C13,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B13,C13,1),EOMONTH(F13,0))))</f>
         <v/>
       </c>
       <c r="I13" s="33">
@@ -5016,7 +5052,7 @@
         <v/>
       </c>
       <c r="H14" s="52">
-        <f>IF(F14="","",IFERROR(VLOOKUP(DATE(B14,C14,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B14,C14,1),EOMONTH(F14,0))))</f>
+        <f>IF(F14="","",IFERROR(VLOOKUP(DATE(B14,C14,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B14,C14,1),EOMONTH(F14,0))))</f>
         <v/>
       </c>
       <c r="I14" s="33">
@@ -5090,7 +5126,7 @@
         <v/>
       </c>
       <c r="H15" s="52">
-        <f>IF(F15="","",IFERROR(VLOOKUP(DATE(B15,C15,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B15,C15,1),EOMONTH(F15,0))))</f>
+        <f>IF(F15="","",IFERROR(VLOOKUP(DATE(B15,C15,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B15,C15,1),EOMONTH(F15,0))))</f>
         <v/>
       </c>
       <c r="I15" s="33">
@@ -5164,7 +5200,7 @@
         <v/>
       </c>
       <c r="H16" s="52">
-        <f>IF(F16="","",IFERROR(VLOOKUP(DATE(B16,C16,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B16,C16,1),EOMONTH(F16,0))))</f>
+        <f>IF(F16="","",IFERROR(VLOOKUP(DATE(B16,C16,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B16,C16,1),EOMONTH(F16,0))))</f>
         <v/>
       </c>
       <c r="I16" s="33">
@@ -5238,7 +5274,7 @@
         <v/>
       </c>
       <c r="H17" s="52">
-        <f>IF(F17="","",IFERROR(VLOOKUP(DATE(B17,C17,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B17,C17,1),EOMONTH(F17,0))))</f>
+        <f>IF(F17="","",IFERROR(VLOOKUP(DATE(B17,C17,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B17,C17,1),EOMONTH(F17,0))))</f>
         <v/>
       </c>
       <c r="I17" s="33">
@@ -5312,7 +5348,7 @@
         <v/>
       </c>
       <c r="H18" s="52">
-        <f>IF(F18="","",IFERROR(VLOOKUP(DATE(B18,C18,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B18,C18,1),EOMONTH(F18,0))))</f>
+        <f>IF(F18="","",IFERROR(VLOOKUP(DATE(B18,C18,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B18,C18,1),EOMONTH(F18,0))))</f>
         <v/>
       </c>
       <c r="I18" s="33">
@@ -5386,7 +5422,7 @@
         <v/>
       </c>
       <c r="H19" s="52">
-        <f>IF(F19="","",IFERROR(VLOOKUP(DATE(B19,C19,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B19,C19,1),EOMONTH(F19,0))))</f>
+        <f>IF(F19="","",IFERROR(VLOOKUP(DATE(B19,C19,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B19,C19,1),EOMONTH(F19,0))))</f>
         <v/>
       </c>
       <c r="I19" s="33">
@@ -5460,7 +5496,7 @@
         <v/>
       </c>
       <c r="H20" s="52">
-        <f>IF(F20="","",IFERROR(VLOOKUP(DATE(B20,C20,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B20,C20,1),EOMONTH(F20,0))))</f>
+        <f>IF(F20="","",IFERROR(VLOOKUP(DATE(B20,C20,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B20,C20,1),EOMONTH(F20,0))))</f>
         <v/>
       </c>
       <c r="I20" s="33">
@@ -5534,7 +5570,7 @@
         <v/>
       </c>
       <c r="H21" s="52">
-        <f>IF(F21="","",IFERROR(VLOOKUP(DATE(B21,C21,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B21,C21,1),EOMONTH(F21,0))))</f>
+        <f>IF(F21="","",IFERROR(VLOOKUP(DATE(B21,C21,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B21,C21,1),EOMONTH(F21,0))))</f>
         <v/>
       </c>
       <c r="I21" s="33">
@@ -5608,7 +5644,7 @@
         <v/>
       </c>
       <c r="H22" s="52">
-        <f>IF(F22="","",IFERROR(VLOOKUP(DATE(B22,C22,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B22,C22,1),EOMONTH(F22,0))))</f>
+        <f>IF(F22="","",IFERROR(VLOOKUP(DATE(B22,C22,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B22,C22,1),EOMONTH(F22,0))))</f>
         <v/>
       </c>
       <c r="I22" s="33">
@@ -5682,7 +5718,7 @@
         <v/>
       </c>
       <c r="H23" s="52">
-        <f>IF(F23="","",IFERROR(VLOOKUP(DATE(B23,C23,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B23,C23,1),EOMONTH(F23,0))))</f>
+        <f>IF(F23="","",IFERROR(VLOOKUP(DATE(B23,C23,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B23,C23,1),EOMONTH(F23,0))))</f>
         <v/>
       </c>
       <c r="I23" s="33">
@@ -5756,7 +5792,7 @@
         <v/>
       </c>
       <c r="H24" s="52">
-        <f>IF(F24="","",IFERROR(VLOOKUP(DATE(B24,C24,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B24,C24,1),EOMONTH(F24,0))))</f>
+        <f>IF(F24="","",IFERROR(VLOOKUP(DATE(B24,C24,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B24,C24,1),EOMONTH(F24,0))))</f>
         <v/>
       </c>
       <c r="I24" s="33">
@@ -5830,7 +5866,7 @@
         <v/>
       </c>
       <c r="H25" s="52">
-        <f>IF(F25="","",IFERROR(VLOOKUP(DATE(B25,C25,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B25,C25,1),EOMONTH(F25,0))))</f>
+        <f>IF(F25="","",IFERROR(VLOOKUP(DATE(B25,C25,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B25,C25,1),EOMONTH(F25,0))))</f>
         <v/>
       </c>
       <c r="I25" s="33">
@@ -5904,7 +5940,7 @@
         <v/>
       </c>
       <c r="H26" s="52">
-        <f>IF(F26="","",IFERROR(VLOOKUP(DATE(B26,C26,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B26,C26,1),EOMONTH(F26,0))))</f>
+        <f>IF(F26="","",IFERROR(VLOOKUP(DATE(B26,C26,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B26,C26,1),EOMONTH(F26,0))))</f>
         <v/>
       </c>
       <c r="I26" s="33">
@@ -5978,7 +6014,7 @@
         <v/>
       </c>
       <c r="H27" s="52">
-        <f>IF(F27="","",IFERROR(VLOOKUP(DATE(B27,C27,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B27,C27,1),EOMONTH(F27,0))))</f>
+        <f>IF(F27="","",IFERROR(VLOOKUP(DATE(B27,C27,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B27,C27,1),EOMONTH(F27,0))))</f>
         <v/>
       </c>
       <c r="I27" s="33">
@@ -6052,7 +6088,7 @@
         <v/>
       </c>
       <c r="H28" s="52">
-        <f>IF(F28="","",IFERROR(VLOOKUP(DATE(B28,C28,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B28,C28,1),EOMONTH(F28,0))))</f>
+        <f>IF(F28="","",IFERROR(VLOOKUP(DATE(B28,C28,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B28,C28,1),EOMONTH(F28,0))))</f>
         <v/>
       </c>
       <c r="I28" s="33">
@@ -6126,7 +6162,7 @@
         <v/>
       </c>
       <c r="H29" s="52">
-        <f>IF(F29="","",IFERROR(VLOOKUP(DATE(B29,C29,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B29,C29,1),EOMONTH(F29,0))))</f>
+        <f>IF(F29="","",IFERROR(VLOOKUP(DATE(B29,C29,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B29,C29,1),EOMONTH(F29,0))))</f>
         <v/>
       </c>
       <c r="I29" s="33">
@@ -6200,7 +6236,7 @@
         <v/>
       </c>
       <c r="H30" s="52">
-        <f>IF(F30="","",IFERROR(VLOOKUP(DATE(B30,C30,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B30,C30,1),EOMONTH(F30,0))))</f>
+        <f>IF(F30="","",IFERROR(VLOOKUP(DATE(B30,C30,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B30,C30,1),EOMONTH(F30,0))))</f>
         <v/>
       </c>
       <c r="I30" s="33">
@@ -6274,7 +6310,7 @@
         <v/>
       </c>
       <c r="H31" s="52">
-        <f>IF(F31="","",IFERROR(VLOOKUP(DATE(B31,C31,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B31,C31,1),EOMONTH(F31,0))))</f>
+        <f>IF(F31="","",IFERROR(VLOOKUP(DATE(B31,C31,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B31,C31,1),EOMONTH(F31,0))))</f>
         <v/>
       </c>
       <c r="I31" s="33">
@@ -6348,7 +6384,7 @@
         <v/>
       </c>
       <c r="H32" s="52">
-        <f>IF(F32="","",IFERROR(VLOOKUP(DATE(B32,C32,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B32,C32,1),EOMONTH(F32,0))))</f>
+        <f>IF(F32="","",IFERROR(VLOOKUP(DATE(B32,C32,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B32,C32,1),EOMONTH(F32,0))))</f>
         <v/>
       </c>
       <c r="I32" s="33">
@@ -6422,7 +6458,7 @@
         <v/>
       </c>
       <c r="H33" s="52">
-        <f>IF(F33="","",IFERROR(VLOOKUP(DATE(B33,C33,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B33,C33,1),EOMONTH(F33,0))))</f>
+        <f>IF(F33="","",IFERROR(VLOOKUP(DATE(B33,C33,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B33,C33,1),EOMONTH(F33,0))))</f>
         <v/>
       </c>
       <c r="I33" s="33">
@@ -6496,7 +6532,7 @@
         <v/>
       </c>
       <c r="H34" s="52">
-        <f>IF(F34="","",IFERROR(VLOOKUP(DATE(B34,C34,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B34,C34,1),EOMONTH(F34,0))))</f>
+        <f>IF(F34="","",IFERROR(VLOOKUP(DATE(B34,C34,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B34,C34,1),EOMONTH(F34,0))))</f>
         <v/>
       </c>
       <c r="I34" s="33">
@@ -6570,7 +6606,7 @@
         <v/>
       </c>
       <c r="H35" s="52">
-        <f>IF(F35="","",IFERROR(VLOOKUP(DATE(B35,C35,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B35,C35,1),EOMONTH(F35,0))))</f>
+        <f>IF(F35="","",IFERROR(VLOOKUP(DATE(B35,C35,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B35,C35,1),EOMONTH(F35,0))))</f>
         <v/>
       </c>
       <c r="I35" s="33">
@@ -6644,7 +6680,7 @@
         <v/>
       </c>
       <c r="H36" s="52">
-        <f>IF(F36="","",IFERROR(VLOOKUP(DATE(B36,C36,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B36,C36,1),EOMONTH(F36,0))))</f>
+        <f>IF(F36="","",IFERROR(VLOOKUP(DATE(B36,C36,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B36,C36,1),EOMONTH(F36,0))))</f>
         <v/>
       </c>
       <c r="I36" s="33">
@@ -6718,7 +6754,7 @@
         <v/>
       </c>
       <c r="H37" s="52">
-        <f>IF(F37="","",IFERROR(VLOOKUP(DATE(B37,C37,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B37,C37,1),EOMONTH(F37,0))))</f>
+        <f>IF(F37="","",IFERROR(VLOOKUP(DATE(B37,C37,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B37,C37,1),EOMONTH(F37,0))))</f>
         <v/>
       </c>
       <c r="I37" s="33">
@@ -6792,7 +6828,7 @@
         <v/>
       </c>
       <c r="H38" s="52">
-        <f>IF(F38="","",IFERROR(VLOOKUP(DATE(B38,C38,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B38,C38,1),EOMONTH(F38,0))))</f>
+        <f>IF(F38="","",IFERROR(VLOOKUP(DATE(B38,C38,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B38,C38,1),EOMONTH(F38,0))))</f>
         <v/>
       </c>
       <c r="I38" s="33">
@@ -6866,7 +6902,7 @@
         <v/>
       </c>
       <c r="H39" s="52">
-        <f>IF(F39="","",IFERROR(VLOOKUP(DATE(B39,C39,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B39,C39,1),EOMONTH(F39,0))))</f>
+        <f>IF(F39="","",IFERROR(VLOOKUP(DATE(B39,C39,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B39,C39,1),EOMONTH(F39,0))))</f>
         <v/>
       </c>
       <c r="I39" s="33">
@@ -6940,7 +6976,7 @@
         <v/>
       </c>
       <c r="H40" s="52">
-        <f>IF(F40="","",IFERROR(VLOOKUP(DATE(B40,C40,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B40,C40,1),EOMONTH(F40,0))))</f>
+        <f>IF(F40="","",IFERROR(VLOOKUP(DATE(B40,C40,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B40,C40,1),EOMONTH(F40,0))))</f>
         <v/>
       </c>
       <c r="I40" s="33">
@@ -7014,7 +7050,7 @@
         <v/>
       </c>
       <c r="H41" s="52">
-        <f>IF(F41="","",IFERROR(VLOOKUP(DATE(B41,C41,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B41,C41,1),EOMONTH(F41,0))))</f>
+        <f>IF(F41="","",IFERROR(VLOOKUP(DATE(B41,C41,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B41,C41,1),EOMONTH(F41,0))))</f>
         <v/>
       </c>
       <c r="I41" s="33">
@@ -7088,7 +7124,7 @@
         <v/>
       </c>
       <c r="H42" s="52">
-        <f>IF(F42="","",IFERROR(VLOOKUP(DATE(B42,C42,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B42,C42,1),EOMONTH(F42,0))))</f>
+        <f>IF(F42="","",IFERROR(VLOOKUP(DATE(B42,C42,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B42,C42,1),EOMONTH(F42,0))))</f>
         <v/>
       </c>
       <c r="I42" s="33">
@@ -7162,7 +7198,7 @@
         <v/>
       </c>
       <c r="H43" s="52">
-        <f>IF(F43="","",IFERROR(VLOOKUP(DATE(B43,C43,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B43,C43,1),EOMONTH(F43,0))))</f>
+        <f>IF(F43="","",IFERROR(VLOOKUP(DATE(B43,C43,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B43,C43,1),EOMONTH(F43,0))))</f>
         <v/>
       </c>
       <c r="I43" s="33">
@@ -7236,7 +7272,7 @@
         <v/>
       </c>
       <c r="H44" s="52">
-        <f>IF(F44="","",IFERROR(VLOOKUP(DATE(B44,C44,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B44,C44,1),EOMONTH(F44,0))))</f>
+        <f>IF(F44="","",IFERROR(VLOOKUP(DATE(B44,C44,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B44,C44,1),EOMONTH(F44,0))))</f>
         <v/>
       </c>
       <c r="I44" s="33">
@@ -7310,7 +7346,7 @@
         <v/>
       </c>
       <c r="H45" s="52">
-        <f>IF(F45="","",IFERROR(VLOOKUP(DATE(B45,C45,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B45,C45,1),EOMONTH(F45,0))))</f>
+        <f>IF(F45="","",IFERROR(VLOOKUP(DATE(B45,C45,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B45,C45,1),EOMONTH(F45,0))))</f>
         <v/>
       </c>
       <c r="I45" s="33">
@@ -7384,7 +7420,7 @@
         <v/>
       </c>
       <c r="H46" s="52">
-        <f>IF(F46="","",IFERROR(VLOOKUP(DATE(B46,C46,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B46,C46,1),EOMONTH(F46,0))))</f>
+        <f>IF(F46="","",IFERROR(VLOOKUP(DATE(B46,C46,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B46,C46,1),EOMONTH(F46,0))))</f>
         <v/>
       </c>
       <c r="I46" s="33">
@@ -7458,7 +7494,7 @@
         <v/>
       </c>
       <c r="H47" s="52">
-        <f>IF(F47="","",IFERROR(VLOOKUP(DATE(B47,C47,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B47,C47,1),EOMONTH(F47,0))))</f>
+        <f>IF(F47="","",IFERROR(VLOOKUP(DATE(B47,C47,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B47,C47,1),EOMONTH(F47,0))))</f>
         <v/>
       </c>
       <c r="I47" s="33">
@@ -7532,7 +7568,7 @@
         <v/>
       </c>
       <c r="H48" s="52">
-        <f>IF(F48="","",IFERROR(VLOOKUP(DATE(B48,C48,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B48,C48,1),EOMONTH(F48,0))))</f>
+        <f>IF(F48="","",IFERROR(VLOOKUP(DATE(B48,C48,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B48,C48,1),EOMONTH(F48,0))))</f>
         <v/>
       </c>
       <c r="I48" s="33">
@@ -7606,7 +7642,7 @@
         <v/>
       </c>
       <c r="H49" s="52">
-        <f>IF(F49="","",IFERROR(VLOOKUP(DATE(B49,C49,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B49,C49,1),EOMONTH(F49,0))))</f>
+        <f>IF(F49="","",IFERROR(VLOOKUP(DATE(B49,C49,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B49,C49,1),EOMONTH(F49,0))))</f>
         <v/>
       </c>
       <c r="I49" s="33">
@@ -7680,7 +7716,7 @@
         <v/>
       </c>
       <c r="H50" s="52">
-        <f>IF(F50="","",IFERROR(VLOOKUP(DATE(B50,C50,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B50,C50,1),EOMONTH(F50,0))))</f>
+        <f>IF(F50="","",IFERROR(VLOOKUP(DATE(B50,C50,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B50,C50,1),EOMONTH(F50,0))))</f>
         <v/>
       </c>
       <c r="I50" s="33">
@@ -7754,7 +7790,7 @@
         <v/>
       </c>
       <c r="H51" s="52">
-        <f>IF(F51="","",IFERROR(VLOOKUP(DATE(B51,C51,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B51,C51,1),EOMONTH(F51,0))))</f>
+        <f>IF(F51="","",IFERROR(VLOOKUP(DATE(B51,C51,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B51,C51,1),EOMONTH(F51,0))))</f>
         <v/>
       </c>
       <c r="I51" s="33">
@@ -7828,7 +7864,7 @@
         <v/>
       </c>
       <c r="H52" s="52">
-        <f>IF(F52="","",IFERROR(VLOOKUP(DATE(B52,C52,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B52,C52,1),EOMONTH(F52,0))))</f>
+        <f>IF(F52="","",IFERROR(VLOOKUP(DATE(B52,C52,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B52,C52,1),EOMONTH(F52,0))))</f>
         <v/>
       </c>
       <c r="I52" s="33">
@@ -7902,7 +7938,7 @@
         <v/>
       </c>
       <c r="H53" s="52">
-        <f>IF(F53="","",IFERROR(VLOOKUP(DATE(B53,C53,1),カレンダーマスタ!$A$2:$B$97,2,0),NETWORKDAYS(DATE(B53,C53,1),EOMONTH(F53,0))))</f>
+        <f>IF(F53="","",IFERROR(VLOOKUP(DATE(B53,C53,1),カレンダーマスタ!$A$2:$B$121,2,0),NETWORKDAYS(DATE(B53,C53,1),EOMONTH(F53,0))))</f>
         <v/>
       </c>
       <c r="I53" s="33">
@@ -8157,803 +8193,2368 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col width="12" customWidth="1" style="39" min="1" max="1"/>
+    <col width="11" customWidth="1" style="39" min="1" max="1"/>
     <col width="16" customWidth="1" style="39" min="2" max="2"/>
+    <col width="14" customWidth="1" style="39" min="3" max="3"/>
+    <col width="11" customWidth="1" style="39" min="4" max="4"/>
+    <col width="3" customWidth="1" style="39" min="5" max="5"/>
+    <col width="16" customWidth="1" style="39" min="6" max="6"/>
+    <col width="10" customWidth="1" style="39" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>日付</t>
-        </is>
-      </c>
-      <c r="B1" s="41" t="inlineStr">
-        <is>
-          <t>勤務を要する日数</t>
-        </is>
-      </c>
-      <c r="D1" s="11" t="inlineStr">
-        <is>
-          <t>※月初日と、その月の「勤務を要する日数」（土日除く）。祝日等で変更する月はB列を直接修正。表にない月は自動で土日除外日数を計算します。</t>
+    <row r="1" ht="32" customHeight="1" s="39">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>勤務を要する日数
+（算定表で使う値）</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>土日を除く日数
+（自動）</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>個別修正</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>■ カレンダーマスタの使い方（月ごとの「勤務を要する日数」）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="n">
+      <c r="A2" s="66">
+        <f>DATE(YEAR($G$4),MONTH($G$4),1)</f>
+        <v/>
+      </c>
+      <c r="B2" s="48">
+        <f>IFERROR(IF(VLOOKUP(A2,$F$8:$G$37,2,0)="",C2,VLOOKUP(A2,$F$8:$G$37,2,0)),C2)</f>
+        <v/>
+      </c>
+      <c r="C2" s="48">
+        <f>NETWORKDAYS(A2,EOMONTH(A2,0))</f>
+        <v/>
+      </c>
+      <c r="D2" s="67">
+        <f>IF(ISNUMBER(MATCH(A2,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>※左の表は、下の「作成の開始月」から120か月分（10年）が自動で作られます。土日を除く日数が入ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="66">
+        <f>EDATE(A2,1)</f>
+        <v/>
+      </c>
+      <c r="B3" s="48">
+        <f>IFERROR(IF(VLOOKUP(A3,$F$8:$G$37,2,0)="",C3,VLOOKUP(A3,$F$8:$G$37,2,0)),C3)</f>
+        <v/>
+      </c>
+      <c r="C3" s="48">
+        <f>NETWORKDAYS(A3,EOMONTH(A3,0))</f>
+        <v/>
+      </c>
+      <c r="D3" s="67">
+        <f>IF(ISNUMBER(MATCH(A3,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>※祝日などで日数を変える月だけ、下の「個別に変える月」に入力します（左の表の B 列は自動で入れ替わります）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="66">
+        <f>EDATE(A3,1)</f>
+        <v/>
+      </c>
+      <c r="B4" s="48">
+        <f>IFERROR(IF(VLOOKUP(A4,$F$8:$G$37,2,0)="",C4,VLOOKUP(A4,$F$8:$G$37,2,0)),C4)</f>
+        <v/>
+      </c>
+      <c r="C4" s="48">
+        <f>NETWORKDAYS(A4,EOMONTH(A4,0))</f>
+        <v/>
+      </c>
+      <c r="D4" s="67">
+        <f>IF(ISNUMBER(MATCH(A4,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>作成の開始月</t>
+        </is>
+      </c>
+      <c r="G4" s="68" t="n">
         <v>43831</v>
       </c>
-      <c r="B2" s="43" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="58" t="n">
-        <v>43862</v>
-      </c>
-      <c r="B3" s="43" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="58" t="n">
-        <v>43891</v>
-      </c>
-      <c r="B4" s="43" t="n">
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>← 月を入れると、その月から120か月分が作られます（例：2020/1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="66">
+        <f>EDATE(A4,1)</f>
+        <v/>
+      </c>
+      <c r="B5" s="48">
+        <f>IFERROR(IF(VLOOKUP(A5,$F$8:$G$37,2,0)="",C5,VLOOKUP(A5,$F$8:$G$37,2,0)),C5)</f>
+        <v/>
+      </c>
+      <c r="C5" s="48">
+        <f>NETWORKDAYS(A5,EOMONTH(A5,0))</f>
+        <v/>
+      </c>
+      <c r="D5" s="67">
+        <f>IF(ISNUMBER(MATCH(A5,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="66">
+        <f>EDATE(A5,1)</f>
+        <v/>
+      </c>
+      <c r="B6" s="48">
+        <f>IFERROR(IF(VLOOKUP(A6,$F$8:$G$37,2,0)="",C6,VLOOKUP(A6,$F$8:$G$37,2,0)),C6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="48">
+        <f>NETWORKDAYS(A6,EOMONTH(A6,0))</f>
+        <v/>
+      </c>
+      <c r="D6" s="67">
+        <f>IF(ISNUMBER(MATCH(A6,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>■ 個別に変える月（30件まで）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="66">
+        <f>EDATE(A6,1)</f>
+        <v/>
+      </c>
+      <c r="B7" s="48">
+        <f>IFERROR(IF(VLOOKUP(A7,$F$8:$G$37,2,0)="",C7,VLOOKUP(A7,$F$8:$G$37,2,0)),C7)</f>
+        <v/>
+      </c>
+      <c r="C7" s="48">
+        <f>NETWORKDAYS(A7,EOMONTH(A7,0))</f>
+        <v/>
+      </c>
+      <c r="D7" s="67">
+        <f>IF(ISNUMBER(MATCH(A7,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>月（例：2025/1）</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>日数</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="66">
+        <f>EDATE(A7,1)</f>
+        <v/>
+      </c>
+      <c r="B8" s="48">
+        <f>IFERROR(IF(VLOOKUP(A8,$F$8:$G$37,2,0)="",C8,VLOOKUP(A8,$F$8:$G$37,2,0)),C8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="48">
+        <f>NETWORKDAYS(A8,EOMONTH(A8,0))</f>
+        <v/>
+      </c>
+      <c r="D8" s="67">
+        <f>IF(ISNUMBER(MATCH(A8,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F8" s="68" t="n">
+        <v>44531</v>
+      </c>
+      <c r="G8" s="69" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="58" t="n">
-        <v>43922</v>
-      </c>
-      <c r="B5" s="43" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="58" t="n">
-        <v>43952</v>
-      </c>
-      <c r="B6" s="43" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="58" t="n">
-        <v>43983</v>
-      </c>
-      <c r="B7" s="43" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="58" t="n">
-        <v>44013</v>
-      </c>
-      <c r="B8" s="43" t="n">
-        <v>23</v>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="58" t="n">
-        <v>44044</v>
-      </c>
-      <c r="B9" s="43" t="n">
-        <v>21</v>
-      </c>
+      <c r="A9" s="66">
+        <f>EDATE(A8,1)</f>
+        <v/>
+      </c>
+      <c r="B9" s="48">
+        <f>IFERROR(IF(VLOOKUP(A9,$F$8:$G$37,2,0)="",C9,VLOOKUP(A9,$F$8:$G$37,2,0)),C9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="48">
+        <f>NETWORKDAYS(A9,EOMONTH(A9,0))</f>
+        <v/>
+      </c>
+      <c r="D9" s="67">
+        <f>IF(ISNUMBER(MATCH(A9,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F9" s="68" t="n"/>
+      <c r="G9" s="69" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="58" t="n">
-        <v>44075</v>
-      </c>
-      <c r="B10" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A10" s="66">
+        <f>EDATE(A9,1)</f>
+        <v/>
+      </c>
+      <c r="B10" s="48">
+        <f>IFERROR(IF(VLOOKUP(A10,$F$8:$G$37,2,0)="",C10,VLOOKUP(A10,$F$8:$G$37,2,0)),C10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="48">
+        <f>NETWORKDAYS(A10,EOMONTH(A10,0))</f>
+        <v/>
+      </c>
+      <c r="D10" s="67">
+        <f>IF(ISNUMBER(MATCH(A10,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F10" s="68" t="n"/>
+      <c r="G10" s="69" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="58" t="n">
-        <v>44105</v>
-      </c>
-      <c r="B11" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A11" s="66">
+        <f>EDATE(A10,1)</f>
+        <v/>
+      </c>
+      <c r="B11" s="48">
+        <f>IFERROR(IF(VLOOKUP(A11,$F$8:$G$37,2,0)="",C11,VLOOKUP(A11,$F$8:$G$37,2,0)),C11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="48">
+        <f>NETWORKDAYS(A11,EOMONTH(A11,0))</f>
+        <v/>
+      </c>
+      <c r="D11" s="67">
+        <f>IF(ISNUMBER(MATCH(A11,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F11" s="68" t="n"/>
+      <c r="G11" s="69" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="58" t="n">
-        <v>44136</v>
-      </c>
-      <c r="B12" s="43" t="n">
-        <v>21</v>
-      </c>
+      <c r="A12" s="66">
+        <f>EDATE(A11,1)</f>
+        <v/>
+      </c>
+      <c r="B12" s="48">
+        <f>IFERROR(IF(VLOOKUP(A12,$F$8:$G$37,2,0)="",C12,VLOOKUP(A12,$F$8:$G$37,2,0)),C12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="48">
+        <f>NETWORKDAYS(A12,EOMONTH(A12,0))</f>
+        <v/>
+      </c>
+      <c r="D12" s="67">
+        <f>IF(ISNUMBER(MATCH(A12,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F12" s="68" t="n"/>
+      <c r="G12" s="69" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="58" t="n">
-        <v>44166</v>
-      </c>
-      <c r="B13" s="43" t="n">
-        <v>23</v>
-      </c>
+      <c r="A13" s="66">
+        <f>EDATE(A12,1)</f>
+        <v/>
+      </c>
+      <c r="B13" s="48">
+        <f>IFERROR(IF(VLOOKUP(A13,$F$8:$G$37,2,0)="",C13,VLOOKUP(A13,$F$8:$G$37,2,0)),C13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="48">
+        <f>NETWORKDAYS(A13,EOMONTH(A13,0))</f>
+        <v/>
+      </c>
+      <c r="D13" s="67">
+        <f>IF(ISNUMBER(MATCH(A13,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F13" s="68" t="n"/>
+      <c r="G13" s="69" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="58" t="n">
-        <v>44197</v>
-      </c>
-      <c r="B14" s="43" t="n">
-        <v>21</v>
-      </c>
+      <c r="A14" s="66">
+        <f>EDATE(A13,1)</f>
+        <v/>
+      </c>
+      <c r="B14" s="48">
+        <f>IFERROR(IF(VLOOKUP(A14,$F$8:$G$37,2,0)="",C14,VLOOKUP(A14,$F$8:$G$37,2,0)),C14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="48">
+        <f>NETWORKDAYS(A14,EOMONTH(A14,0))</f>
+        <v/>
+      </c>
+      <c r="D14" s="67">
+        <f>IF(ISNUMBER(MATCH(A14,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F14" s="68" t="n"/>
+      <c r="G14" s="69" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="58" t="n">
-        <v>44228</v>
-      </c>
-      <c r="B15" s="43" t="n">
-        <v>20</v>
-      </c>
+      <c r="A15" s="66">
+        <f>EDATE(A14,1)</f>
+        <v/>
+      </c>
+      <c r="B15" s="48">
+        <f>IFERROR(IF(VLOOKUP(A15,$F$8:$G$37,2,0)="",C15,VLOOKUP(A15,$F$8:$G$37,2,0)),C15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="48">
+        <f>NETWORKDAYS(A15,EOMONTH(A15,0))</f>
+        <v/>
+      </c>
+      <c r="D15" s="67">
+        <f>IF(ISNUMBER(MATCH(A15,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F15" s="68" t="n"/>
+      <c r="G15" s="69" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="58" t="n">
-        <v>44256</v>
-      </c>
-      <c r="B16" s="43" t="n">
-        <v>23</v>
-      </c>
+      <c r="A16" s="66">
+        <f>EDATE(A15,1)</f>
+        <v/>
+      </c>
+      <c r="B16" s="48">
+        <f>IFERROR(IF(VLOOKUP(A16,$F$8:$G$37,2,0)="",C16,VLOOKUP(A16,$F$8:$G$37,2,0)),C16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="48">
+        <f>NETWORKDAYS(A16,EOMONTH(A16,0))</f>
+        <v/>
+      </c>
+      <c r="D16" s="67">
+        <f>IF(ISNUMBER(MATCH(A16,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F16" s="68" t="n"/>
+      <c r="G16" s="69" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="58" t="n">
-        <v>44287</v>
-      </c>
-      <c r="B17" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A17" s="66">
+        <f>EDATE(A16,1)</f>
+        <v/>
+      </c>
+      <c r="B17" s="48">
+        <f>IFERROR(IF(VLOOKUP(A17,$F$8:$G$37,2,0)="",C17,VLOOKUP(A17,$F$8:$G$37,2,0)),C17)</f>
+        <v/>
+      </c>
+      <c r="C17" s="48">
+        <f>NETWORKDAYS(A17,EOMONTH(A17,0))</f>
+        <v/>
+      </c>
+      <c r="D17" s="67">
+        <f>IF(ISNUMBER(MATCH(A17,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F17" s="68" t="n"/>
+      <c r="G17" s="69" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="58" t="n">
-        <v>44317</v>
-      </c>
-      <c r="B18" s="43" t="n">
-        <v>21</v>
-      </c>
+      <c r="A18" s="66">
+        <f>EDATE(A17,1)</f>
+        <v/>
+      </c>
+      <c r="B18" s="48">
+        <f>IFERROR(IF(VLOOKUP(A18,$F$8:$G$37,2,0)="",C18,VLOOKUP(A18,$F$8:$G$37,2,0)),C18)</f>
+        <v/>
+      </c>
+      <c r="C18" s="48">
+        <f>NETWORKDAYS(A18,EOMONTH(A18,0))</f>
+        <v/>
+      </c>
+      <c r="D18" s="67">
+        <f>IF(ISNUMBER(MATCH(A18,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F18" s="68" t="n"/>
+      <c r="G18" s="69" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="58" t="n">
-        <v>44348</v>
-      </c>
-      <c r="B19" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A19" s="66">
+        <f>EDATE(A18,1)</f>
+        <v/>
+      </c>
+      <c r="B19" s="48">
+        <f>IFERROR(IF(VLOOKUP(A19,$F$8:$G$37,2,0)="",C19,VLOOKUP(A19,$F$8:$G$37,2,0)),C19)</f>
+        <v/>
+      </c>
+      <c r="C19" s="48">
+        <f>NETWORKDAYS(A19,EOMONTH(A19,0))</f>
+        <v/>
+      </c>
+      <c r="D19" s="67">
+        <f>IF(ISNUMBER(MATCH(A19,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F19" s="68" t="n"/>
+      <c r="G19" s="69" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="58" t="n">
-        <v>44378</v>
-      </c>
-      <c r="B20" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A20" s="66">
+        <f>EDATE(A19,1)</f>
+        <v/>
+      </c>
+      <c r="B20" s="48">
+        <f>IFERROR(IF(VLOOKUP(A20,$F$8:$G$37,2,0)="",C20,VLOOKUP(A20,$F$8:$G$37,2,0)),C20)</f>
+        <v/>
+      </c>
+      <c r="C20" s="48">
+        <f>NETWORKDAYS(A20,EOMONTH(A20,0))</f>
+        <v/>
+      </c>
+      <c r="D20" s="67">
+        <f>IF(ISNUMBER(MATCH(A20,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F20" s="68" t="n"/>
+      <c r="G20" s="69" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="58" t="n">
-        <v>44409</v>
-      </c>
-      <c r="B21" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A21" s="66">
+        <f>EDATE(A20,1)</f>
+        <v/>
+      </c>
+      <c r="B21" s="48">
+        <f>IFERROR(IF(VLOOKUP(A21,$F$8:$G$37,2,0)="",C21,VLOOKUP(A21,$F$8:$G$37,2,0)),C21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="48">
+        <f>NETWORKDAYS(A21,EOMONTH(A21,0))</f>
+        <v/>
+      </c>
+      <c r="D21" s="67">
+        <f>IF(ISNUMBER(MATCH(A21,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F21" s="68" t="n"/>
+      <c r="G21" s="69" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="58" t="n">
-        <v>44440</v>
-      </c>
-      <c r="B22" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A22" s="66">
+        <f>EDATE(A21,1)</f>
+        <v/>
+      </c>
+      <c r="B22" s="48">
+        <f>IFERROR(IF(VLOOKUP(A22,$F$8:$G$37,2,0)="",C22,VLOOKUP(A22,$F$8:$G$37,2,0)),C22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="48">
+        <f>NETWORKDAYS(A22,EOMONTH(A22,0))</f>
+        <v/>
+      </c>
+      <c r="D22" s="67">
+        <f>IF(ISNUMBER(MATCH(A22,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F22" s="68" t="n"/>
+      <c r="G22" s="69" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="58" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B23" s="43" t="n">
-        <v>21</v>
-      </c>
+      <c r="A23" s="66">
+        <f>EDATE(A22,1)</f>
+        <v/>
+      </c>
+      <c r="B23" s="48">
+        <f>IFERROR(IF(VLOOKUP(A23,$F$8:$G$37,2,0)="",C23,VLOOKUP(A23,$F$8:$G$37,2,0)),C23)</f>
+        <v/>
+      </c>
+      <c r="C23" s="48">
+        <f>NETWORKDAYS(A23,EOMONTH(A23,0))</f>
+        <v/>
+      </c>
+      <c r="D23" s="67">
+        <f>IF(ISNUMBER(MATCH(A23,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F23" s="68" t="n"/>
+      <c r="G23" s="69" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="58" t="n">
-        <v>44501</v>
-      </c>
-      <c r="B24" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A24" s="66">
+        <f>EDATE(A23,1)</f>
+        <v/>
+      </c>
+      <c r="B24" s="48">
+        <f>IFERROR(IF(VLOOKUP(A24,$F$8:$G$37,2,0)="",C24,VLOOKUP(A24,$F$8:$G$37,2,0)),C24)</f>
+        <v/>
+      </c>
+      <c r="C24" s="48">
+        <f>NETWORKDAYS(A24,EOMONTH(A24,0))</f>
+        <v/>
+      </c>
+      <c r="D24" s="67">
+        <f>IF(ISNUMBER(MATCH(A24,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F24" s="68" t="n"/>
+      <c r="G24" s="69" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="58" t="n">
-        <v>44531</v>
-      </c>
-      <c r="B25" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A25" s="66">
+        <f>EDATE(A24,1)</f>
+        <v/>
+      </c>
+      <c r="B25" s="48">
+        <f>IFERROR(IF(VLOOKUP(A25,$F$8:$G$37,2,0)="",C25,VLOOKUP(A25,$F$8:$G$37,2,0)),C25)</f>
+        <v/>
+      </c>
+      <c r="C25" s="48">
+        <f>NETWORKDAYS(A25,EOMONTH(A25,0))</f>
+        <v/>
+      </c>
+      <c r="D25" s="67">
+        <f>IF(ISNUMBER(MATCH(A25,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F25" s="68" t="n"/>
+      <c r="G25" s="69" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="58" t="n">
-        <v>44562</v>
-      </c>
-      <c r="B26" s="43" t="n">
-        <v>21</v>
-      </c>
+      <c r="A26" s="66">
+        <f>EDATE(A25,1)</f>
+        <v/>
+      </c>
+      <c r="B26" s="48">
+        <f>IFERROR(IF(VLOOKUP(A26,$F$8:$G$37,2,0)="",C26,VLOOKUP(A26,$F$8:$G$37,2,0)),C26)</f>
+        <v/>
+      </c>
+      <c r="C26" s="48">
+        <f>NETWORKDAYS(A26,EOMONTH(A26,0))</f>
+        <v/>
+      </c>
+      <c r="D26" s="67">
+        <f>IF(ISNUMBER(MATCH(A26,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F26" s="68" t="n"/>
+      <c r="G26" s="69" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="58" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B27" s="43" t="n">
-        <v>20</v>
-      </c>
+      <c r="A27" s="66">
+        <f>EDATE(A26,1)</f>
+        <v/>
+      </c>
+      <c r="B27" s="48">
+        <f>IFERROR(IF(VLOOKUP(A27,$F$8:$G$37,2,0)="",C27,VLOOKUP(A27,$F$8:$G$37,2,0)),C27)</f>
+        <v/>
+      </c>
+      <c r="C27" s="48">
+        <f>NETWORKDAYS(A27,EOMONTH(A27,0))</f>
+        <v/>
+      </c>
+      <c r="D27" s="67">
+        <f>IF(ISNUMBER(MATCH(A27,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F27" s="68" t="n"/>
+      <c r="G27" s="69" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="58" t="n">
-        <v>44621</v>
-      </c>
-      <c r="B28" s="43" t="n">
-        <v>23</v>
-      </c>
+      <c r="A28" s="66">
+        <f>EDATE(A27,1)</f>
+        <v/>
+      </c>
+      <c r="B28" s="48">
+        <f>IFERROR(IF(VLOOKUP(A28,$F$8:$G$37,2,0)="",C28,VLOOKUP(A28,$F$8:$G$37,2,0)),C28)</f>
+        <v/>
+      </c>
+      <c r="C28" s="48">
+        <f>NETWORKDAYS(A28,EOMONTH(A28,0))</f>
+        <v/>
+      </c>
+      <c r="D28" s="67">
+        <f>IF(ISNUMBER(MATCH(A28,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F28" s="68" t="n"/>
+      <c r="G28" s="69" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="58" t="n">
-        <v>44652</v>
-      </c>
-      <c r="B29" s="43" t="n">
-        <v>21</v>
-      </c>
+      <c r="A29" s="66">
+        <f>EDATE(A28,1)</f>
+        <v/>
+      </c>
+      <c r="B29" s="48">
+        <f>IFERROR(IF(VLOOKUP(A29,$F$8:$G$37,2,0)="",C29,VLOOKUP(A29,$F$8:$G$37,2,0)),C29)</f>
+        <v/>
+      </c>
+      <c r="C29" s="48">
+        <f>NETWORKDAYS(A29,EOMONTH(A29,0))</f>
+        <v/>
+      </c>
+      <c r="D29" s="67">
+        <f>IF(ISNUMBER(MATCH(A29,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F29" s="68" t="n"/>
+      <c r="G29" s="69" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="58" t="n">
-        <v>44682</v>
-      </c>
-      <c r="B30" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A30" s="66">
+        <f>EDATE(A29,1)</f>
+        <v/>
+      </c>
+      <c r="B30" s="48">
+        <f>IFERROR(IF(VLOOKUP(A30,$F$8:$G$37,2,0)="",C30,VLOOKUP(A30,$F$8:$G$37,2,0)),C30)</f>
+        <v/>
+      </c>
+      <c r="C30" s="48">
+        <f>NETWORKDAYS(A30,EOMONTH(A30,0))</f>
+        <v/>
+      </c>
+      <c r="D30" s="67">
+        <f>IF(ISNUMBER(MATCH(A30,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F30" s="68" t="n"/>
+      <c r="G30" s="69" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="58" t="n">
-        <v>44713</v>
-      </c>
-      <c r="B31" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A31" s="66">
+        <f>EDATE(A30,1)</f>
+        <v/>
+      </c>
+      <c r="B31" s="48">
+        <f>IFERROR(IF(VLOOKUP(A31,$F$8:$G$37,2,0)="",C31,VLOOKUP(A31,$F$8:$G$37,2,0)),C31)</f>
+        <v/>
+      </c>
+      <c r="C31" s="48">
+        <f>NETWORKDAYS(A31,EOMONTH(A31,0))</f>
+        <v/>
+      </c>
+      <c r="D31" s="67">
+        <f>IF(ISNUMBER(MATCH(A31,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F31" s="68" t="n"/>
+      <c r="G31" s="69" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="58" t="n">
-        <v>44743</v>
-      </c>
-      <c r="B32" s="43" t="n">
-        <v>21</v>
-      </c>
+      <c r="A32" s="66">
+        <f>EDATE(A31,1)</f>
+        <v/>
+      </c>
+      <c r="B32" s="48">
+        <f>IFERROR(IF(VLOOKUP(A32,$F$8:$G$37,2,0)="",C32,VLOOKUP(A32,$F$8:$G$37,2,0)),C32)</f>
+        <v/>
+      </c>
+      <c r="C32" s="48">
+        <f>NETWORKDAYS(A32,EOMONTH(A32,0))</f>
+        <v/>
+      </c>
+      <c r="D32" s="67">
+        <f>IF(ISNUMBER(MATCH(A32,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F32" s="68" t="n"/>
+      <c r="G32" s="69" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="58" t="n">
-        <v>44774</v>
-      </c>
-      <c r="B33" s="43" t="n">
-        <v>23</v>
-      </c>
+      <c r="A33" s="66">
+        <f>EDATE(A32,1)</f>
+        <v/>
+      </c>
+      <c r="B33" s="48">
+        <f>IFERROR(IF(VLOOKUP(A33,$F$8:$G$37,2,0)="",C33,VLOOKUP(A33,$F$8:$G$37,2,0)),C33)</f>
+        <v/>
+      </c>
+      <c r="C33" s="48">
+        <f>NETWORKDAYS(A33,EOMONTH(A33,0))</f>
+        <v/>
+      </c>
+      <c r="D33" s="67">
+        <f>IF(ISNUMBER(MATCH(A33,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F33" s="68" t="n"/>
+      <c r="G33" s="69" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="58" t="n">
-        <v>44805</v>
-      </c>
-      <c r="B34" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A34" s="66">
+        <f>EDATE(A33,1)</f>
+        <v/>
+      </c>
+      <c r="B34" s="48">
+        <f>IFERROR(IF(VLOOKUP(A34,$F$8:$G$37,2,0)="",C34,VLOOKUP(A34,$F$8:$G$37,2,0)),C34)</f>
+        <v/>
+      </c>
+      <c r="C34" s="48">
+        <f>NETWORKDAYS(A34,EOMONTH(A34,0))</f>
+        <v/>
+      </c>
+      <c r="D34" s="67">
+        <f>IF(ISNUMBER(MATCH(A34,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F34" s="68" t="n"/>
+      <c r="G34" s="69" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="58" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B35" s="43" t="n">
-        <v>21</v>
-      </c>
+      <c r="A35" s="66">
+        <f>EDATE(A34,1)</f>
+        <v/>
+      </c>
+      <c r="B35" s="48">
+        <f>IFERROR(IF(VLOOKUP(A35,$F$8:$G$37,2,0)="",C35,VLOOKUP(A35,$F$8:$G$37,2,0)),C35)</f>
+        <v/>
+      </c>
+      <c r="C35" s="48">
+        <f>NETWORKDAYS(A35,EOMONTH(A35,0))</f>
+        <v/>
+      </c>
+      <c r="D35" s="67">
+        <f>IF(ISNUMBER(MATCH(A35,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F35" s="68" t="n"/>
+      <c r="G35" s="69" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="58" t="n">
-        <v>44866</v>
-      </c>
-      <c r="B36" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A36" s="66">
+        <f>EDATE(A35,1)</f>
+        <v/>
+      </c>
+      <c r="B36" s="48">
+        <f>IFERROR(IF(VLOOKUP(A36,$F$8:$G$37,2,0)="",C36,VLOOKUP(A36,$F$8:$G$37,2,0)),C36)</f>
+        <v/>
+      </c>
+      <c r="C36" s="48">
+        <f>NETWORKDAYS(A36,EOMONTH(A36,0))</f>
+        <v/>
+      </c>
+      <c r="D36" s="67">
+        <f>IF(ISNUMBER(MATCH(A36,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F36" s="68" t="n"/>
+      <c r="G36" s="69" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="58" t="n">
-        <v>44896</v>
-      </c>
-      <c r="B37" s="43" t="n">
-        <v>22</v>
-      </c>
+      <c r="A37" s="66">
+        <f>EDATE(A36,1)</f>
+        <v/>
+      </c>
+      <c r="B37" s="48">
+        <f>IFERROR(IF(VLOOKUP(A37,$F$8:$G$37,2,0)="",C37,VLOOKUP(A37,$F$8:$G$37,2,0)),C37)</f>
+        <v/>
+      </c>
+      <c r="C37" s="48">
+        <f>NETWORKDAYS(A37,EOMONTH(A37,0))</f>
+        <v/>
+      </c>
+      <c r="D37" s="67">
+        <f>IF(ISNUMBER(MATCH(A37,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+      <c r="F37" s="68" t="n"/>
+      <c r="G37" s="69" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="58" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B38" s="43" t="n">
-        <v>22</v>
+      <c r="A38" s="66">
+        <f>EDATE(A37,1)</f>
+        <v/>
+      </c>
+      <c r="B38" s="48">
+        <f>IFERROR(IF(VLOOKUP(A38,$F$8:$G$37,2,0)="",C38,VLOOKUP(A38,$F$8:$G$37,2,0)),C38)</f>
+        <v/>
+      </c>
+      <c r="C38" s="48">
+        <f>NETWORKDAYS(A38,EOMONTH(A38,0))</f>
+        <v/>
+      </c>
+      <c r="D38" s="67">
+        <f>IF(ISNUMBER(MATCH(A38,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="58" t="n">
-        <v>44958</v>
-      </c>
-      <c r="B39" s="43" t="n">
-        <v>20</v>
+      <c r="A39" s="66">
+        <f>EDATE(A38,1)</f>
+        <v/>
+      </c>
+      <c r="B39" s="48">
+        <f>IFERROR(IF(VLOOKUP(A39,$F$8:$G$37,2,0)="",C39,VLOOKUP(A39,$F$8:$G$37,2,0)),C39)</f>
+        <v/>
+      </c>
+      <c r="C39" s="48">
+        <f>NETWORKDAYS(A39,EOMONTH(A39,0))</f>
+        <v/>
+      </c>
+      <c r="D39" s="67">
+        <f>IF(ISNUMBER(MATCH(A39,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="58" t="n">
-        <v>44986</v>
-      </c>
-      <c r="B40" s="43" t="n">
-        <v>23</v>
+      <c r="A40" s="66">
+        <f>EDATE(A39,1)</f>
+        <v/>
+      </c>
+      <c r="B40" s="48">
+        <f>IFERROR(IF(VLOOKUP(A40,$F$8:$G$37,2,0)="",C40,VLOOKUP(A40,$F$8:$G$37,2,0)),C40)</f>
+        <v/>
+      </c>
+      <c r="C40" s="48">
+        <f>NETWORKDAYS(A40,EOMONTH(A40,0))</f>
+        <v/>
+      </c>
+      <c r="D40" s="67">
+        <f>IF(ISNUMBER(MATCH(A40,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="58" t="n">
-        <v>45017</v>
-      </c>
-      <c r="B41" s="43" t="n">
-        <v>20</v>
+      <c r="A41" s="66">
+        <f>EDATE(A40,1)</f>
+        <v/>
+      </c>
+      <c r="B41" s="48">
+        <f>IFERROR(IF(VLOOKUP(A41,$F$8:$G$37,2,0)="",C41,VLOOKUP(A41,$F$8:$G$37,2,0)),C41)</f>
+        <v/>
+      </c>
+      <c r="C41" s="48">
+        <f>NETWORKDAYS(A41,EOMONTH(A41,0))</f>
+        <v/>
+      </c>
+      <c r="D41" s="67">
+        <f>IF(ISNUMBER(MATCH(A41,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="58" t="n">
-        <v>45047</v>
-      </c>
-      <c r="B42" s="43" t="n">
-        <v>23</v>
+      <c r="A42" s="66">
+        <f>EDATE(A41,1)</f>
+        <v/>
+      </c>
+      <c r="B42" s="48">
+        <f>IFERROR(IF(VLOOKUP(A42,$F$8:$G$37,2,0)="",C42,VLOOKUP(A42,$F$8:$G$37,2,0)),C42)</f>
+        <v/>
+      </c>
+      <c r="C42" s="48">
+        <f>NETWORKDAYS(A42,EOMONTH(A42,0))</f>
+        <v/>
+      </c>
+      <c r="D42" s="67">
+        <f>IF(ISNUMBER(MATCH(A42,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="58" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B43" s="43" t="n">
-        <v>22</v>
+      <c r="A43" s="66">
+        <f>EDATE(A42,1)</f>
+        <v/>
+      </c>
+      <c r="B43" s="48">
+        <f>IFERROR(IF(VLOOKUP(A43,$F$8:$G$37,2,0)="",C43,VLOOKUP(A43,$F$8:$G$37,2,0)),C43)</f>
+        <v/>
+      </c>
+      <c r="C43" s="48">
+        <f>NETWORKDAYS(A43,EOMONTH(A43,0))</f>
+        <v/>
+      </c>
+      <c r="D43" s="67">
+        <f>IF(ISNUMBER(MATCH(A43,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="58" t="n">
-        <v>45108</v>
-      </c>
-      <c r="B44" s="43" t="n">
-        <v>21</v>
+      <c r="A44" s="66">
+        <f>EDATE(A43,1)</f>
+        <v/>
+      </c>
+      <c r="B44" s="48">
+        <f>IFERROR(IF(VLOOKUP(A44,$F$8:$G$37,2,0)="",C44,VLOOKUP(A44,$F$8:$G$37,2,0)),C44)</f>
+        <v/>
+      </c>
+      <c r="C44" s="48">
+        <f>NETWORKDAYS(A44,EOMONTH(A44,0))</f>
+        <v/>
+      </c>
+      <c r="D44" s="67">
+        <f>IF(ISNUMBER(MATCH(A44,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="58" t="n">
-        <v>45139</v>
-      </c>
-      <c r="B45" s="43" t="n">
-        <v>23</v>
+      <c r="A45" s="66">
+        <f>EDATE(A44,1)</f>
+        <v/>
+      </c>
+      <c r="B45" s="48">
+        <f>IFERROR(IF(VLOOKUP(A45,$F$8:$G$37,2,0)="",C45,VLOOKUP(A45,$F$8:$G$37,2,0)),C45)</f>
+        <v/>
+      </c>
+      <c r="C45" s="48">
+        <f>NETWORKDAYS(A45,EOMONTH(A45,0))</f>
+        <v/>
+      </c>
+      <c r="D45" s="67">
+        <f>IF(ISNUMBER(MATCH(A45,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="58" t="n">
-        <v>45170</v>
-      </c>
-      <c r="B46" s="43" t="n">
-        <v>21</v>
+      <c r="A46" s="66">
+        <f>EDATE(A45,1)</f>
+        <v/>
+      </c>
+      <c r="B46" s="48">
+        <f>IFERROR(IF(VLOOKUP(A46,$F$8:$G$37,2,0)="",C46,VLOOKUP(A46,$F$8:$G$37,2,0)),C46)</f>
+        <v/>
+      </c>
+      <c r="C46" s="48">
+        <f>NETWORKDAYS(A46,EOMONTH(A46,0))</f>
+        <v/>
+      </c>
+      <c r="D46" s="67">
+        <f>IF(ISNUMBER(MATCH(A46,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="58" t="n">
-        <v>45200</v>
-      </c>
-      <c r="B47" s="43" t="n">
-        <v>22</v>
+      <c r="A47" s="66">
+        <f>EDATE(A46,1)</f>
+        <v/>
+      </c>
+      <c r="B47" s="48">
+        <f>IFERROR(IF(VLOOKUP(A47,$F$8:$G$37,2,0)="",C47,VLOOKUP(A47,$F$8:$G$37,2,0)),C47)</f>
+        <v/>
+      </c>
+      <c r="C47" s="48">
+        <f>NETWORKDAYS(A47,EOMONTH(A47,0))</f>
+        <v/>
+      </c>
+      <c r="D47" s="67">
+        <f>IF(ISNUMBER(MATCH(A47,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="58" t="n">
-        <v>45231</v>
-      </c>
-      <c r="B48" s="43" t="n">
-        <v>22</v>
+      <c r="A48" s="66">
+        <f>EDATE(A47,1)</f>
+        <v/>
+      </c>
+      <c r="B48" s="48">
+        <f>IFERROR(IF(VLOOKUP(A48,$F$8:$G$37,2,0)="",C48,VLOOKUP(A48,$F$8:$G$37,2,0)),C48)</f>
+        <v/>
+      </c>
+      <c r="C48" s="48">
+        <f>NETWORKDAYS(A48,EOMONTH(A48,0))</f>
+        <v/>
+      </c>
+      <c r="D48" s="67">
+        <f>IF(ISNUMBER(MATCH(A48,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="58" t="n">
-        <v>45261</v>
-      </c>
-      <c r="B49" s="43" t="n">
-        <v>21</v>
+      <c r="A49" s="66">
+        <f>EDATE(A48,1)</f>
+        <v/>
+      </c>
+      <c r="B49" s="48">
+        <f>IFERROR(IF(VLOOKUP(A49,$F$8:$G$37,2,0)="",C49,VLOOKUP(A49,$F$8:$G$37,2,0)),C49)</f>
+        <v/>
+      </c>
+      <c r="C49" s="48">
+        <f>NETWORKDAYS(A49,EOMONTH(A49,0))</f>
+        <v/>
+      </c>
+      <c r="D49" s="67">
+        <f>IF(ISNUMBER(MATCH(A49,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="58" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B50" s="43" t="n">
-        <v>23</v>
+      <c r="A50" s="66">
+        <f>EDATE(A49,1)</f>
+        <v/>
+      </c>
+      <c r="B50" s="48">
+        <f>IFERROR(IF(VLOOKUP(A50,$F$8:$G$37,2,0)="",C50,VLOOKUP(A50,$F$8:$G$37,2,0)),C50)</f>
+        <v/>
+      </c>
+      <c r="C50" s="48">
+        <f>NETWORKDAYS(A50,EOMONTH(A50,0))</f>
+        <v/>
+      </c>
+      <c r="D50" s="67">
+        <f>IF(ISNUMBER(MATCH(A50,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="58" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B51" s="43" t="n">
-        <v>21</v>
+      <c r="A51" s="66">
+        <f>EDATE(A50,1)</f>
+        <v/>
+      </c>
+      <c r="B51" s="48">
+        <f>IFERROR(IF(VLOOKUP(A51,$F$8:$G$37,2,0)="",C51,VLOOKUP(A51,$F$8:$G$37,2,0)),C51)</f>
+        <v/>
+      </c>
+      <c r="C51" s="48">
+        <f>NETWORKDAYS(A51,EOMONTH(A51,0))</f>
+        <v/>
+      </c>
+      <c r="D51" s="67">
+        <f>IF(ISNUMBER(MATCH(A51,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="58" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B52" s="43" t="n">
-        <v>21</v>
+      <c r="A52" s="66">
+        <f>EDATE(A51,1)</f>
+        <v/>
+      </c>
+      <c r="B52" s="48">
+        <f>IFERROR(IF(VLOOKUP(A52,$F$8:$G$37,2,0)="",C52,VLOOKUP(A52,$F$8:$G$37,2,0)),C52)</f>
+        <v/>
+      </c>
+      <c r="C52" s="48">
+        <f>NETWORKDAYS(A52,EOMONTH(A52,0))</f>
+        <v/>
+      </c>
+      <c r="D52" s="67">
+        <f>IF(ISNUMBER(MATCH(A52,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="58" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B53" s="43" t="n">
-        <v>22</v>
+      <c r="A53" s="66">
+        <f>EDATE(A52,1)</f>
+        <v/>
+      </c>
+      <c r="B53" s="48">
+        <f>IFERROR(IF(VLOOKUP(A53,$F$8:$G$37,2,0)="",C53,VLOOKUP(A53,$F$8:$G$37,2,0)),C53)</f>
+        <v/>
+      </c>
+      <c r="C53" s="48">
+        <f>NETWORKDAYS(A53,EOMONTH(A53,0))</f>
+        <v/>
+      </c>
+      <c r="D53" s="67">
+        <f>IF(ISNUMBER(MATCH(A53,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="58" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B54" s="43" t="n">
-        <v>23</v>
+      <c r="A54" s="66">
+        <f>EDATE(A53,1)</f>
+        <v/>
+      </c>
+      <c r="B54" s="48">
+        <f>IFERROR(IF(VLOOKUP(A54,$F$8:$G$37,2,0)="",C54,VLOOKUP(A54,$F$8:$G$37,2,0)),C54)</f>
+        <v/>
+      </c>
+      <c r="C54" s="48">
+        <f>NETWORKDAYS(A54,EOMONTH(A54,0))</f>
+        <v/>
+      </c>
+      <c r="D54" s="67">
+        <f>IF(ISNUMBER(MATCH(A54,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="58" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B55" s="43" t="n">
-        <v>20</v>
+      <c r="A55" s="66">
+        <f>EDATE(A54,1)</f>
+        <v/>
+      </c>
+      <c r="B55" s="48">
+        <f>IFERROR(IF(VLOOKUP(A55,$F$8:$G$37,2,0)="",C55,VLOOKUP(A55,$F$8:$G$37,2,0)),C55)</f>
+        <v/>
+      </c>
+      <c r="C55" s="48">
+        <f>NETWORKDAYS(A55,EOMONTH(A55,0))</f>
+        <v/>
+      </c>
+      <c r="D55" s="67">
+        <f>IF(ISNUMBER(MATCH(A55,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="58" t="n">
-        <v>45474</v>
-      </c>
-      <c r="B56" s="43" t="n">
-        <v>23</v>
+      <c r="A56" s="66">
+        <f>EDATE(A55,1)</f>
+        <v/>
+      </c>
+      <c r="B56" s="48">
+        <f>IFERROR(IF(VLOOKUP(A56,$F$8:$G$37,2,0)="",C56,VLOOKUP(A56,$F$8:$G$37,2,0)),C56)</f>
+        <v/>
+      </c>
+      <c r="C56" s="48">
+        <f>NETWORKDAYS(A56,EOMONTH(A56,0))</f>
+        <v/>
+      </c>
+      <c r="D56" s="67">
+        <f>IF(ISNUMBER(MATCH(A56,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="58" t="n">
-        <v>45505</v>
-      </c>
-      <c r="B57" s="43" t="n">
-        <v>22</v>
+      <c r="A57" s="66">
+        <f>EDATE(A56,1)</f>
+        <v/>
+      </c>
+      <c r="B57" s="48">
+        <f>IFERROR(IF(VLOOKUP(A57,$F$8:$G$37,2,0)="",C57,VLOOKUP(A57,$F$8:$G$37,2,0)),C57)</f>
+        <v/>
+      </c>
+      <c r="C57" s="48">
+        <f>NETWORKDAYS(A57,EOMONTH(A57,0))</f>
+        <v/>
+      </c>
+      <c r="D57" s="67">
+        <f>IF(ISNUMBER(MATCH(A57,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="58" t="n">
-        <v>45536</v>
-      </c>
-      <c r="B58" s="43" t="n">
-        <v>21</v>
+      <c r="A58" s="66">
+        <f>EDATE(A57,1)</f>
+        <v/>
+      </c>
+      <c r="B58" s="48">
+        <f>IFERROR(IF(VLOOKUP(A58,$F$8:$G$37,2,0)="",C58,VLOOKUP(A58,$F$8:$G$37,2,0)),C58)</f>
+        <v/>
+      </c>
+      <c r="C58" s="48">
+        <f>NETWORKDAYS(A58,EOMONTH(A58,0))</f>
+        <v/>
+      </c>
+      <c r="D58" s="67">
+        <f>IF(ISNUMBER(MATCH(A58,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="58" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B59" s="43" t="n">
-        <v>23</v>
+      <c r="A59" s="66">
+        <f>EDATE(A58,1)</f>
+        <v/>
+      </c>
+      <c r="B59" s="48">
+        <f>IFERROR(IF(VLOOKUP(A59,$F$8:$G$37,2,0)="",C59,VLOOKUP(A59,$F$8:$G$37,2,0)),C59)</f>
+        <v/>
+      </c>
+      <c r="C59" s="48">
+        <f>NETWORKDAYS(A59,EOMONTH(A59,0))</f>
+        <v/>
+      </c>
+      <c r="D59" s="67">
+        <f>IF(ISNUMBER(MATCH(A59,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="58" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B60" s="43" t="n">
-        <v>21</v>
+      <c r="A60" s="66">
+        <f>EDATE(A59,1)</f>
+        <v/>
+      </c>
+      <c r="B60" s="48">
+        <f>IFERROR(IF(VLOOKUP(A60,$F$8:$G$37,2,0)="",C60,VLOOKUP(A60,$F$8:$G$37,2,0)),C60)</f>
+        <v/>
+      </c>
+      <c r="C60" s="48">
+        <f>NETWORKDAYS(A60,EOMONTH(A60,0))</f>
+        <v/>
+      </c>
+      <c r="D60" s="67">
+        <f>IF(ISNUMBER(MATCH(A60,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="58" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B61" s="43" t="n">
-        <v>22</v>
+      <c r="A61" s="66">
+        <f>EDATE(A60,1)</f>
+        <v/>
+      </c>
+      <c r="B61" s="48">
+        <f>IFERROR(IF(VLOOKUP(A61,$F$8:$G$37,2,0)="",C61,VLOOKUP(A61,$F$8:$G$37,2,0)),C61)</f>
+        <v/>
+      </c>
+      <c r="C61" s="48">
+        <f>NETWORKDAYS(A61,EOMONTH(A61,0))</f>
+        <v/>
+      </c>
+      <c r="D61" s="67">
+        <f>IF(ISNUMBER(MATCH(A61,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="58" t="n">
-        <v>45658</v>
-      </c>
-      <c r="B62" s="43" t="n">
-        <v>23</v>
+      <c r="A62" s="66">
+        <f>EDATE(A61,1)</f>
+        <v/>
+      </c>
+      <c r="B62" s="48">
+        <f>IFERROR(IF(VLOOKUP(A62,$F$8:$G$37,2,0)="",C62,VLOOKUP(A62,$F$8:$G$37,2,0)),C62)</f>
+        <v/>
+      </c>
+      <c r="C62" s="48">
+        <f>NETWORKDAYS(A62,EOMONTH(A62,0))</f>
+        <v/>
+      </c>
+      <c r="D62" s="67">
+        <f>IF(ISNUMBER(MATCH(A62,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="58" t="n">
-        <v>45689</v>
-      </c>
-      <c r="B63" s="43" t="n">
-        <v>20</v>
+      <c r="A63" s="66">
+        <f>EDATE(A62,1)</f>
+        <v/>
+      </c>
+      <c r="B63" s="48">
+        <f>IFERROR(IF(VLOOKUP(A63,$F$8:$G$37,2,0)="",C63,VLOOKUP(A63,$F$8:$G$37,2,0)),C63)</f>
+        <v/>
+      </c>
+      <c r="C63" s="48">
+        <f>NETWORKDAYS(A63,EOMONTH(A63,0))</f>
+        <v/>
+      </c>
+      <c r="D63" s="67">
+        <f>IF(ISNUMBER(MATCH(A63,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="58" t="n">
-        <v>45717</v>
-      </c>
-      <c r="B64" s="43" t="n">
-        <v>21</v>
+      <c r="A64" s="66">
+        <f>EDATE(A63,1)</f>
+        <v/>
+      </c>
+      <c r="B64" s="48">
+        <f>IFERROR(IF(VLOOKUP(A64,$F$8:$G$37,2,0)="",C64,VLOOKUP(A64,$F$8:$G$37,2,0)),C64)</f>
+        <v/>
+      </c>
+      <c r="C64" s="48">
+        <f>NETWORKDAYS(A64,EOMONTH(A64,0))</f>
+        <v/>
+      </c>
+      <c r="D64" s="67">
+        <f>IF(ISNUMBER(MATCH(A64,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="58" t="n">
-        <v>45748</v>
-      </c>
-      <c r="B65" s="43" t="n">
-        <v>22</v>
+      <c r="A65" s="66">
+        <f>EDATE(A64,1)</f>
+        <v/>
+      </c>
+      <c r="B65" s="48">
+        <f>IFERROR(IF(VLOOKUP(A65,$F$8:$G$37,2,0)="",C65,VLOOKUP(A65,$F$8:$G$37,2,0)),C65)</f>
+        <v/>
+      </c>
+      <c r="C65" s="48">
+        <f>NETWORKDAYS(A65,EOMONTH(A65,0))</f>
+        <v/>
+      </c>
+      <c r="D65" s="67">
+        <f>IF(ISNUMBER(MATCH(A65,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="58" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B66" s="43" t="n">
-        <v>22</v>
+      <c r="A66" s="66">
+        <f>EDATE(A65,1)</f>
+        <v/>
+      </c>
+      <c r="B66" s="48">
+        <f>IFERROR(IF(VLOOKUP(A66,$F$8:$G$37,2,0)="",C66,VLOOKUP(A66,$F$8:$G$37,2,0)),C66)</f>
+        <v/>
+      </c>
+      <c r="C66" s="48">
+        <f>NETWORKDAYS(A66,EOMONTH(A66,0))</f>
+        <v/>
+      </c>
+      <c r="D66" s="67">
+        <f>IF(ISNUMBER(MATCH(A66,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="58" t="n">
-        <v>45809</v>
-      </c>
-      <c r="B67" s="43" t="n">
-        <v>21</v>
+      <c r="A67" s="66">
+        <f>EDATE(A66,1)</f>
+        <v/>
+      </c>
+      <c r="B67" s="48">
+        <f>IFERROR(IF(VLOOKUP(A67,$F$8:$G$37,2,0)="",C67,VLOOKUP(A67,$F$8:$G$37,2,0)),C67)</f>
+        <v/>
+      </c>
+      <c r="C67" s="48">
+        <f>NETWORKDAYS(A67,EOMONTH(A67,0))</f>
+        <v/>
+      </c>
+      <c r="D67" s="67">
+        <f>IF(ISNUMBER(MATCH(A67,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="58" t="n">
-        <v>45839</v>
-      </c>
-      <c r="B68" s="43" t="n">
-        <v>23</v>
+      <c r="A68" s="66">
+        <f>EDATE(A67,1)</f>
+        <v/>
+      </c>
+      <c r="B68" s="48">
+        <f>IFERROR(IF(VLOOKUP(A68,$F$8:$G$37,2,0)="",C68,VLOOKUP(A68,$F$8:$G$37,2,0)),C68)</f>
+        <v/>
+      </c>
+      <c r="C68" s="48">
+        <f>NETWORKDAYS(A68,EOMONTH(A68,0))</f>
+        <v/>
+      </c>
+      <c r="D68" s="67">
+        <f>IF(ISNUMBER(MATCH(A68,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="58" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B69" s="43" t="n">
-        <v>21</v>
+      <c r="A69" s="66">
+        <f>EDATE(A68,1)</f>
+        <v/>
+      </c>
+      <c r="B69" s="48">
+        <f>IFERROR(IF(VLOOKUP(A69,$F$8:$G$37,2,0)="",C69,VLOOKUP(A69,$F$8:$G$37,2,0)),C69)</f>
+        <v/>
+      </c>
+      <c r="C69" s="48">
+        <f>NETWORKDAYS(A69,EOMONTH(A69,0))</f>
+        <v/>
+      </c>
+      <c r="D69" s="67">
+        <f>IF(ISNUMBER(MATCH(A69,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="58" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B70" s="43" t="n">
-        <v>22</v>
+      <c r="A70" s="66">
+        <f>EDATE(A69,1)</f>
+        <v/>
+      </c>
+      <c r="B70" s="48">
+        <f>IFERROR(IF(VLOOKUP(A70,$F$8:$G$37,2,0)="",C70,VLOOKUP(A70,$F$8:$G$37,2,0)),C70)</f>
+        <v/>
+      </c>
+      <c r="C70" s="48">
+        <f>NETWORKDAYS(A70,EOMONTH(A70,0))</f>
+        <v/>
+      </c>
+      <c r="D70" s="67">
+        <f>IF(ISNUMBER(MATCH(A70,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="58" t="n">
-        <v>45931</v>
-      </c>
-      <c r="B71" s="43" t="n">
-        <v>23</v>
+      <c r="A71" s="66">
+        <f>EDATE(A70,1)</f>
+        <v/>
+      </c>
+      <c r="B71" s="48">
+        <f>IFERROR(IF(VLOOKUP(A71,$F$8:$G$37,2,0)="",C71,VLOOKUP(A71,$F$8:$G$37,2,0)),C71)</f>
+        <v/>
+      </c>
+      <c r="C71" s="48">
+        <f>NETWORKDAYS(A71,EOMONTH(A71,0))</f>
+        <v/>
+      </c>
+      <c r="D71" s="67">
+        <f>IF(ISNUMBER(MATCH(A71,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="58" t="n">
-        <v>45962</v>
-      </c>
-      <c r="B72" s="43" t="n">
-        <v>20</v>
+      <c r="A72" s="66">
+        <f>EDATE(A71,1)</f>
+        <v/>
+      </c>
+      <c r="B72" s="48">
+        <f>IFERROR(IF(VLOOKUP(A72,$F$8:$G$37,2,0)="",C72,VLOOKUP(A72,$F$8:$G$37,2,0)),C72)</f>
+        <v/>
+      </c>
+      <c r="C72" s="48">
+        <f>NETWORKDAYS(A72,EOMONTH(A72,0))</f>
+        <v/>
+      </c>
+      <c r="D72" s="67">
+        <f>IF(ISNUMBER(MATCH(A72,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="58" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B73" s="43" t="n">
-        <v>23</v>
+      <c r="A73" s="66">
+        <f>EDATE(A72,1)</f>
+        <v/>
+      </c>
+      <c r="B73" s="48">
+        <f>IFERROR(IF(VLOOKUP(A73,$F$8:$G$37,2,0)="",C73,VLOOKUP(A73,$F$8:$G$37,2,0)),C73)</f>
+        <v/>
+      </c>
+      <c r="C73" s="48">
+        <f>NETWORKDAYS(A73,EOMONTH(A73,0))</f>
+        <v/>
+      </c>
+      <c r="D73" s="67">
+        <f>IF(ISNUMBER(MATCH(A73,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="58" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B74" s="43" t="n">
-        <v>22</v>
+      <c r="A74" s="66">
+        <f>EDATE(A73,1)</f>
+        <v/>
+      </c>
+      <c r="B74" s="48">
+        <f>IFERROR(IF(VLOOKUP(A74,$F$8:$G$37,2,0)="",C74,VLOOKUP(A74,$F$8:$G$37,2,0)),C74)</f>
+        <v/>
+      </c>
+      <c r="C74" s="48">
+        <f>NETWORKDAYS(A74,EOMONTH(A74,0))</f>
+        <v/>
+      </c>
+      <c r="D74" s="67">
+        <f>IF(ISNUMBER(MATCH(A74,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="58" t="n">
-        <v>46054</v>
-      </c>
-      <c r="B75" s="43" t="n">
-        <v>20</v>
+      <c r="A75" s="66">
+        <f>EDATE(A74,1)</f>
+        <v/>
+      </c>
+      <c r="B75" s="48">
+        <f>IFERROR(IF(VLOOKUP(A75,$F$8:$G$37,2,0)="",C75,VLOOKUP(A75,$F$8:$G$37,2,0)),C75)</f>
+        <v/>
+      </c>
+      <c r="C75" s="48">
+        <f>NETWORKDAYS(A75,EOMONTH(A75,0))</f>
+        <v/>
+      </c>
+      <c r="D75" s="67">
+        <f>IF(ISNUMBER(MATCH(A75,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="58" t="n">
-        <v>46082</v>
-      </c>
-      <c r="B76" s="43" t="n">
-        <v>22</v>
+      <c r="A76" s="66">
+        <f>EDATE(A75,1)</f>
+        <v/>
+      </c>
+      <c r="B76" s="48">
+        <f>IFERROR(IF(VLOOKUP(A76,$F$8:$G$37,2,0)="",C76,VLOOKUP(A76,$F$8:$G$37,2,0)),C76)</f>
+        <v/>
+      </c>
+      <c r="C76" s="48">
+        <f>NETWORKDAYS(A76,EOMONTH(A76,0))</f>
+        <v/>
+      </c>
+      <c r="D76" s="67">
+        <f>IF(ISNUMBER(MATCH(A76,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="58" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B77" s="43" t="n">
-        <v>22</v>
+      <c r="A77" s="66">
+        <f>EDATE(A76,1)</f>
+        <v/>
+      </c>
+      <c r="B77" s="48">
+        <f>IFERROR(IF(VLOOKUP(A77,$F$8:$G$37,2,0)="",C77,VLOOKUP(A77,$F$8:$G$37,2,0)),C77)</f>
+        <v/>
+      </c>
+      <c r="C77" s="48">
+        <f>NETWORKDAYS(A77,EOMONTH(A77,0))</f>
+        <v/>
+      </c>
+      <c r="D77" s="67">
+        <f>IF(ISNUMBER(MATCH(A77,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="58" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B78" s="43" t="n">
-        <v>21</v>
+      <c r="A78" s="66">
+        <f>EDATE(A77,1)</f>
+        <v/>
+      </c>
+      <c r="B78" s="48">
+        <f>IFERROR(IF(VLOOKUP(A78,$F$8:$G$37,2,0)="",C78,VLOOKUP(A78,$F$8:$G$37,2,0)),C78)</f>
+        <v/>
+      </c>
+      <c r="C78" s="48">
+        <f>NETWORKDAYS(A78,EOMONTH(A78,0))</f>
+        <v/>
+      </c>
+      <c r="D78" s="67">
+        <f>IF(ISNUMBER(MATCH(A78,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="58" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B79" s="43" t="n">
-        <v>22</v>
+      <c r="A79" s="66">
+        <f>EDATE(A78,1)</f>
+        <v/>
+      </c>
+      <c r="B79" s="48">
+        <f>IFERROR(IF(VLOOKUP(A79,$F$8:$G$37,2,0)="",C79,VLOOKUP(A79,$F$8:$G$37,2,0)),C79)</f>
+        <v/>
+      </c>
+      <c r="C79" s="48">
+        <f>NETWORKDAYS(A79,EOMONTH(A79,0))</f>
+        <v/>
+      </c>
+      <c r="D79" s="67">
+        <f>IF(ISNUMBER(MATCH(A79,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="58" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B80" s="43" t="n">
-        <v>23</v>
+      <c r="A80" s="66">
+        <f>EDATE(A79,1)</f>
+        <v/>
+      </c>
+      <c r="B80" s="48">
+        <f>IFERROR(IF(VLOOKUP(A80,$F$8:$G$37,2,0)="",C80,VLOOKUP(A80,$F$8:$G$37,2,0)),C80)</f>
+        <v/>
+      </c>
+      <c r="C80" s="48">
+        <f>NETWORKDAYS(A80,EOMONTH(A80,0))</f>
+        <v/>
+      </c>
+      <c r="D80" s="67">
+        <f>IF(ISNUMBER(MATCH(A80,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="58" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B81" s="43" t="n">
-        <v>21</v>
+      <c r="A81" s="66">
+        <f>EDATE(A80,1)</f>
+        <v/>
+      </c>
+      <c r="B81" s="48">
+        <f>IFERROR(IF(VLOOKUP(A81,$F$8:$G$37,2,0)="",C81,VLOOKUP(A81,$F$8:$G$37,2,0)),C81)</f>
+        <v/>
+      </c>
+      <c r="C81" s="48">
+        <f>NETWORKDAYS(A81,EOMONTH(A81,0))</f>
+        <v/>
+      </c>
+      <c r="D81" s="67">
+        <f>IF(ISNUMBER(MATCH(A81,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="58" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B82" s="43" t="n">
-        <v>22</v>
+      <c r="A82" s="66">
+        <f>EDATE(A81,1)</f>
+        <v/>
+      </c>
+      <c r="B82" s="48">
+        <f>IFERROR(IF(VLOOKUP(A82,$F$8:$G$37,2,0)="",C82,VLOOKUP(A82,$F$8:$G$37,2,0)),C82)</f>
+        <v/>
+      </c>
+      <c r="C82" s="48">
+        <f>NETWORKDAYS(A82,EOMONTH(A82,0))</f>
+        <v/>
+      </c>
+      <c r="D82" s="67">
+        <f>IF(ISNUMBER(MATCH(A82,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="58" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B83" s="43" t="n">
-        <v>22</v>
+      <c r="A83" s="66">
+        <f>EDATE(A82,1)</f>
+        <v/>
+      </c>
+      <c r="B83" s="48">
+        <f>IFERROR(IF(VLOOKUP(A83,$F$8:$G$37,2,0)="",C83,VLOOKUP(A83,$F$8:$G$37,2,0)),C83)</f>
+        <v/>
+      </c>
+      <c r="C83" s="48">
+        <f>NETWORKDAYS(A83,EOMONTH(A83,0))</f>
+        <v/>
+      </c>
+      <c r="D83" s="67">
+        <f>IF(ISNUMBER(MATCH(A83,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="58" t="n">
-        <v>46327</v>
-      </c>
-      <c r="B84" s="43" t="n">
-        <v>21</v>
+      <c r="A84" s="66">
+        <f>EDATE(A83,1)</f>
+        <v/>
+      </c>
+      <c r="B84" s="48">
+        <f>IFERROR(IF(VLOOKUP(A84,$F$8:$G$37,2,0)="",C84,VLOOKUP(A84,$F$8:$G$37,2,0)),C84)</f>
+        <v/>
+      </c>
+      <c r="C84" s="48">
+        <f>NETWORKDAYS(A84,EOMONTH(A84,0))</f>
+        <v/>
+      </c>
+      <c r="D84" s="67">
+        <f>IF(ISNUMBER(MATCH(A84,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="58" t="n">
-        <v>46357</v>
-      </c>
-      <c r="B85" s="43" t="n">
-        <v>23</v>
+      <c r="A85" s="66">
+        <f>EDATE(A84,1)</f>
+        <v/>
+      </c>
+      <c r="B85" s="48">
+        <f>IFERROR(IF(VLOOKUP(A85,$F$8:$G$37,2,0)="",C85,VLOOKUP(A85,$F$8:$G$37,2,0)),C85)</f>
+        <v/>
+      </c>
+      <c r="C85" s="48">
+        <f>NETWORKDAYS(A85,EOMONTH(A85,0))</f>
+        <v/>
+      </c>
+      <c r="D85" s="67">
+        <f>IF(ISNUMBER(MATCH(A85,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="58" t="n">
-        <v>46388</v>
-      </c>
-      <c r="B86" s="43" t="n">
-        <v>21</v>
+      <c r="A86" s="66">
+        <f>EDATE(A85,1)</f>
+        <v/>
+      </c>
+      <c r="B86" s="48">
+        <f>IFERROR(IF(VLOOKUP(A86,$F$8:$G$37,2,0)="",C86,VLOOKUP(A86,$F$8:$G$37,2,0)),C86)</f>
+        <v/>
+      </c>
+      <c r="C86" s="48">
+        <f>NETWORKDAYS(A86,EOMONTH(A86,0))</f>
+        <v/>
+      </c>
+      <c r="D86" s="67">
+        <f>IF(ISNUMBER(MATCH(A86,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="58" t="n">
-        <v>46419</v>
-      </c>
-      <c r="B87" s="43" t="n">
-        <v>20</v>
+      <c r="A87" s="66">
+        <f>EDATE(A86,1)</f>
+        <v/>
+      </c>
+      <c r="B87" s="48">
+        <f>IFERROR(IF(VLOOKUP(A87,$F$8:$G$37,2,0)="",C87,VLOOKUP(A87,$F$8:$G$37,2,0)),C87)</f>
+        <v/>
+      </c>
+      <c r="C87" s="48">
+        <f>NETWORKDAYS(A87,EOMONTH(A87,0))</f>
+        <v/>
+      </c>
+      <c r="D87" s="67">
+        <f>IF(ISNUMBER(MATCH(A87,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="58" t="n">
-        <v>46447</v>
-      </c>
-      <c r="B88" s="43" t="n">
-        <v>23</v>
+      <c r="A88" s="66">
+        <f>EDATE(A87,1)</f>
+        <v/>
+      </c>
+      <c r="B88" s="48">
+        <f>IFERROR(IF(VLOOKUP(A88,$F$8:$G$37,2,0)="",C88,VLOOKUP(A88,$F$8:$G$37,2,0)),C88)</f>
+        <v/>
+      </c>
+      <c r="C88" s="48">
+        <f>NETWORKDAYS(A88,EOMONTH(A88,0))</f>
+        <v/>
+      </c>
+      <c r="D88" s="67">
+        <f>IF(ISNUMBER(MATCH(A88,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="58" t="n">
-        <v>46478</v>
-      </c>
-      <c r="B89" s="43" t="n">
-        <v>22</v>
+      <c r="A89" s="66">
+        <f>EDATE(A88,1)</f>
+        <v/>
+      </c>
+      <c r="B89" s="48">
+        <f>IFERROR(IF(VLOOKUP(A89,$F$8:$G$37,2,0)="",C89,VLOOKUP(A89,$F$8:$G$37,2,0)),C89)</f>
+        <v/>
+      </c>
+      <c r="C89" s="48">
+        <f>NETWORKDAYS(A89,EOMONTH(A89,0))</f>
+        <v/>
+      </c>
+      <c r="D89" s="67">
+        <f>IF(ISNUMBER(MATCH(A89,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="58" t="n">
-        <v>46508</v>
-      </c>
-      <c r="B90" s="43" t="n">
-        <v>21</v>
+      <c r="A90" s="66">
+        <f>EDATE(A89,1)</f>
+        <v/>
+      </c>
+      <c r="B90" s="48">
+        <f>IFERROR(IF(VLOOKUP(A90,$F$8:$G$37,2,0)="",C90,VLOOKUP(A90,$F$8:$G$37,2,0)),C90)</f>
+        <v/>
+      </c>
+      <c r="C90" s="48">
+        <f>NETWORKDAYS(A90,EOMONTH(A90,0))</f>
+        <v/>
+      </c>
+      <c r="D90" s="67">
+        <f>IF(ISNUMBER(MATCH(A90,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="58" t="n">
-        <v>46539</v>
-      </c>
-      <c r="B91" s="43" t="n">
-        <v>22</v>
+      <c r="A91" s="66">
+        <f>EDATE(A90,1)</f>
+        <v/>
+      </c>
+      <c r="B91" s="48">
+        <f>IFERROR(IF(VLOOKUP(A91,$F$8:$G$37,2,0)="",C91,VLOOKUP(A91,$F$8:$G$37,2,0)),C91)</f>
+        <v/>
+      </c>
+      <c r="C91" s="48">
+        <f>NETWORKDAYS(A91,EOMONTH(A91,0))</f>
+        <v/>
+      </c>
+      <c r="D91" s="67">
+        <f>IF(ISNUMBER(MATCH(A91,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="58" t="n">
-        <v>46569</v>
-      </c>
-      <c r="B92" s="43" t="n">
-        <v>22</v>
+      <c r="A92" s="66">
+        <f>EDATE(A91,1)</f>
+        <v/>
+      </c>
+      <c r="B92" s="48">
+        <f>IFERROR(IF(VLOOKUP(A92,$F$8:$G$37,2,0)="",C92,VLOOKUP(A92,$F$8:$G$37,2,0)),C92)</f>
+        <v/>
+      </c>
+      <c r="C92" s="48">
+        <f>NETWORKDAYS(A92,EOMONTH(A92,0))</f>
+        <v/>
+      </c>
+      <c r="D92" s="67">
+        <f>IF(ISNUMBER(MATCH(A92,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="58" t="n">
-        <v>46600</v>
-      </c>
-      <c r="B93" s="43" t="n">
-        <v>22</v>
+      <c r="A93" s="66">
+        <f>EDATE(A92,1)</f>
+        <v/>
+      </c>
+      <c r="B93" s="48">
+        <f>IFERROR(IF(VLOOKUP(A93,$F$8:$G$37,2,0)="",C93,VLOOKUP(A93,$F$8:$G$37,2,0)),C93)</f>
+        <v/>
+      </c>
+      <c r="C93" s="48">
+        <f>NETWORKDAYS(A93,EOMONTH(A93,0))</f>
+        <v/>
+      </c>
+      <c r="D93" s="67">
+        <f>IF(ISNUMBER(MATCH(A93,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="58" t="n">
-        <v>46631</v>
-      </c>
-      <c r="B94" s="43" t="n">
-        <v>22</v>
+      <c r="A94" s="66">
+        <f>EDATE(A93,1)</f>
+        <v/>
+      </c>
+      <c r="B94" s="48">
+        <f>IFERROR(IF(VLOOKUP(A94,$F$8:$G$37,2,0)="",C94,VLOOKUP(A94,$F$8:$G$37,2,0)),C94)</f>
+        <v/>
+      </c>
+      <c r="C94" s="48">
+        <f>NETWORKDAYS(A94,EOMONTH(A94,0))</f>
+        <v/>
+      </c>
+      <c r="D94" s="67">
+        <f>IF(ISNUMBER(MATCH(A94,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="58" t="n">
-        <v>46661</v>
-      </c>
-      <c r="B95" s="43" t="n">
-        <v>21</v>
+      <c r="A95" s="66">
+        <f>EDATE(A94,1)</f>
+        <v/>
+      </c>
+      <c r="B95" s="48">
+        <f>IFERROR(IF(VLOOKUP(A95,$F$8:$G$37,2,0)="",C95,VLOOKUP(A95,$F$8:$G$37,2,0)),C95)</f>
+        <v/>
+      </c>
+      <c r="C95" s="48">
+        <f>NETWORKDAYS(A95,EOMONTH(A95,0))</f>
+        <v/>
+      </c>
+      <c r="D95" s="67">
+        <f>IF(ISNUMBER(MATCH(A95,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="58" t="n">
-        <v>46692</v>
-      </c>
-      <c r="B96" s="43" t="n">
-        <v>22</v>
+      <c r="A96" s="66">
+        <f>EDATE(A95,1)</f>
+        <v/>
+      </c>
+      <c r="B96" s="48">
+        <f>IFERROR(IF(VLOOKUP(A96,$F$8:$G$37,2,0)="",C96,VLOOKUP(A96,$F$8:$G$37,2,0)),C96)</f>
+        <v/>
+      </c>
+      <c r="C96" s="48">
+        <f>NETWORKDAYS(A96,EOMONTH(A96,0))</f>
+        <v/>
+      </c>
+      <c r="D96" s="67">
+        <f>IF(ISNUMBER(MATCH(A96,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="58" t="n">
-        <v>46722</v>
-      </c>
-      <c r="B97" s="43" t="n">
-        <v>23</v>
-      </c>
+      <c r="A97" s="66">
+        <f>EDATE(A96,1)</f>
+        <v/>
+      </c>
+      <c r="B97" s="48">
+        <f>IFERROR(IF(VLOOKUP(A97,$F$8:$G$37,2,0)="",C97,VLOOKUP(A97,$F$8:$G$37,2,0)),C97)</f>
+        <v/>
+      </c>
+      <c r="C97" s="48">
+        <f>NETWORKDAYS(A97,EOMONTH(A97,0))</f>
+        <v/>
+      </c>
+      <c r="D97" s="67">
+        <f>IF(ISNUMBER(MATCH(A97,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="66">
+        <f>EDATE(A97,1)</f>
+        <v/>
+      </c>
+      <c r="B98" s="48">
+        <f>IFERROR(IF(VLOOKUP(A98,$F$8:$G$37,2,0)="",C98,VLOOKUP(A98,$F$8:$G$37,2,0)),C98)</f>
+        <v/>
+      </c>
+      <c r="C98" s="48">
+        <f>NETWORKDAYS(A98,EOMONTH(A98,0))</f>
+        <v/>
+      </c>
+      <c r="D98" s="67">
+        <f>IF(ISNUMBER(MATCH(A98,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="66">
+        <f>EDATE(A98,1)</f>
+        <v/>
+      </c>
+      <c r="B99" s="48">
+        <f>IFERROR(IF(VLOOKUP(A99,$F$8:$G$37,2,0)="",C99,VLOOKUP(A99,$F$8:$G$37,2,0)),C99)</f>
+        <v/>
+      </c>
+      <c r="C99" s="48">
+        <f>NETWORKDAYS(A99,EOMONTH(A99,0))</f>
+        <v/>
+      </c>
+      <c r="D99" s="67">
+        <f>IF(ISNUMBER(MATCH(A99,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="66">
+        <f>EDATE(A99,1)</f>
+        <v/>
+      </c>
+      <c r="B100" s="48">
+        <f>IFERROR(IF(VLOOKUP(A100,$F$8:$G$37,2,0)="",C100,VLOOKUP(A100,$F$8:$G$37,2,0)),C100)</f>
+        <v/>
+      </c>
+      <c r="C100" s="48">
+        <f>NETWORKDAYS(A100,EOMONTH(A100,0))</f>
+        <v/>
+      </c>
+      <c r="D100" s="67">
+        <f>IF(ISNUMBER(MATCH(A100,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="66">
+        <f>EDATE(A100,1)</f>
+        <v/>
+      </c>
+      <c r="B101" s="48">
+        <f>IFERROR(IF(VLOOKUP(A101,$F$8:$G$37,2,0)="",C101,VLOOKUP(A101,$F$8:$G$37,2,0)),C101)</f>
+        <v/>
+      </c>
+      <c r="C101" s="48">
+        <f>NETWORKDAYS(A101,EOMONTH(A101,0))</f>
+        <v/>
+      </c>
+      <c r="D101" s="67">
+        <f>IF(ISNUMBER(MATCH(A101,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="66">
+        <f>EDATE(A101,1)</f>
+        <v/>
+      </c>
+      <c r="B102" s="48">
+        <f>IFERROR(IF(VLOOKUP(A102,$F$8:$G$37,2,0)="",C102,VLOOKUP(A102,$F$8:$G$37,2,0)),C102)</f>
+        <v/>
+      </c>
+      <c r="C102" s="48">
+        <f>NETWORKDAYS(A102,EOMONTH(A102,0))</f>
+        <v/>
+      </c>
+      <c r="D102" s="67">
+        <f>IF(ISNUMBER(MATCH(A102,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="66">
+        <f>EDATE(A102,1)</f>
+        <v/>
+      </c>
+      <c r="B103" s="48">
+        <f>IFERROR(IF(VLOOKUP(A103,$F$8:$G$37,2,0)="",C103,VLOOKUP(A103,$F$8:$G$37,2,0)),C103)</f>
+        <v/>
+      </c>
+      <c r="C103" s="48">
+        <f>NETWORKDAYS(A103,EOMONTH(A103,0))</f>
+        <v/>
+      </c>
+      <c r="D103" s="67">
+        <f>IF(ISNUMBER(MATCH(A103,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="66">
+        <f>EDATE(A103,1)</f>
+        <v/>
+      </c>
+      <c r="B104" s="48">
+        <f>IFERROR(IF(VLOOKUP(A104,$F$8:$G$37,2,0)="",C104,VLOOKUP(A104,$F$8:$G$37,2,0)),C104)</f>
+        <v/>
+      </c>
+      <c r="C104" s="48">
+        <f>NETWORKDAYS(A104,EOMONTH(A104,0))</f>
+        <v/>
+      </c>
+      <c r="D104" s="67">
+        <f>IF(ISNUMBER(MATCH(A104,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="66">
+        <f>EDATE(A104,1)</f>
+        <v/>
+      </c>
+      <c r="B105" s="48">
+        <f>IFERROR(IF(VLOOKUP(A105,$F$8:$G$37,2,0)="",C105,VLOOKUP(A105,$F$8:$G$37,2,0)),C105)</f>
+        <v/>
+      </c>
+      <c r="C105" s="48">
+        <f>NETWORKDAYS(A105,EOMONTH(A105,0))</f>
+        <v/>
+      </c>
+      <c r="D105" s="67">
+        <f>IF(ISNUMBER(MATCH(A105,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="66">
+        <f>EDATE(A105,1)</f>
+        <v/>
+      </c>
+      <c r="B106" s="48">
+        <f>IFERROR(IF(VLOOKUP(A106,$F$8:$G$37,2,0)="",C106,VLOOKUP(A106,$F$8:$G$37,2,0)),C106)</f>
+        <v/>
+      </c>
+      <c r="C106" s="48">
+        <f>NETWORKDAYS(A106,EOMONTH(A106,0))</f>
+        <v/>
+      </c>
+      <c r="D106" s="67">
+        <f>IF(ISNUMBER(MATCH(A106,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="66">
+        <f>EDATE(A106,1)</f>
+        <v/>
+      </c>
+      <c r="B107" s="48">
+        <f>IFERROR(IF(VLOOKUP(A107,$F$8:$G$37,2,0)="",C107,VLOOKUP(A107,$F$8:$G$37,2,0)),C107)</f>
+        <v/>
+      </c>
+      <c r="C107" s="48">
+        <f>NETWORKDAYS(A107,EOMONTH(A107,0))</f>
+        <v/>
+      </c>
+      <c r="D107" s="67">
+        <f>IF(ISNUMBER(MATCH(A107,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="66">
+        <f>EDATE(A107,1)</f>
+        <v/>
+      </c>
+      <c r="B108" s="48">
+        <f>IFERROR(IF(VLOOKUP(A108,$F$8:$G$37,2,0)="",C108,VLOOKUP(A108,$F$8:$G$37,2,0)),C108)</f>
+        <v/>
+      </c>
+      <c r="C108" s="48">
+        <f>NETWORKDAYS(A108,EOMONTH(A108,0))</f>
+        <v/>
+      </c>
+      <c r="D108" s="67">
+        <f>IF(ISNUMBER(MATCH(A108,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="66">
+        <f>EDATE(A108,1)</f>
+        <v/>
+      </c>
+      <c r="B109" s="48">
+        <f>IFERROR(IF(VLOOKUP(A109,$F$8:$G$37,2,0)="",C109,VLOOKUP(A109,$F$8:$G$37,2,0)),C109)</f>
+        <v/>
+      </c>
+      <c r="C109" s="48">
+        <f>NETWORKDAYS(A109,EOMONTH(A109,0))</f>
+        <v/>
+      </c>
+      <c r="D109" s="67">
+        <f>IF(ISNUMBER(MATCH(A109,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="66">
+        <f>EDATE(A109,1)</f>
+        <v/>
+      </c>
+      <c r="B110" s="48">
+        <f>IFERROR(IF(VLOOKUP(A110,$F$8:$G$37,2,0)="",C110,VLOOKUP(A110,$F$8:$G$37,2,0)),C110)</f>
+        <v/>
+      </c>
+      <c r="C110" s="48">
+        <f>NETWORKDAYS(A110,EOMONTH(A110,0))</f>
+        <v/>
+      </c>
+      <c r="D110" s="67">
+        <f>IF(ISNUMBER(MATCH(A110,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="66">
+        <f>EDATE(A110,1)</f>
+        <v/>
+      </c>
+      <c r="B111" s="48">
+        <f>IFERROR(IF(VLOOKUP(A111,$F$8:$G$37,2,0)="",C111,VLOOKUP(A111,$F$8:$G$37,2,0)),C111)</f>
+        <v/>
+      </c>
+      <c r="C111" s="48">
+        <f>NETWORKDAYS(A111,EOMONTH(A111,0))</f>
+        <v/>
+      </c>
+      <c r="D111" s="67">
+        <f>IF(ISNUMBER(MATCH(A111,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="66">
+        <f>EDATE(A111,1)</f>
+        <v/>
+      </c>
+      <c r="B112" s="48">
+        <f>IFERROR(IF(VLOOKUP(A112,$F$8:$G$37,2,0)="",C112,VLOOKUP(A112,$F$8:$G$37,2,0)),C112)</f>
+        <v/>
+      </c>
+      <c r="C112" s="48">
+        <f>NETWORKDAYS(A112,EOMONTH(A112,0))</f>
+        <v/>
+      </c>
+      <c r="D112" s="67">
+        <f>IF(ISNUMBER(MATCH(A112,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="66">
+        <f>EDATE(A112,1)</f>
+        <v/>
+      </c>
+      <c r="B113" s="48">
+        <f>IFERROR(IF(VLOOKUP(A113,$F$8:$G$37,2,0)="",C113,VLOOKUP(A113,$F$8:$G$37,2,0)),C113)</f>
+        <v/>
+      </c>
+      <c r="C113" s="48">
+        <f>NETWORKDAYS(A113,EOMONTH(A113,0))</f>
+        <v/>
+      </c>
+      <c r="D113" s="67">
+        <f>IF(ISNUMBER(MATCH(A113,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="66">
+        <f>EDATE(A113,1)</f>
+        <v/>
+      </c>
+      <c r="B114" s="48">
+        <f>IFERROR(IF(VLOOKUP(A114,$F$8:$G$37,2,0)="",C114,VLOOKUP(A114,$F$8:$G$37,2,0)),C114)</f>
+        <v/>
+      </c>
+      <c r="C114" s="48">
+        <f>NETWORKDAYS(A114,EOMONTH(A114,0))</f>
+        <v/>
+      </c>
+      <c r="D114" s="67">
+        <f>IF(ISNUMBER(MATCH(A114,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="66">
+        <f>EDATE(A114,1)</f>
+        <v/>
+      </c>
+      <c r="B115" s="48">
+        <f>IFERROR(IF(VLOOKUP(A115,$F$8:$G$37,2,0)="",C115,VLOOKUP(A115,$F$8:$G$37,2,0)),C115)</f>
+        <v/>
+      </c>
+      <c r="C115" s="48">
+        <f>NETWORKDAYS(A115,EOMONTH(A115,0))</f>
+        <v/>
+      </c>
+      <c r="D115" s="67">
+        <f>IF(ISNUMBER(MATCH(A115,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="66">
+        <f>EDATE(A115,1)</f>
+        <v/>
+      </c>
+      <c r="B116" s="48">
+        <f>IFERROR(IF(VLOOKUP(A116,$F$8:$G$37,2,0)="",C116,VLOOKUP(A116,$F$8:$G$37,2,0)),C116)</f>
+        <v/>
+      </c>
+      <c r="C116" s="48">
+        <f>NETWORKDAYS(A116,EOMONTH(A116,0))</f>
+        <v/>
+      </c>
+      <c r="D116" s="67">
+        <f>IF(ISNUMBER(MATCH(A116,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="66">
+        <f>EDATE(A116,1)</f>
+        <v/>
+      </c>
+      <c r="B117" s="48">
+        <f>IFERROR(IF(VLOOKUP(A117,$F$8:$G$37,2,0)="",C117,VLOOKUP(A117,$F$8:$G$37,2,0)),C117)</f>
+        <v/>
+      </c>
+      <c r="C117" s="48">
+        <f>NETWORKDAYS(A117,EOMONTH(A117,0))</f>
+        <v/>
+      </c>
+      <c r="D117" s="67">
+        <f>IF(ISNUMBER(MATCH(A117,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="66">
+        <f>EDATE(A117,1)</f>
+        <v/>
+      </c>
+      <c r="B118" s="48">
+        <f>IFERROR(IF(VLOOKUP(A118,$F$8:$G$37,2,0)="",C118,VLOOKUP(A118,$F$8:$G$37,2,0)),C118)</f>
+        <v/>
+      </c>
+      <c r="C118" s="48">
+        <f>NETWORKDAYS(A118,EOMONTH(A118,0))</f>
+        <v/>
+      </c>
+      <c r="D118" s="67">
+        <f>IF(ISNUMBER(MATCH(A118,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="66">
+        <f>EDATE(A118,1)</f>
+        <v/>
+      </c>
+      <c r="B119" s="48">
+        <f>IFERROR(IF(VLOOKUP(A119,$F$8:$G$37,2,0)="",C119,VLOOKUP(A119,$F$8:$G$37,2,0)),C119)</f>
+        <v/>
+      </c>
+      <c r="C119" s="48">
+        <f>NETWORKDAYS(A119,EOMONTH(A119,0))</f>
+        <v/>
+      </c>
+      <c r="D119" s="67">
+        <f>IF(ISNUMBER(MATCH(A119,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="66">
+        <f>EDATE(A119,1)</f>
+        <v/>
+      </c>
+      <c r="B120" s="48">
+        <f>IFERROR(IF(VLOOKUP(A120,$F$8:$G$37,2,0)="",C120,VLOOKUP(A120,$F$8:$G$37,2,0)),C120)</f>
+        <v/>
+      </c>
+      <c r="C120" s="48">
+        <f>NETWORKDAYS(A120,EOMONTH(A120,0))</f>
+        <v/>
+      </c>
+      <c r="D120" s="67">
+        <f>IF(ISNUMBER(MATCH(A120,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="66">
+        <f>EDATE(A120,1)</f>
+        <v/>
+      </c>
+      <c r="B121" s="48">
+        <f>IFERROR(IF(VLOOKUP(A121,$F$8:$G$37,2,0)="",C121,VLOOKUP(A121,$F$8:$G$37,2,0)),C121)</f>
+        <v/>
+      </c>
+      <c r="C121" s="48">
+        <f>NETWORKDAYS(A121,EOMONTH(A121,0))</f>
+        <v/>
+      </c>
+      <c r="D121" s="67">
+        <f>IF(ISNUMBER(MATCH(A121,$F$8:$F$37,0)),"修正あり","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="61" t="n"/>
+      <c r="B122" s="61" t="n"/>
+      <c r="C122" s="61" t="n"/>
+      <c r="D122" s="61" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="61" t="n"/>
+      <c r="B123" s="61" t="n"/>
+      <c r="C123" s="61" t="n"/>
+      <c r="D123" s="61" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="61" t="n"/>
+      <c r="B124" s="61" t="n"/>
+      <c r="C124" s="61" t="n"/>
+      <c r="D124" s="61" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="61" t="n"/>
+      <c r="B125" s="61" t="n"/>
+      <c r="C125" s="61" t="n"/>
+      <c r="D125" s="61" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="61" t="n"/>
+      <c r="B126" s="61" t="n"/>
+      <c r="C126" s="61" t="n"/>
+      <c r="D126" s="61" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="61" t="n"/>
+      <c r="B127" s="61" t="n"/>
+      <c r="C127" s="61" t="n"/>
+      <c r="D127" s="61" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="61" t="n"/>
+      <c r="B128" s="61" t="n"/>
+      <c r="C128" s="61" t="n"/>
+      <c r="D128" s="61" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="61" t="n"/>
+      <c r="B129" s="61" t="n"/>
+      <c r="C129" s="61" t="n"/>
+      <c r="D129" s="61" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="61" t="n"/>
+      <c r="B130" s="61" t="n"/>
+      <c r="C130" s="61" t="n"/>
+      <c r="D130" s="61" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -8997,7 +10598,13 @@
           <t>職員番号</t>
         </is>
       </c>
-      <c r="F3" s="66" t="n"/>
+      <c r="F3" s="70" t="n"/>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>支給開始日（待機3日後）</t>
+        </is>
+      </c>
+      <c r="N3" s="71" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -9005,7 +10612,13 @@
           <t>氏名</t>
         </is>
       </c>
-      <c r="F4" s="67" t="n"/>
+      <c r="F4" s="72" t="n"/>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>法定給付の末日（1年6月＋出勤）</t>
+        </is>
+      </c>
+      <c r="N4" s="71" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -9013,13 +10626,19 @@
           <t>請求期間</t>
         </is>
       </c>
-      <c r="F5" s="68" t="n"/>
-      <c r="G5" s="69" t="inlineStr">
+      <c r="F5" s="71" t="n"/>
+      <c r="G5" s="73" t="inlineStr">
         <is>
           <t>～</t>
         </is>
       </c>
-      <c r="H5" s="68" t="n"/>
+      <c r="H5" s="71" t="n"/>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>附加給付の開始日</t>
+        </is>
+      </c>
+      <c r="N5" s="71" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -9027,7 +10646,13 @@
           <t>傷病手当日額（支給開始月で固定）</t>
         </is>
       </c>
-      <c r="F6" s="70" t="n"/>
+      <c r="F6" s="74" t="n"/>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>附加給付の末日（+6月＋出勤）</t>
+        </is>
+      </c>
+      <c r="N6" s="71" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -9035,7 +10660,21 @@
           <t>作成日</t>
         </is>
       </c>
-      <c r="F7" s="68" t="n"/>
+      <c r="F7" s="71" t="n"/>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>算定の最終日</t>
+        </is>
+      </c>
+      <c r="N7" s="71" t="n"/>
+    </row>
+    <row r="8">
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>出勤による延長日数</t>
+        </is>
+      </c>
+      <c r="N8" s="75" t="n"/>
     </row>
     <row r="9" ht="42" customHeight="1" s="39">
       <c r="A9" s="18" t="inlineStr">
@@ -10495,14 +12134,20 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="14">
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A43:H43"/>
     <mergeCell ref="A7:E7"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="J4:M4"/>
     <mergeCell ref="A42:H42"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="A5:E5"/>
+    <mergeCell ref="J6:M6"/>
     <mergeCell ref="A6:E6"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="J7:M7"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="A10:O39">
@@ -10530,7 +12175,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="71" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>マクロ用の設定（シート名の文字と、メッセージの文言です。必要なときだけ直してください）</t>
         </is>
@@ -10542,7 +12187,7 @@
           <t>請求シート名の先頭</t>
         </is>
       </c>
-      <c r="B3" s="72" t="inlineStr">
+      <c r="B3" s="77" t="inlineStr">
         <is>
           <t>請求_</t>
         </is>
@@ -10554,7 +12199,7 @@
           <t>同名があるときに付ける文字</t>
         </is>
       </c>
-      <c r="B4" s="72" t="inlineStr">
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t>_</t>
         </is>
@@ -10566,7 +12211,7 @@
           <t>メッセージ：請求期間が未入力</t>
         </is>
       </c>
-      <c r="B5" s="72" t="inlineStr">
+      <c r="B5" s="77" t="inlineStr">
         <is>
           <t>請求期間の開始日と終了日を、入力シートの「請求期間（始）」「請求期間（終）」に入力してください。</t>
         </is>
@@ -10578,7 +12223,7 @@
           <t>メッセージ：開始日が終了日より後</t>
         </is>
       </c>
-      <c r="B6" s="72" t="inlineStr">
+      <c r="B6" s="77" t="inlineStr">
         <is>
           <t>請求期間の開始日が終了日より後になっています。</t>
         </is>
@@ -10590,7 +12235,7 @@
           <t>メッセージ：該当する行がない</t>
         </is>
       </c>
-      <c r="B7" s="72" t="inlineStr">
+      <c r="B7" s="77" t="inlineStr">
         <is>
           <t>この請求期間に該当する算定表の行がありません。入力シートと算定表を確認してください。</t>
         </is>
@@ -10602,7 +12247,7 @@
           <t>メッセージ：行が多すぎる</t>
         </is>
       </c>
-      <c r="B8" s="72" t="inlineStr">
+      <c r="B8" s="77" t="inlineStr">
         <is>
           <t>行数が雛形に入りきりません。請求期間を短くしてください。</t>
         </is>
@@ -10614,7 +12259,7 @@
           <t>メッセージ：完了</t>
         </is>
       </c>
-      <c r="B9" s="72" t="inlineStr">
+      <c r="B9" s="77" t="inlineStr">
         <is>
           <t>請求シートを追加しました。</t>
         </is>
@@ -10626,7 +12271,7 @@
           <t>シート名の期間の区切り</t>
         </is>
       </c>
-      <c r="B10" s="72" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10638,7 +12283,7 @@
           <t>雛形のシート名（コピー元）</t>
         </is>
       </c>
-      <c r="B11" s="72" t="inlineStr">
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>請求シート雛形</t>
         </is>
@@ -10650,7 +12295,7 @@
           <t>雛形：明細の先頭行</t>
         </is>
       </c>
-      <c r="B12" s="73" t="n">
+      <c r="B12" s="78" t="n">
         <v>10</v>
       </c>
     </row>
@@ -10660,7 +12305,7 @@
           <t>雛形：明細の行数</t>
         </is>
       </c>
-      <c r="B13" s="73" t="n">
+      <c r="B13" s="78" t="n">
         <v>30</v>
       </c>
     </row>

--- a/傷病手当金算定表_v2.xlsx
+++ b/傷病手当金算定表_v2.xlsx
@@ -15,8 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="CLAIM_FROM">'入力'!$C$69</definedName>
-    <definedName name="CLAIM_TO">'入力'!$C$70</definedName>
+    <definedName name="CLAIM_FROM">'入力'!$C$100</definedName>
+    <definedName name="CLAIM_TO">'入力'!$C$101</definedName>
     <definedName name="EMP_ID">'入力'!$C$4</definedName>
     <definedName name="EMP_NAME">'入力'!$C$5</definedName>
     <definedName name="P_START">'入力'!$J$5</definedName>
@@ -24,7 +24,8 @@
     <definedName name="P_ADD_START">'入力'!$J$7</definedName>
     <definedName name="P_ADD_END">'入力'!$J$8</definedName>
     <definedName name="P_FINAL">'入力'!$J$9</definedName>
-    <definedName name="EXT_DAYS">'入力'!$D$55</definedName>
+    <definedName name="EXT_MONTHS">'入力'!$D$85</definedName>
+    <definedName name="EXT_DAYS">'入力'!$E$85</definedName>
     <definedName name="DAILY_RATE">'入力'!$J$10</definedName>
     <definedName name="CALC_TABLE">'算定表'!$A$6:$O$53</definedName>
     <definedName name="SET_PREFIX">'設定'!$B$3</definedName>
@@ -46,15 +47,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0;0"/>
     <numFmt numFmtId="165" formatCode="yyyy/m"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="yyyy/m/d"/>
     <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="169" formatCode="0&quot;日&quot;"/>
+    <numFmt numFmtId="169" formatCode="0&quot;か月&quot;"/>
+    <numFmt numFmtId="170" formatCode="0&quot;日（土日除く）&quot;"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -168,13 +170,6 @@
       <sz val="6"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Meiryo UI"/>
       <b val="1"/>
       <color rgb="FFC00000"/>
@@ -182,11 +177,35 @@
     </font>
     <font>
       <name val="Meiryo UI"/>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -221,6 +240,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
         <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -294,9 +323,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -419,18 +448,24 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="18" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="3" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -441,6 +476,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -459,7 +495,10 @@
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -834,7 +873,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>5．出勤した期間があれば、「入力」シートの出勤期間（52行目〜、10件まで）に開始日・終了日を入力。法定末日・附加開始日・附加末日・最終日が自動で延びます。</t>
+          <t>5．出勤した期間があれば、「入力」シートの出勤期間（82行目〜、10件まで）に開始日・終了日を入力。法定末日・附加開始日・附加末日・最終日が自動で延びます。</t>
         </is>
       </c>
     </row>
@@ -889,7 +928,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>・給付期間：待機3日の後に支給開始、法定給付は1年6か月、附加給付は続く6か月（傷病手当金・附加金マニュアルによる）。出勤期間があればその日数分延びます。</t>
+          <t>・給付期間：待機3日の後に支給開始、法定給付は1年6か月、附加給付は続く6か月（傷病手当金・附加金マニュアルによる）。出勤期間があれば、丸ごと1か月は1か月、残りは土日を除く日数だけ延びます。</t>
         </is>
       </c>
     </row>
@@ -910,11 +949,17 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>・延びる日数は出勤期間の暦日数です。数え方を変えるときは「入力」シートの出勤期間の D 列の式を直してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
+          <t>・出勤による延び方は「月数」と「土日を除く日数」です。数え方を変えるときは「入力」シートの出勤期間の D列・E列の式を直してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>・標準報酬の表は、支給開始月より後の月も「参考」として残しています（算定表のP列にも参考日額が出ます）。傷病手当日額は支給開始月の額で固定です。</t>
+        </is>
+      </c>
+    </row>
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
@@ -941,7 +986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="39" min="1" max="2"/>
@@ -954,6 +999,9 @@
     <col width="12" customWidth="1" style="39" min="8" max="8"/>
     <col width="12" customWidth="1" style="39" min="9" max="9"/>
     <col width="12" customWidth="1" style="39" min="10" max="10"/>
+    <col width="12" customWidth="1" style="39" min="11" max="11"/>
+    <col width="12" customWidth="1" style="39" min="12" max="12"/>
+    <col width="12" customWidth="1" style="39" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.4" customHeight="1" s="39">
@@ -966,7 +1014,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>黄色のセル（青字）だけ入力してください。試算・調整額・差額は「算定表」シートに自動表示されます。（出勤期間・請求期間は52行目以降）</t>
+          <t>黄色のセル（青字）だけ入力してください。試算・調整額・差額は「算定表」シートに自動表示されます。（出勤期間・請求期間は82行目以降）</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1077,7 @@
         </is>
       </c>
       <c r="J6" s="15">
-        <f>MAX($F$55:$F$65)</f>
+        <f>MAX($K$85:$K$95)</f>
         <v/>
       </c>
     </row>
@@ -1073,7 +1121,7 @@
         </is>
       </c>
       <c r="J8" s="15">
-        <f>DATE(YEAR(J7),MONTH(J7)+6,DAY(J7)-1)+MAX($G$55:$G$65)</f>
+        <f>WORKDAY(EDATE(DATE(YEAR(J7),MONTH(J7)+6,DAY(J7)-1),MAX($I$85:$I$95)),MAX($J$85:$J$95))</f>
         <v/>
       </c>
     </row>
@@ -1675,7 +1723,7 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>■ 標準報酬月額と傷病手当日額の試算（支給開始月までの直近12か月平均 ÷ 22 → 10円未満四捨五入 → ×2/3 → 1円未満四捨五入）</t>
+          <t>■ 標準報酬月額と傷病手当日額の試算（直近12か月平均 ÷ 22 → 10円未満四捨五入 → ×2/3 → 1円未満四捨五入）</t>
         </is>
       </c>
     </row>
@@ -1882,625 +1930,1561 @@
       <c r="B48" s="47" t="n">
         <v>320000</v>
       </c>
-      <c r="C48" s="28" t="n"/>
-      <c r="D48" s="28" t="n"/>
-      <c r="E48" s="28" t="n"/>
-      <c r="F48" s="28" t="n"/>
-      <c r="G48" s="28" t="n"/>
+      <c r="C48" s="48">
+        <f>AVERAGE(B37:B48)</f>
+        <v/>
+      </c>
+      <c r="D48" s="50">
+        <f>C48/22</f>
+        <v/>
+      </c>
+      <c r="E48" s="48">
+        <f>ROUND(D48,-1)</f>
+        <v/>
+      </c>
+      <c r="F48" s="50">
+        <f>E48/3*2</f>
+        <v/>
+      </c>
+      <c r="G48" s="48">
+        <f>ROUND(F48,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="49">
+      <c r="A49" s="60">
         <f>DATE(YEAR($J$5),MONTH($J$5)-12+12,1)</f>
         <v/>
       </c>
       <c r="B49" s="47" t="n">
         <v>320000</v>
       </c>
-      <c r="C49" s="48">
+      <c r="C49" s="61">
         <f>AVERAGE(B38:B49)</f>
         <v/>
       </c>
-      <c r="D49" s="50">
+      <c r="D49" s="62">
         <f>C49/22</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="61">
         <f>ROUND(D49,-1)</f>
         <v/>
       </c>
-      <c r="F49" s="50">
+      <c r="F49" s="62">
         <f>E49/3*2</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="63">
         <f>ROUND(F49,0)</f>
         <v/>
       </c>
-      <c r="H49" s="60" t="inlineStr">
+      <c r="H49" s="64" t="inlineStr">
         <is>
           <t>← 支給開始月の額を、全期間の傷病手当日額として固定して使います</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="61" t="n"/>
-      <c r="B50" s="61" t="n"/>
-      <c r="C50" s="61" t="n"/>
-      <c r="D50" s="61" t="n"/>
-      <c r="E50" s="61" t="n"/>
-      <c r="F50" s="61" t="n"/>
-      <c r="G50" s="61" t="n"/>
-      <c r="H50" s="61" t="n"/>
-      <c r="I50" s="61" t="n"/>
-      <c r="J50" s="61" t="n"/>
+      <c r="A50" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+13,1)</f>
+        <v/>
+      </c>
+      <c r="B50" s="47" t="n">
+        <v>320000</v>
+      </c>
+      <c r="C50" s="48">
+        <f>AVERAGE(B39:B50)</f>
+        <v/>
+      </c>
+      <c r="D50" s="50">
+        <f>C50/22</f>
+        <v/>
+      </c>
+      <c r="E50" s="48">
+        <f>ROUND(D50,-1)</f>
+        <v/>
+      </c>
+      <c r="F50" s="50">
+        <f>E50/3*2</f>
+        <v/>
+      </c>
+      <c r="G50" s="48">
+        <f>ROUND(F50,0)</f>
+        <v/>
+      </c>
+      <c r="H50" s="65" t="inlineStr">
+        <is>
+          <t>↓ これより後の月は参考（算定には使いません。月ごとの日額を見る用）</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="61" t="n"/>
-      <c r="B51" s="61" t="n"/>
-      <c r="C51" s="61" t="n"/>
-      <c r="D51" s="61" t="n"/>
-      <c r="E51" s="61" t="n"/>
-      <c r="F51" s="61" t="n"/>
-      <c r="G51" s="61" t="n"/>
-      <c r="H51" s="61" t="n"/>
-      <c r="I51" s="61" t="n"/>
-      <c r="J51" s="61" t="n"/>
+      <c r="A51" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+14,1)</f>
+        <v/>
+      </c>
+      <c r="B51" s="47" t="n">
+        <v>320000</v>
+      </c>
+      <c r="C51" s="48">
+        <f>AVERAGE(B40:B51)</f>
+        <v/>
+      </c>
+      <c r="D51" s="50">
+        <f>C51/22</f>
+        <v/>
+      </c>
+      <c r="E51" s="48">
+        <f>ROUND(D51,-1)</f>
+        <v/>
+      </c>
+      <c r="F51" s="50">
+        <f>E51/3*2</f>
+        <v/>
+      </c>
+      <c r="G51" s="48">
+        <f>ROUND(F51,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>■ 出勤期間（出勤して傷病手当を受けない期間。その日数だけ支給期間が延びます）</t>
-        </is>
-      </c>
-      <c r="B52" s="61" t="n"/>
-      <c r="C52" s="61" t="n"/>
-      <c r="D52" s="61" t="n"/>
-      <c r="E52" s="61" t="n"/>
-      <c r="F52" s="61" t="n"/>
-      <c r="G52" s="61" t="n"/>
-      <c r="H52" s="61" t="n"/>
-      <c r="I52" s="61" t="n"/>
-      <c r="J52" s="61" t="n"/>
+      <c r="A52" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+15,1)</f>
+        <v/>
+      </c>
+      <c r="B52" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C52" s="48">
+        <f>AVERAGE(B41:B52)</f>
+        <v/>
+      </c>
+      <c r="D52" s="50">
+        <f>C52/22</f>
+        <v/>
+      </c>
+      <c r="E52" s="48">
+        <f>ROUND(D52,-1)</f>
+        <v/>
+      </c>
+      <c r="F52" s="50">
+        <f>E52/3*2</f>
+        <v/>
+      </c>
+      <c r="G52" s="48">
+        <f>ROUND(F52,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>※出勤した期間の開始日・終了日を、古い順に入力（10件まで）。法定給付の期間中の出勤は「法定末日・附加開始日・附加末日・最終日」が、附加給付の期間中の出勤は「附加末日・最終日」が、出勤した日数（暦日）だけ後ろにずれます。</t>
-        </is>
-      </c>
-      <c r="B53" s="61" t="n"/>
-      <c r="C53" s="61" t="n"/>
-      <c r="D53" s="61" t="n"/>
-      <c r="E53" s="61" t="n"/>
-      <c r="F53" s="61" t="n"/>
-      <c r="G53" s="61" t="n"/>
-      <c r="H53" s="61" t="n"/>
-      <c r="I53" s="61" t="n"/>
-      <c r="J53" s="61" t="n"/>
-    </row>
-    <row r="54" ht="42" customHeight="1" s="39">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A53" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+16,1)</f>
+        <v/>
+      </c>
+      <c r="B53" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C53" s="48">
+        <f>AVERAGE(B42:B53)</f>
+        <v/>
+      </c>
+      <c r="D53" s="50">
+        <f>C53/22</f>
+        <v/>
+      </c>
+      <c r="E53" s="48">
+        <f>ROUND(D53,-1)</f>
+        <v/>
+      </c>
+      <c r="F53" s="50">
+        <f>E53/3*2</f>
+        <v/>
+      </c>
+      <c r="G53" s="48">
+        <f>ROUND(F53,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+17,1)</f>
+        <v/>
+      </c>
+      <c r="B54" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C54" s="48">
+        <f>AVERAGE(B43:B54)</f>
+        <v/>
+      </c>
+      <c r="D54" s="50">
+        <f>C54/22</f>
+        <v/>
+      </c>
+      <c r="E54" s="48">
+        <f>ROUND(D54,-1)</f>
+        <v/>
+      </c>
+      <c r="F54" s="50">
+        <f>E54/3*2</f>
+        <v/>
+      </c>
+      <c r="G54" s="48">
+        <f>ROUND(F54,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+18,1)</f>
+        <v/>
+      </c>
+      <c r="B55" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C55" s="48">
+        <f>AVERAGE(B44:B55)</f>
+        <v/>
+      </c>
+      <c r="D55" s="50">
+        <f>C55/22</f>
+        <v/>
+      </c>
+      <c r="E55" s="48">
+        <f>ROUND(D55,-1)</f>
+        <v/>
+      </c>
+      <c r="F55" s="50">
+        <f>E55/3*2</f>
+        <v/>
+      </c>
+      <c r="G55" s="48">
+        <f>ROUND(F55,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+19,1)</f>
+        <v/>
+      </c>
+      <c r="B56" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C56" s="48">
+        <f>AVERAGE(B45:B56)</f>
+        <v/>
+      </c>
+      <c r="D56" s="50">
+        <f>C56/22</f>
+        <v/>
+      </c>
+      <c r="E56" s="48">
+        <f>ROUND(D56,-1)</f>
+        <v/>
+      </c>
+      <c r="F56" s="50">
+        <f>E56/3*2</f>
+        <v/>
+      </c>
+      <c r="G56" s="48">
+        <f>ROUND(F56,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+20,1)</f>
+        <v/>
+      </c>
+      <c r="B57" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C57" s="48">
+        <f>AVERAGE(B46:B57)</f>
+        <v/>
+      </c>
+      <c r="D57" s="50">
+        <f>C57/22</f>
+        <v/>
+      </c>
+      <c r="E57" s="48">
+        <f>ROUND(D57,-1)</f>
+        <v/>
+      </c>
+      <c r="F57" s="50">
+        <f>E57/3*2</f>
+        <v/>
+      </c>
+      <c r="G57" s="48">
+        <f>ROUND(F57,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+21,1)</f>
+        <v/>
+      </c>
+      <c r="B58" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C58" s="48">
+        <f>AVERAGE(B47:B58)</f>
+        <v/>
+      </c>
+      <c r="D58" s="50">
+        <f>C58/22</f>
+        <v/>
+      </c>
+      <c r="E58" s="48">
+        <f>ROUND(D58,-1)</f>
+        <v/>
+      </c>
+      <c r="F58" s="50">
+        <f>E58/3*2</f>
+        <v/>
+      </c>
+      <c r="G58" s="48">
+        <f>ROUND(F58,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+22,1)</f>
+        <v/>
+      </c>
+      <c r="B59" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C59" s="48">
+        <f>AVERAGE(B48:B59)</f>
+        <v/>
+      </c>
+      <c r="D59" s="50">
+        <f>C59/22</f>
+        <v/>
+      </c>
+      <c r="E59" s="48">
+        <f>ROUND(D59,-1)</f>
+        <v/>
+      </c>
+      <c r="F59" s="50">
+        <f>E59/3*2</f>
+        <v/>
+      </c>
+      <c r="G59" s="48">
+        <f>ROUND(F59,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+23,1)</f>
+        <v/>
+      </c>
+      <c r="B60" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C60" s="48">
+        <f>AVERAGE(B49:B60)</f>
+        <v/>
+      </c>
+      <c r="D60" s="50">
+        <f>C60/22</f>
+        <v/>
+      </c>
+      <c r="E60" s="48">
+        <f>ROUND(D60,-1)</f>
+        <v/>
+      </c>
+      <c r="F60" s="50">
+        <f>E60/3*2</f>
+        <v/>
+      </c>
+      <c r="G60" s="48">
+        <f>ROUND(F60,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+24,1)</f>
+        <v/>
+      </c>
+      <c r="B61" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C61" s="48">
+        <f>AVERAGE(B50:B61)</f>
+        <v/>
+      </c>
+      <c r="D61" s="50">
+        <f>C61/22</f>
+        <v/>
+      </c>
+      <c r="E61" s="48">
+        <f>ROUND(D61,-1)</f>
+        <v/>
+      </c>
+      <c r="F61" s="50">
+        <f>E61/3*2</f>
+        <v/>
+      </c>
+      <c r="G61" s="48">
+        <f>ROUND(F61,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+25,1)</f>
+        <v/>
+      </c>
+      <c r="B62" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C62" s="48">
+        <f>AVERAGE(B51:B62)</f>
+        <v/>
+      </c>
+      <c r="D62" s="50">
+        <f>C62/22</f>
+        <v/>
+      </c>
+      <c r="E62" s="48">
+        <f>ROUND(D62,-1)</f>
+        <v/>
+      </c>
+      <c r="F62" s="50">
+        <f>E62/3*2</f>
+        <v/>
+      </c>
+      <c r="G62" s="48">
+        <f>ROUND(F62,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+26,1)</f>
+        <v/>
+      </c>
+      <c r="B63" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C63" s="48">
+        <f>AVERAGE(B52:B63)</f>
+        <v/>
+      </c>
+      <c r="D63" s="50">
+        <f>C63/22</f>
+        <v/>
+      </c>
+      <c r="E63" s="48">
+        <f>ROUND(D63,-1)</f>
+        <v/>
+      </c>
+      <c r="F63" s="50">
+        <f>E63/3*2</f>
+        <v/>
+      </c>
+      <c r="G63" s="48">
+        <f>ROUND(F63,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+27,1)</f>
+        <v/>
+      </c>
+      <c r="B64" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C64" s="48">
+        <f>AVERAGE(B53:B64)</f>
+        <v/>
+      </c>
+      <c r="D64" s="50">
+        <f>C64/22</f>
+        <v/>
+      </c>
+      <c r="E64" s="48">
+        <f>ROUND(D64,-1)</f>
+        <v/>
+      </c>
+      <c r="F64" s="50">
+        <f>E64/3*2</f>
+        <v/>
+      </c>
+      <c r="G64" s="48">
+        <f>ROUND(F64,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+28,1)</f>
+        <v/>
+      </c>
+      <c r="B65" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C65" s="48">
+        <f>AVERAGE(B54:B65)</f>
+        <v/>
+      </c>
+      <c r="D65" s="50">
+        <f>C65/22</f>
+        <v/>
+      </c>
+      <c r="E65" s="48">
+        <f>ROUND(D65,-1)</f>
+        <v/>
+      </c>
+      <c r="F65" s="50">
+        <f>E65/3*2</f>
+        <v/>
+      </c>
+      <c r="G65" s="48">
+        <f>ROUND(F65,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+29,1)</f>
+        <v/>
+      </c>
+      <c r="B66" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C66" s="48">
+        <f>AVERAGE(B55:B66)</f>
+        <v/>
+      </c>
+      <c r="D66" s="50">
+        <f>C66/22</f>
+        <v/>
+      </c>
+      <c r="E66" s="48">
+        <f>ROUND(D66,-1)</f>
+        <v/>
+      </c>
+      <c r="F66" s="50">
+        <f>E66/3*2</f>
+        <v/>
+      </c>
+      <c r="G66" s="48">
+        <f>ROUND(F66,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+30,1)</f>
+        <v/>
+      </c>
+      <c r="B67" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C67" s="48">
+        <f>AVERAGE(B56:B67)</f>
+        <v/>
+      </c>
+      <c r="D67" s="50">
+        <f>C67/22</f>
+        <v/>
+      </c>
+      <c r="E67" s="48">
+        <f>ROUND(D67,-1)</f>
+        <v/>
+      </c>
+      <c r="F67" s="50">
+        <f>E67/3*2</f>
+        <v/>
+      </c>
+      <c r="G67" s="48">
+        <f>ROUND(F67,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+31,1)</f>
+        <v/>
+      </c>
+      <c r="B68" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C68" s="48">
+        <f>AVERAGE(B57:B68)</f>
+        <v/>
+      </c>
+      <c r="D68" s="50">
+        <f>C68/22</f>
+        <v/>
+      </c>
+      <c r="E68" s="48">
+        <f>ROUND(D68,-1)</f>
+        <v/>
+      </c>
+      <c r="F68" s="50">
+        <f>E68/3*2</f>
+        <v/>
+      </c>
+      <c r="G68" s="48">
+        <f>ROUND(F68,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+32,1)</f>
+        <v/>
+      </c>
+      <c r="B69" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C69" s="48">
+        <f>AVERAGE(B58:B69)</f>
+        <v/>
+      </c>
+      <c r="D69" s="50">
+        <f>C69/22</f>
+        <v/>
+      </c>
+      <c r="E69" s="48">
+        <f>ROUND(D69,-1)</f>
+        <v/>
+      </c>
+      <c r="F69" s="50">
+        <f>E69/3*2</f>
+        <v/>
+      </c>
+      <c r="G69" s="48">
+        <f>ROUND(F69,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+33,1)</f>
+        <v/>
+      </c>
+      <c r="B70" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C70" s="48">
+        <f>AVERAGE(B59:B70)</f>
+        <v/>
+      </c>
+      <c r="D70" s="50">
+        <f>C70/22</f>
+        <v/>
+      </c>
+      <c r="E70" s="48">
+        <f>ROUND(D70,-1)</f>
+        <v/>
+      </c>
+      <c r="F70" s="50">
+        <f>E70/3*2</f>
+        <v/>
+      </c>
+      <c r="G70" s="48">
+        <f>ROUND(F70,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+34,1)</f>
+        <v/>
+      </c>
+      <c r="B71" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C71" s="48">
+        <f>AVERAGE(B60:B71)</f>
+        <v/>
+      </c>
+      <c r="D71" s="50">
+        <f>C71/22</f>
+        <v/>
+      </c>
+      <c r="E71" s="48">
+        <f>ROUND(D71,-1)</f>
+        <v/>
+      </c>
+      <c r="F71" s="50">
+        <f>E71/3*2</f>
+        <v/>
+      </c>
+      <c r="G71" s="48">
+        <f>ROUND(F71,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+35,1)</f>
+        <v/>
+      </c>
+      <c r="B72" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C72" s="48">
+        <f>AVERAGE(B61:B72)</f>
+        <v/>
+      </c>
+      <c r="D72" s="50">
+        <f>C72/22</f>
+        <v/>
+      </c>
+      <c r="E72" s="48">
+        <f>ROUND(D72,-1)</f>
+        <v/>
+      </c>
+      <c r="F72" s="50">
+        <f>E72/3*2</f>
+        <v/>
+      </c>
+      <c r="G72" s="48">
+        <f>ROUND(F72,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+36,1)</f>
+        <v/>
+      </c>
+      <c r="B73" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C73" s="48">
+        <f>AVERAGE(B62:B73)</f>
+        <v/>
+      </c>
+      <c r="D73" s="50">
+        <f>C73/22</f>
+        <v/>
+      </c>
+      <c r="E73" s="48">
+        <f>ROUND(D73,-1)</f>
+        <v/>
+      </c>
+      <c r="F73" s="50">
+        <f>E73/3*2</f>
+        <v/>
+      </c>
+      <c r="G73" s="48">
+        <f>ROUND(F73,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+37,1)</f>
+        <v/>
+      </c>
+      <c r="B74" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C74" s="48">
+        <f>AVERAGE(B63:B74)</f>
+        <v/>
+      </c>
+      <c r="D74" s="50">
+        <f>C74/22</f>
+        <v/>
+      </c>
+      <c r="E74" s="48">
+        <f>ROUND(D74,-1)</f>
+        <v/>
+      </c>
+      <c r="F74" s="50">
+        <f>E74/3*2</f>
+        <v/>
+      </c>
+      <c r="G74" s="48">
+        <f>ROUND(F74,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+38,1)</f>
+        <v/>
+      </c>
+      <c r="B75" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C75" s="48">
+        <f>AVERAGE(B64:B75)</f>
+        <v/>
+      </c>
+      <c r="D75" s="50">
+        <f>C75/22</f>
+        <v/>
+      </c>
+      <c r="E75" s="48">
+        <f>ROUND(D75,-1)</f>
+        <v/>
+      </c>
+      <c r="F75" s="50">
+        <f>E75/3*2</f>
+        <v/>
+      </c>
+      <c r="G75" s="48">
+        <f>ROUND(F75,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+39,1)</f>
+        <v/>
+      </c>
+      <c r="B76" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C76" s="48">
+        <f>AVERAGE(B65:B76)</f>
+        <v/>
+      </c>
+      <c r="D76" s="50">
+        <f>C76/22</f>
+        <v/>
+      </c>
+      <c r="E76" s="48">
+        <f>ROUND(D76,-1)</f>
+        <v/>
+      </c>
+      <c r="F76" s="50">
+        <f>E76/3*2</f>
+        <v/>
+      </c>
+      <c r="G76" s="48">
+        <f>ROUND(F76,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+40,1)</f>
+        <v/>
+      </c>
+      <c r="B77" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C77" s="48">
+        <f>AVERAGE(B66:B77)</f>
+        <v/>
+      </c>
+      <c r="D77" s="50">
+        <f>C77/22</f>
+        <v/>
+      </c>
+      <c r="E77" s="48">
+        <f>ROUND(D77,-1)</f>
+        <v/>
+      </c>
+      <c r="F77" s="50">
+        <f>E77/3*2</f>
+        <v/>
+      </c>
+      <c r="G77" s="48">
+        <f>ROUND(F77,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="49">
+        <f>DATE(YEAR($J$5),MONTH($J$5)-12+41,1)</f>
+        <v/>
+      </c>
+      <c r="B78" s="47" t="n">
+        <v>340000</v>
+      </c>
+      <c r="C78" s="48">
+        <f>AVERAGE(B67:B78)</f>
+        <v/>
+      </c>
+      <c r="D78" s="50">
+        <f>C78/22</f>
+        <v/>
+      </c>
+      <c r="E78" s="48">
+        <f>ROUND(D78,-1)</f>
+        <v/>
+      </c>
+      <c r="F78" s="50">
+        <f>E78/3*2</f>
+        <v/>
+      </c>
+      <c r="G78" s="48">
+        <f>ROUND(F78,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>※標準報酬月額は、支給開始月の12か月前〜支給開始月（太字の行）が算定に使われます。それより後の月は参考用（月ごとの日額を見る）で、将来月は現在の額を見込みで入力し、定時決定・随時改定があれば更新します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>■ 出勤期間（出勤して傷病手当を受けない期間。その分だけ支給期間が延びます）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>※出勤した期間の開始日・終了日を、古い順に入力（10件まで）。期間のうち、丸ごと1か月ある月は「1か月」、残りは「土日を除く日数」だけ後ろにずれます。例：2/1〜3/15 → 1か月＋3/1〜3/15の土日を除く日数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="44" customHeight="1" s="39">
+      <c r="A84" s="18" t="inlineStr">
         <is>
           <t>番号</t>
         </is>
       </c>
-      <c r="B54" s="18" t="inlineStr">
+      <c r="B84" s="18" t="inlineStr">
         <is>
           <t>開始日</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C84" s="18" t="inlineStr">
         <is>
           <t>終了日</t>
         </is>
       </c>
-      <c r="D54" s="18" t="inlineStr">
+      <c r="D84" s="18" t="inlineStr">
+        <is>
+          <t>延びる月数
+（自動）</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
         <is>
           <t>延びる日数
-（自動）</t>
-        </is>
-      </c>
-      <c r="E54" s="18" t="inlineStr">
+（土日除く・自動）</t>
+        </is>
+      </c>
+      <c r="F84" s="18" t="inlineStr">
         <is>
           <t>区分
 （自動）</t>
         </is>
       </c>
-      <c r="F54" s="18" t="inlineStr">
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>法定：月数
+（累計）</t>
+        </is>
+      </c>
+      <c r="H84" s="18" t="inlineStr">
+        <is>
+          <t>法定：日数
+（累計）</t>
+        </is>
+      </c>
+      <c r="I84" s="18" t="inlineStr">
+        <is>
+          <t>附加：月数
+（累計）</t>
+        </is>
+      </c>
+      <c r="J84" s="18" t="inlineStr">
+        <is>
+          <t>附加：日数
+（累計）</t>
+        </is>
+      </c>
+      <c r="K84" s="18" t="inlineStr">
         <is>
           <t>法定末日
 （この行まで）</t>
         </is>
       </c>
-      <c r="G54" s="18" t="inlineStr">
-        <is>
-          <t>附加の延長日数
-（累計）</t>
-        </is>
-      </c>
-      <c r="H54" s="61" t="n"/>
-      <c r="I54" s="61" t="n"/>
-      <c r="J54" s="61" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="62" t="inlineStr">
+      <c r="L84" s="18" t="inlineStr">
+        <is>
+          <t>全月の始め
+（途中経過）</t>
+        </is>
+      </c>
+      <c r="M84" s="18" t="inlineStr">
+        <is>
+          <t>全月の終わり
+（途中経過）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="66" t="inlineStr">
         <is>
           <t>基準・合計</t>
         </is>
       </c>
-      <c r="B55" s="28" t="n"/>
-      <c r="C55" s="28" t="n"/>
-      <c r="D55" s="48">
-        <f>SUMIFS(D56:D65,E56:E65,"法定")+SUMIFS(D56:D65,E56:E65,"附加")</f>
-        <v/>
-      </c>
-      <c r="E55" s="28" t="n"/>
-      <c r="F55" s="15">
+      <c r="B85" s="28" t="n"/>
+      <c r="C85" s="28" t="n"/>
+      <c r="D85" s="48">
+        <f>MAX(G85:G95)+MAX(I85:I95)</f>
+        <v/>
+      </c>
+      <c r="E85" s="48">
+        <f>MAX(H85:H95)+MAX(J85:J95)</f>
+        <v/>
+      </c>
+      <c r="F85" s="28" t="n"/>
+      <c r="G85" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="67">
         <f>DATE(YEAR($J$5)+1,MONTH($J$5)+6,DAY($J$5)-1)</f>
         <v/>
       </c>
-      <c r="G55" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="61" t="n"/>
-      <c r="I55" s="61" t="n"/>
-      <c r="J55" s="61" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="62" t="n">
+      <c r="L85" s="28" t="n"/>
+      <c r="M85" s="28" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="B56" s="63" t="n"/>
-      <c r="C56" s="63" t="n"/>
-      <c r="D56" s="48">
-        <f>IF(OR(B56="",C56=""),0,MAX(0,C56-B56+1))</f>
-        <v/>
-      </c>
-      <c r="E56" s="62">
-        <f>IF(OR(B56="",C56=""),"",IF(C56&lt;B56,"日付エラー",IF(B56&lt;$J$5,"対象外",IF(B56&lt;=F55,"法定",IF(B56&lt;=DATE(YEAR(F55+1),MONTH(F55+1)+6,DAY(F55+1)-1)+G55,"附加","対象外")))))</f>
-        <v/>
-      </c>
-      <c r="F56" s="64">
-        <f>F55+IF(E56="法定",D56,0)</f>
-        <v/>
-      </c>
-      <c r="G56" s="48">
-        <f>G55+IF(E56="附加",D56,0)</f>
-        <v/>
-      </c>
-      <c r="H56" s="61" t="n"/>
-      <c r="I56" s="61" t="n"/>
-      <c r="J56" s="61" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="62" t="n">
+      <c r="B86" s="68" t="n"/>
+      <c r="C86" s="68" t="n"/>
+      <c r="D86" s="48">
+        <f>IF(OR(L86="",M86=""),0,IF(L86&gt;M86,0,(YEAR(M86)-YEAR(L86))*12+MONTH(M86)-MONTH(L86)+1))</f>
+        <v/>
+      </c>
+      <c r="E86" s="48">
+        <f>IF(OR(B86="",C86="",C86&lt;B86),0,NETWORKDAYS(B86,C86)-IF(D86&gt;0,NETWORKDAYS(L86,M86),0))</f>
+        <v/>
+      </c>
+      <c r="F86" s="66">
+        <f>IF(OR(B86="",C86=""),"",IF(C86&lt;B86,"日付エラー",IF(B86&lt;$J$5,"対象外",IF(B86&lt;=K85,"法定",IF(B86&lt;=WORKDAY(EDATE(DATE(YEAR(K85+1),MONTH(K85+1)+6,DAY(K85+1)-1),I85),J85),"附加","対象外")))))</f>
+        <v/>
+      </c>
+      <c r="G86" s="48">
+        <f>G85+IF(F86="法定",D86,0)</f>
+        <v/>
+      </c>
+      <c r="H86" s="48">
+        <f>H85+IF(F86="法定",E86,0)</f>
+        <v/>
+      </c>
+      <c r="I86" s="48">
+        <f>I85+IF(F86="附加",D86,0)</f>
+        <v/>
+      </c>
+      <c r="J86" s="48">
+        <f>J85+IF(F86="附加",E86,0)</f>
+        <v/>
+      </c>
+      <c r="K86" s="67">
+        <f>WORKDAY(EDATE($K$85,G86),H86)</f>
+        <v/>
+      </c>
+      <c r="L86" s="67">
+        <f>IF(OR(B86="",C86="",C86&lt;B86),"",IF(DAY(B86)=1,B86,EOMONTH(B86,0)+1))</f>
+        <v/>
+      </c>
+      <c r="M86" s="67">
+        <f>IF(OR(B86="",C86="",C86&lt;B86),"",IF(C86=EOMONTH(C86,0),C86,EOMONTH(C86,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="66" t="n">
         <v>2</v>
       </c>
-      <c r="B57" s="63" t="n"/>
-      <c r="C57" s="63" t="n"/>
-      <c r="D57" s="48">
-        <f>IF(OR(B57="",C57=""),0,MAX(0,C57-B57+1))</f>
-        <v/>
-      </c>
-      <c r="E57" s="62">
-        <f>IF(OR(B57="",C57=""),"",IF(C57&lt;B57,"日付エラー",IF(B57&lt;$J$5,"対象外",IF(B57&lt;=F56,"法定",IF(B57&lt;=DATE(YEAR(F56+1),MONTH(F56+1)+6,DAY(F56+1)-1)+G56,"附加","対象外")))))</f>
-        <v/>
-      </c>
-      <c r="F57" s="64">
-        <f>F56+IF(E57="法定",D57,0)</f>
-        <v/>
-      </c>
-      <c r="G57" s="48">
-        <f>G56+IF(E57="附加",D57,0)</f>
-        <v/>
-      </c>
-      <c r="H57" s="61" t="n"/>
-      <c r="I57" s="61" t="n"/>
-      <c r="J57" s="61" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="62" t="n">
+      <c r="B87" s="68" t="n"/>
+      <c r="C87" s="68" t="n"/>
+      <c r="D87" s="48">
+        <f>IF(OR(L87="",M87=""),0,IF(L87&gt;M87,0,(YEAR(M87)-YEAR(L87))*12+MONTH(M87)-MONTH(L87)+1))</f>
+        <v/>
+      </c>
+      <c r="E87" s="48">
+        <f>IF(OR(B87="",C87="",C87&lt;B87),0,NETWORKDAYS(B87,C87)-IF(D87&gt;0,NETWORKDAYS(L87,M87),0))</f>
+        <v/>
+      </c>
+      <c r="F87" s="66">
+        <f>IF(OR(B87="",C87=""),"",IF(C87&lt;B87,"日付エラー",IF(B87&lt;$J$5,"対象外",IF(B87&lt;=K86,"法定",IF(B87&lt;=WORKDAY(EDATE(DATE(YEAR(K86+1),MONTH(K86+1)+6,DAY(K86+1)-1),I86),J86),"附加","対象外")))))</f>
+        <v/>
+      </c>
+      <c r="G87" s="48">
+        <f>G86+IF(F87="法定",D87,0)</f>
+        <v/>
+      </c>
+      <c r="H87" s="48">
+        <f>H86+IF(F87="法定",E87,0)</f>
+        <v/>
+      </c>
+      <c r="I87" s="48">
+        <f>I86+IF(F87="附加",D87,0)</f>
+        <v/>
+      </c>
+      <c r="J87" s="48">
+        <f>J86+IF(F87="附加",E87,0)</f>
+        <v/>
+      </c>
+      <c r="K87" s="67">
+        <f>WORKDAY(EDATE($K$85,G87),H87)</f>
+        <v/>
+      </c>
+      <c r="L87" s="67">
+        <f>IF(OR(B87="",C87="",C87&lt;B87),"",IF(DAY(B87)=1,B87,EOMONTH(B87,0)+1))</f>
+        <v/>
+      </c>
+      <c r="M87" s="67">
+        <f>IF(OR(B87="",C87="",C87&lt;B87),"",IF(C87=EOMONTH(C87,0),C87,EOMONTH(C87,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="66" t="n">
         <v>3</v>
       </c>
-      <c r="B58" s="63" t="n"/>
-      <c r="C58" s="63" t="n"/>
-      <c r="D58" s="48">
-        <f>IF(OR(B58="",C58=""),0,MAX(0,C58-B58+1))</f>
-        <v/>
-      </c>
-      <c r="E58" s="62">
-        <f>IF(OR(B58="",C58=""),"",IF(C58&lt;B58,"日付エラー",IF(B58&lt;$J$5,"対象外",IF(B58&lt;=F57,"法定",IF(B58&lt;=DATE(YEAR(F57+1),MONTH(F57+1)+6,DAY(F57+1)-1)+G57,"附加","対象外")))))</f>
-        <v/>
-      </c>
-      <c r="F58" s="64">
-        <f>F57+IF(E58="法定",D58,0)</f>
-        <v/>
-      </c>
-      <c r="G58" s="48">
-        <f>G57+IF(E58="附加",D58,0)</f>
-        <v/>
-      </c>
-      <c r="H58" s="61" t="n"/>
-      <c r="I58" s="61" t="n"/>
-      <c r="J58" s="61" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="62" t="n">
+      <c r="B88" s="68" t="n"/>
+      <c r="C88" s="68" t="n"/>
+      <c r="D88" s="48">
+        <f>IF(OR(L88="",M88=""),0,IF(L88&gt;M88,0,(YEAR(M88)-YEAR(L88))*12+MONTH(M88)-MONTH(L88)+1))</f>
+        <v/>
+      </c>
+      <c r="E88" s="48">
+        <f>IF(OR(B88="",C88="",C88&lt;B88),0,NETWORKDAYS(B88,C88)-IF(D88&gt;0,NETWORKDAYS(L88,M88),0))</f>
+        <v/>
+      </c>
+      <c r="F88" s="66">
+        <f>IF(OR(B88="",C88=""),"",IF(C88&lt;B88,"日付エラー",IF(B88&lt;$J$5,"対象外",IF(B88&lt;=K87,"法定",IF(B88&lt;=WORKDAY(EDATE(DATE(YEAR(K87+1),MONTH(K87+1)+6,DAY(K87+1)-1),I87),J87),"附加","対象外")))))</f>
+        <v/>
+      </c>
+      <c r="G88" s="48">
+        <f>G87+IF(F88="法定",D88,0)</f>
+        <v/>
+      </c>
+      <c r="H88" s="48">
+        <f>H87+IF(F88="法定",E88,0)</f>
+        <v/>
+      </c>
+      <c r="I88" s="48">
+        <f>I87+IF(F88="附加",D88,0)</f>
+        <v/>
+      </c>
+      <c r="J88" s="48">
+        <f>J87+IF(F88="附加",E88,0)</f>
+        <v/>
+      </c>
+      <c r="K88" s="67">
+        <f>WORKDAY(EDATE($K$85,G88),H88)</f>
+        <v/>
+      </c>
+      <c r="L88" s="67">
+        <f>IF(OR(B88="",C88="",C88&lt;B88),"",IF(DAY(B88)=1,B88,EOMONTH(B88,0)+1))</f>
+        <v/>
+      </c>
+      <c r="M88" s="67">
+        <f>IF(OR(B88="",C88="",C88&lt;B88),"",IF(C88=EOMONTH(C88,0),C88,EOMONTH(C88,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="66" t="n">
         <v>4</v>
       </c>
-      <c r="B59" s="63" t="n"/>
-      <c r="C59" s="63" t="n"/>
-      <c r="D59" s="48">
-        <f>IF(OR(B59="",C59=""),0,MAX(0,C59-B59+1))</f>
-        <v/>
-      </c>
-      <c r="E59" s="62">
-        <f>IF(OR(B59="",C59=""),"",IF(C59&lt;B59,"日付エラー",IF(B59&lt;$J$5,"対象外",IF(B59&lt;=F58,"法定",IF(B59&lt;=DATE(YEAR(F58+1),MONTH(F58+1)+6,DAY(F58+1)-1)+G58,"附加","対象外")))))</f>
-        <v/>
-      </c>
-      <c r="F59" s="64">
-        <f>F58+IF(E59="法定",D59,0)</f>
-        <v/>
-      </c>
-      <c r="G59" s="48">
-        <f>G58+IF(E59="附加",D59,0)</f>
-        <v/>
-      </c>
-      <c r="H59" s="61" t="n"/>
-      <c r="I59" s="61" t="n"/>
-      <c r="J59" s="61" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="62" t="n">
+      <c r="B89" s="68" t="n"/>
+      <c r="C89" s="68" t="n"/>
+      <c r="D89" s="48">
+        <f>IF(OR(L89="",M89=""),0,IF(L89&gt;M89,0,(YEAR(M89)-YEAR(L89))*12+MONTH(M89)-MONTH(L89)+1))</f>
+        <v/>
+      </c>
+      <c r="E89" s="48">
+        <f>IF(OR(B89="",C89="",C89&lt;B89),0,NETWORKDAYS(B89,C89)-IF(D89&gt;0,NETWORKDAYS(L89,M89),0))</f>
+        <v/>
+      </c>
+      <c r="F89" s="66">
+        <f>IF(OR(B89="",C89=""),"",IF(C89&lt;B89,"日付エラー",IF(B89&lt;$J$5,"対象外",IF(B89&lt;=K88,"法定",IF(B89&lt;=WORKDAY(EDATE(DATE(YEAR(K88+1),MONTH(K88+1)+6,DAY(K88+1)-1),I88),J88),"附加","対象外")))))</f>
+        <v/>
+      </c>
+      <c r="G89" s="48">
+        <f>G88+IF(F89="法定",D89,0)</f>
+        <v/>
+      </c>
+      <c r="H89" s="48">
+        <f>H88+IF(F89="法定",E89,0)</f>
+        <v/>
+      </c>
+      <c r="I89" s="48">
+        <f>I88+IF(F89="附加",D89,0)</f>
+        <v/>
+      </c>
+      <c r="J89" s="48">
+        <f>J88+IF(F89="附加",E89,0)</f>
+        <v/>
+      </c>
+      <c r="K89" s="67">
+        <f>WORKDAY(EDATE($K$85,G89),H89)</f>
+        <v/>
+      </c>
+      <c r="L89" s="67">
+        <f>IF(OR(B89="",C89="",C89&lt;B89),"",IF(DAY(B89)=1,B89,EOMONTH(B89,0)+1))</f>
+        <v/>
+      </c>
+      <c r="M89" s="67">
+        <f>IF(OR(B89="",C89="",C89&lt;B89),"",IF(C89=EOMONTH(C89,0),C89,EOMONTH(C89,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="66" t="n">
         <v>5</v>
       </c>
-      <c r="B60" s="63" t="n"/>
-      <c r="C60" s="63" t="n"/>
-      <c r="D60" s="48">
-        <f>IF(OR(B60="",C60=""),0,MAX(0,C60-B60+1))</f>
-        <v/>
-      </c>
-      <c r="E60" s="62">
-        <f>IF(OR(B60="",C60=""),"",IF(C60&lt;B60,"日付エラー",IF(B60&lt;$J$5,"対象外",IF(B60&lt;=F59,"法定",IF(B60&lt;=DATE(YEAR(F59+1),MONTH(F59+1)+6,DAY(F59+1)-1)+G59,"附加","対象外")))))</f>
-        <v/>
-      </c>
-      <c r="F60" s="64">
-        <f>F59+IF(E60="法定",D60,0)</f>
-        <v/>
-      </c>
-      <c r="G60" s="48">
-        <f>G59+IF(E60="附加",D60,0)</f>
-        <v/>
-      </c>
-      <c r="H60" s="61" t="n"/>
-      <c r="I60" s="61" t="n"/>
-      <c r="J60" s="61" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="62" t="n">
+      <c r="B90" s="68" t="n"/>
+      <c r="C90" s="68" t="n"/>
+      <c r="D90" s="48">
+        <f>IF(OR(L90="",M90=""),0,IF(L90&gt;M90,0,(YEAR(M90)-YEAR(L90))*12+MONTH(M90)-MONTH(L90)+1))</f>
+        <v/>
+      </c>
+      <c r="E90" s="48">
+        <f>IF(OR(B90="",C90="",C90&lt;B90),0,NETWORKDAYS(B90,C90)-IF(D90&gt;0,NETWORKDAYS(L90,M90),0))</f>
+        <v/>
+      </c>
+      <c r="F90" s="66">
+        <f>IF(OR(B90="",C90=""),"",IF(C90&lt;B90,"日付エラー",IF(B90&lt;$J$5,"対象外",IF(B90&lt;=K89,"法定",IF(B90&lt;=WORKDAY(EDATE(DATE(YEAR(K89+1),MONTH(K89+1)+6,DAY(K89+1)-1),I89),J89),"附加","対象外")))))</f>
+        <v/>
+      </c>
+      <c r="G90" s="48">
+        <f>G89+IF(F90="法定",D90,0)</f>
+        <v/>
+      </c>
+      <c r="H90" s="48">
+        <f>H89+IF(F90="法定",E90,0)</f>
+        <v/>
+      </c>
+      <c r="I90" s="48">
+        <f>I89+IF(F90="附加",D90,0)</f>
+        <v/>
+      </c>
+      <c r="J90" s="48">
+        <f>J89+IF(F90="附加",E90,0)</f>
+        <v/>
+      </c>
+      <c r="K90" s="67">
+        <f>WORKDAY(EDATE($K$85,G90),H90)</f>
+        <v/>
+      </c>
+      <c r="L90" s="67">
+        <f>IF(OR(B90="",C90="",C90&lt;B90),"",IF(DAY(B90)=1,B90,EOMONTH(B90,0)+1))</f>
+        <v/>
+      </c>
+      <c r="M90" s="67">
+        <f>IF(OR(B90="",C90="",C90&lt;B90),"",IF(C90=EOMONTH(C90,0),C90,EOMONTH(C90,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="66" t="n">
         <v>6</v>
       </c>
-      <c r="B61" s="63" t="n"/>
-      <c r="C61" s="63" t="n"/>
-      <c r="D61" s="48">
-        <f>IF(OR(B61="",C61=""),0,MAX(0,C61-B61+1))</f>
-        <v/>
-      </c>
-      <c r="E61" s="62">
-        <f>IF(OR(B61="",C61=""),"",IF(C61&lt;B61,"日付エラー",IF(B61&lt;$J$5,"対象外",IF(B61&lt;=F60,"法定",IF(B61&lt;=DATE(YEAR(F60+1),MONTH(F60+1)+6,DAY(F60+1)-1)+G60,"附加","対象外")))))</f>
-        <v/>
-      </c>
-      <c r="F61" s="64">
-        <f>F60+IF(E61="法定",D61,0)</f>
-        <v/>
-      </c>
-      <c r="G61" s="48">
-        <f>G60+IF(E61="附加",D61,0)</f>
-        <v/>
-      </c>
-      <c r="H61" s="61" t="n"/>
-      <c r="I61" s="61" t="n"/>
-      <c r="J61" s="61" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="62" t="n">
+      <c r="B91" s="68" t="n"/>
+      <c r="C91" s="68" t="n"/>
+      <c r="D91" s="48">
+        <f>IF(OR(L91="",M91=""),0,IF(L91&gt;M91,0,(YEAR(M91)-YEAR(L91))*12+MONTH(M91)-MONTH(L91)+1))</f>
+        <v/>
+      </c>
+      <c r="E91" s="48">
+        <f>IF(OR(B91="",C91="",C91&lt;B91),0,NETWORKDAYS(B91,C91)-IF(D91&gt;0,NETWORKDAYS(L91,M91),0))</f>
+        <v/>
+      </c>
+      <c r="F91" s="66">
+        <f>IF(OR(B91="",C91=""),"",IF(C91&lt;B91,"日付エラー",IF(B91&lt;$J$5,"対象外",IF(B91&lt;=K90,"法定",IF(B91&lt;=WORKDAY(EDATE(DATE(YEAR(K90+1),MONTH(K90+1)+6,DAY(K90+1)-1),I90),J90),"附加","対象外")))))</f>
+        <v/>
+      </c>
+      <c r="G91" s="48">
+        <f>G90+IF(F91="法定",D91,0)</f>
+        <v/>
+      </c>
+      <c r="H91" s="48">
+        <f>H90+IF(F91="法定",E91,0)</f>
+        <v/>
+      </c>
+      <c r="I91" s="48">
+        <f>I90+IF(F91="附加",D91,0)</f>
+        <v/>
+      </c>
+      <c r="J91" s="48">
+        <f>J90+IF(F91="附加",E91,0)</f>
+        <v/>
+      </c>
+      <c r="K91" s="67">
+        <f>WORKDAY(EDATE($K$85,G91),H91)</f>
+        <v/>
+      </c>
+      <c r="L91" s="67">
+        <f>IF(OR(B91="",C91="",C91&lt;B91),"",IF(DAY(B91)=1,B91,EOMONTH(B91,0)+1))</f>
+        <v/>
+      </c>
+      <c r="M91" s="67">
+        <f>IF(OR(B91="",C91="",C91&lt;B91),"",IF(C91=EOMONTH(C91,0),C91,EOMONTH(C91,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="66" t="n">
         <v>7</v>
       </c>
-      <c r="B62" s="63" t="n"/>
-      <c r="C62" s="63" t="n"/>
-      <c r="D62" s="48">
-        <f>IF(OR(B62="",C62=""),0,MAX(0,C62-B62+1))</f>
-        <v/>
-      </c>
-      <c r="E62" s="62">
-        <f>IF(OR(B62="",C62=""),"",IF(C62&lt;B62,"日付エラー",IF(B62&lt;$J$5,"対象外",IF(B62&lt;=F61,"法定",IF(B62&lt;=DATE(YEAR(F61+1),MONTH(F61+1)+6,DAY(F61+1)-1)+G61,"附加","対象外")))))</f>
-        <v/>
-      </c>
-      <c r="F62" s="64">
-        <f>F61+IF(E62="法定",D62,0)</f>
-        <v/>
-      </c>
-      <c r="G62" s="48">
-        <f>G61+IF(E62="附加",D62,0)</f>
-        <v/>
-      </c>
-      <c r="H62" s="61" t="n"/>
-      <c r="I62" s="61" t="n"/>
-      <c r="J62" s="61" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="62" t="n">
+      <c r="B92" s="68" t="n"/>
+      <c r="C92" s="68" t="n"/>
+      <c r="D92" s="48">
+        <f>IF(OR(L92="",M92=""),0,IF(L92&gt;M92,0,(YEAR(M92)-YEAR(L92))*12+MONTH(M92)-MONTH(L92)+1))</f>
+        <v/>
+      </c>
+      <c r="E92" s="48">
+        <f>IF(OR(B92="",C92="",C92&lt;B92),0,NETWORKDAYS(B92,C92)-IF(D92&gt;0,NETWORKDAYS(L92,M92),0))</f>
+        <v/>
+      </c>
+      <c r="F92" s="66">
+        <f>IF(OR(B92="",C92=""),"",IF(C92&lt;B92,"日付エラー",IF(B92&lt;$J$5,"対象外",IF(B92&lt;=K91,"法定",IF(B92&lt;=WORKDAY(EDATE(DATE(YEAR(K91+1),MONTH(K91+1)+6,DAY(K91+1)-1),I91),J91),"附加","対象外")))))</f>
+        <v/>
+      </c>
+      <c r="G92" s="48">
+        <f>G91+IF(F92="法定",D92,0)</f>
+        <v/>
+      </c>
+      <c r="H92" s="48">
+        <f>H91+IF(F92="法定",E92,0)</f>
+        <v/>
+      </c>
+      <c r="I92" s="48">
+        <f>I91+IF(F92="附加",D92,0)</f>
+        <v/>
+      </c>
+      <c r="J92" s="48">
+        <f>J91+IF(F92="附加",E92,0)</f>
+        <v/>
+      </c>
+      <c r="K92" s="67">
+        <f>WORKDAY(EDATE($K$85,G92),H92)</f>
+        <v/>
+      </c>
+      <c r="L92" s="67">
+        <f>IF(OR(B92="",C92="",C92&lt;B92),"",IF(DAY(B92)=1,B92,EOMONTH(B92,0)+1))</f>
+        <v/>
+      </c>
+      <c r="M92" s="67">
+        <f>IF(OR(B92="",C92="",C92&lt;B92),"",IF(C92=EOMONTH(C92,0),C92,EOMONTH(C92,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="66" t="n">
         <v>8</v>
       </c>
-      <c r="B63" s="63" t="n"/>
-      <c r="C63" s="63" t="n"/>
-      <c r="D63" s="48">
-        <f>IF(OR(B63="",C63=""),0,MAX(0,C63-B63+1))</f>
-        <v/>
-      </c>
-      <c r="E63" s="62">
-        <f>IF(OR(B63="",C63=""),"",IF(C63&lt;B63,"日付エラー",IF(B63&lt;$J$5,"対象外",IF(B63&lt;=F62,"法定",IF(B63&lt;=DATE(YEAR(F62+1),MONTH(F62+1)+6,DAY(F62+1)-1)+G62,"附加","対象外")))))</f>
-        <v/>
-      </c>
-      <c r="F63" s="64">
-        <f>F62+IF(E63="法定",D63,0)</f>
-        <v/>
-      </c>
-      <c r="G63" s="48">
-        <f>G62+IF(E63="附加",D63,0)</f>
-        <v/>
-      </c>
-      <c r="H63" s="61" t="n"/>
-      <c r="I63" s="61" t="n"/>
-      <c r="J63" s="61" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="62" t="n">
+      <c r="B93" s="68" t="n"/>
+      <c r="C93" s="68" t="n"/>
+      <c r="D93" s="48">
+        <f>IF(OR(L93="",M93=""),0,IF(L93&gt;M93,0,(YEAR(M93)-YEAR(L93))*12+MONTH(M93)-MONTH(L93)+1))</f>
+        <v/>
+      </c>
+      <c r="E93" s="48">
+        <f>IF(OR(B93="",C93="",C93&lt;B93),0,NETWORKDAYS(B93,C93)-IF(D93&gt;0,NETWORKDAYS(L93,M93),0))</f>
+        <v/>
+      </c>
+      <c r="F93" s="66">
+        <f>IF(OR(B93="",C93=""),"",IF(C93&lt;B93,"日付エラー",IF(B93&lt;$J$5,"対象外",IF(B93&lt;=K92,"法定",IF(B93&lt;=WORKDAY(EDATE(DATE(YEAR(K92+1),MONTH(K92+1)+6,DAY(K92+1)-1),I92),J92),"附加","対象外")))))</f>
+        <v/>
+      </c>
+      <c r="G93" s="48">
+        <f>G92+IF(F93="法定",D93,0)</f>
+        <v/>
+      </c>
+      <c r="H93" s="48">
+        <f>H92+IF(F93="法定",E93,0)</f>
+        <v/>
+      </c>
+      <c r="I93" s="48">
+        <f>I92+IF(F93="附加",D93,0)</f>
+        <v/>
+      </c>
+      <c r="J93" s="48">
+        <f>J92+IF(F93="附加",E93,0)</f>
+        <v/>
+      </c>
+      <c r="K93" s="67">
+        <f>WORKDAY(EDATE($K$85,G93),H93)</f>
+        <v/>
+      </c>
+      <c r="L93" s="67">
+        <f>IF(OR(B93="",C93="",C93&lt;B93),"",IF(DAY(B93)=1,B93,EOMONTH(B93,0)+1))</f>
+        <v/>
+      </c>
+      <c r="M93" s="67">
+        <f>IF(OR(B93="",C93="",C93&lt;B93),"",IF(C93=EOMONTH(C93,0),C93,EOMONTH(C93,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="66" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="63" t="n"/>
-      <c r="C64" s="63" t="n"/>
-      <c r="D64" s="48">
-        <f>IF(OR(B64="",C64=""),0,MAX(0,C64-B64+1))</f>
-        <v/>
-      </c>
-      <c r="E64" s="62">
-        <f>IF(OR(B64="",C64=""),"",IF(C64&lt;B64,"日付エラー",IF(B64&lt;$J$5,"対象外",IF(B64&lt;=F63,"法定",IF(B64&lt;=DATE(YEAR(F63+1),MONTH(F63+1)+6,DAY(F63+1)-1)+G63,"附加","対象外")))))</f>
-        <v/>
-      </c>
-      <c r="F64" s="64">
-        <f>F63+IF(E64="法定",D64,0)</f>
-        <v/>
-      </c>
-      <c r="G64" s="48">
-        <f>G63+IF(E64="附加",D64,0)</f>
-        <v/>
-      </c>
-      <c r="H64" s="61" t="n"/>
-      <c r="I64" s="61" t="n"/>
-      <c r="J64" s="61" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="62" t="n">
+      <c r="B94" s="68" t="n"/>
+      <c r="C94" s="68" t="n"/>
+      <c r="D94" s="48">
+        <f>IF(OR(L94="",M94=""),0,IF(L94&gt;M94,0,(YEAR(M94)-YEAR(L94))*12+MONTH(M94)-MONTH(L94)+1))</f>
+        <v/>
+      </c>
+      <c r="E94" s="48">
+        <f>IF(OR(B94="",C94="",C94&lt;B94),0,NETWORKDAYS(B94,C94)-IF(D94&gt;0,NETWORKDAYS(L94,M94),0))</f>
+        <v/>
+      </c>
+      <c r="F94" s="66">
+        <f>IF(OR(B94="",C94=""),"",IF(C94&lt;B94,"日付エラー",IF(B94&lt;$J$5,"対象外",IF(B94&lt;=K93,"法定",IF(B94&lt;=WORKDAY(EDATE(DATE(YEAR(K93+1),MONTH(K93+1)+6,DAY(K93+1)-1),I93),J93),"附加","対象外")))))</f>
+        <v/>
+      </c>
+      <c r="G94" s="48">
+        <f>G93+IF(F94="法定",D94,0)</f>
+        <v/>
+      </c>
+      <c r="H94" s="48">
+        <f>H93+IF(F94="法定",E94,0)</f>
+        <v/>
+      </c>
+      <c r="I94" s="48">
+        <f>I93+IF(F94="附加",D94,0)</f>
+        <v/>
+      </c>
+      <c r="J94" s="48">
+        <f>J93+IF(F94="附加",E94,0)</f>
+        <v/>
+      </c>
+      <c r="K94" s="67">
+        <f>WORKDAY(EDATE($K$85,G94),H94)</f>
+        <v/>
+      </c>
+      <c r="L94" s="67">
+        <f>IF(OR(B94="",C94="",C94&lt;B94),"",IF(DAY(B94)=1,B94,EOMONTH(B94,0)+1))</f>
+        <v/>
+      </c>
+      <c r="M94" s="67">
+        <f>IF(OR(B94="",C94="",C94&lt;B94),"",IF(C94=EOMONTH(C94,0),C94,EOMONTH(C94,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="66" t="n">
         <v>10</v>
       </c>
-      <c r="B65" s="63" t="n"/>
-      <c r="C65" s="63" t="n"/>
-      <c r="D65" s="48">
-        <f>IF(OR(B65="",C65=""),0,MAX(0,C65-B65+1))</f>
-        <v/>
-      </c>
-      <c r="E65" s="62">
-        <f>IF(OR(B65="",C65=""),"",IF(C65&lt;B65,"日付エラー",IF(B65&lt;$J$5,"対象外",IF(B65&lt;=F64,"法定",IF(B65&lt;=DATE(YEAR(F64+1),MONTH(F64+1)+6,DAY(F64+1)-1)+G64,"附加","対象外")))))</f>
-        <v/>
-      </c>
-      <c r="F65" s="64">
-        <f>F64+IF(E65="法定",D65,0)</f>
-        <v/>
-      </c>
-      <c r="G65" s="48">
-        <f>G64+IF(E65="附加",D65,0)</f>
-        <v/>
-      </c>
-      <c r="H65" s="61" t="n"/>
-      <c r="I65" s="61" t="n"/>
-      <c r="J65" s="61" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="11" t="inlineStr">
+      <c r="B95" s="68" t="n"/>
+      <c r="C95" s="68" t="n"/>
+      <c r="D95" s="48">
+        <f>IF(OR(L95="",M95=""),0,IF(L95&gt;M95,0,(YEAR(M95)-YEAR(L95))*12+MONTH(M95)-MONTH(L95)+1))</f>
+        <v/>
+      </c>
+      <c r="E95" s="48">
+        <f>IF(OR(B95="",C95="",C95&lt;B95),0,NETWORKDAYS(B95,C95)-IF(D95&gt;0,NETWORKDAYS(L95,M95),0))</f>
+        <v/>
+      </c>
+      <c r="F95" s="66">
+        <f>IF(OR(B95="",C95=""),"",IF(C95&lt;B95,"日付エラー",IF(B95&lt;$J$5,"対象外",IF(B95&lt;=K94,"法定",IF(B95&lt;=WORKDAY(EDATE(DATE(YEAR(K94+1),MONTH(K94+1)+6,DAY(K94+1)-1),I94),J94),"附加","対象外")))))</f>
+        <v/>
+      </c>
+      <c r="G95" s="48">
+        <f>G94+IF(F95="法定",D95,0)</f>
+        <v/>
+      </c>
+      <c r="H95" s="48">
+        <f>H94+IF(F95="法定",E95,0)</f>
+        <v/>
+      </c>
+      <c r="I95" s="48">
+        <f>I94+IF(F95="附加",D95,0)</f>
+        <v/>
+      </c>
+      <c r="J95" s="48">
+        <f>J94+IF(F95="附加",E95,0)</f>
+        <v/>
+      </c>
+      <c r="K95" s="67">
+        <f>WORKDAY(EDATE($K$85,G95),H95)</f>
+        <v/>
+      </c>
+      <c r="L95" s="67">
+        <f>IF(OR(B95="",C95="",C95&lt;B95),"",IF(DAY(B95)=1,B95,EOMONTH(B95,0)+1))</f>
+        <v/>
+      </c>
+      <c r="M95" s="67">
+        <f>IF(OR(B95="",C95="",C95&lt;B95),"",IF(C95=EOMONTH(C95,0),C95,EOMONTH(C95,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>※10件を超えるときは、途中の行を挿入し、挿入した行から最終行までを選択して Ctrl+D（上の行の式をコピー）してください。範囲は自動で広がります。</t>
         </is>
       </c>
-      <c r="B66" s="61" t="n"/>
-      <c r="C66" s="61" t="n"/>
-      <c r="D66" s="61" t="n"/>
-      <c r="E66" s="61" t="n"/>
-      <c r="F66" s="61" t="n"/>
-      <c r="G66" s="61" t="n"/>
-      <c r="H66" s="61" t="n"/>
-      <c r="I66" s="61" t="n"/>
-      <c r="J66" s="61" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>※「延びる日数」は、開始日〜終了日の暦日数です。数え方を変えるときは D 列の式だけ直せば、すべてに反映されます。</t>
-        </is>
-      </c>
-      <c r="B67" s="61" t="n"/>
-      <c r="C67" s="61" t="n"/>
-      <c r="D67" s="61" t="n"/>
-      <c r="E67" s="61" t="n"/>
-      <c r="F67" s="61" t="n"/>
-      <c r="G67" s="61" t="n"/>
-      <c r="H67" s="61" t="n"/>
-      <c r="I67" s="61" t="n"/>
-      <c r="J67" s="61" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="inlineStr">
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>※ずらし方（月数・土日を除く日数）を変えるときは、D列・E列の式だけ直せば、すべてに反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
         <is>
           <t>■ 請求期間（マクロ AddClaimSheet で、この期間の請求シートを追加します）</t>
         </is>
       </c>
-      <c r="B68" s="61" t="n"/>
-      <c r="C68" s="61" t="n"/>
-      <c r="D68" s="61" t="n"/>
-      <c r="E68" s="61" t="n"/>
-      <c r="F68" s="61" t="n"/>
-      <c r="G68" s="61" t="n"/>
-      <c r="H68" s="61" t="n"/>
-      <c r="I68" s="61" t="n"/>
-      <c r="J68" s="61" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="65" t="inlineStr">
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
         <is>
           <t>請求期間（始）</t>
         </is>
       </c>
-      <c r="C69" s="63" t="n"/>
-      <c r="D69" s="61" t="n"/>
-      <c r="E69" s="61" t="n"/>
-      <c r="F69" s="61" t="n"/>
-      <c r="G69" s="61" t="n"/>
-      <c r="H69" s="61" t="n"/>
-      <c r="I69" s="61" t="n"/>
-      <c r="J69" s="61" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="65" t="inlineStr">
+      <c r="C100" s="68" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
         <is>
           <t>請求期間（終）</t>
         </is>
       </c>
-      <c r="C70" s="63" t="n"/>
-      <c r="D70" s="61" t="n"/>
-      <c r="E70" s="61" t="n"/>
-      <c r="F70" s="61" t="n"/>
-      <c r="G70" s="61" t="n"/>
-      <c r="H70" s="61" t="n"/>
-      <c r="I70" s="61" t="n"/>
-      <c r="J70" s="61" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
+      <c r="C101" s="68" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>※入力したら Alt+F8 →「AddClaimSheet」→実行。マクロ（AddClaimSheet.bas）を取り込んだ .xlsm でのみ使えます。例：4月分の請求なら 2025/4/1 〜 2025/4/30。</t>
         </is>
       </c>
-      <c r="B71" s="61" t="n"/>
-      <c r="C71" s="61" t="n"/>
-      <c r="D71" s="61" t="n"/>
-      <c r="E71" s="61" t="n"/>
-      <c r="F71" s="61" t="n"/>
-      <c r="G71" s="61" t="n"/>
-      <c r="H71" s="61" t="n"/>
-      <c r="I71" s="61" t="n"/>
-      <c r="J71" s="61" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="61" t="n"/>
-      <c r="B72" s="61" t="n"/>
-      <c r="C72" s="61" t="n"/>
-      <c r="D72" s="61" t="n"/>
-      <c r="E72" s="61" t="n"/>
-      <c r="F72" s="61" t="n"/>
-      <c r="G72" s="61" t="n"/>
-      <c r="H72" s="61" t="n"/>
-      <c r="I72" s="61" t="n"/>
-      <c r="J72" s="61" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="61" t="n"/>
-      <c r="B73" s="61" t="n"/>
-      <c r="C73" s="61" t="n"/>
-      <c r="D73" s="61" t="n"/>
-      <c r="E73" s="61" t="n"/>
-      <c r="F73" s="61" t="n"/>
-      <c r="G73" s="61" t="n"/>
-      <c r="H73" s="61" t="n"/>
-      <c r="I73" s="61" t="n"/>
-      <c r="J73" s="61" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="61" t="n"/>
-      <c r="B74" s="61" t="n"/>
-      <c r="C74" s="61" t="n"/>
-      <c r="D74" s="61" t="n"/>
-      <c r="E74" s="61" t="n"/>
-      <c r="F74" s="61" t="n"/>
-      <c r="G74" s="61" t="n"/>
-      <c r="H74" s="61" t="n"/>
-      <c r="I74" s="61" t="n"/>
-      <c r="J74" s="61" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="61" t="n"/>
-      <c r="B75" s="61" t="n"/>
-      <c r="C75" s="61" t="n"/>
-      <c r="D75" s="61" t="n"/>
-      <c r="E75" s="61" t="n"/>
-      <c r="F75" s="61" t="n"/>
-      <c r="G75" s="61" t="n"/>
-      <c r="H75" s="61" t="n"/>
-      <c r="I75" s="61" t="n"/>
-      <c r="J75" s="61" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="61" t="n"/>
-      <c r="B76" s="61" t="n"/>
-      <c r="C76" s="61" t="n"/>
-      <c r="D76" s="61" t="n"/>
-      <c r="E76" s="61" t="n"/>
-      <c r="F76" s="61" t="n"/>
-      <c r="G76" s="61" t="n"/>
-      <c r="H76" s="61" t="n"/>
-      <c r="I76" s="61" t="n"/>
-      <c r="J76" s="61" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="61" t="n"/>
-      <c r="B77" s="61" t="n"/>
-      <c r="C77" s="61" t="n"/>
-      <c r="D77" s="61" t="n"/>
-      <c r="E77" s="61" t="n"/>
-      <c r="F77" s="61" t="n"/>
-      <c r="G77" s="61" t="n"/>
-      <c r="H77" s="61" t="n"/>
-      <c r="I77" s="61" t="n"/>
-      <c r="J77" s="61" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="61" t="n"/>
-      <c r="B78" s="61" t="n"/>
-      <c r="C78" s="61" t="n"/>
-      <c r="D78" s="61" t="n"/>
-      <c r="E78" s="61" t="n"/>
-      <c r="F78" s="61" t="n"/>
-      <c r="G78" s="61" t="n"/>
-      <c r="H78" s="61" t="n"/>
-      <c r="I78" s="61" t="n"/>
-      <c r="J78" s="61" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="61" t="n"/>
-      <c r="B79" s="61" t="n"/>
-      <c r="C79" s="61" t="n"/>
-      <c r="D79" s="61" t="n"/>
-      <c r="E79" s="61" t="n"/>
-      <c r="F79" s="61" t="n"/>
-      <c r="G79" s="61" t="n"/>
-      <c r="H79" s="61" t="n"/>
-      <c r="I79" s="61" t="n"/>
-      <c r="J79" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A101:B101"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A70:B70"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="D9:F9"/>
@@ -2508,11 +3492,10 @@
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A69:B69"/>
   </mergeCells>
-  <conditionalFormatting sqref="E56:E65">
+  <conditionalFormatting sqref="F86:F95">
     <cfRule type="expression" priority="1" dxfId="1">
-      <formula>OR($E56="日付エラー",$E56="対象外")</formula>
+      <formula>OR($F86="日付エラー",$F86="対象外")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -2523,15 +3506,18 @@
     <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"有,無"</formula1>
     </dataValidation>
-    <dataValidation sqref="B56:C65" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="日付を入力" error="日付（例：2025/9/1）を入力してください。" type="date" operator="greaterThan">
+    <dataValidation sqref="B86:C95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="日付を入力" error="日付（例：2025/9/1）を入力してください。" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
-    <dataValidation sqref="C69:C70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="日付を入力" error="日付（例：2025/4/1）を入力してください。" type="date" operator="greaterThan">
+    <dataValidation sqref="C100:C101" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="日付を入力" error="日付（例：2025/4/1）を入力してください。" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="80" min="0" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -2579,7 +3565,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14">
-        <f>"傷病手当日額（支給開始月で固定）：" &amp; TEXT(入力!J10,"#,##0") &amp; "円" &amp; IF(入力!D55&gt;0,"　　出勤による延長：" &amp; 入力!D55 &amp; "日","")</f>
+        <f>"傷病手当日額（支給開始月で固定）：" &amp; TEXT(入力!J10,"#,##0") &amp; "円" &amp; IF(OR(入力!D85&gt;0,入力!E85&gt;0),"　　出勤による延長：" &amp; IF(入力!D85&gt;0,入力!D85 &amp; "か月","") &amp; IF(AND(入力!D85&gt;0,入力!E85&gt;0),"＋","") &amp; IF(入力!E85&gt;0,入力!E85 &amp; "日（土日を除く）",""),"")</f>
         <v/>
       </c>
     </row>
@@ -4289,7 +5275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S71"/>
+  <dimension ref="A1:S72"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" style="39" min="1" max="1"/>
@@ -4302,6 +5288,7 @@
     <col width="10" customWidth="1" style="39" min="11" max="11"/>
     <col width="8" customWidth="1" style="39" min="12" max="12"/>
     <col width="13" customWidth="1" style="39" min="13" max="15"/>
+    <col width="14" customWidth="1" style="39" min="16" max="16"/>
     <col hidden="1" width="13" customWidth="1" style="39" min="17" max="17"/>
     <col hidden="1" width="13" customWidth="1" style="39" min="18" max="18"/>
     <col hidden="1" width="13" customWidth="1" style="39" min="19" max="19"/>
@@ -4414,6 +5401,12 @@
 （E=F−G）</t>
         </is>
       </c>
+      <c r="P5" s="18" t="inlineStr">
+        <is>
+          <t>参考
+月ごとの試算日額</t>
+        </is>
+      </c>
       <c r="Q5" s="18" t="inlineStr">
         <is>
           <t>集計用</t>
@@ -4456,7 +5449,7 @@
         <v/>
       </c>
       <c r="G6" s="31">
-        <f>IF(F6="","",MIN(EOMONTH(F6,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F6),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F6),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F6),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F6),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F6),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F6),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F6),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F6),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F6),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F6)+1)-1,999999)))</f>
+        <f>IF(F6="","",MIN(EOMONTH(F6,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F6),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F6),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F6),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F6),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F6),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F6),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F6),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F6),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F6),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F6)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H6" s="52">
@@ -4491,16 +5484,20 @@
         <f>IF(F6="","",M6-N6)</f>
         <v/>
       </c>
+      <c r="P6" s="69">
+        <f>IF(F6="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B6,C6,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q6">
         <f>IF(F6="","",IF(COUNTIFS($B$6:B6,B6,$C$6:C6,C6,$E$6:E6,E6)=1,MAX($Q$5:Q5)+1,""))</f>
         <v/>
       </c>
       <c r="R6">
-        <f>IF(G6="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G6+1),入力!$C$56:$C$65,"&gt;="&amp;(G6+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G6+1),入力!$C$56:$C$65,"&gt;="&amp;(G6+1))+1,G6+1))</f>
+        <f>IF(G6="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G6+1),入力!$C$86:$C$95,"&gt;="&amp;(G6+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G6+1),入力!$C$86:$C$95,"&gt;="&amp;(G6+1))+1,G6+1))</f>
         <v/>
       </c>
       <c r="S6">
-        <f>IF(R6="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R6),入力!$C$56:$C$65,"&gt;="&amp;(R6))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R6),入力!$C$56:$C$65,"&gt;="&amp;(R6))+1,R6))</f>
+        <f>IF(R6="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R6),入力!$C$86:$C$95,"&gt;="&amp;(R6))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R6),入力!$C$86:$C$95,"&gt;="&amp;(R6))+1,R6))</f>
         <v/>
       </c>
     </row>
@@ -4530,7 +5527,7 @@
         <v/>
       </c>
       <c r="G7" s="31">
-        <f>IF(F7="","",MIN(EOMONTH(F7,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F7),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F7),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F7),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F7),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F7),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F7),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F7),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F7),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F7),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F7)+1)-1,999999)))</f>
+        <f>IF(F7="","",MIN(EOMONTH(F7,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F7),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F7),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F7),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F7),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F7),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F7),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F7),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F7),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F7),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F7)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H7" s="52">
@@ -4565,16 +5562,20 @@
         <f>IF(F7="","",M7-N7)</f>
         <v/>
       </c>
+      <c r="P7" s="69">
+        <f>IF(F7="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B7,C7,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q7">
         <f>IF(F7="","",IF(COUNTIFS($B$6:B7,B7,$C$6:C7,C7,$E$6:E7,E7)=1,MAX($Q$5:Q6)+1,""))</f>
         <v/>
       </c>
       <c r="R7">
-        <f>IF(G7="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G7+1),入力!$C$56:$C$65,"&gt;="&amp;(G7+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G7+1),入力!$C$56:$C$65,"&gt;="&amp;(G7+1))+1,G7+1))</f>
+        <f>IF(G7="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G7+1),入力!$C$86:$C$95,"&gt;="&amp;(G7+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G7+1),入力!$C$86:$C$95,"&gt;="&amp;(G7+1))+1,G7+1))</f>
         <v/>
       </c>
       <c r="S7">
-        <f>IF(R7="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R7),入力!$C$56:$C$65,"&gt;="&amp;(R7))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R7),入力!$C$56:$C$65,"&gt;="&amp;(R7))+1,R7))</f>
+        <f>IF(R7="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R7),入力!$C$86:$C$95,"&gt;="&amp;(R7))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R7),入力!$C$86:$C$95,"&gt;="&amp;(R7))+1,R7))</f>
         <v/>
       </c>
     </row>
@@ -4604,7 +5605,7 @@
         <v/>
       </c>
       <c r="G8" s="31">
-        <f>IF(F8="","",MIN(EOMONTH(F8,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F8),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F8),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F8),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F8),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F8),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F8),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F8),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F8),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F8),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F8)+1)-1,999999)))</f>
+        <f>IF(F8="","",MIN(EOMONTH(F8,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F8),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F8),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F8),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F8),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F8),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F8),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F8),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F8),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F8),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F8)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H8" s="52">
@@ -4639,16 +5640,20 @@
         <f>IF(F8="","",M8-N8)</f>
         <v/>
       </c>
+      <c r="P8" s="69">
+        <f>IF(F8="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B8,C8,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q8">
         <f>IF(F8="","",IF(COUNTIFS($B$6:B8,B8,$C$6:C8,C8,$E$6:E8,E8)=1,MAX($Q$5:Q7)+1,""))</f>
         <v/>
       </c>
       <c r="R8">
-        <f>IF(G8="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G8+1),入力!$C$56:$C$65,"&gt;="&amp;(G8+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G8+1),入力!$C$56:$C$65,"&gt;="&amp;(G8+1))+1,G8+1))</f>
+        <f>IF(G8="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G8+1),入力!$C$86:$C$95,"&gt;="&amp;(G8+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G8+1),入力!$C$86:$C$95,"&gt;="&amp;(G8+1))+1,G8+1))</f>
         <v/>
       </c>
       <c r="S8">
-        <f>IF(R8="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R8),入力!$C$56:$C$65,"&gt;="&amp;(R8))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R8),入力!$C$56:$C$65,"&gt;="&amp;(R8))+1,R8))</f>
+        <f>IF(R8="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R8),入力!$C$86:$C$95,"&gt;="&amp;(R8))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R8),入力!$C$86:$C$95,"&gt;="&amp;(R8))+1,R8))</f>
         <v/>
       </c>
     </row>
@@ -4678,7 +5683,7 @@
         <v/>
       </c>
       <c r="G9" s="31">
-        <f>IF(F9="","",MIN(EOMONTH(F9,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F9),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F9),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F9),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F9),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F9),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F9),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F9),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F9),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F9),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F9)+1)-1,999999)))</f>
+        <f>IF(F9="","",MIN(EOMONTH(F9,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F9),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F9),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F9),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F9),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F9),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F9),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F9),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F9),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F9),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F9)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H9" s="52">
@@ -4713,16 +5718,20 @@
         <f>IF(F9="","",M9-N9)</f>
         <v/>
       </c>
+      <c r="P9" s="69">
+        <f>IF(F9="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B9,C9,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q9">
         <f>IF(F9="","",IF(COUNTIFS($B$6:B9,B9,$C$6:C9,C9,$E$6:E9,E9)=1,MAX($Q$5:Q8)+1,""))</f>
         <v/>
       </c>
       <c r="R9">
-        <f>IF(G9="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G9+1),入力!$C$56:$C$65,"&gt;="&amp;(G9+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G9+1),入力!$C$56:$C$65,"&gt;="&amp;(G9+1))+1,G9+1))</f>
+        <f>IF(G9="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G9+1),入力!$C$86:$C$95,"&gt;="&amp;(G9+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G9+1),入力!$C$86:$C$95,"&gt;="&amp;(G9+1))+1,G9+1))</f>
         <v/>
       </c>
       <c r="S9">
-        <f>IF(R9="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R9),入力!$C$56:$C$65,"&gt;="&amp;(R9))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R9),入力!$C$56:$C$65,"&gt;="&amp;(R9))+1,R9))</f>
+        <f>IF(R9="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R9),入力!$C$86:$C$95,"&gt;="&amp;(R9))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R9),入力!$C$86:$C$95,"&gt;="&amp;(R9))+1,R9))</f>
         <v/>
       </c>
     </row>
@@ -4752,7 +5761,7 @@
         <v/>
       </c>
       <c r="G10" s="31">
-        <f>IF(F10="","",MIN(EOMONTH(F10,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F10),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F10),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F10),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F10),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F10),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F10),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F10),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F10),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F10),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F10)+1)-1,999999)))</f>
+        <f>IF(F10="","",MIN(EOMONTH(F10,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F10),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F10),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F10),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F10),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F10),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F10),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F10),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F10),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F10),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F10)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H10" s="52">
@@ -4787,16 +5796,20 @@
         <f>IF(F10="","",M10-N10)</f>
         <v/>
       </c>
+      <c r="P10" s="69">
+        <f>IF(F10="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B10,C10,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q10">
         <f>IF(F10="","",IF(COUNTIFS($B$6:B10,B10,$C$6:C10,C10,$E$6:E10,E10)=1,MAX($Q$5:Q9)+1,""))</f>
         <v/>
       </c>
       <c r="R10">
-        <f>IF(G10="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G10+1),入力!$C$56:$C$65,"&gt;="&amp;(G10+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G10+1),入力!$C$56:$C$65,"&gt;="&amp;(G10+1))+1,G10+1))</f>
+        <f>IF(G10="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G10+1),入力!$C$86:$C$95,"&gt;="&amp;(G10+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G10+1),入力!$C$86:$C$95,"&gt;="&amp;(G10+1))+1,G10+1))</f>
         <v/>
       </c>
       <c r="S10">
-        <f>IF(R10="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R10),入力!$C$56:$C$65,"&gt;="&amp;(R10))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R10),入力!$C$56:$C$65,"&gt;="&amp;(R10))+1,R10))</f>
+        <f>IF(R10="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R10),入力!$C$86:$C$95,"&gt;="&amp;(R10))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R10),入力!$C$86:$C$95,"&gt;="&amp;(R10))+1,R10))</f>
         <v/>
       </c>
     </row>
@@ -4826,7 +5839,7 @@
         <v/>
       </c>
       <c r="G11" s="31">
-        <f>IF(F11="","",MIN(EOMONTH(F11,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F11),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F11),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F11),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F11),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F11),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F11),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F11),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F11),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F11),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F11)+1)-1,999999)))</f>
+        <f>IF(F11="","",MIN(EOMONTH(F11,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F11),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F11),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F11),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F11),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F11),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F11),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F11),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F11),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F11),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F11)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H11" s="52">
@@ -4861,16 +5874,20 @@
         <f>IF(F11="","",M11-N11)</f>
         <v/>
       </c>
+      <c r="P11" s="69">
+        <f>IF(F11="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B11,C11,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q11">
         <f>IF(F11="","",IF(COUNTIFS($B$6:B11,B11,$C$6:C11,C11,$E$6:E11,E11)=1,MAX($Q$5:Q10)+1,""))</f>
         <v/>
       </c>
       <c r="R11">
-        <f>IF(G11="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G11+1),入力!$C$56:$C$65,"&gt;="&amp;(G11+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G11+1),入力!$C$56:$C$65,"&gt;="&amp;(G11+1))+1,G11+1))</f>
+        <f>IF(G11="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G11+1),入力!$C$86:$C$95,"&gt;="&amp;(G11+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G11+1),入力!$C$86:$C$95,"&gt;="&amp;(G11+1))+1,G11+1))</f>
         <v/>
       </c>
       <c r="S11">
-        <f>IF(R11="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R11),入力!$C$56:$C$65,"&gt;="&amp;(R11))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R11),入力!$C$56:$C$65,"&gt;="&amp;(R11))+1,R11))</f>
+        <f>IF(R11="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R11),入力!$C$86:$C$95,"&gt;="&amp;(R11))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R11),入力!$C$86:$C$95,"&gt;="&amp;(R11))+1,R11))</f>
         <v/>
       </c>
     </row>
@@ -4900,7 +5917,7 @@
         <v/>
       </c>
       <c r="G12" s="31">
-        <f>IF(F12="","",MIN(EOMONTH(F12,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F12),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F12),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F12),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F12),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F12),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F12),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F12),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F12),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F12),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F12)+1)-1,999999)))</f>
+        <f>IF(F12="","",MIN(EOMONTH(F12,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F12),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F12),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F12),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F12),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F12),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F12),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F12),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F12),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F12),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F12)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H12" s="52">
@@ -4935,16 +5952,20 @@
         <f>IF(F12="","",M12-N12)</f>
         <v/>
       </c>
+      <c r="P12" s="69">
+        <f>IF(F12="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B12,C12,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q12">
         <f>IF(F12="","",IF(COUNTIFS($B$6:B12,B12,$C$6:C12,C12,$E$6:E12,E12)=1,MAX($Q$5:Q11)+1,""))</f>
         <v/>
       </c>
       <c r="R12">
-        <f>IF(G12="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G12+1),入力!$C$56:$C$65,"&gt;="&amp;(G12+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G12+1),入力!$C$56:$C$65,"&gt;="&amp;(G12+1))+1,G12+1))</f>
+        <f>IF(G12="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G12+1),入力!$C$86:$C$95,"&gt;="&amp;(G12+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G12+1),入力!$C$86:$C$95,"&gt;="&amp;(G12+1))+1,G12+1))</f>
         <v/>
       </c>
       <c r="S12">
-        <f>IF(R12="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R12),入力!$C$56:$C$65,"&gt;="&amp;(R12))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R12),入力!$C$56:$C$65,"&gt;="&amp;(R12))+1,R12))</f>
+        <f>IF(R12="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R12),入力!$C$86:$C$95,"&gt;="&amp;(R12))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R12),入力!$C$86:$C$95,"&gt;="&amp;(R12))+1,R12))</f>
         <v/>
       </c>
     </row>
@@ -4974,7 +5995,7 @@
         <v/>
       </c>
       <c r="G13" s="31">
-        <f>IF(F13="","",MIN(EOMONTH(F13,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F13),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F13),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F13),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F13),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F13),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F13),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F13),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F13),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F13),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F13)+1)-1,999999)))</f>
+        <f>IF(F13="","",MIN(EOMONTH(F13,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F13),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F13),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F13),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F13),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F13),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F13),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F13),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F13),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F13),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F13)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H13" s="52">
@@ -5009,16 +6030,20 @@
         <f>IF(F13="","",M13-N13)</f>
         <v/>
       </c>
+      <c r="P13" s="69">
+        <f>IF(F13="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B13,C13,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q13">
         <f>IF(F13="","",IF(COUNTIFS($B$6:B13,B13,$C$6:C13,C13,$E$6:E13,E13)=1,MAX($Q$5:Q12)+1,""))</f>
         <v/>
       </c>
       <c r="R13">
-        <f>IF(G13="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G13+1),入力!$C$56:$C$65,"&gt;="&amp;(G13+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G13+1),入力!$C$56:$C$65,"&gt;="&amp;(G13+1))+1,G13+1))</f>
+        <f>IF(G13="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G13+1),入力!$C$86:$C$95,"&gt;="&amp;(G13+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G13+1),入力!$C$86:$C$95,"&gt;="&amp;(G13+1))+1,G13+1))</f>
         <v/>
       </c>
       <c r="S13">
-        <f>IF(R13="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R13),入力!$C$56:$C$65,"&gt;="&amp;(R13))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R13),入力!$C$56:$C$65,"&gt;="&amp;(R13))+1,R13))</f>
+        <f>IF(R13="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R13),入力!$C$86:$C$95,"&gt;="&amp;(R13))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R13),入力!$C$86:$C$95,"&gt;="&amp;(R13))+1,R13))</f>
         <v/>
       </c>
     </row>
@@ -5048,7 +6073,7 @@
         <v/>
       </c>
       <c r="G14" s="31">
-        <f>IF(F14="","",MIN(EOMONTH(F14,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F14),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F14),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F14),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F14),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F14),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F14),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F14),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F14),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F14),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F14)+1)-1,999999)))</f>
+        <f>IF(F14="","",MIN(EOMONTH(F14,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F14),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F14),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F14),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F14),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F14),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F14),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F14),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F14),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F14),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F14)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H14" s="52">
@@ -5083,16 +6108,20 @@
         <f>IF(F14="","",M14-N14)</f>
         <v/>
       </c>
+      <c r="P14" s="69">
+        <f>IF(F14="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B14,C14,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q14">
         <f>IF(F14="","",IF(COUNTIFS($B$6:B14,B14,$C$6:C14,C14,$E$6:E14,E14)=1,MAX($Q$5:Q13)+1,""))</f>
         <v/>
       </c>
       <c r="R14">
-        <f>IF(G14="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G14+1),入力!$C$56:$C$65,"&gt;="&amp;(G14+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G14+1),入力!$C$56:$C$65,"&gt;="&amp;(G14+1))+1,G14+1))</f>
+        <f>IF(G14="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G14+1),入力!$C$86:$C$95,"&gt;="&amp;(G14+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G14+1),入力!$C$86:$C$95,"&gt;="&amp;(G14+1))+1,G14+1))</f>
         <v/>
       </c>
       <c r="S14">
-        <f>IF(R14="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R14),入力!$C$56:$C$65,"&gt;="&amp;(R14))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R14),入力!$C$56:$C$65,"&gt;="&amp;(R14))+1,R14))</f>
+        <f>IF(R14="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R14),入力!$C$86:$C$95,"&gt;="&amp;(R14))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R14),入力!$C$86:$C$95,"&gt;="&amp;(R14))+1,R14))</f>
         <v/>
       </c>
     </row>
@@ -5122,7 +6151,7 @@
         <v/>
       </c>
       <c r="G15" s="31">
-        <f>IF(F15="","",MIN(EOMONTH(F15,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F15),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F15),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F15),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F15),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F15),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F15),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F15),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F15),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F15),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F15)+1)-1,999999)))</f>
+        <f>IF(F15="","",MIN(EOMONTH(F15,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F15),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F15),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F15),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F15),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F15),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F15),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F15),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F15),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F15),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F15)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H15" s="52">
@@ -5157,16 +6186,20 @@
         <f>IF(F15="","",M15-N15)</f>
         <v/>
       </c>
+      <c r="P15" s="69">
+        <f>IF(F15="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B15,C15,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q15">
         <f>IF(F15="","",IF(COUNTIFS($B$6:B15,B15,$C$6:C15,C15,$E$6:E15,E15)=1,MAX($Q$5:Q14)+1,""))</f>
         <v/>
       </c>
       <c r="R15">
-        <f>IF(G15="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G15+1),入力!$C$56:$C$65,"&gt;="&amp;(G15+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G15+1),入力!$C$56:$C$65,"&gt;="&amp;(G15+1))+1,G15+1))</f>
+        <f>IF(G15="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G15+1),入力!$C$86:$C$95,"&gt;="&amp;(G15+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G15+1),入力!$C$86:$C$95,"&gt;="&amp;(G15+1))+1,G15+1))</f>
         <v/>
       </c>
       <c r="S15">
-        <f>IF(R15="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R15),入力!$C$56:$C$65,"&gt;="&amp;(R15))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R15),入力!$C$56:$C$65,"&gt;="&amp;(R15))+1,R15))</f>
+        <f>IF(R15="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R15),入力!$C$86:$C$95,"&gt;="&amp;(R15))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R15),入力!$C$86:$C$95,"&gt;="&amp;(R15))+1,R15))</f>
         <v/>
       </c>
     </row>
@@ -5196,7 +6229,7 @@
         <v/>
       </c>
       <c r="G16" s="31">
-        <f>IF(F16="","",MIN(EOMONTH(F16,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F16),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F16),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F16),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F16),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F16),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F16),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F16),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F16),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F16),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F16)+1)-1,999999)))</f>
+        <f>IF(F16="","",MIN(EOMONTH(F16,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F16),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F16),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F16),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F16),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F16),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F16),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F16),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F16),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F16),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F16)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H16" s="52">
@@ -5231,16 +6264,20 @@
         <f>IF(F16="","",M16-N16)</f>
         <v/>
       </c>
+      <c r="P16" s="69">
+        <f>IF(F16="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B16,C16,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q16">
         <f>IF(F16="","",IF(COUNTIFS($B$6:B16,B16,$C$6:C16,C16,$E$6:E16,E16)=1,MAX($Q$5:Q15)+1,""))</f>
         <v/>
       </c>
       <c r="R16">
-        <f>IF(G16="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G16+1),入力!$C$56:$C$65,"&gt;="&amp;(G16+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G16+1),入力!$C$56:$C$65,"&gt;="&amp;(G16+1))+1,G16+1))</f>
+        <f>IF(G16="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G16+1),入力!$C$86:$C$95,"&gt;="&amp;(G16+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G16+1),入力!$C$86:$C$95,"&gt;="&amp;(G16+1))+1,G16+1))</f>
         <v/>
       </c>
       <c r="S16">
-        <f>IF(R16="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R16),入力!$C$56:$C$65,"&gt;="&amp;(R16))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R16),入力!$C$56:$C$65,"&gt;="&amp;(R16))+1,R16))</f>
+        <f>IF(R16="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R16),入力!$C$86:$C$95,"&gt;="&amp;(R16))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R16),入力!$C$86:$C$95,"&gt;="&amp;(R16))+1,R16))</f>
         <v/>
       </c>
     </row>
@@ -5270,7 +6307,7 @@
         <v/>
       </c>
       <c r="G17" s="31">
-        <f>IF(F17="","",MIN(EOMONTH(F17,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F17),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F17),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F17),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F17),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F17),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F17),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F17),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F17),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F17),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F17)+1)-1,999999)))</f>
+        <f>IF(F17="","",MIN(EOMONTH(F17,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F17),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F17),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F17),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F17),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F17),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F17),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F17),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F17),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F17),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F17)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H17" s="52">
@@ -5305,16 +6342,20 @@
         <f>IF(F17="","",M17-N17)</f>
         <v/>
       </c>
+      <c r="P17" s="69">
+        <f>IF(F17="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B17,C17,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q17">
         <f>IF(F17="","",IF(COUNTIFS($B$6:B17,B17,$C$6:C17,C17,$E$6:E17,E17)=1,MAX($Q$5:Q16)+1,""))</f>
         <v/>
       </c>
       <c r="R17">
-        <f>IF(G17="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G17+1),入力!$C$56:$C$65,"&gt;="&amp;(G17+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G17+1),入力!$C$56:$C$65,"&gt;="&amp;(G17+1))+1,G17+1))</f>
+        <f>IF(G17="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G17+1),入力!$C$86:$C$95,"&gt;="&amp;(G17+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G17+1),入力!$C$86:$C$95,"&gt;="&amp;(G17+1))+1,G17+1))</f>
         <v/>
       </c>
       <c r="S17">
-        <f>IF(R17="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R17),入力!$C$56:$C$65,"&gt;="&amp;(R17))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R17),入力!$C$56:$C$65,"&gt;="&amp;(R17))+1,R17))</f>
+        <f>IF(R17="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R17),入力!$C$86:$C$95,"&gt;="&amp;(R17))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R17),入力!$C$86:$C$95,"&gt;="&amp;(R17))+1,R17))</f>
         <v/>
       </c>
     </row>
@@ -5344,7 +6385,7 @@
         <v/>
       </c>
       <c r="G18" s="31">
-        <f>IF(F18="","",MIN(EOMONTH(F18,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F18),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F18),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F18),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F18),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F18),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F18),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F18),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F18),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F18),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F18)+1)-1,999999)))</f>
+        <f>IF(F18="","",MIN(EOMONTH(F18,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F18),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F18),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F18),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F18),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F18),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F18),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F18),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F18),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F18),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F18)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H18" s="52">
@@ -5379,16 +6420,20 @@
         <f>IF(F18="","",M18-N18)</f>
         <v/>
       </c>
+      <c r="P18" s="69">
+        <f>IF(F18="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B18,C18,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q18">
         <f>IF(F18="","",IF(COUNTIFS($B$6:B18,B18,$C$6:C18,C18,$E$6:E18,E18)=1,MAX($Q$5:Q17)+1,""))</f>
         <v/>
       </c>
       <c r="R18">
-        <f>IF(G18="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G18+1),入力!$C$56:$C$65,"&gt;="&amp;(G18+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G18+1),入力!$C$56:$C$65,"&gt;="&amp;(G18+1))+1,G18+1))</f>
+        <f>IF(G18="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G18+1),入力!$C$86:$C$95,"&gt;="&amp;(G18+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G18+1),入力!$C$86:$C$95,"&gt;="&amp;(G18+1))+1,G18+1))</f>
         <v/>
       </c>
       <c r="S18">
-        <f>IF(R18="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R18),入力!$C$56:$C$65,"&gt;="&amp;(R18))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R18),入力!$C$56:$C$65,"&gt;="&amp;(R18))+1,R18))</f>
+        <f>IF(R18="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R18),入力!$C$86:$C$95,"&gt;="&amp;(R18))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R18),入力!$C$86:$C$95,"&gt;="&amp;(R18))+1,R18))</f>
         <v/>
       </c>
     </row>
@@ -5418,7 +6463,7 @@
         <v/>
       </c>
       <c r="G19" s="31">
-        <f>IF(F19="","",MIN(EOMONTH(F19,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F19),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F19),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F19),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F19),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F19),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F19),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F19),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F19),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F19),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F19)+1)-1,999999)))</f>
+        <f>IF(F19="","",MIN(EOMONTH(F19,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F19),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F19),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F19),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F19),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F19),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F19),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F19),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F19),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F19),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F19)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H19" s="52">
@@ -5453,16 +6498,20 @@
         <f>IF(F19="","",M19-N19)</f>
         <v/>
       </c>
+      <c r="P19" s="69">
+        <f>IF(F19="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B19,C19,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q19">
         <f>IF(F19="","",IF(COUNTIFS($B$6:B19,B19,$C$6:C19,C19,$E$6:E19,E19)=1,MAX($Q$5:Q18)+1,""))</f>
         <v/>
       </c>
       <c r="R19">
-        <f>IF(G19="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G19+1),入力!$C$56:$C$65,"&gt;="&amp;(G19+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G19+1),入力!$C$56:$C$65,"&gt;="&amp;(G19+1))+1,G19+1))</f>
+        <f>IF(G19="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G19+1),入力!$C$86:$C$95,"&gt;="&amp;(G19+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G19+1),入力!$C$86:$C$95,"&gt;="&amp;(G19+1))+1,G19+1))</f>
         <v/>
       </c>
       <c r="S19">
-        <f>IF(R19="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R19),入力!$C$56:$C$65,"&gt;="&amp;(R19))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R19),入力!$C$56:$C$65,"&gt;="&amp;(R19))+1,R19))</f>
+        <f>IF(R19="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R19),入力!$C$86:$C$95,"&gt;="&amp;(R19))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R19),入力!$C$86:$C$95,"&gt;="&amp;(R19))+1,R19))</f>
         <v/>
       </c>
     </row>
@@ -5492,7 +6541,7 @@
         <v/>
       </c>
       <c r="G20" s="31">
-        <f>IF(F20="","",MIN(EOMONTH(F20,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F20),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F20),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F20),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F20),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F20),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F20),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F20),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F20),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F20),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F20)+1)-1,999999)))</f>
+        <f>IF(F20="","",MIN(EOMONTH(F20,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F20),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F20),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F20),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F20),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F20),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F20),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F20),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F20),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F20),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F20)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H20" s="52">
@@ -5527,16 +6576,20 @@
         <f>IF(F20="","",M20-N20)</f>
         <v/>
       </c>
+      <c r="P20" s="69">
+        <f>IF(F20="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B20,C20,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q20">
         <f>IF(F20="","",IF(COUNTIFS($B$6:B20,B20,$C$6:C20,C20,$E$6:E20,E20)=1,MAX($Q$5:Q19)+1,""))</f>
         <v/>
       </c>
       <c r="R20">
-        <f>IF(G20="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G20+1),入力!$C$56:$C$65,"&gt;="&amp;(G20+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G20+1),入力!$C$56:$C$65,"&gt;="&amp;(G20+1))+1,G20+1))</f>
+        <f>IF(G20="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G20+1),入力!$C$86:$C$95,"&gt;="&amp;(G20+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G20+1),入力!$C$86:$C$95,"&gt;="&amp;(G20+1))+1,G20+1))</f>
         <v/>
       </c>
       <c r="S20">
-        <f>IF(R20="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R20),入力!$C$56:$C$65,"&gt;="&amp;(R20))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R20),入力!$C$56:$C$65,"&gt;="&amp;(R20))+1,R20))</f>
+        <f>IF(R20="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R20),入力!$C$86:$C$95,"&gt;="&amp;(R20))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R20),入力!$C$86:$C$95,"&gt;="&amp;(R20))+1,R20))</f>
         <v/>
       </c>
     </row>
@@ -5566,7 +6619,7 @@
         <v/>
       </c>
       <c r="G21" s="31">
-        <f>IF(F21="","",MIN(EOMONTH(F21,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F21),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F21),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F21),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F21),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F21),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F21),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F21),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F21),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F21),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F21)+1)-1,999999)))</f>
+        <f>IF(F21="","",MIN(EOMONTH(F21,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F21),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F21),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F21),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F21),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F21),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F21),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F21),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F21),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F21),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F21)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H21" s="52">
@@ -5601,16 +6654,20 @@
         <f>IF(F21="","",M21-N21)</f>
         <v/>
       </c>
+      <c r="P21" s="69">
+        <f>IF(F21="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B21,C21,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q21">
         <f>IF(F21="","",IF(COUNTIFS($B$6:B21,B21,$C$6:C21,C21,$E$6:E21,E21)=1,MAX($Q$5:Q20)+1,""))</f>
         <v/>
       </c>
       <c r="R21">
-        <f>IF(G21="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G21+1),入力!$C$56:$C$65,"&gt;="&amp;(G21+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G21+1),入力!$C$56:$C$65,"&gt;="&amp;(G21+1))+1,G21+1))</f>
+        <f>IF(G21="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G21+1),入力!$C$86:$C$95,"&gt;="&amp;(G21+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G21+1),入力!$C$86:$C$95,"&gt;="&amp;(G21+1))+1,G21+1))</f>
         <v/>
       </c>
       <c r="S21">
-        <f>IF(R21="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R21),入力!$C$56:$C$65,"&gt;="&amp;(R21))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R21),入力!$C$56:$C$65,"&gt;="&amp;(R21))+1,R21))</f>
+        <f>IF(R21="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R21),入力!$C$86:$C$95,"&gt;="&amp;(R21))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R21),入力!$C$86:$C$95,"&gt;="&amp;(R21))+1,R21))</f>
         <v/>
       </c>
     </row>
@@ -5640,7 +6697,7 @@
         <v/>
       </c>
       <c r="G22" s="31">
-        <f>IF(F22="","",MIN(EOMONTH(F22,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F22),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F22),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F22),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F22),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F22),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F22),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F22),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F22),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F22),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F22)+1)-1,999999)))</f>
+        <f>IF(F22="","",MIN(EOMONTH(F22,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F22),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F22),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F22),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F22),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F22),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F22),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F22),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F22),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F22),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F22)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H22" s="52">
@@ -5675,16 +6732,20 @@
         <f>IF(F22="","",M22-N22)</f>
         <v/>
       </c>
+      <c r="P22" s="69">
+        <f>IF(F22="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B22,C22,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q22">
         <f>IF(F22="","",IF(COUNTIFS($B$6:B22,B22,$C$6:C22,C22,$E$6:E22,E22)=1,MAX($Q$5:Q21)+1,""))</f>
         <v/>
       </c>
       <c r="R22">
-        <f>IF(G22="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G22+1),入力!$C$56:$C$65,"&gt;="&amp;(G22+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G22+1),入力!$C$56:$C$65,"&gt;="&amp;(G22+1))+1,G22+1))</f>
+        <f>IF(G22="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G22+1),入力!$C$86:$C$95,"&gt;="&amp;(G22+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G22+1),入力!$C$86:$C$95,"&gt;="&amp;(G22+1))+1,G22+1))</f>
         <v/>
       </c>
       <c r="S22">
-        <f>IF(R22="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R22),入力!$C$56:$C$65,"&gt;="&amp;(R22))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R22),入力!$C$56:$C$65,"&gt;="&amp;(R22))+1,R22))</f>
+        <f>IF(R22="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R22),入力!$C$86:$C$95,"&gt;="&amp;(R22))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R22),入力!$C$86:$C$95,"&gt;="&amp;(R22))+1,R22))</f>
         <v/>
       </c>
     </row>
@@ -5714,7 +6775,7 @@
         <v/>
       </c>
       <c r="G23" s="31">
-        <f>IF(F23="","",MIN(EOMONTH(F23,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F23),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F23),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F23),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F23),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F23),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F23),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F23),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F23),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F23),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F23)+1)-1,999999)))</f>
+        <f>IF(F23="","",MIN(EOMONTH(F23,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F23),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F23),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F23),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F23),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F23),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F23),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F23),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F23),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F23),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F23)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H23" s="52">
@@ -5749,16 +6810,20 @@
         <f>IF(F23="","",M23-N23)</f>
         <v/>
       </c>
+      <c r="P23" s="69">
+        <f>IF(F23="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B23,C23,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q23">
         <f>IF(F23="","",IF(COUNTIFS($B$6:B23,B23,$C$6:C23,C23,$E$6:E23,E23)=1,MAX($Q$5:Q22)+1,""))</f>
         <v/>
       </c>
       <c r="R23">
-        <f>IF(G23="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G23+1),入力!$C$56:$C$65,"&gt;="&amp;(G23+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G23+1),入力!$C$56:$C$65,"&gt;="&amp;(G23+1))+1,G23+1))</f>
+        <f>IF(G23="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G23+1),入力!$C$86:$C$95,"&gt;="&amp;(G23+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G23+1),入力!$C$86:$C$95,"&gt;="&amp;(G23+1))+1,G23+1))</f>
         <v/>
       </c>
       <c r="S23">
-        <f>IF(R23="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R23),入力!$C$56:$C$65,"&gt;="&amp;(R23))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R23),入力!$C$56:$C$65,"&gt;="&amp;(R23))+1,R23))</f>
+        <f>IF(R23="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R23),入力!$C$86:$C$95,"&gt;="&amp;(R23))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R23),入力!$C$86:$C$95,"&gt;="&amp;(R23))+1,R23))</f>
         <v/>
       </c>
     </row>
@@ -5788,7 +6853,7 @@
         <v/>
       </c>
       <c r="G24" s="31">
-        <f>IF(F24="","",MIN(EOMONTH(F24,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F24),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F24),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F24),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F24),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F24),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F24),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F24),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F24),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F24),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F24)+1)-1,999999)))</f>
+        <f>IF(F24="","",MIN(EOMONTH(F24,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F24),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F24),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F24),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F24),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F24),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F24),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F24),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F24),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F24),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F24)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H24" s="52">
@@ -5823,16 +6888,20 @@
         <f>IF(F24="","",M24-N24)</f>
         <v/>
       </c>
+      <c r="P24" s="69">
+        <f>IF(F24="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B24,C24,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q24">
         <f>IF(F24="","",IF(COUNTIFS($B$6:B24,B24,$C$6:C24,C24,$E$6:E24,E24)=1,MAX($Q$5:Q23)+1,""))</f>
         <v/>
       </c>
       <c r="R24">
-        <f>IF(G24="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G24+1),入力!$C$56:$C$65,"&gt;="&amp;(G24+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G24+1),入力!$C$56:$C$65,"&gt;="&amp;(G24+1))+1,G24+1))</f>
+        <f>IF(G24="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G24+1),入力!$C$86:$C$95,"&gt;="&amp;(G24+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G24+1),入力!$C$86:$C$95,"&gt;="&amp;(G24+1))+1,G24+1))</f>
         <v/>
       </c>
       <c r="S24">
-        <f>IF(R24="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R24),入力!$C$56:$C$65,"&gt;="&amp;(R24))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R24),入力!$C$56:$C$65,"&gt;="&amp;(R24))+1,R24))</f>
+        <f>IF(R24="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R24),入力!$C$86:$C$95,"&gt;="&amp;(R24))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R24),入力!$C$86:$C$95,"&gt;="&amp;(R24))+1,R24))</f>
         <v/>
       </c>
     </row>
@@ -5862,7 +6931,7 @@
         <v/>
       </c>
       <c r="G25" s="31">
-        <f>IF(F25="","",MIN(EOMONTH(F25,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F25),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F25),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F25),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F25),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F25),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F25),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F25),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F25),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F25),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F25)+1)-1,999999)))</f>
+        <f>IF(F25="","",MIN(EOMONTH(F25,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F25),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F25),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F25),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F25),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F25),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F25),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F25),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F25),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F25),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F25)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H25" s="52">
@@ -5897,16 +6966,20 @@
         <f>IF(F25="","",M25-N25)</f>
         <v/>
       </c>
+      <c r="P25" s="69">
+        <f>IF(F25="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B25,C25,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q25">
         <f>IF(F25="","",IF(COUNTIFS($B$6:B25,B25,$C$6:C25,C25,$E$6:E25,E25)=1,MAX($Q$5:Q24)+1,""))</f>
         <v/>
       </c>
       <c r="R25">
-        <f>IF(G25="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G25+1),入力!$C$56:$C$65,"&gt;="&amp;(G25+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G25+1),入力!$C$56:$C$65,"&gt;="&amp;(G25+1))+1,G25+1))</f>
+        <f>IF(G25="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G25+1),入力!$C$86:$C$95,"&gt;="&amp;(G25+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G25+1),入力!$C$86:$C$95,"&gt;="&amp;(G25+1))+1,G25+1))</f>
         <v/>
       </c>
       <c r="S25">
-        <f>IF(R25="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R25),入力!$C$56:$C$65,"&gt;="&amp;(R25))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R25),入力!$C$56:$C$65,"&gt;="&amp;(R25))+1,R25))</f>
+        <f>IF(R25="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R25),入力!$C$86:$C$95,"&gt;="&amp;(R25))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R25),入力!$C$86:$C$95,"&gt;="&amp;(R25))+1,R25))</f>
         <v/>
       </c>
     </row>
@@ -5936,7 +7009,7 @@
         <v/>
       </c>
       <c r="G26" s="31">
-        <f>IF(F26="","",MIN(EOMONTH(F26,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F26),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F26),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F26),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F26),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F26),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F26),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F26),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F26),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F26),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F26)+1)-1,999999)))</f>
+        <f>IF(F26="","",MIN(EOMONTH(F26,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F26),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F26),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F26),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F26),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F26),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F26),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F26),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F26),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F26),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F26)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H26" s="52">
@@ -5971,16 +7044,20 @@
         <f>IF(F26="","",M26-N26)</f>
         <v/>
       </c>
+      <c r="P26" s="69">
+        <f>IF(F26="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B26,C26,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q26">
         <f>IF(F26="","",IF(COUNTIFS($B$6:B26,B26,$C$6:C26,C26,$E$6:E26,E26)=1,MAX($Q$5:Q25)+1,""))</f>
         <v/>
       </c>
       <c r="R26">
-        <f>IF(G26="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G26+1),入力!$C$56:$C$65,"&gt;="&amp;(G26+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G26+1),入力!$C$56:$C$65,"&gt;="&amp;(G26+1))+1,G26+1))</f>
+        <f>IF(G26="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G26+1),入力!$C$86:$C$95,"&gt;="&amp;(G26+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G26+1),入力!$C$86:$C$95,"&gt;="&amp;(G26+1))+1,G26+1))</f>
         <v/>
       </c>
       <c r="S26">
-        <f>IF(R26="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R26),入力!$C$56:$C$65,"&gt;="&amp;(R26))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R26),入力!$C$56:$C$65,"&gt;="&amp;(R26))+1,R26))</f>
+        <f>IF(R26="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R26),入力!$C$86:$C$95,"&gt;="&amp;(R26))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R26),入力!$C$86:$C$95,"&gt;="&amp;(R26))+1,R26))</f>
         <v/>
       </c>
     </row>
@@ -6010,7 +7087,7 @@
         <v/>
       </c>
       <c r="G27" s="31">
-        <f>IF(F27="","",MIN(EOMONTH(F27,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F27),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F27),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F27),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F27),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F27),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F27),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F27),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F27),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F27),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F27)+1)-1,999999)))</f>
+        <f>IF(F27="","",MIN(EOMONTH(F27,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F27),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F27),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F27),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F27),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F27),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F27),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F27),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F27),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F27),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F27)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H27" s="52">
@@ -6045,16 +7122,20 @@
         <f>IF(F27="","",M27-N27)</f>
         <v/>
       </c>
+      <c r="P27" s="69">
+        <f>IF(F27="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B27,C27,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q27">
         <f>IF(F27="","",IF(COUNTIFS($B$6:B27,B27,$C$6:C27,C27,$E$6:E27,E27)=1,MAX($Q$5:Q26)+1,""))</f>
         <v/>
       </c>
       <c r="R27">
-        <f>IF(G27="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G27+1),入力!$C$56:$C$65,"&gt;="&amp;(G27+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G27+1),入力!$C$56:$C$65,"&gt;="&amp;(G27+1))+1,G27+1))</f>
+        <f>IF(G27="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G27+1),入力!$C$86:$C$95,"&gt;="&amp;(G27+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G27+1),入力!$C$86:$C$95,"&gt;="&amp;(G27+1))+1,G27+1))</f>
         <v/>
       </c>
       <c r="S27">
-        <f>IF(R27="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R27),入力!$C$56:$C$65,"&gt;="&amp;(R27))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R27),入力!$C$56:$C$65,"&gt;="&amp;(R27))+1,R27))</f>
+        <f>IF(R27="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R27),入力!$C$86:$C$95,"&gt;="&amp;(R27))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R27),入力!$C$86:$C$95,"&gt;="&amp;(R27))+1,R27))</f>
         <v/>
       </c>
     </row>
@@ -6084,7 +7165,7 @@
         <v/>
       </c>
       <c r="G28" s="31">
-        <f>IF(F28="","",MIN(EOMONTH(F28,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F28),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F28),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F28),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F28),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F28),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F28),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F28),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F28),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F28),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F28)+1)-1,999999)))</f>
+        <f>IF(F28="","",MIN(EOMONTH(F28,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F28),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F28),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F28),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F28),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F28),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F28),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F28),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F28),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F28),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F28)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H28" s="52">
@@ -6119,16 +7200,20 @@
         <f>IF(F28="","",M28-N28)</f>
         <v/>
       </c>
+      <c r="P28" s="69">
+        <f>IF(F28="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B28,C28,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q28">
         <f>IF(F28="","",IF(COUNTIFS($B$6:B28,B28,$C$6:C28,C28,$E$6:E28,E28)=1,MAX($Q$5:Q27)+1,""))</f>
         <v/>
       </c>
       <c r="R28">
-        <f>IF(G28="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G28+1),入力!$C$56:$C$65,"&gt;="&amp;(G28+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G28+1),入力!$C$56:$C$65,"&gt;="&amp;(G28+1))+1,G28+1))</f>
+        <f>IF(G28="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G28+1),入力!$C$86:$C$95,"&gt;="&amp;(G28+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G28+1),入力!$C$86:$C$95,"&gt;="&amp;(G28+1))+1,G28+1))</f>
         <v/>
       </c>
       <c r="S28">
-        <f>IF(R28="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R28),入力!$C$56:$C$65,"&gt;="&amp;(R28))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R28),入力!$C$56:$C$65,"&gt;="&amp;(R28))+1,R28))</f>
+        <f>IF(R28="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R28),入力!$C$86:$C$95,"&gt;="&amp;(R28))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R28),入力!$C$86:$C$95,"&gt;="&amp;(R28))+1,R28))</f>
         <v/>
       </c>
     </row>
@@ -6158,7 +7243,7 @@
         <v/>
       </c>
       <c r="G29" s="31">
-        <f>IF(F29="","",MIN(EOMONTH(F29,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F29),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F29),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F29),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F29),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F29),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F29),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F29),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F29),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F29),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F29)+1)-1,999999)))</f>
+        <f>IF(F29="","",MIN(EOMONTH(F29,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F29),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F29),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F29),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F29),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F29),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F29),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F29),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F29),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F29),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F29)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H29" s="52">
@@ -6193,16 +7278,20 @@
         <f>IF(F29="","",M29-N29)</f>
         <v/>
       </c>
+      <c r="P29" s="69">
+        <f>IF(F29="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B29,C29,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q29">
         <f>IF(F29="","",IF(COUNTIFS($B$6:B29,B29,$C$6:C29,C29,$E$6:E29,E29)=1,MAX($Q$5:Q28)+1,""))</f>
         <v/>
       </c>
       <c r="R29">
-        <f>IF(G29="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G29+1),入力!$C$56:$C$65,"&gt;="&amp;(G29+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G29+1),入力!$C$56:$C$65,"&gt;="&amp;(G29+1))+1,G29+1))</f>
+        <f>IF(G29="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G29+1),入力!$C$86:$C$95,"&gt;="&amp;(G29+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G29+1),入力!$C$86:$C$95,"&gt;="&amp;(G29+1))+1,G29+1))</f>
         <v/>
       </c>
       <c r="S29">
-        <f>IF(R29="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R29),入力!$C$56:$C$65,"&gt;="&amp;(R29))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R29),入力!$C$56:$C$65,"&gt;="&amp;(R29))+1,R29))</f>
+        <f>IF(R29="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R29),入力!$C$86:$C$95,"&gt;="&amp;(R29))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R29),入力!$C$86:$C$95,"&gt;="&amp;(R29))+1,R29))</f>
         <v/>
       </c>
     </row>
@@ -6232,7 +7321,7 @@
         <v/>
       </c>
       <c r="G30" s="31">
-        <f>IF(F30="","",MIN(EOMONTH(F30,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F30),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F30),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F30),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F30),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F30),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F30),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F30),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F30),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F30),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F30)+1)-1,999999)))</f>
+        <f>IF(F30="","",MIN(EOMONTH(F30,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F30),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F30),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F30),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F30),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F30),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F30),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F30),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F30),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F30),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F30)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H30" s="52">
@@ -6267,16 +7356,20 @@
         <f>IF(F30="","",M30-N30)</f>
         <v/>
       </c>
+      <c r="P30" s="69">
+        <f>IF(F30="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B30,C30,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q30">
         <f>IF(F30="","",IF(COUNTIFS($B$6:B30,B30,$C$6:C30,C30,$E$6:E30,E30)=1,MAX($Q$5:Q29)+1,""))</f>
         <v/>
       </c>
       <c r="R30">
-        <f>IF(G30="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G30+1),入力!$C$56:$C$65,"&gt;="&amp;(G30+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G30+1),入力!$C$56:$C$65,"&gt;="&amp;(G30+1))+1,G30+1))</f>
+        <f>IF(G30="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G30+1),入力!$C$86:$C$95,"&gt;="&amp;(G30+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G30+1),入力!$C$86:$C$95,"&gt;="&amp;(G30+1))+1,G30+1))</f>
         <v/>
       </c>
       <c r="S30">
-        <f>IF(R30="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R30),入力!$C$56:$C$65,"&gt;="&amp;(R30))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R30),入力!$C$56:$C$65,"&gt;="&amp;(R30))+1,R30))</f>
+        <f>IF(R30="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R30),入力!$C$86:$C$95,"&gt;="&amp;(R30))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R30),入力!$C$86:$C$95,"&gt;="&amp;(R30))+1,R30))</f>
         <v/>
       </c>
     </row>
@@ -6306,7 +7399,7 @@
         <v/>
       </c>
       <c r="G31" s="31">
-        <f>IF(F31="","",MIN(EOMONTH(F31,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F31),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F31),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F31),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F31),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F31),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F31),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F31),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F31),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F31),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F31)+1)-1,999999)))</f>
+        <f>IF(F31="","",MIN(EOMONTH(F31,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F31),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F31),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F31),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F31),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F31),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F31),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F31),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F31),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F31),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F31)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H31" s="52">
@@ -6341,16 +7434,20 @@
         <f>IF(F31="","",M31-N31)</f>
         <v/>
       </c>
+      <c r="P31" s="69">
+        <f>IF(F31="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B31,C31,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q31">
         <f>IF(F31="","",IF(COUNTIFS($B$6:B31,B31,$C$6:C31,C31,$E$6:E31,E31)=1,MAX($Q$5:Q30)+1,""))</f>
         <v/>
       </c>
       <c r="R31">
-        <f>IF(G31="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G31+1),入力!$C$56:$C$65,"&gt;="&amp;(G31+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G31+1),入力!$C$56:$C$65,"&gt;="&amp;(G31+1))+1,G31+1))</f>
+        <f>IF(G31="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G31+1),入力!$C$86:$C$95,"&gt;="&amp;(G31+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G31+1),入力!$C$86:$C$95,"&gt;="&amp;(G31+1))+1,G31+1))</f>
         <v/>
       </c>
       <c r="S31">
-        <f>IF(R31="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R31),入力!$C$56:$C$65,"&gt;="&amp;(R31))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R31),入力!$C$56:$C$65,"&gt;="&amp;(R31))+1,R31))</f>
+        <f>IF(R31="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R31),入力!$C$86:$C$95,"&gt;="&amp;(R31))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R31),入力!$C$86:$C$95,"&gt;="&amp;(R31))+1,R31))</f>
         <v/>
       </c>
     </row>
@@ -6380,7 +7477,7 @@
         <v/>
       </c>
       <c r="G32" s="31">
-        <f>IF(F32="","",MIN(EOMONTH(F32,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F32),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F32),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F32),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F32),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F32),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F32),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F32),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F32),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F32),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F32)+1)-1,999999)))</f>
+        <f>IF(F32="","",MIN(EOMONTH(F32,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F32),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F32),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F32),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F32),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F32),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F32),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F32),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F32),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F32),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F32)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H32" s="52">
@@ -6415,16 +7512,20 @@
         <f>IF(F32="","",M32-N32)</f>
         <v/>
       </c>
+      <c r="P32" s="69">
+        <f>IF(F32="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B32,C32,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q32">
         <f>IF(F32="","",IF(COUNTIFS($B$6:B32,B32,$C$6:C32,C32,$E$6:E32,E32)=1,MAX($Q$5:Q31)+1,""))</f>
         <v/>
       </c>
       <c r="R32">
-        <f>IF(G32="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G32+1),入力!$C$56:$C$65,"&gt;="&amp;(G32+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G32+1),入力!$C$56:$C$65,"&gt;="&amp;(G32+1))+1,G32+1))</f>
+        <f>IF(G32="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G32+1),入力!$C$86:$C$95,"&gt;="&amp;(G32+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G32+1),入力!$C$86:$C$95,"&gt;="&amp;(G32+1))+1,G32+1))</f>
         <v/>
       </c>
       <c r="S32">
-        <f>IF(R32="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R32),入力!$C$56:$C$65,"&gt;="&amp;(R32))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R32),入力!$C$56:$C$65,"&gt;="&amp;(R32))+1,R32))</f>
+        <f>IF(R32="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R32),入力!$C$86:$C$95,"&gt;="&amp;(R32))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R32),入力!$C$86:$C$95,"&gt;="&amp;(R32))+1,R32))</f>
         <v/>
       </c>
     </row>
@@ -6454,7 +7555,7 @@
         <v/>
       </c>
       <c r="G33" s="31">
-        <f>IF(F33="","",MIN(EOMONTH(F33,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F33),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F33),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F33),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F33),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F33),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F33),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F33),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F33),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F33),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F33)+1)-1,999999)))</f>
+        <f>IF(F33="","",MIN(EOMONTH(F33,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F33),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F33),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F33),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F33),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F33),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F33),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F33),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F33),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F33),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F33)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H33" s="52">
@@ -6489,16 +7590,20 @@
         <f>IF(F33="","",M33-N33)</f>
         <v/>
       </c>
+      <c r="P33" s="69">
+        <f>IF(F33="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B33,C33,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q33">
         <f>IF(F33="","",IF(COUNTIFS($B$6:B33,B33,$C$6:C33,C33,$E$6:E33,E33)=1,MAX($Q$5:Q32)+1,""))</f>
         <v/>
       </c>
       <c r="R33">
-        <f>IF(G33="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G33+1),入力!$C$56:$C$65,"&gt;="&amp;(G33+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G33+1),入力!$C$56:$C$65,"&gt;="&amp;(G33+1))+1,G33+1))</f>
+        <f>IF(G33="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G33+1),入力!$C$86:$C$95,"&gt;="&amp;(G33+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G33+1),入力!$C$86:$C$95,"&gt;="&amp;(G33+1))+1,G33+1))</f>
         <v/>
       </c>
       <c r="S33">
-        <f>IF(R33="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R33),入力!$C$56:$C$65,"&gt;="&amp;(R33))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R33),入力!$C$56:$C$65,"&gt;="&amp;(R33))+1,R33))</f>
+        <f>IF(R33="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R33),入力!$C$86:$C$95,"&gt;="&amp;(R33))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R33),入力!$C$86:$C$95,"&gt;="&amp;(R33))+1,R33))</f>
         <v/>
       </c>
     </row>
@@ -6528,7 +7633,7 @@
         <v/>
       </c>
       <c r="G34" s="31">
-        <f>IF(F34="","",MIN(EOMONTH(F34,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F34),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F34),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F34),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F34),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F34),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F34),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F34),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F34),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F34),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F34)+1)-1,999999)))</f>
+        <f>IF(F34="","",MIN(EOMONTH(F34,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F34),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F34),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F34),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F34),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F34),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F34),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F34),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F34),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F34),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F34)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H34" s="52">
@@ -6563,16 +7668,20 @@
         <f>IF(F34="","",M34-N34)</f>
         <v/>
       </c>
+      <c r="P34" s="69">
+        <f>IF(F34="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B34,C34,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q34">
         <f>IF(F34="","",IF(COUNTIFS($B$6:B34,B34,$C$6:C34,C34,$E$6:E34,E34)=1,MAX($Q$5:Q33)+1,""))</f>
         <v/>
       </c>
       <c r="R34">
-        <f>IF(G34="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G34+1),入力!$C$56:$C$65,"&gt;="&amp;(G34+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G34+1),入力!$C$56:$C$65,"&gt;="&amp;(G34+1))+1,G34+1))</f>
+        <f>IF(G34="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G34+1),入力!$C$86:$C$95,"&gt;="&amp;(G34+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G34+1),入力!$C$86:$C$95,"&gt;="&amp;(G34+1))+1,G34+1))</f>
         <v/>
       </c>
       <c r="S34">
-        <f>IF(R34="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R34),入力!$C$56:$C$65,"&gt;="&amp;(R34))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R34),入力!$C$56:$C$65,"&gt;="&amp;(R34))+1,R34))</f>
+        <f>IF(R34="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R34),入力!$C$86:$C$95,"&gt;="&amp;(R34))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R34),入力!$C$86:$C$95,"&gt;="&amp;(R34))+1,R34))</f>
         <v/>
       </c>
     </row>
@@ -6602,7 +7711,7 @@
         <v/>
       </c>
       <c r="G35" s="31">
-        <f>IF(F35="","",MIN(EOMONTH(F35,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F35),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F35),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F35),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F35),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F35),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F35),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F35),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F35),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F35),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F35)+1)-1,999999)))</f>
+        <f>IF(F35="","",MIN(EOMONTH(F35,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F35),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F35),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F35),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F35),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F35),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F35),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F35),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F35),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F35),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F35)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H35" s="52">
@@ -6637,16 +7746,20 @@
         <f>IF(F35="","",M35-N35)</f>
         <v/>
       </c>
+      <c r="P35" s="69">
+        <f>IF(F35="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B35,C35,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q35">
         <f>IF(F35="","",IF(COUNTIFS($B$6:B35,B35,$C$6:C35,C35,$E$6:E35,E35)=1,MAX($Q$5:Q34)+1,""))</f>
         <v/>
       </c>
       <c r="R35">
-        <f>IF(G35="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G35+1),入力!$C$56:$C$65,"&gt;="&amp;(G35+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G35+1),入力!$C$56:$C$65,"&gt;="&amp;(G35+1))+1,G35+1))</f>
+        <f>IF(G35="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G35+1),入力!$C$86:$C$95,"&gt;="&amp;(G35+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G35+1),入力!$C$86:$C$95,"&gt;="&amp;(G35+1))+1,G35+1))</f>
         <v/>
       </c>
       <c r="S35">
-        <f>IF(R35="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R35),入力!$C$56:$C$65,"&gt;="&amp;(R35))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R35),入力!$C$56:$C$65,"&gt;="&amp;(R35))+1,R35))</f>
+        <f>IF(R35="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R35),入力!$C$86:$C$95,"&gt;="&amp;(R35))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R35),入力!$C$86:$C$95,"&gt;="&amp;(R35))+1,R35))</f>
         <v/>
       </c>
     </row>
@@ -6676,7 +7789,7 @@
         <v/>
       </c>
       <c r="G36" s="31">
-        <f>IF(F36="","",MIN(EOMONTH(F36,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F36),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F36),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F36),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F36),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F36),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F36),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F36),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F36),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F36),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F36)+1)-1,999999)))</f>
+        <f>IF(F36="","",MIN(EOMONTH(F36,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F36),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F36),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F36),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F36),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F36),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F36),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F36),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F36),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F36),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F36)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H36" s="52">
@@ -6711,16 +7824,20 @@
         <f>IF(F36="","",M36-N36)</f>
         <v/>
       </c>
+      <c r="P36" s="69">
+        <f>IF(F36="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B36,C36,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q36">
         <f>IF(F36="","",IF(COUNTIFS($B$6:B36,B36,$C$6:C36,C36,$E$6:E36,E36)=1,MAX($Q$5:Q35)+1,""))</f>
         <v/>
       </c>
       <c r="R36">
-        <f>IF(G36="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G36+1),入力!$C$56:$C$65,"&gt;="&amp;(G36+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G36+1),入力!$C$56:$C$65,"&gt;="&amp;(G36+1))+1,G36+1))</f>
+        <f>IF(G36="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G36+1),入力!$C$86:$C$95,"&gt;="&amp;(G36+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G36+1),入力!$C$86:$C$95,"&gt;="&amp;(G36+1))+1,G36+1))</f>
         <v/>
       </c>
       <c r="S36">
-        <f>IF(R36="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R36),入力!$C$56:$C$65,"&gt;="&amp;(R36))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R36),入力!$C$56:$C$65,"&gt;="&amp;(R36))+1,R36))</f>
+        <f>IF(R36="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R36),入力!$C$86:$C$95,"&gt;="&amp;(R36))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R36),入力!$C$86:$C$95,"&gt;="&amp;(R36))+1,R36))</f>
         <v/>
       </c>
     </row>
@@ -6750,7 +7867,7 @@
         <v/>
       </c>
       <c r="G37" s="31">
-        <f>IF(F37="","",MIN(EOMONTH(F37,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F37),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F37),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F37),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F37),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F37),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F37),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F37),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F37),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F37),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F37)+1)-1,999999)))</f>
+        <f>IF(F37="","",MIN(EOMONTH(F37,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F37),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F37),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F37),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F37),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F37),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F37),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F37),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F37),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F37),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F37)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H37" s="52">
@@ -6785,16 +7902,20 @@
         <f>IF(F37="","",M37-N37)</f>
         <v/>
       </c>
+      <c r="P37" s="69">
+        <f>IF(F37="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B37,C37,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q37">
         <f>IF(F37="","",IF(COUNTIFS($B$6:B37,B37,$C$6:C37,C37,$E$6:E37,E37)=1,MAX($Q$5:Q36)+1,""))</f>
         <v/>
       </c>
       <c r="R37">
-        <f>IF(G37="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G37+1),入力!$C$56:$C$65,"&gt;="&amp;(G37+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G37+1),入力!$C$56:$C$65,"&gt;="&amp;(G37+1))+1,G37+1))</f>
+        <f>IF(G37="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G37+1),入力!$C$86:$C$95,"&gt;="&amp;(G37+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G37+1),入力!$C$86:$C$95,"&gt;="&amp;(G37+1))+1,G37+1))</f>
         <v/>
       </c>
       <c r="S37">
-        <f>IF(R37="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R37),入力!$C$56:$C$65,"&gt;="&amp;(R37))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R37),入力!$C$56:$C$65,"&gt;="&amp;(R37))+1,R37))</f>
+        <f>IF(R37="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R37),入力!$C$86:$C$95,"&gt;="&amp;(R37))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R37),入力!$C$86:$C$95,"&gt;="&amp;(R37))+1,R37))</f>
         <v/>
       </c>
     </row>
@@ -6824,7 +7945,7 @@
         <v/>
       </c>
       <c r="G38" s="31">
-        <f>IF(F38="","",MIN(EOMONTH(F38,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F38),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F38),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F38),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F38),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F38),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F38),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F38),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F38),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F38),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F38)+1)-1,999999)))</f>
+        <f>IF(F38="","",MIN(EOMONTH(F38,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F38),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F38),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F38),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F38),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F38),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F38),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F38),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F38),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F38),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F38)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H38" s="52">
@@ -6859,16 +7980,20 @@
         <f>IF(F38="","",M38-N38)</f>
         <v/>
       </c>
+      <c r="P38" s="69">
+        <f>IF(F38="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B38,C38,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q38">
         <f>IF(F38="","",IF(COUNTIFS($B$6:B38,B38,$C$6:C38,C38,$E$6:E38,E38)=1,MAX($Q$5:Q37)+1,""))</f>
         <v/>
       </c>
       <c r="R38">
-        <f>IF(G38="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G38+1),入力!$C$56:$C$65,"&gt;="&amp;(G38+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G38+1),入力!$C$56:$C$65,"&gt;="&amp;(G38+1))+1,G38+1))</f>
+        <f>IF(G38="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G38+1),入力!$C$86:$C$95,"&gt;="&amp;(G38+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G38+1),入力!$C$86:$C$95,"&gt;="&amp;(G38+1))+1,G38+1))</f>
         <v/>
       </c>
       <c r="S38">
-        <f>IF(R38="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R38),入力!$C$56:$C$65,"&gt;="&amp;(R38))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R38),入力!$C$56:$C$65,"&gt;="&amp;(R38))+1,R38))</f>
+        <f>IF(R38="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R38),入力!$C$86:$C$95,"&gt;="&amp;(R38))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R38),入力!$C$86:$C$95,"&gt;="&amp;(R38))+1,R38))</f>
         <v/>
       </c>
     </row>
@@ -6898,7 +8023,7 @@
         <v/>
       </c>
       <c r="G39" s="31">
-        <f>IF(F39="","",MIN(EOMONTH(F39,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F39),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F39),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F39),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F39),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F39),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F39),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F39),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F39),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F39),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F39)+1)-1,999999)))</f>
+        <f>IF(F39="","",MIN(EOMONTH(F39,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F39),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F39),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F39),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F39),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F39),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F39),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F39),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F39),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F39),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F39)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H39" s="52">
@@ -6933,16 +8058,20 @@
         <f>IF(F39="","",M39-N39)</f>
         <v/>
       </c>
+      <c r="P39" s="69">
+        <f>IF(F39="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B39,C39,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q39">
         <f>IF(F39="","",IF(COUNTIFS($B$6:B39,B39,$C$6:C39,C39,$E$6:E39,E39)=1,MAX($Q$5:Q38)+1,""))</f>
         <v/>
       </c>
       <c r="R39">
-        <f>IF(G39="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G39+1),入力!$C$56:$C$65,"&gt;="&amp;(G39+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G39+1),入力!$C$56:$C$65,"&gt;="&amp;(G39+1))+1,G39+1))</f>
+        <f>IF(G39="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G39+1),入力!$C$86:$C$95,"&gt;="&amp;(G39+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G39+1),入力!$C$86:$C$95,"&gt;="&amp;(G39+1))+1,G39+1))</f>
         <v/>
       </c>
       <c r="S39">
-        <f>IF(R39="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R39),入力!$C$56:$C$65,"&gt;="&amp;(R39))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R39),入力!$C$56:$C$65,"&gt;="&amp;(R39))+1,R39))</f>
+        <f>IF(R39="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R39),入力!$C$86:$C$95,"&gt;="&amp;(R39))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R39),入力!$C$86:$C$95,"&gt;="&amp;(R39))+1,R39))</f>
         <v/>
       </c>
     </row>
@@ -6972,7 +8101,7 @@
         <v/>
       </c>
       <c r="G40" s="31">
-        <f>IF(F40="","",MIN(EOMONTH(F40,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F40),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F40),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F40),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F40),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F40),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F40),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F40),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F40),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F40),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F40)+1)-1,999999)))</f>
+        <f>IF(F40="","",MIN(EOMONTH(F40,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F40),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F40),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F40),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F40),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F40),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F40),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F40),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F40),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F40),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F40)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H40" s="52">
@@ -7007,16 +8136,20 @@
         <f>IF(F40="","",M40-N40)</f>
         <v/>
       </c>
+      <c r="P40" s="69">
+        <f>IF(F40="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B40,C40,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q40">
         <f>IF(F40="","",IF(COUNTIFS($B$6:B40,B40,$C$6:C40,C40,$E$6:E40,E40)=1,MAX($Q$5:Q39)+1,""))</f>
         <v/>
       </c>
       <c r="R40">
-        <f>IF(G40="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G40+1),入力!$C$56:$C$65,"&gt;="&amp;(G40+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G40+1),入力!$C$56:$C$65,"&gt;="&amp;(G40+1))+1,G40+1))</f>
+        <f>IF(G40="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G40+1),入力!$C$86:$C$95,"&gt;="&amp;(G40+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G40+1),入力!$C$86:$C$95,"&gt;="&amp;(G40+1))+1,G40+1))</f>
         <v/>
       </c>
       <c r="S40">
-        <f>IF(R40="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R40),入力!$C$56:$C$65,"&gt;="&amp;(R40))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R40),入力!$C$56:$C$65,"&gt;="&amp;(R40))+1,R40))</f>
+        <f>IF(R40="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R40),入力!$C$86:$C$95,"&gt;="&amp;(R40))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R40),入力!$C$86:$C$95,"&gt;="&amp;(R40))+1,R40))</f>
         <v/>
       </c>
     </row>
@@ -7046,7 +8179,7 @@
         <v/>
       </c>
       <c r="G41" s="31">
-        <f>IF(F41="","",MIN(EOMONTH(F41,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F41),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F41),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F41),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F41),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F41),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F41),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F41),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F41),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F41),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F41)+1)-1,999999)))</f>
+        <f>IF(F41="","",MIN(EOMONTH(F41,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F41),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F41),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F41),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F41),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F41),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F41),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F41),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F41),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F41),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F41)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H41" s="52">
@@ -7081,16 +8214,20 @@
         <f>IF(F41="","",M41-N41)</f>
         <v/>
       </c>
+      <c r="P41" s="69">
+        <f>IF(F41="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B41,C41,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q41">
         <f>IF(F41="","",IF(COUNTIFS($B$6:B41,B41,$C$6:C41,C41,$E$6:E41,E41)=1,MAX($Q$5:Q40)+1,""))</f>
         <v/>
       </c>
       <c r="R41">
-        <f>IF(G41="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G41+1),入力!$C$56:$C$65,"&gt;="&amp;(G41+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G41+1),入力!$C$56:$C$65,"&gt;="&amp;(G41+1))+1,G41+1))</f>
+        <f>IF(G41="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G41+1),入力!$C$86:$C$95,"&gt;="&amp;(G41+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G41+1),入力!$C$86:$C$95,"&gt;="&amp;(G41+1))+1,G41+1))</f>
         <v/>
       </c>
       <c r="S41">
-        <f>IF(R41="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R41),入力!$C$56:$C$65,"&gt;="&amp;(R41))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R41),入力!$C$56:$C$65,"&gt;="&amp;(R41))+1,R41))</f>
+        <f>IF(R41="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R41),入力!$C$86:$C$95,"&gt;="&amp;(R41))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R41),入力!$C$86:$C$95,"&gt;="&amp;(R41))+1,R41))</f>
         <v/>
       </c>
     </row>
@@ -7120,7 +8257,7 @@
         <v/>
       </c>
       <c r="G42" s="31">
-        <f>IF(F42="","",MIN(EOMONTH(F42,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F42),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F42),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F42),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F42),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F42),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F42),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F42),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F42),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F42),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F42)+1)-1,999999)))</f>
+        <f>IF(F42="","",MIN(EOMONTH(F42,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F42),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F42),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F42),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F42),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F42),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F42),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F42),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F42),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F42),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F42)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H42" s="52">
@@ -7155,16 +8292,20 @@
         <f>IF(F42="","",M42-N42)</f>
         <v/>
       </c>
+      <c r="P42" s="69">
+        <f>IF(F42="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B42,C42,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q42">
         <f>IF(F42="","",IF(COUNTIFS($B$6:B42,B42,$C$6:C42,C42,$E$6:E42,E42)=1,MAX($Q$5:Q41)+1,""))</f>
         <v/>
       </c>
       <c r="R42">
-        <f>IF(G42="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G42+1),入力!$C$56:$C$65,"&gt;="&amp;(G42+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G42+1),入力!$C$56:$C$65,"&gt;="&amp;(G42+1))+1,G42+1))</f>
+        <f>IF(G42="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G42+1),入力!$C$86:$C$95,"&gt;="&amp;(G42+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G42+1),入力!$C$86:$C$95,"&gt;="&amp;(G42+1))+1,G42+1))</f>
         <v/>
       </c>
       <c r="S42">
-        <f>IF(R42="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R42),入力!$C$56:$C$65,"&gt;="&amp;(R42))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R42),入力!$C$56:$C$65,"&gt;="&amp;(R42))+1,R42))</f>
+        <f>IF(R42="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R42),入力!$C$86:$C$95,"&gt;="&amp;(R42))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R42),入力!$C$86:$C$95,"&gt;="&amp;(R42))+1,R42))</f>
         <v/>
       </c>
     </row>
@@ -7194,7 +8335,7 @@
         <v/>
       </c>
       <c r="G43" s="31">
-        <f>IF(F43="","",MIN(EOMONTH(F43,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F43),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F43),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F43),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F43),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F43),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F43),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F43),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F43),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F43),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F43)+1)-1,999999)))</f>
+        <f>IF(F43="","",MIN(EOMONTH(F43,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F43),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F43),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F43),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F43),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F43),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F43),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F43),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F43),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F43),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F43)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H43" s="52">
@@ -7229,16 +8370,20 @@
         <f>IF(F43="","",M43-N43)</f>
         <v/>
       </c>
+      <c r="P43" s="69">
+        <f>IF(F43="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B43,C43,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q43">
         <f>IF(F43="","",IF(COUNTIFS($B$6:B43,B43,$C$6:C43,C43,$E$6:E43,E43)=1,MAX($Q$5:Q42)+1,""))</f>
         <v/>
       </c>
       <c r="R43">
-        <f>IF(G43="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G43+1),入力!$C$56:$C$65,"&gt;="&amp;(G43+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G43+1),入力!$C$56:$C$65,"&gt;="&amp;(G43+1))+1,G43+1))</f>
+        <f>IF(G43="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G43+1),入力!$C$86:$C$95,"&gt;="&amp;(G43+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G43+1),入力!$C$86:$C$95,"&gt;="&amp;(G43+1))+1,G43+1))</f>
         <v/>
       </c>
       <c r="S43">
-        <f>IF(R43="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R43),入力!$C$56:$C$65,"&gt;="&amp;(R43))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R43),入力!$C$56:$C$65,"&gt;="&amp;(R43))+1,R43))</f>
+        <f>IF(R43="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R43),入力!$C$86:$C$95,"&gt;="&amp;(R43))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R43),入力!$C$86:$C$95,"&gt;="&amp;(R43))+1,R43))</f>
         <v/>
       </c>
     </row>
@@ -7268,7 +8413,7 @@
         <v/>
       </c>
       <c r="G44" s="31">
-        <f>IF(F44="","",MIN(EOMONTH(F44,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F44),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F44),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F44),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F44),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F44),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F44),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F44),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F44),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F44),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F44)+1)-1,999999)))</f>
+        <f>IF(F44="","",MIN(EOMONTH(F44,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F44),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F44),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F44),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F44),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F44),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F44),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F44),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F44),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F44),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F44)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H44" s="52">
@@ -7303,16 +8448,20 @@
         <f>IF(F44="","",M44-N44)</f>
         <v/>
       </c>
+      <c r="P44" s="69">
+        <f>IF(F44="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B44,C44,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q44">
         <f>IF(F44="","",IF(COUNTIFS($B$6:B44,B44,$C$6:C44,C44,$E$6:E44,E44)=1,MAX($Q$5:Q43)+1,""))</f>
         <v/>
       </c>
       <c r="R44">
-        <f>IF(G44="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G44+1),入力!$C$56:$C$65,"&gt;="&amp;(G44+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G44+1),入力!$C$56:$C$65,"&gt;="&amp;(G44+1))+1,G44+1))</f>
+        <f>IF(G44="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G44+1),入力!$C$86:$C$95,"&gt;="&amp;(G44+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G44+1),入力!$C$86:$C$95,"&gt;="&amp;(G44+1))+1,G44+1))</f>
         <v/>
       </c>
       <c r="S44">
-        <f>IF(R44="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R44),入力!$C$56:$C$65,"&gt;="&amp;(R44))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R44),入力!$C$56:$C$65,"&gt;="&amp;(R44))+1,R44))</f>
+        <f>IF(R44="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R44),入力!$C$86:$C$95,"&gt;="&amp;(R44))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R44),入力!$C$86:$C$95,"&gt;="&amp;(R44))+1,R44))</f>
         <v/>
       </c>
     </row>
@@ -7342,7 +8491,7 @@
         <v/>
       </c>
       <c r="G45" s="31">
-        <f>IF(F45="","",MIN(EOMONTH(F45,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F45),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F45),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F45),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F45),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F45),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F45),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F45),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F45),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F45),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F45)+1)-1,999999)))</f>
+        <f>IF(F45="","",MIN(EOMONTH(F45,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F45),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F45),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F45),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F45),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F45),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F45),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F45),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F45),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F45),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F45)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H45" s="52">
@@ -7377,16 +8526,20 @@
         <f>IF(F45="","",M45-N45)</f>
         <v/>
       </c>
+      <c r="P45" s="69">
+        <f>IF(F45="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B45,C45,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q45">
         <f>IF(F45="","",IF(COUNTIFS($B$6:B45,B45,$C$6:C45,C45,$E$6:E45,E45)=1,MAX($Q$5:Q44)+1,""))</f>
         <v/>
       </c>
       <c r="R45">
-        <f>IF(G45="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G45+1),入力!$C$56:$C$65,"&gt;="&amp;(G45+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G45+1),入力!$C$56:$C$65,"&gt;="&amp;(G45+1))+1,G45+1))</f>
+        <f>IF(G45="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G45+1),入力!$C$86:$C$95,"&gt;="&amp;(G45+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G45+1),入力!$C$86:$C$95,"&gt;="&amp;(G45+1))+1,G45+1))</f>
         <v/>
       </c>
       <c r="S45">
-        <f>IF(R45="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R45),入力!$C$56:$C$65,"&gt;="&amp;(R45))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R45),入力!$C$56:$C$65,"&gt;="&amp;(R45))+1,R45))</f>
+        <f>IF(R45="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R45),入力!$C$86:$C$95,"&gt;="&amp;(R45))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R45),入力!$C$86:$C$95,"&gt;="&amp;(R45))+1,R45))</f>
         <v/>
       </c>
     </row>
@@ -7416,7 +8569,7 @@
         <v/>
       </c>
       <c r="G46" s="31">
-        <f>IF(F46="","",MIN(EOMONTH(F46,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F46),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F46),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F46),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F46),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F46),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F46),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F46),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F46),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F46),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F46)+1)-1,999999)))</f>
+        <f>IF(F46="","",MIN(EOMONTH(F46,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F46),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F46),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F46),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F46),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F46),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F46),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F46),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F46),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F46),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F46)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H46" s="52">
@@ -7451,16 +8604,20 @@
         <f>IF(F46="","",M46-N46)</f>
         <v/>
       </c>
+      <c r="P46" s="69">
+        <f>IF(F46="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B46,C46,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q46">
         <f>IF(F46="","",IF(COUNTIFS($B$6:B46,B46,$C$6:C46,C46,$E$6:E46,E46)=1,MAX($Q$5:Q45)+1,""))</f>
         <v/>
       </c>
       <c r="R46">
-        <f>IF(G46="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G46+1),入力!$C$56:$C$65,"&gt;="&amp;(G46+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G46+1),入力!$C$56:$C$65,"&gt;="&amp;(G46+1))+1,G46+1))</f>
+        <f>IF(G46="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G46+1),入力!$C$86:$C$95,"&gt;="&amp;(G46+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G46+1),入力!$C$86:$C$95,"&gt;="&amp;(G46+1))+1,G46+1))</f>
         <v/>
       </c>
       <c r="S46">
-        <f>IF(R46="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R46),入力!$C$56:$C$65,"&gt;="&amp;(R46))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R46),入力!$C$56:$C$65,"&gt;="&amp;(R46))+1,R46))</f>
+        <f>IF(R46="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R46),入力!$C$86:$C$95,"&gt;="&amp;(R46))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R46),入力!$C$86:$C$95,"&gt;="&amp;(R46))+1,R46))</f>
         <v/>
       </c>
     </row>
@@ -7490,7 +8647,7 @@
         <v/>
       </c>
       <c r="G47" s="31">
-        <f>IF(F47="","",MIN(EOMONTH(F47,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F47),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F47),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F47),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F47),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F47),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F47),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F47),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F47),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F47),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F47)+1)-1,999999)))</f>
+        <f>IF(F47="","",MIN(EOMONTH(F47,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F47),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F47),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F47),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F47),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F47),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F47),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F47),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F47),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F47),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F47)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H47" s="52">
@@ -7525,16 +8682,20 @@
         <f>IF(F47="","",M47-N47)</f>
         <v/>
       </c>
+      <c r="P47" s="69">
+        <f>IF(F47="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B47,C47,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q47">
         <f>IF(F47="","",IF(COUNTIFS($B$6:B47,B47,$C$6:C47,C47,$E$6:E47,E47)=1,MAX($Q$5:Q46)+1,""))</f>
         <v/>
       </c>
       <c r="R47">
-        <f>IF(G47="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G47+1),入力!$C$56:$C$65,"&gt;="&amp;(G47+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G47+1),入力!$C$56:$C$65,"&gt;="&amp;(G47+1))+1,G47+1))</f>
+        <f>IF(G47="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G47+1),入力!$C$86:$C$95,"&gt;="&amp;(G47+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G47+1),入力!$C$86:$C$95,"&gt;="&amp;(G47+1))+1,G47+1))</f>
         <v/>
       </c>
       <c r="S47">
-        <f>IF(R47="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R47),入力!$C$56:$C$65,"&gt;="&amp;(R47))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R47),入力!$C$56:$C$65,"&gt;="&amp;(R47))+1,R47))</f>
+        <f>IF(R47="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R47),入力!$C$86:$C$95,"&gt;="&amp;(R47))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R47),入力!$C$86:$C$95,"&gt;="&amp;(R47))+1,R47))</f>
         <v/>
       </c>
     </row>
@@ -7564,7 +8725,7 @@
         <v/>
       </c>
       <c r="G48" s="31">
-        <f>IF(F48="","",MIN(EOMONTH(F48,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F48),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F48),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F48),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F48),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F48),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F48),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F48),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F48),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F48),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F48)+1)-1,999999)))</f>
+        <f>IF(F48="","",MIN(EOMONTH(F48,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F48),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F48),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F48),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F48),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F48),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F48),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F48),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F48),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F48),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F48)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H48" s="52">
@@ -7599,16 +8760,20 @@
         <f>IF(F48="","",M48-N48)</f>
         <v/>
       </c>
+      <c r="P48" s="69">
+        <f>IF(F48="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B48,C48,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q48">
         <f>IF(F48="","",IF(COUNTIFS($B$6:B48,B48,$C$6:C48,C48,$E$6:E48,E48)=1,MAX($Q$5:Q47)+1,""))</f>
         <v/>
       </c>
       <c r="R48">
-        <f>IF(G48="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G48+1),入力!$C$56:$C$65,"&gt;="&amp;(G48+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G48+1),入力!$C$56:$C$65,"&gt;="&amp;(G48+1))+1,G48+1))</f>
+        <f>IF(G48="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G48+1),入力!$C$86:$C$95,"&gt;="&amp;(G48+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G48+1),入力!$C$86:$C$95,"&gt;="&amp;(G48+1))+1,G48+1))</f>
         <v/>
       </c>
       <c r="S48">
-        <f>IF(R48="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R48),入力!$C$56:$C$65,"&gt;="&amp;(R48))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R48),入力!$C$56:$C$65,"&gt;="&amp;(R48))+1,R48))</f>
+        <f>IF(R48="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R48),入力!$C$86:$C$95,"&gt;="&amp;(R48))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R48),入力!$C$86:$C$95,"&gt;="&amp;(R48))+1,R48))</f>
         <v/>
       </c>
     </row>
@@ -7638,7 +8803,7 @@
         <v/>
       </c>
       <c r="G49" s="31">
-        <f>IF(F49="","",MIN(EOMONTH(F49,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F49),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F49),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F49),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F49),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F49),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F49),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F49),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F49),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F49),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F49)+1)-1,999999)))</f>
+        <f>IF(F49="","",MIN(EOMONTH(F49,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F49),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F49),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F49),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F49),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F49),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F49),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F49),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F49),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F49),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F49)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H49" s="52">
@@ -7673,16 +8838,20 @@
         <f>IF(F49="","",M49-N49)</f>
         <v/>
       </c>
+      <c r="P49" s="69">
+        <f>IF(F49="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B49,C49,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q49">
         <f>IF(F49="","",IF(COUNTIFS($B$6:B49,B49,$C$6:C49,C49,$E$6:E49,E49)=1,MAX($Q$5:Q48)+1,""))</f>
         <v/>
       </c>
       <c r="R49">
-        <f>IF(G49="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G49+1),入力!$C$56:$C$65,"&gt;="&amp;(G49+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G49+1),入力!$C$56:$C$65,"&gt;="&amp;(G49+1))+1,G49+1))</f>
+        <f>IF(G49="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G49+1),入力!$C$86:$C$95,"&gt;="&amp;(G49+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G49+1),入力!$C$86:$C$95,"&gt;="&amp;(G49+1))+1,G49+1))</f>
         <v/>
       </c>
       <c r="S49">
-        <f>IF(R49="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R49),入力!$C$56:$C$65,"&gt;="&amp;(R49))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R49),入力!$C$56:$C$65,"&gt;="&amp;(R49))+1,R49))</f>
+        <f>IF(R49="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R49),入力!$C$86:$C$95,"&gt;="&amp;(R49))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R49),入力!$C$86:$C$95,"&gt;="&amp;(R49))+1,R49))</f>
         <v/>
       </c>
     </row>
@@ -7712,7 +8881,7 @@
         <v/>
       </c>
       <c r="G50" s="31">
-        <f>IF(F50="","",MIN(EOMONTH(F50,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F50),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F50),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F50),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F50),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F50),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F50),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F50),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F50),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F50),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F50)+1)-1,999999)))</f>
+        <f>IF(F50="","",MIN(EOMONTH(F50,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F50),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F50),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F50),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F50),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F50),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F50),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F50),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F50),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F50),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F50)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H50" s="52">
@@ -7747,16 +8916,20 @@
         <f>IF(F50="","",M50-N50)</f>
         <v/>
       </c>
+      <c r="P50" s="69">
+        <f>IF(F50="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B50,C50,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q50">
         <f>IF(F50="","",IF(COUNTIFS($B$6:B50,B50,$C$6:C50,C50,$E$6:E50,E50)=1,MAX($Q$5:Q49)+1,""))</f>
         <v/>
       </c>
       <c r="R50">
-        <f>IF(G50="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G50+1),入力!$C$56:$C$65,"&gt;="&amp;(G50+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G50+1),入力!$C$56:$C$65,"&gt;="&amp;(G50+1))+1,G50+1))</f>
+        <f>IF(G50="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G50+1),入力!$C$86:$C$95,"&gt;="&amp;(G50+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G50+1),入力!$C$86:$C$95,"&gt;="&amp;(G50+1))+1,G50+1))</f>
         <v/>
       </c>
       <c r="S50">
-        <f>IF(R50="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R50),入力!$C$56:$C$65,"&gt;="&amp;(R50))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R50),入力!$C$56:$C$65,"&gt;="&amp;(R50))+1,R50))</f>
+        <f>IF(R50="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R50),入力!$C$86:$C$95,"&gt;="&amp;(R50))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R50),入力!$C$86:$C$95,"&gt;="&amp;(R50))+1,R50))</f>
         <v/>
       </c>
     </row>
@@ -7786,7 +8959,7 @@
         <v/>
       </c>
       <c r="G51" s="31">
-        <f>IF(F51="","",MIN(EOMONTH(F51,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F51),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F51),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F51),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F51),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F51),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F51),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F51),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F51),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F51),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F51)+1)-1,999999)))</f>
+        <f>IF(F51="","",MIN(EOMONTH(F51,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F51),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F51),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F51),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F51),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F51),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F51),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F51),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F51),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F51),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F51)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H51" s="52">
@@ -7821,16 +8994,20 @@
         <f>IF(F51="","",M51-N51)</f>
         <v/>
       </c>
+      <c r="P51" s="69">
+        <f>IF(F51="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B51,C51,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q51">
         <f>IF(F51="","",IF(COUNTIFS($B$6:B51,B51,$C$6:C51,C51,$E$6:E51,E51)=1,MAX($Q$5:Q50)+1,""))</f>
         <v/>
       </c>
       <c r="R51">
-        <f>IF(G51="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G51+1),入力!$C$56:$C$65,"&gt;="&amp;(G51+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G51+1),入力!$C$56:$C$65,"&gt;="&amp;(G51+1))+1,G51+1))</f>
+        <f>IF(G51="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G51+1),入力!$C$86:$C$95,"&gt;="&amp;(G51+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G51+1),入力!$C$86:$C$95,"&gt;="&amp;(G51+1))+1,G51+1))</f>
         <v/>
       </c>
       <c r="S51">
-        <f>IF(R51="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R51),入力!$C$56:$C$65,"&gt;="&amp;(R51))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R51),入力!$C$56:$C$65,"&gt;="&amp;(R51))+1,R51))</f>
+        <f>IF(R51="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R51),入力!$C$86:$C$95,"&gt;="&amp;(R51))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R51),入力!$C$86:$C$95,"&gt;="&amp;(R51))+1,R51))</f>
         <v/>
       </c>
     </row>
@@ -7860,7 +9037,7 @@
         <v/>
       </c>
       <c r="G52" s="31">
-        <f>IF(F52="","",MIN(EOMONTH(F52,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F52),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F52),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F52),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F52),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F52),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F52),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F52),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F52),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F52),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F52)+1)-1,999999)))</f>
+        <f>IF(F52="","",MIN(EOMONTH(F52,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F52),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F52),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F52),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F52),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F52),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F52),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F52),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F52),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F52),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F52)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H52" s="52">
@@ -7895,16 +9072,20 @@
         <f>IF(F52="","",M52-N52)</f>
         <v/>
       </c>
+      <c r="P52" s="69">
+        <f>IF(F52="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B52,C52,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q52">
         <f>IF(F52="","",IF(COUNTIFS($B$6:B52,B52,$C$6:C52,C52,$E$6:E52,E52)=1,MAX($Q$5:Q51)+1,""))</f>
         <v/>
       </c>
       <c r="R52">
-        <f>IF(G52="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G52+1),入力!$C$56:$C$65,"&gt;="&amp;(G52+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G52+1),入力!$C$56:$C$65,"&gt;="&amp;(G52+1))+1,G52+1))</f>
+        <f>IF(G52="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G52+1),入力!$C$86:$C$95,"&gt;="&amp;(G52+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G52+1),入力!$C$86:$C$95,"&gt;="&amp;(G52+1))+1,G52+1))</f>
         <v/>
       </c>
       <c r="S52">
-        <f>IF(R52="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R52),入力!$C$56:$C$65,"&gt;="&amp;(R52))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R52),入力!$C$56:$C$65,"&gt;="&amp;(R52))+1,R52))</f>
+        <f>IF(R52="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R52),入力!$C$86:$C$95,"&gt;="&amp;(R52))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R52),入力!$C$86:$C$95,"&gt;="&amp;(R52))+1,R52))</f>
         <v/>
       </c>
     </row>
@@ -7934,7 +9115,7 @@
         <v/>
       </c>
       <c r="G53" s="31">
-        <f>IF(F53="","",MIN(EOMONTH(F53,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F53),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F53),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F53),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F53),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F53),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F53),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F53),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F53),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F53),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$56:$B$65,COUNTIF(入力!$B$56:$B$65,"&lt;="&amp;F53)+1)-1,999999)))</f>
+        <f>IF(F53="","",MIN(EOMONTH(F53,0),入力!$J$9,IF(AND(入力!$B$13&lt;&gt;"",入力!$B$13&gt;F53),入力!$B$13-1,999999),IF(AND(入力!$B$14&lt;&gt;"",入力!$B$14&gt;F53),入力!$B$14-1,999999),IF(AND(入力!$B$15&lt;&gt;"",入力!$B$15&gt;F53),入力!$B$15-1,999999),IF(AND(入力!$B$16&lt;&gt;"",入力!$B$16&gt;F53),入力!$B$16-1,999999),IF(AND(入力!$B$17&lt;&gt;"",入力!$B$17&gt;F53),入力!$B$17-1,999999),IF(AND(入力!$B$18&lt;&gt;"",入力!$B$18&gt;F53),入力!$B$18-1,999999),IF(AND(入力!$B$19&lt;&gt;"",入力!$B$19&gt;F53),入力!$B$19-1,999999),IF(AND(入力!$B$20&lt;&gt;"",入力!$B$20&gt;F53),入力!$B$20-1,999999),IF(AND(入力!$J$7&lt;&gt;"",入力!$J$7&gt;F53),入力!$J$7-1,999999),IFERROR(SMALL(入力!$B$86:$B$95,COUNTIF(入力!$B$86:$B$95,"&lt;="&amp;F53)+1)-1,999999)))</f>
         <v/>
       </c>
       <c r="H53" s="52">
@@ -7969,16 +9150,20 @@
         <f>IF(F53="","",M53-N53)</f>
         <v/>
       </c>
+      <c r="P53" s="69">
+        <f>IF(F53="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B53,C53,1),入力!$A$37:$A$78,0)),""))</f>
+        <v/>
+      </c>
       <c r="Q53">
         <f>IF(F53="","",IF(COUNTIFS($B$6:B53,B53,$C$6:C53,C53,$E$6:E53,E53)=1,MAX($Q$5:Q52)+1,""))</f>
         <v/>
       </c>
       <c r="R53">
-        <f>IF(G53="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(G53+1),入力!$C$56:$C$65,"&gt;="&amp;(G53+1))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(G53+1),入力!$C$56:$C$65,"&gt;="&amp;(G53+1))+1,G53+1))</f>
+        <f>IF(G53="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(G53+1),入力!$C$86:$C$95,"&gt;="&amp;(G53+1))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(G53+1),入力!$C$86:$C$95,"&gt;="&amp;(G53+1))+1,G53+1))</f>
         <v/>
       </c>
       <c r="S53">
-        <f>IF(R53="","",IF(COUNTIFS(入力!$B$56:$B$65,"&lt;="&amp;(R53),入力!$C$56:$C$65,"&gt;="&amp;(R53))&gt;0,SUMIFS(入力!$C$56:$C$65,入力!$B$56:$B$65,"&lt;="&amp;(R53),入力!$C$56:$C$65,"&gt;="&amp;(R53))+1,R53))</f>
+        <f>IF(R53="","",IF(COUNTIFS(入力!$B$86:$B$95,"&lt;="&amp;(R53),入力!$C$86:$C$95,"&gt;="&amp;(R53))&gt;0,SUMIFS(入力!$C$86:$C$95,入力!$B$86:$B$95,"&lt;="&amp;(R53),入力!$C$86:$C$95,"&gt;="&amp;(R53))+1,R53))</f>
         <v/>
       </c>
     </row>
@@ -8169,7 +9354,14 @@
     <row r="71">
       <c r="A71" s="40" t="inlineStr">
         <is>
-          <t>・出勤期間（入力シート）がある場合は、その期間を算定から除き、法定末日・附加開始日・附加末日・最終日を、出勤した日数（暦日）だけ後ろにずらします。</t>
+          <t>・出勤期間（入力シート）がある場合は、その期間を算定から除き、法定末日・附加開始日・附加末日・最終日を、出勤した分（丸ごと1か月は1か月、残りは土日を除く日数）だけ後ろにずらします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="40" t="inlineStr">
+        <is>
+          <t>・P列「参考」は、その月の標準報酬月額から試算した日額です。月ごとの比較用で、算定（B列）には使いません。</t>
         </is>
       </c>
     </row>
@@ -8237,7 +9429,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="66">
+      <c r="A2" s="70">
         <f>DATE(YEAR($G$4),MONTH($G$4),1)</f>
         <v/>
       </c>
@@ -8249,7 +9441,7 @@
         <f>NETWORKDAYS(A2,EOMONTH(A2,0))</f>
         <v/>
       </c>
-      <c r="D2" s="67">
+      <c r="D2" s="71">
         <f>IF(ISNUMBER(MATCH(A2,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
@@ -8260,7 +9452,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="66">
+      <c r="A3" s="70">
         <f>EDATE(A2,1)</f>
         <v/>
       </c>
@@ -8272,7 +9464,7 @@
         <f>NETWORKDAYS(A3,EOMONTH(A3,0))</f>
         <v/>
       </c>
-      <c r="D3" s="67">
+      <c r="D3" s="71">
         <f>IF(ISNUMBER(MATCH(A3,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
@@ -8283,7 +9475,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="66">
+      <c r="A4" s="70">
         <f>EDATE(A3,1)</f>
         <v/>
       </c>
@@ -8295,7 +9487,7 @@
         <f>NETWORKDAYS(A4,EOMONTH(A4,0))</f>
         <v/>
       </c>
-      <c r="D4" s="67">
+      <c r="D4" s="71">
         <f>IF(ISNUMBER(MATCH(A4,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
@@ -8304,7 +9496,7 @@
           <t>作成の開始月</t>
         </is>
       </c>
-      <c r="G4" s="68" t="n">
+      <c r="G4" s="72" t="n">
         <v>43831</v>
       </c>
       <c r="H4" s="11" t="inlineStr">
@@ -8314,7 +9506,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="66">
+      <c r="A5" s="70">
         <f>EDATE(A4,1)</f>
         <v/>
       </c>
@@ -8326,13 +9518,13 @@
         <f>NETWORKDAYS(A5,EOMONTH(A5,0))</f>
         <v/>
       </c>
-      <c r="D5" s="67">
+      <c r="D5" s="71">
         <f>IF(ISNUMBER(MATCH(A5,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="66">
+      <c r="A6" s="70">
         <f>EDATE(A5,1)</f>
         <v/>
       </c>
@@ -8344,7 +9536,7 @@
         <f>NETWORKDAYS(A6,EOMONTH(A6,0))</f>
         <v/>
       </c>
-      <c r="D6" s="67">
+      <c r="D6" s="71">
         <f>IF(ISNUMBER(MATCH(A6,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
@@ -8355,7 +9547,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="66">
+      <c r="A7" s="70">
         <f>EDATE(A6,1)</f>
         <v/>
       </c>
@@ -8367,7 +9559,7 @@
         <f>NETWORKDAYS(A7,EOMONTH(A7,0))</f>
         <v/>
       </c>
-      <c r="D7" s="67">
+      <c r="D7" s="71">
         <f>IF(ISNUMBER(MATCH(A7,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
@@ -8383,7 +9575,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="66">
+      <c r="A8" s="70">
         <f>EDATE(A7,1)</f>
         <v/>
       </c>
@@ -8395,19 +9587,19 @@
         <f>NETWORKDAYS(A8,EOMONTH(A8,0))</f>
         <v/>
       </c>
-      <c r="D8" s="67">
+      <c r="D8" s="71">
         <f>IF(ISNUMBER(MATCH(A8,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F8" s="68" t="n">
+      <c r="F8" s="72" t="n">
         <v>44531</v>
       </c>
-      <c r="G8" s="69" t="n">
+      <c r="G8" s="73" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="66">
+      <c r="A9" s="70">
         <f>EDATE(A8,1)</f>
         <v/>
       </c>
@@ -8419,15 +9611,15 @@
         <f>NETWORKDAYS(A9,EOMONTH(A9,0))</f>
         <v/>
       </c>
-      <c r="D9" s="67">
+      <c r="D9" s="71">
         <f>IF(ISNUMBER(MATCH(A9,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F9" s="68" t="n"/>
-      <c r="G9" s="69" t="n"/>
+      <c r="F9" s="72" t="n"/>
+      <c r="G9" s="73" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="66">
+      <c r="A10" s="70">
         <f>EDATE(A9,1)</f>
         <v/>
       </c>
@@ -8439,15 +9631,15 @@
         <f>NETWORKDAYS(A10,EOMONTH(A10,0))</f>
         <v/>
       </c>
-      <c r="D10" s="67">
+      <c r="D10" s="71">
         <f>IF(ISNUMBER(MATCH(A10,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F10" s="68" t="n"/>
-      <c r="G10" s="69" t="n"/>
+      <c r="F10" s="72" t="n"/>
+      <c r="G10" s="73" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="66">
+      <c r="A11" s="70">
         <f>EDATE(A10,1)</f>
         <v/>
       </c>
@@ -8459,15 +9651,15 @@
         <f>NETWORKDAYS(A11,EOMONTH(A11,0))</f>
         <v/>
       </c>
-      <c r="D11" s="67">
+      <c r="D11" s="71">
         <f>IF(ISNUMBER(MATCH(A11,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F11" s="68" t="n"/>
-      <c r="G11" s="69" t="n"/>
+      <c r="F11" s="72" t="n"/>
+      <c r="G11" s="73" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="66">
+      <c r="A12" s="70">
         <f>EDATE(A11,1)</f>
         <v/>
       </c>
@@ -8479,15 +9671,15 @@
         <f>NETWORKDAYS(A12,EOMONTH(A12,0))</f>
         <v/>
       </c>
-      <c r="D12" s="67">
+      <c r="D12" s="71">
         <f>IF(ISNUMBER(MATCH(A12,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F12" s="68" t="n"/>
-      <c r="G12" s="69" t="n"/>
+      <c r="F12" s="72" t="n"/>
+      <c r="G12" s="73" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="66">
+      <c r="A13" s="70">
         <f>EDATE(A12,1)</f>
         <v/>
       </c>
@@ -8499,15 +9691,15 @@
         <f>NETWORKDAYS(A13,EOMONTH(A13,0))</f>
         <v/>
       </c>
-      <c r="D13" s="67">
+      <c r="D13" s="71">
         <f>IF(ISNUMBER(MATCH(A13,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F13" s="68" t="n"/>
-      <c r="G13" s="69" t="n"/>
+      <c r="F13" s="72" t="n"/>
+      <c r="G13" s="73" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="66">
+      <c r="A14" s="70">
         <f>EDATE(A13,1)</f>
         <v/>
       </c>
@@ -8519,15 +9711,15 @@
         <f>NETWORKDAYS(A14,EOMONTH(A14,0))</f>
         <v/>
       </c>
-      <c r="D14" s="67">
+      <c r="D14" s="71">
         <f>IF(ISNUMBER(MATCH(A14,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F14" s="68" t="n"/>
-      <c r="G14" s="69" t="n"/>
+      <c r="F14" s="72" t="n"/>
+      <c r="G14" s="73" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="66">
+      <c r="A15" s="70">
         <f>EDATE(A14,1)</f>
         <v/>
       </c>
@@ -8539,15 +9731,15 @@
         <f>NETWORKDAYS(A15,EOMONTH(A15,0))</f>
         <v/>
       </c>
-      <c r="D15" s="67">
+      <c r="D15" s="71">
         <f>IF(ISNUMBER(MATCH(A15,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F15" s="68" t="n"/>
-      <c r="G15" s="69" t="n"/>
+      <c r="F15" s="72" t="n"/>
+      <c r="G15" s="73" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="66">
+      <c r="A16" s="70">
         <f>EDATE(A15,1)</f>
         <v/>
       </c>
@@ -8559,15 +9751,15 @@
         <f>NETWORKDAYS(A16,EOMONTH(A16,0))</f>
         <v/>
       </c>
-      <c r="D16" s="67">
+      <c r="D16" s="71">
         <f>IF(ISNUMBER(MATCH(A16,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F16" s="68" t="n"/>
-      <c r="G16" s="69" t="n"/>
+      <c r="F16" s="72" t="n"/>
+      <c r="G16" s="73" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="66">
+      <c r="A17" s="70">
         <f>EDATE(A16,1)</f>
         <v/>
       </c>
@@ -8579,15 +9771,15 @@
         <f>NETWORKDAYS(A17,EOMONTH(A17,0))</f>
         <v/>
       </c>
-      <c r="D17" s="67">
+      <c r="D17" s="71">
         <f>IF(ISNUMBER(MATCH(A17,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F17" s="68" t="n"/>
-      <c r="G17" s="69" t="n"/>
+      <c r="F17" s="72" t="n"/>
+      <c r="G17" s="73" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="66">
+      <c r="A18" s="70">
         <f>EDATE(A17,1)</f>
         <v/>
       </c>
@@ -8599,15 +9791,15 @@
         <f>NETWORKDAYS(A18,EOMONTH(A18,0))</f>
         <v/>
       </c>
-      <c r="D18" s="67">
+      <c r="D18" s="71">
         <f>IF(ISNUMBER(MATCH(A18,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F18" s="68" t="n"/>
-      <c r="G18" s="69" t="n"/>
+      <c r="F18" s="72" t="n"/>
+      <c r="G18" s="73" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="66">
+      <c r="A19" s="70">
         <f>EDATE(A18,1)</f>
         <v/>
       </c>
@@ -8619,15 +9811,15 @@
         <f>NETWORKDAYS(A19,EOMONTH(A19,0))</f>
         <v/>
       </c>
-      <c r="D19" s="67">
+      <c r="D19" s="71">
         <f>IF(ISNUMBER(MATCH(A19,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F19" s="68" t="n"/>
-      <c r="G19" s="69" t="n"/>
+      <c r="F19" s="72" t="n"/>
+      <c r="G19" s="73" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="66">
+      <c r="A20" s="70">
         <f>EDATE(A19,1)</f>
         <v/>
       </c>
@@ -8639,15 +9831,15 @@
         <f>NETWORKDAYS(A20,EOMONTH(A20,0))</f>
         <v/>
       </c>
-      <c r="D20" s="67">
+      <c r="D20" s="71">
         <f>IF(ISNUMBER(MATCH(A20,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F20" s="68" t="n"/>
-      <c r="G20" s="69" t="n"/>
+      <c r="F20" s="72" t="n"/>
+      <c r="G20" s="73" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="66">
+      <c r="A21" s="70">
         <f>EDATE(A20,1)</f>
         <v/>
       </c>
@@ -8659,15 +9851,15 @@
         <f>NETWORKDAYS(A21,EOMONTH(A21,0))</f>
         <v/>
       </c>
-      <c r="D21" s="67">
+      <c r="D21" s="71">
         <f>IF(ISNUMBER(MATCH(A21,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F21" s="68" t="n"/>
-      <c r="G21" s="69" t="n"/>
+      <c r="F21" s="72" t="n"/>
+      <c r="G21" s="73" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="66">
+      <c r="A22" s="70">
         <f>EDATE(A21,1)</f>
         <v/>
       </c>
@@ -8679,15 +9871,15 @@
         <f>NETWORKDAYS(A22,EOMONTH(A22,0))</f>
         <v/>
       </c>
-      <c r="D22" s="67">
+      <c r="D22" s="71">
         <f>IF(ISNUMBER(MATCH(A22,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F22" s="68" t="n"/>
-      <c r="G22" s="69" t="n"/>
+      <c r="F22" s="72" t="n"/>
+      <c r="G22" s="73" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="66">
+      <c r="A23" s="70">
         <f>EDATE(A22,1)</f>
         <v/>
       </c>
@@ -8699,15 +9891,15 @@
         <f>NETWORKDAYS(A23,EOMONTH(A23,0))</f>
         <v/>
       </c>
-      <c r="D23" s="67">
+      <c r="D23" s="71">
         <f>IF(ISNUMBER(MATCH(A23,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F23" s="68" t="n"/>
-      <c r="G23" s="69" t="n"/>
+      <c r="F23" s="72" t="n"/>
+      <c r="G23" s="73" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="66">
+      <c r="A24" s="70">
         <f>EDATE(A23,1)</f>
         <v/>
       </c>
@@ -8719,15 +9911,15 @@
         <f>NETWORKDAYS(A24,EOMONTH(A24,0))</f>
         <v/>
       </c>
-      <c r="D24" s="67">
+      <c r="D24" s="71">
         <f>IF(ISNUMBER(MATCH(A24,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F24" s="68" t="n"/>
-      <c r="G24" s="69" t="n"/>
+      <c r="F24" s="72" t="n"/>
+      <c r="G24" s="73" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="66">
+      <c r="A25" s="70">
         <f>EDATE(A24,1)</f>
         <v/>
       </c>
@@ -8739,15 +9931,15 @@
         <f>NETWORKDAYS(A25,EOMONTH(A25,0))</f>
         <v/>
       </c>
-      <c r="D25" s="67">
+      <c r="D25" s="71">
         <f>IF(ISNUMBER(MATCH(A25,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F25" s="68" t="n"/>
-      <c r="G25" s="69" t="n"/>
+      <c r="F25" s="72" t="n"/>
+      <c r="G25" s="73" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="66">
+      <c r="A26" s="70">
         <f>EDATE(A25,1)</f>
         <v/>
       </c>
@@ -8759,15 +9951,15 @@
         <f>NETWORKDAYS(A26,EOMONTH(A26,0))</f>
         <v/>
       </c>
-      <c r="D26" s="67">
+      <c r="D26" s="71">
         <f>IF(ISNUMBER(MATCH(A26,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F26" s="68" t="n"/>
-      <c r="G26" s="69" t="n"/>
+      <c r="F26" s="72" t="n"/>
+      <c r="G26" s="73" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="66">
+      <c r="A27" s="70">
         <f>EDATE(A26,1)</f>
         <v/>
       </c>
@@ -8779,15 +9971,15 @@
         <f>NETWORKDAYS(A27,EOMONTH(A27,0))</f>
         <v/>
       </c>
-      <c r="D27" s="67">
+      <c r="D27" s="71">
         <f>IF(ISNUMBER(MATCH(A27,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F27" s="68" t="n"/>
-      <c r="G27" s="69" t="n"/>
+      <c r="F27" s="72" t="n"/>
+      <c r="G27" s="73" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="66">
+      <c r="A28" s="70">
         <f>EDATE(A27,1)</f>
         <v/>
       </c>
@@ -8799,15 +9991,15 @@
         <f>NETWORKDAYS(A28,EOMONTH(A28,0))</f>
         <v/>
       </c>
-      <c r="D28" s="67">
+      <c r="D28" s="71">
         <f>IF(ISNUMBER(MATCH(A28,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F28" s="68" t="n"/>
-      <c r="G28" s="69" t="n"/>
+      <c r="F28" s="72" t="n"/>
+      <c r="G28" s="73" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="66">
+      <c r="A29" s="70">
         <f>EDATE(A28,1)</f>
         <v/>
       </c>
@@ -8819,15 +10011,15 @@
         <f>NETWORKDAYS(A29,EOMONTH(A29,0))</f>
         <v/>
       </c>
-      <c r="D29" s="67">
+      <c r="D29" s="71">
         <f>IF(ISNUMBER(MATCH(A29,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F29" s="68" t="n"/>
-      <c r="G29" s="69" t="n"/>
+      <c r="F29" s="72" t="n"/>
+      <c r="G29" s="73" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="66">
+      <c r="A30" s="70">
         <f>EDATE(A29,1)</f>
         <v/>
       </c>
@@ -8839,15 +10031,15 @@
         <f>NETWORKDAYS(A30,EOMONTH(A30,0))</f>
         <v/>
       </c>
-      <c r="D30" s="67">
+      <c r="D30" s="71">
         <f>IF(ISNUMBER(MATCH(A30,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F30" s="68" t="n"/>
-      <c r="G30" s="69" t="n"/>
+      <c r="F30" s="72" t="n"/>
+      <c r="G30" s="73" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="66">
+      <c r="A31" s="70">
         <f>EDATE(A30,1)</f>
         <v/>
       </c>
@@ -8859,15 +10051,15 @@
         <f>NETWORKDAYS(A31,EOMONTH(A31,0))</f>
         <v/>
       </c>
-      <c r="D31" s="67">
+      <c r="D31" s="71">
         <f>IF(ISNUMBER(MATCH(A31,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F31" s="68" t="n"/>
-      <c r="G31" s="69" t="n"/>
+      <c r="F31" s="72" t="n"/>
+      <c r="G31" s="73" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="66">
+      <c r="A32" s="70">
         <f>EDATE(A31,1)</f>
         <v/>
       </c>
@@ -8879,15 +10071,15 @@
         <f>NETWORKDAYS(A32,EOMONTH(A32,0))</f>
         <v/>
       </c>
-      <c r="D32" s="67">
+      <c r="D32" s="71">
         <f>IF(ISNUMBER(MATCH(A32,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F32" s="68" t="n"/>
-      <c r="G32" s="69" t="n"/>
+      <c r="F32" s="72" t="n"/>
+      <c r="G32" s="73" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="66">
+      <c r="A33" s="70">
         <f>EDATE(A32,1)</f>
         <v/>
       </c>
@@ -8899,15 +10091,15 @@
         <f>NETWORKDAYS(A33,EOMONTH(A33,0))</f>
         <v/>
       </c>
-      <c r="D33" s="67">
+      <c r="D33" s="71">
         <f>IF(ISNUMBER(MATCH(A33,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F33" s="68" t="n"/>
-      <c r="G33" s="69" t="n"/>
+      <c r="F33" s="72" t="n"/>
+      <c r="G33" s="73" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="66">
+      <c r="A34" s="70">
         <f>EDATE(A33,1)</f>
         <v/>
       </c>
@@ -8919,15 +10111,15 @@
         <f>NETWORKDAYS(A34,EOMONTH(A34,0))</f>
         <v/>
       </c>
-      <c r="D34" s="67">
+      <c r="D34" s="71">
         <f>IF(ISNUMBER(MATCH(A34,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F34" s="68" t="n"/>
-      <c r="G34" s="69" t="n"/>
+      <c r="F34" s="72" t="n"/>
+      <c r="G34" s="73" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="66">
+      <c r="A35" s="70">
         <f>EDATE(A34,1)</f>
         <v/>
       </c>
@@ -8939,15 +10131,15 @@
         <f>NETWORKDAYS(A35,EOMONTH(A35,0))</f>
         <v/>
       </c>
-      <c r="D35" s="67">
+      <c r="D35" s="71">
         <f>IF(ISNUMBER(MATCH(A35,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F35" s="68" t="n"/>
-      <c r="G35" s="69" t="n"/>
+      <c r="F35" s="72" t="n"/>
+      <c r="G35" s="73" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="66">
+      <c r="A36" s="70">
         <f>EDATE(A35,1)</f>
         <v/>
       </c>
@@ -8959,15 +10151,15 @@
         <f>NETWORKDAYS(A36,EOMONTH(A36,0))</f>
         <v/>
       </c>
-      <c r="D36" s="67">
+      <c r="D36" s="71">
         <f>IF(ISNUMBER(MATCH(A36,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F36" s="68" t="n"/>
-      <c r="G36" s="69" t="n"/>
+      <c r="F36" s="72" t="n"/>
+      <c r="G36" s="73" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="66">
+      <c r="A37" s="70">
         <f>EDATE(A36,1)</f>
         <v/>
       </c>
@@ -8979,15 +10171,15 @@
         <f>NETWORKDAYS(A37,EOMONTH(A37,0))</f>
         <v/>
       </c>
-      <c r="D37" s="67">
+      <c r="D37" s="71">
         <f>IF(ISNUMBER(MATCH(A37,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F37" s="68" t="n"/>
-      <c r="G37" s="69" t="n"/>
+      <c r="F37" s="72" t="n"/>
+      <c r="G37" s="73" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="66">
+      <c r="A38" s="70">
         <f>EDATE(A37,1)</f>
         <v/>
       </c>
@@ -8999,13 +10191,13 @@
         <f>NETWORKDAYS(A38,EOMONTH(A38,0))</f>
         <v/>
       </c>
-      <c r="D38" s="67">
+      <c r="D38" s="71">
         <f>IF(ISNUMBER(MATCH(A38,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="66">
+      <c r="A39" s="70">
         <f>EDATE(A38,1)</f>
         <v/>
       </c>
@@ -9017,13 +10209,13 @@
         <f>NETWORKDAYS(A39,EOMONTH(A39,0))</f>
         <v/>
       </c>
-      <c r="D39" s="67">
+      <c r="D39" s="71">
         <f>IF(ISNUMBER(MATCH(A39,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="66">
+      <c r="A40" s="70">
         <f>EDATE(A39,1)</f>
         <v/>
       </c>
@@ -9035,13 +10227,13 @@
         <f>NETWORKDAYS(A40,EOMONTH(A40,0))</f>
         <v/>
       </c>
-      <c r="D40" s="67">
+      <c r="D40" s="71">
         <f>IF(ISNUMBER(MATCH(A40,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="66">
+      <c r="A41" s="70">
         <f>EDATE(A40,1)</f>
         <v/>
       </c>
@@ -9053,13 +10245,13 @@
         <f>NETWORKDAYS(A41,EOMONTH(A41,0))</f>
         <v/>
       </c>
-      <c r="D41" s="67">
+      <c r="D41" s="71">
         <f>IF(ISNUMBER(MATCH(A41,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="66">
+      <c r="A42" s="70">
         <f>EDATE(A41,1)</f>
         <v/>
       </c>
@@ -9071,13 +10263,13 @@
         <f>NETWORKDAYS(A42,EOMONTH(A42,0))</f>
         <v/>
       </c>
-      <c r="D42" s="67">
+      <c r="D42" s="71">
         <f>IF(ISNUMBER(MATCH(A42,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="66">
+      <c r="A43" s="70">
         <f>EDATE(A42,1)</f>
         <v/>
       </c>
@@ -9089,13 +10281,13 @@
         <f>NETWORKDAYS(A43,EOMONTH(A43,0))</f>
         <v/>
       </c>
-      <c r="D43" s="67">
+      <c r="D43" s="71">
         <f>IF(ISNUMBER(MATCH(A43,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="66">
+      <c r="A44" s="70">
         <f>EDATE(A43,1)</f>
         <v/>
       </c>
@@ -9107,13 +10299,13 @@
         <f>NETWORKDAYS(A44,EOMONTH(A44,0))</f>
         <v/>
       </c>
-      <c r="D44" s="67">
+      <c r="D44" s="71">
         <f>IF(ISNUMBER(MATCH(A44,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="66">
+      <c r="A45" s="70">
         <f>EDATE(A44,1)</f>
         <v/>
       </c>
@@ -9125,13 +10317,13 @@
         <f>NETWORKDAYS(A45,EOMONTH(A45,0))</f>
         <v/>
       </c>
-      <c r="D45" s="67">
+      <c r="D45" s="71">
         <f>IF(ISNUMBER(MATCH(A45,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="66">
+      <c r="A46" s="70">
         <f>EDATE(A45,1)</f>
         <v/>
       </c>
@@ -9143,13 +10335,13 @@
         <f>NETWORKDAYS(A46,EOMONTH(A46,0))</f>
         <v/>
       </c>
-      <c r="D46" s="67">
+      <c r="D46" s="71">
         <f>IF(ISNUMBER(MATCH(A46,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="66">
+      <c r="A47" s="70">
         <f>EDATE(A46,1)</f>
         <v/>
       </c>
@@ -9161,13 +10353,13 @@
         <f>NETWORKDAYS(A47,EOMONTH(A47,0))</f>
         <v/>
       </c>
-      <c r="D47" s="67">
+      <c r="D47" s="71">
         <f>IF(ISNUMBER(MATCH(A47,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="66">
+      <c r="A48" s="70">
         <f>EDATE(A47,1)</f>
         <v/>
       </c>
@@ -9179,13 +10371,13 @@
         <f>NETWORKDAYS(A48,EOMONTH(A48,0))</f>
         <v/>
       </c>
-      <c r="D48" s="67">
+      <c r="D48" s="71">
         <f>IF(ISNUMBER(MATCH(A48,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="66">
+      <c r="A49" s="70">
         <f>EDATE(A48,1)</f>
         <v/>
       </c>
@@ -9197,13 +10389,13 @@
         <f>NETWORKDAYS(A49,EOMONTH(A49,0))</f>
         <v/>
       </c>
-      <c r="D49" s="67">
+      <c r="D49" s="71">
         <f>IF(ISNUMBER(MATCH(A49,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="66">
+      <c r="A50" s="70">
         <f>EDATE(A49,1)</f>
         <v/>
       </c>
@@ -9215,13 +10407,13 @@
         <f>NETWORKDAYS(A50,EOMONTH(A50,0))</f>
         <v/>
       </c>
-      <c r="D50" s="67">
+      <c r="D50" s="71">
         <f>IF(ISNUMBER(MATCH(A50,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="66">
+      <c r="A51" s="70">
         <f>EDATE(A50,1)</f>
         <v/>
       </c>
@@ -9233,13 +10425,13 @@
         <f>NETWORKDAYS(A51,EOMONTH(A51,0))</f>
         <v/>
       </c>
-      <c r="D51" s="67">
+      <c r="D51" s="71">
         <f>IF(ISNUMBER(MATCH(A51,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="66">
+      <c r="A52" s="70">
         <f>EDATE(A51,1)</f>
         <v/>
       </c>
@@ -9251,13 +10443,13 @@
         <f>NETWORKDAYS(A52,EOMONTH(A52,0))</f>
         <v/>
       </c>
-      <c r="D52" s="67">
+      <c r="D52" s="71">
         <f>IF(ISNUMBER(MATCH(A52,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="66">
+      <c r="A53" s="70">
         <f>EDATE(A52,1)</f>
         <v/>
       </c>
@@ -9269,13 +10461,13 @@
         <f>NETWORKDAYS(A53,EOMONTH(A53,0))</f>
         <v/>
       </c>
-      <c r="D53" s="67">
+      <c r="D53" s="71">
         <f>IF(ISNUMBER(MATCH(A53,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="66">
+      <c r="A54" s="70">
         <f>EDATE(A53,1)</f>
         <v/>
       </c>
@@ -9287,13 +10479,13 @@
         <f>NETWORKDAYS(A54,EOMONTH(A54,0))</f>
         <v/>
       </c>
-      <c r="D54" s="67">
+      <c r="D54" s="71">
         <f>IF(ISNUMBER(MATCH(A54,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="66">
+      <c r="A55" s="70">
         <f>EDATE(A54,1)</f>
         <v/>
       </c>
@@ -9305,13 +10497,13 @@
         <f>NETWORKDAYS(A55,EOMONTH(A55,0))</f>
         <v/>
       </c>
-      <c r="D55" s="67">
+      <c r="D55" s="71">
         <f>IF(ISNUMBER(MATCH(A55,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="66">
+      <c r="A56" s="70">
         <f>EDATE(A55,1)</f>
         <v/>
       </c>
@@ -9323,13 +10515,13 @@
         <f>NETWORKDAYS(A56,EOMONTH(A56,0))</f>
         <v/>
       </c>
-      <c r="D56" s="67">
+      <c r="D56" s="71">
         <f>IF(ISNUMBER(MATCH(A56,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="66">
+      <c r="A57" s="70">
         <f>EDATE(A56,1)</f>
         <v/>
       </c>
@@ -9341,13 +10533,13 @@
         <f>NETWORKDAYS(A57,EOMONTH(A57,0))</f>
         <v/>
       </c>
-      <c r="D57" s="67">
+      <c r="D57" s="71">
         <f>IF(ISNUMBER(MATCH(A57,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="66">
+      <c r="A58" s="70">
         <f>EDATE(A57,1)</f>
         <v/>
       </c>
@@ -9359,13 +10551,13 @@
         <f>NETWORKDAYS(A58,EOMONTH(A58,0))</f>
         <v/>
       </c>
-      <c r="D58" s="67">
+      <c r="D58" s="71">
         <f>IF(ISNUMBER(MATCH(A58,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="66">
+      <c r="A59" s="70">
         <f>EDATE(A58,1)</f>
         <v/>
       </c>
@@ -9377,13 +10569,13 @@
         <f>NETWORKDAYS(A59,EOMONTH(A59,0))</f>
         <v/>
       </c>
-      <c r="D59" s="67">
+      <c r="D59" s="71">
         <f>IF(ISNUMBER(MATCH(A59,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="66">
+      <c r="A60" s="70">
         <f>EDATE(A59,1)</f>
         <v/>
       </c>
@@ -9395,13 +10587,13 @@
         <f>NETWORKDAYS(A60,EOMONTH(A60,0))</f>
         <v/>
       </c>
-      <c r="D60" s="67">
+      <c r="D60" s="71">
         <f>IF(ISNUMBER(MATCH(A60,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="66">
+      <c r="A61" s="70">
         <f>EDATE(A60,1)</f>
         <v/>
       </c>
@@ -9413,13 +10605,13 @@
         <f>NETWORKDAYS(A61,EOMONTH(A61,0))</f>
         <v/>
       </c>
-      <c r="D61" s="67">
+      <c r="D61" s="71">
         <f>IF(ISNUMBER(MATCH(A61,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="66">
+      <c r="A62" s="70">
         <f>EDATE(A61,1)</f>
         <v/>
       </c>
@@ -9431,13 +10623,13 @@
         <f>NETWORKDAYS(A62,EOMONTH(A62,0))</f>
         <v/>
       </c>
-      <c r="D62" s="67">
+      <c r="D62" s="71">
         <f>IF(ISNUMBER(MATCH(A62,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="66">
+      <c r="A63" s="70">
         <f>EDATE(A62,1)</f>
         <v/>
       </c>
@@ -9449,13 +10641,13 @@
         <f>NETWORKDAYS(A63,EOMONTH(A63,0))</f>
         <v/>
       </c>
-      <c r="D63" s="67">
+      <c r="D63" s="71">
         <f>IF(ISNUMBER(MATCH(A63,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="66">
+      <c r="A64" s="70">
         <f>EDATE(A63,1)</f>
         <v/>
       </c>
@@ -9467,13 +10659,13 @@
         <f>NETWORKDAYS(A64,EOMONTH(A64,0))</f>
         <v/>
       </c>
-      <c r="D64" s="67">
+      <c r="D64" s="71">
         <f>IF(ISNUMBER(MATCH(A64,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="66">
+      <c r="A65" s="70">
         <f>EDATE(A64,1)</f>
         <v/>
       </c>
@@ -9485,13 +10677,13 @@
         <f>NETWORKDAYS(A65,EOMONTH(A65,0))</f>
         <v/>
       </c>
-      <c r="D65" s="67">
+      <c r="D65" s="71">
         <f>IF(ISNUMBER(MATCH(A65,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="66">
+      <c r="A66" s="70">
         <f>EDATE(A65,1)</f>
         <v/>
       </c>
@@ -9503,13 +10695,13 @@
         <f>NETWORKDAYS(A66,EOMONTH(A66,0))</f>
         <v/>
       </c>
-      <c r="D66" s="67">
+      <c r="D66" s="71">
         <f>IF(ISNUMBER(MATCH(A66,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="66">
+      <c r="A67" s="70">
         <f>EDATE(A66,1)</f>
         <v/>
       </c>
@@ -9521,13 +10713,13 @@
         <f>NETWORKDAYS(A67,EOMONTH(A67,0))</f>
         <v/>
       </c>
-      <c r="D67" s="67">
+      <c r="D67" s="71">
         <f>IF(ISNUMBER(MATCH(A67,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="66">
+      <c r="A68" s="70">
         <f>EDATE(A67,1)</f>
         <v/>
       </c>
@@ -9539,13 +10731,13 @@
         <f>NETWORKDAYS(A68,EOMONTH(A68,0))</f>
         <v/>
       </c>
-      <c r="D68" s="67">
+      <c r="D68" s="71">
         <f>IF(ISNUMBER(MATCH(A68,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="66">
+      <c r="A69" s="70">
         <f>EDATE(A68,1)</f>
         <v/>
       </c>
@@ -9557,13 +10749,13 @@
         <f>NETWORKDAYS(A69,EOMONTH(A69,0))</f>
         <v/>
       </c>
-      <c r="D69" s="67">
+      <c r="D69" s="71">
         <f>IF(ISNUMBER(MATCH(A69,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="66">
+      <c r="A70" s="70">
         <f>EDATE(A69,1)</f>
         <v/>
       </c>
@@ -9575,13 +10767,13 @@
         <f>NETWORKDAYS(A70,EOMONTH(A70,0))</f>
         <v/>
       </c>
-      <c r="D70" s="67">
+      <c r="D70" s="71">
         <f>IF(ISNUMBER(MATCH(A70,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="66">
+      <c r="A71" s="70">
         <f>EDATE(A70,1)</f>
         <v/>
       </c>
@@ -9593,13 +10785,13 @@
         <f>NETWORKDAYS(A71,EOMONTH(A71,0))</f>
         <v/>
       </c>
-      <c r="D71" s="67">
+      <c r="D71" s="71">
         <f>IF(ISNUMBER(MATCH(A71,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="66">
+      <c r="A72" s="70">
         <f>EDATE(A71,1)</f>
         <v/>
       </c>
@@ -9611,13 +10803,13 @@
         <f>NETWORKDAYS(A72,EOMONTH(A72,0))</f>
         <v/>
       </c>
-      <c r="D72" s="67">
+      <c r="D72" s="71">
         <f>IF(ISNUMBER(MATCH(A72,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="66">
+      <c r="A73" s="70">
         <f>EDATE(A72,1)</f>
         <v/>
       </c>
@@ -9629,13 +10821,13 @@
         <f>NETWORKDAYS(A73,EOMONTH(A73,0))</f>
         <v/>
       </c>
-      <c r="D73" s="67">
+      <c r="D73" s="71">
         <f>IF(ISNUMBER(MATCH(A73,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="66">
+      <c r="A74" s="70">
         <f>EDATE(A73,1)</f>
         <v/>
       </c>
@@ -9647,13 +10839,13 @@
         <f>NETWORKDAYS(A74,EOMONTH(A74,0))</f>
         <v/>
       </c>
-      <c r="D74" s="67">
+      <c r="D74" s="71">
         <f>IF(ISNUMBER(MATCH(A74,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="66">
+      <c r="A75" s="70">
         <f>EDATE(A74,1)</f>
         <v/>
       </c>
@@ -9665,13 +10857,13 @@
         <f>NETWORKDAYS(A75,EOMONTH(A75,0))</f>
         <v/>
       </c>
-      <c r="D75" s="67">
+      <c r="D75" s="71">
         <f>IF(ISNUMBER(MATCH(A75,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="66">
+      <c r="A76" s="70">
         <f>EDATE(A75,1)</f>
         <v/>
       </c>
@@ -9683,13 +10875,13 @@
         <f>NETWORKDAYS(A76,EOMONTH(A76,0))</f>
         <v/>
       </c>
-      <c r="D76" s="67">
+      <c r="D76" s="71">
         <f>IF(ISNUMBER(MATCH(A76,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="66">
+      <c r="A77" s="70">
         <f>EDATE(A76,1)</f>
         <v/>
       </c>
@@ -9701,13 +10893,13 @@
         <f>NETWORKDAYS(A77,EOMONTH(A77,0))</f>
         <v/>
       </c>
-      <c r="D77" s="67">
+      <c r="D77" s="71">
         <f>IF(ISNUMBER(MATCH(A77,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="66">
+      <c r="A78" s="70">
         <f>EDATE(A77,1)</f>
         <v/>
       </c>
@@ -9719,13 +10911,13 @@
         <f>NETWORKDAYS(A78,EOMONTH(A78,0))</f>
         <v/>
       </c>
-      <c r="D78" s="67">
+      <c r="D78" s="71">
         <f>IF(ISNUMBER(MATCH(A78,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="66">
+      <c r="A79" s="70">
         <f>EDATE(A78,1)</f>
         <v/>
       </c>
@@ -9737,13 +10929,13 @@
         <f>NETWORKDAYS(A79,EOMONTH(A79,0))</f>
         <v/>
       </c>
-      <c r="D79" s="67">
+      <c r="D79" s="71">
         <f>IF(ISNUMBER(MATCH(A79,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="66">
+      <c r="A80" s="70">
         <f>EDATE(A79,1)</f>
         <v/>
       </c>
@@ -9755,13 +10947,13 @@
         <f>NETWORKDAYS(A80,EOMONTH(A80,0))</f>
         <v/>
       </c>
-      <c r="D80" s="67">
+      <c r="D80" s="71">
         <f>IF(ISNUMBER(MATCH(A80,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="66">
+      <c r="A81" s="70">
         <f>EDATE(A80,1)</f>
         <v/>
       </c>
@@ -9773,13 +10965,13 @@
         <f>NETWORKDAYS(A81,EOMONTH(A81,0))</f>
         <v/>
       </c>
-      <c r="D81" s="67">
+      <c r="D81" s="71">
         <f>IF(ISNUMBER(MATCH(A81,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="66">
+      <c r="A82" s="70">
         <f>EDATE(A81,1)</f>
         <v/>
       </c>
@@ -9791,13 +10983,13 @@
         <f>NETWORKDAYS(A82,EOMONTH(A82,0))</f>
         <v/>
       </c>
-      <c r="D82" s="67">
+      <c r="D82" s="71">
         <f>IF(ISNUMBER(MATCH(A82,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="66">
+      <c r="A83" s="70">
         <f>EDATE(A82,1)</f>
         <v/>
       </c>
@@ -9809,13 +11001,13 @@
         <f>NETWORKDAYS(A83,EOMONTH(A83,0))</f>
         <v/>
       </c>
-      <c r="D83" s="67">
+      <c r="D83" s="71">
         <f>IF(ISNUMBER(MATCH(A83,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="66">
+      <c r="A84" s="70">
         <f>EDATE(A83,1)</f>
         <v/>
       </c>
@@ -9827,13 +11019,13 @@
         <f>NETWORKDAYS(A84,EOMONTH(A84,0))</f>
         <v/>
       </c>
-      <c r="D84" s="67">
+      <c r="D84" s="71">
         <f>IF(ISNUMBER(MATCH(A84,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="66">
+      <c r="A85" s="70">
         <f>EDATE(A84,1)</f>
         <v/>
       </c>
@@ -9845,13 +11037,13 @@
         <f>NETWORKDAYS(A85,EOMONTH(A85,0))</f>
         <v/>
       </c>
-      <c r="D85" s="67">
+      <c r="D85" s="71">
         <f>IF(ISNUMBER(MATCH(A85,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="66">
+      <c r="A86" s="70">
         <f>EDATE(A85,1)</f>
         <v/>
       </c>
@@ -9863,13 +11055,13 @@
         <f>NETWORKDAYS(A86,EOMONTH(A86,0))</f>
         <v/>
       </c>
-      <c r="D86" s="67">
+      <c r="D86" s="71">
         <f>IF(ISNUMBER(MATCH(A86,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="66">
+      <c r="A87" s="70">
         <f>EDATE(A86,1)</f>
         <v/>
       </c>
@@ -9881,13 +11073,13 @@
         <f>NETWORKDAYS(A87,EOMONTH(A87,0))</f>
         <v/>
       </c>
-      <c r="D87" s="67">
+      <c r="D87" s="71">
         <f>IF(ISNUMBER(MATCH(A87,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="66">
+      <c r="A88" s="70">
         <f>EDATE(A87,1)</f>
         <v/>
       </c>
@@ -9899,13 +11091,13 @@
         <f>NETWORKDAYS(A88,EOMONTH(A88,0))</f>
         <v/>
       </c>
-      <c r="D88" s="67">
+      <c r="D88" s="71">
         <f>IF(ISNUMBER(MATCH(A88,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="66">
+      <c r="A89" s="70">
         <f>EDATE(A88,1)</f>
         <v/>
       </c>
@@ -9917,13 +11109,13 @@
         <f>NETWORKDAYS(A89,EOMONTH(A89,0))</f>
         <v/>
       </c>
-      <c r="D89" s="67">
+      <c r="D89" s="71">
         <f>IF(ISNUMBER(MATCH(A89,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="66">
+      <c r="A90" s="70">
         <f>EDATE(A89,1)</f>
         <v/>
       </c>
@@ -9935,13 +11127,13 @@
         <f>NETWORKDAYS(A90,EOMONTH(A90,0))</f>
         <v/>
       </c>
-      <c r="D90" s="67">
+      <c r="D90" s="71">
         <f>IF(ISNUMBER(MATCH(A90,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="66">
+      <c r="A91" s="70">
         <f>EDATE(A90,1)</f>
         <v/>
       </c>
@@ -9953,13 +11145,13 @@
         <f>NETWORKDAYS(A91,EOMONTH(A91,0))</f>
         <v/>
       </c>
-      <c r="D91" s="67">
+      <c r="D91" s="71">
         <f>IF(ISNUMBER(MATCH(A91,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="66">
+      <c r="A92" s="70">
         <f>EDATE(A91,1)</f>
         <v/>
       </c>
@@ -9971,13 +11163,13 @@
         <f>NETWORKDAYS(A92,EOMONTH(A92,0))</f>
         <v/>
       </c>
-      <c r="D92" s="67">
+      <c r="D92" s="71">
         <f>IF(ISNUMBER(MATCH(A92,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="66">
+      <c r="A93" s="70">
         <f>EDATE(A92,1)</f>
         <v/>
       </c>
@@ -9989,13 +11181,13 @@
         <f>NETWORKDAYS(A93,EOMONTH(A93,0))</f>
         <v/>
       </c>
-      <c r="D93" s="67">
+      <c r="D93" s="71">
         <f>IF(ISNUMBER(MATCH(A93,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="66">
+      <c r="A94" s="70">
         <f>EDATE(A93,1)</f>
         <v/>
       </c>
@@ -10007,13 +11199,13 @@
         <f>NETWORKDAYS(A94,EOMONTH(A94,0))</f>
         <v/>
       </c>
-      <c r="D94" s="67">
+      <c r="D94" s="71">
         <f>IF(ISNUMBER(MATCH(A94,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="66">
+      <c r="A95" s="70">
         <f>EDATE(A94,1)</f>
         <v/>
       </c>
@@ -10025,13 +11217,13 @@
         <f>NETWORKDAYS(A95,EOMONTH(A95,0))</f>
         <v/>
       </c>
-      <c r="D95" s="67">
+      <c r="D95" s="71">
         <f>IF(ISNUMBER(MATCH(A95,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="66">
+      <c r="A96" s="70">
         <f>EDATE(A95,1)</f>
         <v/>
       </c>
@@ -10043,13 +11235,13 @@
         <f>NETWORKDAYS(A96,EOMONTH(A96,0))</f>
         <v/>
       </c>
-      <c r="D96" s="67">
+      <c r="D96" s="71">
         <f>IF(ISNUMBER(MATCH(A96,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="66">
+      <c r="A97" s="70">
         <f>EDATE(A96,1)</f>
         <v/>
       </c>
@@ -10061,13 +11253,13 @@
         <f>NETWORKDAYS(A97,EOMONTH(A97,0))</f>
         <v/>
       </c>
-      <c r="D97" s="67">
+      <c r="D97" s="71">
         <f>IF(ISNUMBER(MATCH(A97,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="66">
+      <c r="A98" s="70">
         <f>EDATE(A97,1)</f>
         <v/>
       </c>
@@ -10079,13 +11271,13 @@
         <f>NETWORKDAYS(A98,EOMONTH(A98,0))</f>
         <v/>
       </c>
-      <c r="D98" s="67">
+      <c r="D98" s="71">
         <f>IF(ISNUMBER(MATCH(A98,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="66">
+      <c r="A99" s="70">
         <f>EDATE(A98,1)</f>
         <v/>
       </c>
@@ -10097,13 +11289,13 @@
         <f>NETWORKDAYS(A99,EOMONTH(A99,0))</f>
         <v/>
       </c>
-      <c r="D99" s="67">
+      <c r="D99" s="71">
         <f>IF(ISNUMBER(MATCH(A99,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="66">
+      <c r="A100" s="70">
         <f>EDATE(A99,1)</f>
         <v/>
       </c>
@@ -10115,13 +11307,13 @@
         <f>NETWORKDAYS(A100,EOMONTH(A100,0))</f>
         <v/>
       </c>
-      <c r="D100" s="67">
+      <c r="D100" s="71">
         <f>IF(ISNUMBER(MATCH(A100,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="66">
+      <c r="A101" s="70">
         <f>EDATE(A100,1)</f>
         <v/>
       </c>
@@ -10133,13 +11325,13 @@
         <f>NETWORKDAYS(A101,EOMONTH(A101,0))</f>
         <v/>
       </c>
-      <c r="D101" s="67">
+      <c r="D101" s="71">
         <f>IF(ISNUMBER(MATCH(A101,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="66">
+      <c r="A102" s="70">
         <f>EDATE(A101,1)</f>
         <v/>
       </c>
@@ -10151,13 +11343,13 @@
         <f>NETWORKDAYS(A102,EOMONTH(A102,0))</f>
         <v/>
       </c>
-      <c r="D102" s="67">
+      <c r="D102" s="71">
         <f>IF(ISNUMBER(MATCH(A102,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="66">
+      <c r="A103" s="70">
         <f>EDATE(A102,1)</f>
         <v/>
       </c>
@@ -10169,13 +11361,13 @@
         <f>NETWORKDAYS(A103,EOMONTH(A103,0))</f>
         <v/>
       </c>
-      <c r="D103" s="67">
+      <c r="D103" s="71">
         <f>IF(ISNUMBER(MATCH(A103,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="66">
+      <c r="A104" s="70">
         <f>EDATE(A103,1)</f>
         <v/>
       </c>
@@ -10187,13 +11379,13 @@
         <f>NETWORKDAYS(A104,EOMONTH(A104,0))</f>
         <v/>
       </c>
-      <c r="D104" s="67">
+      <c r="D104" s="71">
         <f>IF(ISNUMBER(MATCH(A104,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="66">
+      <c r="A105" s="70">
         <f>EDATE(A104,1)</f>
         <v/>
       </c>
@@ -10205,13 +11397,13 @@
         <f>NETWORKDAYS(A105,EOMONTH(A105,0))</f>
         <v/>
       </c>
-      <c r="D105" s="67">
+      <c r="D105" s="71">
         <f>IF(ISNUMBER(MATCH(A105,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="66">
+      <c r="A106" s="70">
         <f>EDATE(A105,1)</f>
         <v/>
       </c>
@@ -10223,13 +11415,13 @@
         <f>NETWORKDAYS(A106,EOMONTH(A106,0))</f>
         <v/>
       </c>
-      <c r="D106" s="67">
+      <c r="D106" s="71">
         <f>IF(ISNUMBER(MATCH(A106,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="66">
+      <c r="A107" s="70">
         <f>EDATE(A106,1)</f>
         <v/>
       </c>
@@ -10241,13 +11433,13 @@
         <f>NETWORKDAYS(A107,EOMONTH(A107,0))</f>
         <v/>
       </c>
-      <c r="D107" s="67">
+      <c r="D107" s="71">
         <f>IF(ISNUMBER(MATCH(A107,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="66">
+      <c r="A108" s="70">
         <f>EDATE(A107,1)</f>
         <v/>
       </c>
@@ -10259,13 +11451,13 @@
         <f>NETWORKDAYS(A108,EOMONTH(A108,0))</f>
         <v/>
       </c>
-      <c r="D108" s="67">
+      <c r="D108" s="71">
         <f>IF(ISNUMBER(MATCH(A108,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="66">
+      <c r="A109" s="70">
         <f>EDATE(A108,1)</f>
         <v/>
       </c>
@@ -10277,13 +11469,13 @@
         <f>NETWORKDAYS(A109,EOMONTH(A109,0))</f>
         <v/>
       </c>
-      <c r="D109" s="67">
+      <c r="D109" s="71">
         <f>IF(ISNUMBER(MATCH(A109,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="66">
+      <c r="A110" s="70">
         <f>EDATE(A109,1)</f>
         <v/>
       </c>
@@ -10295,13 +11487,13 @@
         <f>NETWORKDAYS(A110,EOMONTH(A110,0))</f>
         <v/>
       </c>
-      <c r="D110" s="67">
+      <c r="D110" s="71">
         <f>IF(ISNUMBER(MATCH(A110,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="66">
+      <c r="A111" s="70">
         <f>EDATE(A110,1)</f>
         <v/>
       </c>
@@ -10313,13 +11505,13 @@
         <f>NETWORKDAYS(A111,EOMONTH(A111,0))</f>
         <v/>
       </c>
-      <c r="D111" s="67">
+      <c r="D111" s="71">
         <f>IF(ISNUMBER(MATCH(A111,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="66">
+      <c r="A112" s="70">
         <f>EDATE(A111,1)</f>
         <v/>
       </c>
@@ -10331,13 +11523,13 @@
         <f>NETWORKDAYS(A112,EOMONTH(A112,0))</f>
         <v/>
       </c>
-      <c r="D112" s="67">
+      <c r="D112" s="71">
         <f>IF(ISNUMBER(MATCH(A112,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="66">
+      <c r="A113" s="70">
         <f>EDATE(A112,1)</f>
         <v/>
       </c>
@@ -10349,13 +11541,13 @@
         <f>NETWORKDAYS(A113,EOMONTH(A113,0))</f>
         <v/>
       </c>
-      <c r="D113" s="67">
+      <c r="D113" s="71">
         <f>IF(ISNUMBER(MATCH(A113,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="66">
+      <c r="A114" s="70">
         <f>EDATE(A113,1)</f>
         <v/>
       </c>
@@ -10367,13 +11559,13 @@
         <f>NETWORKDAYS(A114,EOMONTH(A114,0))</f>
         <v/>
       </c>
-      <c r="D114" s="67">
+      <c r="D114" s="71">
         <f>IF(ISNUMBER(MATCH(A114,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="66">
+      <c r="A115" s="70">
         <f>EDATE(A114,1)</f>
         <v/>
       </c>
@@ -10385,13 +11577,13 @@
         <f>NETWORKDAYS(A115,EOMONTH(A115,0))</f>
         <v/>
       </c>
-      <c r="D115" s="67">
+      <c r="D115" s="71">
         <f>IF(ISNUMBER(MATCH(A115,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="66">
+      <c r="A116" s="70">
         <f>EDATE(A115,1)</f>
         <v/>
       </c>
@@ -10403,13 +11595,13 @@
         <f>NETWORKDAYS(A116,EOMONTH(A116,0))</f>
         <v/>
       </c>
-      <c r="D116" s="67">
+      <c r="D116" s="71">
         <f>IF(ISNUMBER(MATCH(A116,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="66">
+      <c r="A117" s="70">
         <f>EDATE(A116,1)</f>
         <v/>
       </c>
@@ -10421,13 +11613,13 @@
         <f>NETWORKDAYS(A117,EOMONTH(A117,0))</f>
         <v/>
       </c>
-      <c r="D117" s="67">
+      <c r="D117" s="71">
         <f>IF(ISNUMBER(MATCH(A117,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="66">
+      <c r="A118" s="70">
         <f>EDATE(A117,1)</f>
         <v/>
       </c>
@@ -10439,13 +11631,13 @@
         <f>NETWORKDAYS(A118,EOMONTH(A118,0))</f>
         <v/>
       </c>
-      <c r="D118" s="67">
+      <c r="D118" s="71">
         <f>IF(ISNUMBER(MATCH(A118,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="66">
+      <c r="A119" s="70">
         <f>EDATE(A118,1)</f>
         <v/>
       </c>
@@ -10457,13 +11649,13 @@
         <f>NETWORKDAYS(A119,EOMONTH(A119,0))</f>
         <v/>
       </c>
-      <c r="D119" s="67">
+      <c r="D119" s="71">
         <f>IF(ISNUMBER(MATCH(A119,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="66">
+      <c r="A120" s="70">
         <f>EDATE(A119,1)</f>
         <v/>
       </c>
@@ -10475,13 +11667,13 @@
         <f>NETWORKDAYS(A120,EOMONTH(A120,0))</f>
         <v/>
       </c>
-      <c r="D120" s="67">
+      <c r="D120" s="71">
         <f>IF(ISNUMBER(MATCH(A120,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="66">
+      <c r="A121" s="70">
         <f>EDATE(A120,1)</f>
         <v/>
       </c>
@@ -10493,64 +11685,64 @@
         <f>NETWORKDAYS(A121,EOMONTH(A121,0))</f>
         <v/>
       </c>
-      <c r="D121" s="67">
+      <c r="D121" s="71">
         <f>IF(ISNUMBER(MATCH(A121,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="61" t="n"/>
-      <c r="B122" s="61" t="n"/>
-      <c r="C122" s="61" t="n"/>
-      <c r="D122" s="61" t="n"/>
+      <c r="A122" s="74" t="n"/>
+      <c r="B122" s="74" t="n"/>
+      <c r="C122" s="74" t="n"/>
+      <c r="D122" s="74" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="61" t="n"/>
-      <c r="B123" s="61" t="n"/>
-      <c r="C123" s="61" t="n"/>
-      <c r="D123" s="61" t="n"/>
+      <c r="A123" s="74" t="n"/>
+      <c r="B123" s="74" t="n"/>
+      <c r="C123" s="74" t="n"/>
+      <c r="D123" s="74" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="61" t="n"/>
-      <c r="B124" s="61" t="n"/>
-      <c r="C124" s="61" t="n"/>
-      <c r="D124" s="61" t="n"/>
+      <c r="A124" s="74" t="n"/>
+      <c r="B124" s="74" t="n"/>
+      <c r="C124" s="74" t="n"/>
+      <c r="D124" s="74" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="61" t="n"/>
-      <c r="B125" s="61" t="n"/>
-      <c r="C125" s="61" t="n"/>
-      <c r="D125" s="61" t="n"/>
+      <c r="A125" s="74" t="n"/>
+      <c r="B125" s="74" t="n"/>
+      <c r="C125" s="74" t="n"/>
+      <c r="D125" s="74" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="61" t="n"/>
-      <c r="B126" s="61" t="n"/>
-      <c r="C126" s="61" t="n"/>
-      <c r="D126" s="61" t="n"/>
+      <c r="A126" s="74" t="n"/>
+      <c r="B126" s="74" t="n"/>
+      <c r="C126" s="74" t="n"/>
+      <c r="D126" s="74" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="61" t="n"/>
-      <c r="B127" s="61" t="n"/>
-      <c r="C127" s="61" t="n"/>
-      <c r="D127" s="61" t="n"/>
+      <c r="A127" s="74" t="n"/>
+      <c r="B127" s="74" t="n"/>
+      <c r="C127" s="74" t="n"/>
+      <c r="D127" s="74" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="61" t="n"/>
-      <c r="B128" s="61" t="n"/>
-      <c r="C128" s="61" t="n"/>
-      <c r="D128" s="61" t="n"/>
+      <c r="A128" s="74" t="n"/>
+      <c r="B128" s="74" t="n"/>
+      <c r="C128" s="74" t="n"/>
+      <c r="D128" s="74" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="61" t="n"/>
-      <c r="B129" s="61" t="n"/>
-      <c r="C129" s="61" t="n"/>
-      <c r="D129" s="61" t="n"/>
+      <c r="A129" s="74" t="n"/>
+      <c r="B129" s="74" t="n"/>
+      <c r="C129" s="74" t="n"/>
+      <c r="D129" s="74" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="61" t="n"/>
-      <c r="B130" s="61" t="n"/>
-      <c r="C130" s="61" t="n"/>
-      <c r="D130" s="61" t="n"/>
+      <c r="A130" s="74" t="n"/>
+      <c r="B130" s="74" t="n"/>
+      <c r="C130" s="74" t="n"/>
+      <c r="D130" s="74" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10583,6 +11775,7 @@
     <col width="13" customWidth="1" style="39" min="13" max="13"/>
     <col width="12" customWidth="1" style="39" min="14" max="14"/>
     <col width="13" customWidth="1" style="39" min="15" max="15"/>
+    <col width="14" customWidth="1" style="39" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10598,13 +11791,13 @@
           <t>職員番号</t>
         </is>
       </c>
-      <c r="F3" s="70" t="n"/>
+      <c r="F3" s="75" t="n"/>
       <c r="J3" s="12" t="inlineStr">
         <is>
           <t>支給開始日（待機3日後）</t>
         </is>
       </c>
-      <c r="N3" s="71" t="n"/>
+      <c r="N3" s="76" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -10612,13 +11805,13 @@
           <t>氏名</t>
         </is>
       </c>
-      <c r="F4" s="72" t="n"/>
+      <c r="F4" s="77" t="n"/>
       <c r="J4" s="12" t="inlineStr">
         <is>
           <t>法定給付の末日（1年6月＋出勤）</t>
         </is>
       </c>
-      <c r="N4" s="71" t="n"/>
+      <c r="N4" s="76" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -10626,19 +11819,19 @@
           <t>請求期間</t>
         </is>
       </c>
-      <c r="F5" s="71" t="n"/>
-      <c r="G5" s="73" t="inlineStr">
+      <c r="F5" s="76" t="n"/>
+      <c r="G5" s="78" t="inlineStr">
         <is>
           <t>～</t>
         </is>
       </c>
-      <c r="H5" s="71" t="n"/>
+      <c r="H5" s="76" t="n"/>
       <c r="J5" s="12" t="inlineStr">
         <is>
           <t>附加給付の開始日</t>
         </is>
       </c>
-      <c r="N5" s="71" t="n"/>
+      <c r="N5" s="76" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -10646,13 +11839,13 @@
           <t>傷病手当日額（支給開始月で固定）</t>
         </is>
       </c>
-      <c r="F6" s="74" t="n"/>
+      <c r="F6" s="79" t="n"/>
       <c r="J6" s="12" t="inlineStr">
         <is>
           <t>附加給付の末日（+6月＋出勤）</t>
         </is>
       </c>
-      <c r="N6" s="71" t="n"/>
+      <c r="N6" s="76" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -10660,21 +11853,22 @@
           <t>作成日</t>
         </is>
       </c>
-      <c r="F7" s="71" t="n"/>
+      <c r="F7" s="76" t="n"/>
       <c r="J7" s="12" t="inlineStr">
         <is>
           <t>算定の最終日</t>
         </is>
       </c>
-      <c r="N7" s="71" t="n"/>
+      <c r="N7" s="76" t="n"/>
     </row>
     <row r="8">
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>出勤による延長日数</t>
-        </is>
-      </c>
-      <c r="N8" s="75" t="n"/>
+          <t>出勤による延長（月数／日数）</t>
+        </is>
+      </c>
+      <c r="N8" s="80" t="n"/>
+      <c r="O8" s="81" t="n"/>
     </row>
     <row r="9" ht="42" customHeight="1" s="39">
       <c r="A9" s="18" t="inlineStr">
@@ -12175,7 +13369,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>マクロ用の設定（シート名の文字と、メッセージの文言です。必要なときだけ直してください）</t>
         </is>
@@ -12187,7 +13381,7 @@
           <t>請求シート名の先頭</t>
         </is>
       </c>
-      <c r="B3" s="77" t="inlineStr">
+      <c r="B3" s="83" t="inlineStr">
         <is>
           <t>請求_</t>
         </is>
@@ -12199,7 +13393,7 @@
           <t>同名があるときに付ける文字</t>
         </is>
       </c>
-      <c r="B4" s="77" t="inlineStr">
+      <c r="B4" s="83" t="inlineStr">
         <is>
           <t>_</t>
         </is>
@@ -12211,7 +13405,7 @@
           <t>メッセージ：請求期間が未入力</t>
         </is>
       </c>
-      <c r="B5" s="77" t="inlineStr">
+      <c r="B5" s="83" t="inlineStr">
         <is>
           <t>請求期間の開始日と終了日を、入力シートの「請求期間（始）」「請求期間（終）」に入力してください。</t>
         </is>
@@ -12223,7 +13417,7 @@
           <t>メッセージ：開始日が終了日より後</t>
         </is>
       </c>
-      <c r="B6" s="77" t="inlineStr">
+      <c r="B6" s="83" t="inlineStr">
         <is>
           <t>請求期間の開始日が終了日より後になっています。</t>
         </is>
@@ -12235,7 +13429,7 @@
           <t>メッセージ：該当する行がない</t>
         </is>
       </c>
-      <c r="B7" s="77" t="inlineStr">
+      <c r="B7" s="83" t="inlineStr">
         <is>
           <t>この請求期間に該当する算定表の行がありません。入力シートと算定表を確認してください。</t>
         </is>
@@ -12247,7 +13441,7 @@
           <t>メッセージ：行が多すぎる</t>
         </is>
       </c>
-      <c r="B8" s="77" t="inlineStr">
+      <c r="B8" s="83" t="inlineStr">
         <is>
           <t>行数が雛形に入りきりません。請求期間を短くしてください。</t>
         </is>
@@ -12259,7 +13453,7 @@
           <t>メッセージ：完了</t>
         </is>
       </c>
-      <c r="B9" s="77" t="inlineStr">
+      <c r="B9" s="83" t="inlineStr">
         <is>
           <t>請求シートを追加しました。</t>
         </is>
@@ -12271,7 +13465,7 @@
           <t>シート名の期間の区切り</t>
         </is>
       </c>
-      <c r="B10" s="77" t="inlineStr">
+      <c r="B10" s="83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12283,7 +13477,7 @@
           <t>雛形のシート名（コピー元）</t>
         </is>
       </c>
-      <c r="B11" s="77" t="inlineStr">
+      <c r="B11" s="83" t="inlineStr">
         <is>
           <t>請求シート雛形</t>
         </is>
@@ -12295,7 +13489,7 @@
           <t>雛形：明細の先頭行</t>
         </is>
       </c>
-      <c r="B12" s="78" t="n">
+      <c r="B12" s="84" t="n">
         <v>10</v>
       </c>
     </row>
@@ -12305,7 +13499,7 @@
           <t>雛形：明細の行数</t>
         </is>
       </c>
-      <c r="B13" s="78" t="n">
+      <c r="B13" s="84" t="n">
         <v>30</v>
       </c>
     </row>

--- a/傷病手当金算定表_v2.xlsx
+++ b/傷病手当金算定表_v2.xlsx
@@ -54,7 +54,7 @@
     <numFmt numFmtId="167" formatCode="yyyy/m/d"/>
     <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="169" formatCode="0&quot;か月&quot;"/>
-    <numFmt numFmtId="170" formatCode="0&quot;日（土日除く）&quot;"/>
+    <numFmt numFmtId="170" formatCode="0&quot;日&quot;"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -11864,7 +11864,7 @@
     <row r="8">
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>出勤による延長（月数／日数）</t>
+          <t>出勤による延長（月数／土日を除く日数）</t>
         </is>
       </c>
       <c r="N8" s="80" t="n"/>

--- a/傷病手当金算定表_v2.xlsx
+++ b/傷病手当金算定表_v2.xlsx
@@ -56,7 +56,7 @@
     <numFmt numFmtId="169" formatCode="0&quot;か月&quot;"/>
     <numFmt numFmtId="170" formatCode="0&quot;日&quot;"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -171,19 +171,8 @@
     </font>
     <font>
       <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFC00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
       <i val="1"/>
       <color rgb="FF595959"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -205,7 +194,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -240,11 +229,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
         <bgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -323,9 +307,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -448,12 +432,7 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="18" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -463,7 +442,7 @@
     <xf numFmtId="167" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -476,7 +455,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -498,7 +477,7 @@
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -510,7 +489,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="Normal" xfId="1" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Meiryo UI"/>
@@ -520,6 +499,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="00E2EFDA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -928,7 +917,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>・給付期間：待機3日の後に支給開始、法定給付は1年6か月、附加給付は続く6か月（傷病手当金・附加金マニュアルによる）。出勤期間があれば、丸ごと1か月は1か月、残りは土日を除く日数だけ延びます。</t>
+          <t>・給付期間：待機3日の後に支給開始、法定給付は1年6か月、附加給付は続く6か月（傷病手当金・附加金マニュアルによる）。月の数え方は民法第140条（初日不算入）で、末日は応当日です。出勤期間があれば、丸ごと1か月は1か月、残りは土日を除く日数だけ延びます。</t>
         </is>
       </c>
     </row>
@@ -1018,6 +1007,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>※期間の数え方は民法第140条（初日不算入）。法定給付の末日は、支給開始日から1年6か月後の応当日（例：7/25 → 翌々年1/25）。</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -1121,7 +1117,7 @@
         </is>
       </c>
       <c r="J8" s="15">
-        <f>WORKDAY(EDATE(DATE(YEAR(J7),MONTH(J7)+6,DAY(J7)-1),MAX($I$85:$I$95)),MAX($J$85:$J$95))</f>
+        <f>WORKDAY(EDATE(J6,6+MAX($I$85:$I$95)),MAX($J$85:$J$95))</f>
         <v/>
       </c>
     </row>
@@ -1781,6 +1777,10 @@
       <c r="E37" s="28" t="n"/>
       <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
+      <c r="H37" s="60">
+        <f>IF($A37=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A37&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="49">
@@ -1795,6 +1795,10 @@
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
       <c r="G38" s="28" t="n"/>
+      <c r="H38" s="60">
+        <f>IF($A38=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A38&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="49">
@@ -1809,6 +1813,10 @@
       <c r="E39" s="28" t="n"/>
       <c r="F39" s="28" t="n"/>
       <c r="G39" s="28" t="n"/>
+      <c r="H39" s="60">
+        <f>IF($A39=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A39&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="49">
@@ -1823,6 +1831,10 @@
       <c r="E40" s="28" t="n"/>
       <c r="F40" s="28" t="n"/>
       <c r="G40" s="28" t="n"/>
+      <c r="H40" s="60">
+        <f>IF($A40=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A40&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="49">
@@ -1837,6 +1849,10 @@
       <c r="E41" s="28" t="n"/>
       <c r="F41" s="28" t="n"/>
       <c r="G41" s="28" t="n"/>
+      <c r="H41" s="60">
+        <f>IF($A41=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A41&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="49">
@@ -1851,6 +1867,10 @@
       <c r="E42" s="28" t="n"/>
       <c r="F42" s="28" t="n"/>
       <c r="G42" s="28" t="n"/>
+      <c r="H42" s="60">
+        <f>IF($A42=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A42&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="49">
@@ -1865,6 +1885,10 @@
       <c r="E43" s="28" t="n"/>
       <c r="F43" s="28" t="n"/>
       <c r="G43" s="28" t="n"/>
+      <c r="H43" s="60">
+        <f>IF($A43=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A43&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="49">
@@ -1879,6 +1903,10 @@
       <c r="E44" s="28" t="n"/>
       <c r="F44" s="28" t="n"/>
       <c r="G44" s="28" t="n"/>
+      <c r="H44" s="60">
+        <f>IF($A44=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A44&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="49">
@@ -1893,6 +1921,10 @@
       <c r="E45" s="28" t="n"/>
       <c r="F45" s="28" t="n"/>
       <c r="G45" s="28" t="n"/>
+      <c r="H45" s="60">
+        <f>IF($A45=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A45&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="49">
@@ -1907,6 +1939,10 @@
       <c r="E46" s="28" t="n"/>
       <c r="F46" s="28" t="n"/>
       <c r="G46" s="28" t="n"/>
+      <c r="H46" s="60">
+        <f>IF($A46=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A46&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="49">
@@ -1921,6 +1957,10 @@
       <c r="E47" s="28" t="n"/>
       <c r="F47" s="28" t="n"/>
       <c r="G47" s="28" t="n"/>
+      <c r="H47" s="60">
+        <f>IF($A47=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A47&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="49">
@@ -1950,39 +1990,42 @@
         <f>ROUND(F48,0)</f>
         <v/>
       </c>
+      <c r="H48" s="60">
+        <f>IF($A48=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A48&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="60">
+      <c r="A49" s="49">
         <f>DATE(YEAR($J$5),MONTH($J$5)-12+12,1)</f>
         <v/>
       </c>
       <c r="B49" s="47" t="n">
         <v>320000</v>
       </c>
-      <c r="C49" s="61">
+      <c r="C49" s="48">
         <f>AVERAGE(B38:B49)</f>
         <v/>
       </c>
-      <c r="D49" s="62">
+      <c r="D49" s="50">
         <f>C49/22</f>
         <v/>
       </c>
-      <c r="E49" s="61">
+      <c r="E49" s="48">
         <f>ROUND(D49,-1)</f>
         <v/>
       </c>
-      <c r="F49" s="62">
+      <c r="F49" s="50">
         <f>E49/3*2</f>
         <v/>
       </c>
-      <c r="G49" s="63">
+      <c r="G49" s="48">
         <f>ROUND(F49,0)</f>
         <v/>
       </c>
-      <c r="H49" s="64" t="inlineStr">
-        <is>
-          <t>← 支給開始月の額を、全期間の傷病手当日額として固定して使います</t>
-        </is>
+      <c r="H49" s="60">
+        <f>IF($A49=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A49&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -2013,10 +2056,9 @@
         <f>ROUND(F50,0)</f>
         <v/>
       </c>
-      <c r="H50" s="65" t="inlineStr">
-        <is>
-          <t>↓ これより後の月は参考（算定には使いません。月ごとの日額を見る用）</t>
-        </is>
+      <c r="H50" s="60">
+        <f>IF($A50=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A50&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -2047,6 +2089,10 @@
         <f>ROUND(F51,0)</f>
         <v/>
       </c>
+      <c r="H51" s="60">
+        <f>IF($A51=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A51&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="49">
@@ -2076,6 +2122,10 @@
         <f>ROUND(F52,0)</f>
         <v/>
       </c>
+      <c r="H52" s="60">
+        <f>IF($A52=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A52&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="49">
@@ -2105,6 +2155,10 @@
         <f>ROUND(F53,0)</f>
         <v/>
       </c>
+      <c r="H53" s="60">
+        <f>IF($A53=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A53&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="49">
@@ -2134,6 +2188,10 @@
         <f>ROUND(F54,0)</f>
         <v/>
       </c>
+      <c r="H54" s="60">
+        <f>IF($A54=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A54&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="49">
@@ -2163,6 +2221,10 @@
         <f>ROUND(F55,0)</f>
         <v/>
       </c>
+      <c r="H55" s="60">
+        <f>IF($A55=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A55&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="49">
@@ -2192,6 +2254,10 @@
         <f>ROUND(F56,0)</f>
         <v/>
       </c>
+      <c r="H56" s="60">
+        <f>IF($A56=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A56&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="49">
@@ -2221,6 +2287,10 @@
         <f>ROUND(F57,0)</f>
         <v/>
       </c>
+      <c r="H57" s="60">
+        <f>IF($A57=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A57&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="49">
@@ -2250,6 +2320,10 @@
         <f>ROUND(F58,0)</f>
         <v/>
       </c>
+      <c r="H58" s="60">
+        <f>IF($A58=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A58&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="49">
@@ -2279,6 +2353,10 @@
         <f>ROUND(F59,0)</f>
         <v/>
       </c>
+      <c r="H59" s="60">
+        <f>IF($A59=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A59&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="49">
@@ -2308,6 +2386,10 @@
         <f>ROUND(F60,0)</f>
         <v/>
       </c>
+      <c r="H60" s="60">
+        <f>IF($A60=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A60&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="49">
@@ -2337,6 +2419,10 @@
         <f>ROUND(F61,0)</f>
         <v/>
       </c>
+      <c r="H61" s="60">
+        <f>IF($A61=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A61&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="49">
@@ -2366,6 +2452,10 @@
         <f>ROUND(F62,0)</f>
         <v/>
       </c>
+      <c r="H62" s="60">
+        <f>IF($A62=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A62&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="49">
@@ -2395,6 +2485,10 @@
         <f>ROUND(F63,0)</f>
         <v/>
       </c>
+      <c r="H63" s="60">
+        <f>IF($A63=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A63&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="49">
@@ -2424,6 +2518,10 @@
         <f>ROUND(F64,0)</f>
         <v/>
       </c>
+      <c r="H64" s="60">
+        <f>IF($A64=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A64&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="49">
@@ -2453,6 +2551,10 @@
         <f>ROUND(F65,0)</f>
         <v/>
       </c>
+      <c r="H65" s="60">
+        <f>IF($A65=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A65&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="49">
@@ -2482,6 +2584,10 @@
         <f>ROUND(F66,0)</f>
         <v/>
       </c>
+      <c r="H66" s="60">
+        <f>IF($A66=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A66&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="49">
@@ -2511,6 +2617,10 @@
         <f>ROUND(F67,0)</f>
         <v/>
       </c>
+      <c r="H67" s="60">
+        <f>IF($A67=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A67&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="49">
@@ -2540,6 +2650,10 @@
         <f>ROUND(F68,0)</f>
         <v/>
       </c>
+      <c r="H68" s="60">
+        <f>IF($A68=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A68&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="49">
@@ -2569,6 +2683,10 @@
         <f>ROUND(F69,0)</f>
         <v/>
       </c>
+      <c r="H69" s="60">
+        <f>IF($A69=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A69&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="49">
@@ -2598,6 +2716,10 @@
         <f>ROUND(F70,0)</f>
         <v/>
       </c>
+      <c r="H70" s="60">
+        <f>IF($A70=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A70&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="49">
@@ -2627,6 +2749,10 @@
         <f>ROUND(F71,0)</f>
         <v/>
       </c>
+      <c r="H71" s="60">
+        <f>IF($A71=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A71&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="49">
@@ -2656,6 +2782,10 @@
         <f>ROUND(F72,0)</f>
         <v/>
       </c>
+      <c r="H72" s="60">
+        <f>IF($A72=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A72&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="49">
@@ -2685,6 +2815,10 @@
         <f>ROUND(F73,0)</f>
         <v/>
       </c>
+      <c r="H73" s="60">
+        <f>IF($A73=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A73&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="49">
@@ -2714,6 +2848,10 @@
         <f>ROUND(F74,0)</f>
         <v/>
       </c>
+      <c r="H74" s="60">
+        <f>IF($A74=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A74&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="49">
@@ -2743,6 +2881,10 @@
         <f>ROUND(F75,0)</f>
         <v/>
       </c>
+      <c r="H75" s="60">
+        <f>IF($A75=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A75&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="49">
@@ -2772,6 +2914,10 @@
         <f>ROUND(F76,0)</f>
         <v/>
       </c>
+      <c r="H76" s="60">
+        <f>IF($A76=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A76&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="49">
@@ -2801,6 +2947,10 @@
         <f>ROUND(F77,0)</f>
         <v/>
       </c>
+      <c r="H77" s="60">
+        <f>IF($A77=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A77&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="49">
@@ -2830,6 +2980,10 @@
         <f>ROUND(F78,0)</f>
         <v/>
       </c>
+      <c r="H78" s="60">
+        <f>IF($A78=DATE(YEAR($J$5),MONTH($J$5),1),IF($C$8&lt;&gt;"","← 確認値（C8）の額を、全期間の傷病手当日額として固定して使います","← 支給開始月の額を、全期間の傷病手当日額として固定して使います"),IF($A78&gt;DATE(YEAR($J$5),MONTH($J$5),1),"参考（算定には使いません）",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
@@ -2930,7 +3084,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="66" t="inlineStr">
+      <c r="A85" s="61" t="inlineStr">
         <is>
           <t>基準・合計</t>
         </is>
@@ -2958,19 +3112,19 @@
       <c r="J85" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="K85" s="67">
-        <f>DATE(YEAR($J$5)+1,MONTH($J$5)+6,DAY($J$5)-1)</f>
+      <c r="K85" s="62">
+        <f>EDATE($J$5,18)</f>
         <v/>
       </c>
       <c r="L85" s="28" t="n"/>
       <c r="M85" s="28" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="66" t="n">
+      <c r="A86" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="B86" s="68" t="n"/>
-      <c r="C86" s="68" t="n"/>
+      <c r="B86" s="63" t="n"/>
+      <c r="C86" s="63" t="n"/>
       <c r="D86" s="48">
         <f>IF(OR(L86="",M86=""),0,IF(L86&gt;M86,0,(YEAR(M86)-YEAR(L86))*12+MONTH(M86)-MONTH(L86)+1))</f>
         <v/>
@@ -2979,8 +3133,8 @@
         <f>IF(OR(B86="",C86="",C86&lt;B86),0,NETWORKDAYS(B86,C86)-IF(D86&gt;0,NETWORKDAYS(L86,M86),0))</f>
         <v/>
       </c>
-      <c r="F86" s="66">
-        <f>IF(OR(B86="",C86=""),"",IF(C86&lt;B86,"日付エラー",IF(B86&lt;$J$5,"対象外",IF(B86&lt;=K85,"法定",IF(B86&lt;=WORKDAY(EDATE(DATE(YEAR(K85+1),MONTH(K85+1)+6,DAY(K85+1)-1),I85),J85),"附加","対象外")))))</f>
+      <c r="F86" s="61">
+        <f>IF(OR(B86="",C86=""),"",IF(C86&lt;B86,"日付エラー",IF(B86&lt;$J$5,"対象外",IF(B86&lt;=K85,"法定",IF(B86&lt;=WORKDAY(EDATE(K85,6+I85),J85),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G86" s="48">
@@ -2999,25 +3153,25 @@
         <f>J85+IF(F86="附加",E86,0)</f>
         <v/>
       </c>
-      <c r="K86" s="67">
+      <c r="K86" s="62">
         <f>WORKDAY(EDATE($K$85,G86),H86)</f>
         <v/>
       </c>
-      <c r="L86" s="67">
+      <c r="L86" s="62">
         <f>IF(OR(B86="",C86="",C86&lt;B86),"",IF(DAY(B86)=1,B86,EOMONTH(B86,0)+1))</f>
         <v/>
       </c>
-      <c r="M86" s="67">
+      <c r="M86" s="62">
         <f>IF(OR(B86="",C86="",C86&lt;B86),"",IF(C86=EOMONTH(C86,0),C86,EOMONTH(C86,-1)))</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="66" t="n">
+      <c r="A87" s="61" t="n">
         <v>2</v>
       </c>
-      <c r="B87" s="68" t="n"/>
-      <c r="C87" s="68" t="n"/>
+      <c r="B87" s="63" t="n"/>
+      <c r="C87" s="63" t="n"/>
       <c r="D87" s="48">
         <f>IF(OR(L87="",M87=""),0,IF(L87&gt;M87,0,(YEAR(M87)-YEAR(L87))*12+MONTH(M87)-MONTH(L87)+1))</f>
         <v/>
@@ -3026,8 +3180,8 @@
         <f>IF(OR(B87="",C87="",C87&lt;B87),0,NETWORKDAYS(B87,C87)-IF(D87&gt;0,NETWORKDAYS(L87,M87),0))</f>
         <v/>
       </c>
-      <c r="F87" s="66">
-        <f>IF(OR(B87="",C87=""),"",IF(C87&lt;B87,"日付エラー",IF(B87&lt;$J$5,"対象外",IF(B87&lt;=K86,"法定",IF(B87&lt;=WORKDAY(EDATE(DATE(YEAR(K86+1),MONTH(K86+1)+6,DAY(K86+1)-1),I86),J86),"附加","対象外")))))</f>
+      <c r="F87" s="61">
+        <f>IF(OR(B87="",C87=""),"",IF(C87&lt;B87,"日付エラー",IF(B87&lt;$J$5,"対象外",IF(B87&lt;=K86,"法定",IF(B87&lt;=WORKDAY(EDATE(K86,6+I86),J86),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G87" s="48">
@@ -3046,25 +3200,25 @@
         <f>J86+IF(F87="附加",E87,0)</f>
         <v/>
       </c>
-      <c r="K87" s="67">
+      <c r="K87" s="62">
         <f>WORKDAY(EDATE($K$85,G87),H87)</f>
         <v/>
       </c>
-      <c r="L87" s="67">
+      <c r="L87" s="62">
         <f>IF(OR(B87="",C87="",C87&lt;B87),"",IF(DAY(B87)=1,B87,EOMONTH(B87,0)+1))</f>
         <v/>
       </c>
-      <c r="M87" s="67">
+      <c r="M87" s="62">
         <f>IF(OR(B87="",C87="",C87&lt;B87),"",IF(C87=EOMONTH(C87,0),C87,EOMONTH(C87,-1)))</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="66" t="n">
+      <c r="A88" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="B88" s="68" t="n"/>
-      <c r="C88" s="68" t="n"/>
+      <c r="B88" s="63" t="n"/>
+      <c r="C88" s="63" t="n"/>
       <c r="D88" s="48">
         <f>IF(OR(L88="",M88=""),0,IF(L88&gt;M88,0,(YEAR(M88)-YEAR(L88))*12+MONTH(M88)-MONTH(L88)+1))</f>
         <v/>
@@ -3073,8 +3227,8 @@
         <f>IF(OR(B88="",C88="",C88&lt;B88),0,NETWORKDAYS(B88,C88)-IF(D88&gt;0,NETWORKDAYS(L88,M88),0))</f>
         <v/>
       </c>
-      <c r="F88" s="66">
-        <f>IF(OR(B88="",C88=""),"",IF(C88&lt;B88,"日付エラー",IF(B88&lt;$J$5,"対象外",IF(B88&lt;=K87,"法定",IF(B88&lt;=WORKDAY(EDATE(DATE(YEAR(K87+1),MONTH(K87+1)+6,DAY(K87+1)-1),I87),J87),"附加","対象外")))))</f>
+      <c r="F88" s="61">
+        <f>IF(OR(B88="",C88=""),"",IF(C88&lt;B88,"日付エラー",IF(B88&lt;$J$5,"対象外",IF(B88&lt;=K87,"法定",IF(B88&lt;=WORKDAY(EDATE(K87,6+I87),J87),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G88" s="48">
@@ -3093,25 +3247,25 @@
         <f>J87+IF(F88="附加",E88,0)</f>
         <v/>
       </c>
-      <c r="K88" s="67">
+      <c r="K88" s="62">
         <f>WORKDAY(EDATE($K$85,G88),H88)</f>
         <v/>
       </c>
-      <c r="L88" s="67">
+      <c r="L88" s="62">
         <f>IF(OR(B88="",C88="",C88&lt;B88),"",IF(DAY(B88)=1,B88,EOMONTH(B88,0)+1))</f>
         <v/>
       </c>
-      <c r="M88" s="67">
+      <c r="M88" s="62">
         <f>IF(OR(B88="",C88="",C88&lt;B88),"",IF(C88=EOMONTH(C88,0),C88,EOMONTH(C88,-1)))</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="66" t="n">
+      <c r="A89" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="B89" s="68" t="n"/>
-      <c r="C89" s="68" t="n"/>
+      <c r="B89" s="63" t="n"/>
+      <c r="C89" s="63" t="n"/>
       <c r="D89" s="48">
         <f>IF(OR(L89="",M89=""),0,IF(L89&gt;M89,0,(YEAR(M89)-YEAR(L89))*12+MONTH(M89)-MONTH(L89)+1))</f>
         <v/>
@@ -3120,8 +3274,8 @@
         <f>IF(OR(B89="",C89="",C89&lt;B89),0,NETWORKDAYS(B89,C89)-IF(D89&gt;0,NETWORKDAYS(L89,M89),0))</f>
         <v/>
       </c>
-      <c r="F89" s="66">
-        <f>IF(OR(B89="",C89=""),"",IF(C89&lt;B89,"日付エラー",IF(B89&lt;$J$5,"対象外",IF(B89&lt;=K88,"法定",IF(B89&lt;=WORKDAY(EDATE(DATE(YEAR(K88+1),MONTH(K88+1)+6,DAY(K88+1)-1),I88),J88),"附加","対象外")))))</f>
+      <c r="F89" s="61">
+        <f>IF(OR(B89="",C89=""),"",IF(C89&lt;B89,"日付エラー",IF(B89&lt;$J$5,"対象外",IF(B89&lt;=K88,"法定",IF(B89&lt;=WORKDAY(EDATE(K88,6+I88),J88),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G89" s="48">
@@ -3140,25 +3294,25 @@
         <f>J88+IF(F89="附加",E89,0)</f>
         <v/>
       </c>
-      <c r="K89" s="67">
+      <c r="K89" s="62">
         <f>WORKDAY(EDATE($K$85,G89),H89)</f>
         <v/>
       </c>
-      <c r="L89" s="67">
+      <c r="L89" s="62">
         <f>IF(OR(B89="",C89="",C89&lt;B89),"",IF(DAY(B89)=1,B89,EOMONTH(B89,0)+1))</f>
         <v/>
       </c>
-      <c r="M89" s="67">
+      <c r="M89" s="62">
         <f>IF(OR(B89="",C89="",C89&lt;B89),"",IF(C89=EOMONTH(C89,0),C89,EOMONTH(C89,-1)))</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="66" t="n">
+      <c r="A90" s="61" t="n">
         <v>5</v>
       </c>
-      <c r="B90" s="68" t="n"/>
-      <c r="C90" s="68" t="n"/>
+      <c r="B90" s="63" t="n"/>
+      <c r="C90" s="63" t="n"/>
       <c r="D90" s="48">
         <f>IF(OR(L90="",M90=""),0,IF(L90&gt;M90,0,(YEAR(M90)-YEAR(L90))*12+MONTH(M90)-MONTH(L90)+1))</f>
         <v/>
@@ -3167,8 +3321,8 @@
         <f>IF(OR(B90="",C90="",C90&lt;B90),0,NETWORKDAYS(B90,C90)-IF(D90&gt;0,NETWORKDAYS(L90,M90),0))</f>
         <v/>
       </c>
-      <c r="F90" s="66">
-        <f>IF(OR(B90="",C90=""),"",IF(C90&lt;B90,"日付エラー",IF(B90&lt;$J$5,"対象外",IF(B90&lt;=K89,"法定",IF(B90&lt;=WORKDAY(EDATE(DATE(YEAR(K89+1),MONTH(K89+1)+6,DAY(K89+1)-1),I89),J89),"附加","対象外")))))</f>
+      <c r="F90" s="61">
+        <f>IF(OR(B90="",C90=""),"",IF(C90&lt;B90,"日付エラー",IF(B90&lt;$J$5,"対象外",IF(B90&lt;=K89,"法定",IF(B90&lt;=WORKDAY(EDATE(K89,6+I89),J89),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G90" s="48">
@@ -3187,25 +3341,25 @@
         <f>J89+IF(F90="附加",E90,0)</f>
         <v/>
       </c>
-      <c r="K90" s="67">
+      <c r="K90" s="62">
         <f>WORKDAY(EDATE($K$85,G90),H90)</f>
         <v/>
       </c>
-      <c r="L90" s="67">
+      <c r="L90" s="62">
         <f>IF(OR(B90="",C90="",C90&lt;B90),"",IF(DAY(B90)=1,B90,EOMONTH(B90,0)+1))</f>
         <v/>
       </c>
-      <c r="M90" s="67">
+      <c r="M90" s="62">
         <f>IF(OR(B90="",C90="",C90&lt;B90),"",IF(C90=EOMONTH(C90,0),C90,EOMONTH(C90,-1)))</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="66" t="n">
+      <c r="A91" s="61" t="n">
         <v>6</v>
       </c>
-      <c r="B91" s="68" t="n"/>
-      <c r="C91" s="68" t="n"/>
+      <c r="B91" s="63" t="n"/>
+      <c r="C91" s="63" t="n"/>
       <c r="D91" s="48">
         <f>IF(OR(L91="",M91=""),0,IF(L91&gt;M91,0,(YEAR(M91)-YEAR(L91))*12+MONTH(M91)-MONTH(L91)+1))</f>
         <v/>
@@ -3214,8 +3368,8 @@
         <f>IF(OR(B91="",C91="",C91&lt;B91),0,NETWORKDAYS(B91,C91)-IF(D91&gt;0,NETWORKDAYS(L91,M91),0))</f>
         <v/>
       </c>
-      <c r="F91" s="66">
-        <f>IF(OR(B91="",C91=""),"",IF(C91&lt;B91,"日付エラー",IF(B91&lt;$J$5,"対象外",IF(B91&lt;=K90,"法定",IF(B91&lt;=WORKDAY(EDATE(DATE(YEAR(K90+1),MONTH(K90+1)+6,DAY(K90+1)-1),I90),J90),"附加","対象外")))))</f>
+      <c r="F91" s="61">
+        <f>IF(OR(B91="",C91=""),"",IF(C91&lt;B91,"日付エラー",IF(B91&lt;$J$5,"対象外",IF(B91&lt;=K90,"法定",IF(B91&lt;=WORKDAY(EDATE(K90,6+I90),J90),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G91" s="48">
@@ -3234,25 +3388,25 @@
         <f>J90+IF(F91="附加",E91,0)</f>
         <v/>
       </c>
-      <c r="K91" s="67">
+      <c r="K91" s="62">
         <f>WORKDAY(EDATE($K$85,G91),H91)</f>
         <v/>
       </c>
-      <c r="L91" s="67">
+      <c r="L91" s="62">
         <f>IF(OR(B91="",C91="",C91&lt;B91),"",IF(DAY(B91)=1,B91,EOMONTH(B91,0)+1))</f>
         <v/>
       </c>
-      <c r="M91" s="67">
+      <c r="M91" s="62">
         <f>IF(OR(B91="",C91="",C91&lt;B91),"",IF(C91=EOMONTH(C91,0),C91,EOMONTH(C91,-1)))</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="66" t="n">
+      <c r="A92" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="B92" s="68" t="n"/>
-      <c r="C92" s="68" t="n"/>
+      <c r="B92" s="63" t="n"/>
+      <c r="C92" s="63" t="n"/>
       <c r="D92" s="48">
         <f>IF(OR(L92="",M92=""),0,IF(L92&gt;M92,0,(YEAR(M92)-YEAR(L92))*12+MONTH(M92)-MONTH(L92)+1))</f>
         <v/>
@@ -3261,8 +3415,8 @@
         <f>IF(OR(B92="",C92="",C92&lt;B92),0,NETWORKDAYS(B92,C92)-IF(D92&gt;0,NETWORKDAYS(L92,M92),0))</f>
         <v/>
       </c>
-      <c r="F92" s="66">
-        <f>IF(OR(B92="",C92=""),"",IF(C92&lt;B92,"日付エラー",IF(B92&lt;$J$5,"対象外",IF(B92&lt;=K91,"法定",IF(B92&lt;=WORKDAY(EDATE(DATE(YEAR(K91+1),MONTH(K91+1)+6,DAY(K91+1)-1),I91),J91),"附加","対象外")))))</f>
+      <c r="F92" s="61">
+        <f>IF(OR(B92="",C92=""),"",IF(C92&lt;B92,"日付エラー",IF(B92&lt;$J$5,"対象外",IF(B92&lt;=K91,"法定",IF(B92&lt;=WORKDAY(EDATE(K91,6+I91),J91),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G92" s="48">
@@ -3281,25 +3435,25 @@
         <f>J91+IF(F92="附加",E92,0)</f>
         <v/>
       </c>
-      <c r="K92" s="67">
+      <c r="K92" s="62">
         <f>WORKDAY(EDATE($K$85,G92),H92)</f>
         <v/>
       </c>
-      <c r="L92" s="67">
+      <c r="L92" s="62">
         <f>IF(OR(B92="",C92="",C92&lt;B92),"",IF(DAY(B92)=1,B92,EOMONTH(B92,0)+1))</f>
         <v/>
       </c>
-      <c r="M92" s="67">
+      <c r="M92" s="62">
         <f>IF(OR(B92="",C92="",C92&lt;B92),"",IF(C92=EOMONTH(C92,0),C92,EOMONTH(C92,-1)))</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="66" t="n">
+      <c r="A93" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="B93" s="68" t="n"/>
-      <c r="C93" s="68" t="n"/>
+      <c r="B93" s="63" t="n"/>
+      <c r="C93" s="63" t="n"/>
       <c r="D93" s="48">
         <f>IF(OR(L93="",M93=""),0,IF(L93&gt;M93,0,(YEAR(M93)-YEAR(L93))*12+MONTH(M93)-MONTH(L93)+1))</f>
         <v/>
@@ -3308,8 +3462,8 @@
         <f>IF(OR(B93="",C93="",C93&lt;B93),0,NETWORKDAYS(B93,C93)-IF(D93&gt;0,NETWORKDAYS(L93,M93),0))</f>
         <v/>
       </c>
-      <c r="F93" s="66">
-        <f>IF(OR(B93="",C93=""),"",IF(C93&lt;B93,"日付エラー",IF(B93&lt;$J$5,"対象外",IF(B93&lt;=K92,"法定",IF(B93&lt;=WORKDAY(EDATE(DATE(YEAR(K92+1),MONTH(K92+1)+6,DAY(K92+1)-1),I92),J92),"附加","対象外")))))</f>
+      <c r="F93" s="61">
+        <f>IF(OR(B93="",C93=""),"",IF(C93&lt;B93,"日付エラー",IF(B93&lt;$J$5,"対象外",IF(B93&lt;=K92,"法定",IF(B93&lt;=WORKDAY(EDATE(K92,6+I92),J92),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G93" s="48">
@@ -3328,25 +3482,25 @@
         <f>J92+IF(F93="附加",E93,0)</f>
         <v/>
       </c>
-      <c r="K93" s="67">
+      <c r="K93" s="62">
         <f>WORKDAY(EDATE($K$85,G93),H93)</f>
         <v/>
       </c>
-      <c r="L93" s="67">
+      <c r="L93" s="62">
         <f>IF(OR(B93="",C93="",C93&lt;B93),"",IF(DAY(B93)=1,B93,EOMONTH(B93,0)+1))</f>
         <v/>
       </c>
-      <c r="M93" s="67">
+      <c r="M93" s="62">
         <f>IF(OR(B93="",C93="",C93&lt;B93),"",IF(C93=EOMONTH(C93,0),C93,EOMONTH(C93,-1)))</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="66" t="n">
+      <c r="A94" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="B94" s="68" t="n"/>
-      <c r="C94" s="68" t="n"/>
+      <c r="B94" s="63" t="n"/>
+      <c r="C94" s="63" t="n"/>
       <c r="D94" s="48">
         <f>IF(OR(L94="",M94=""),0,IF(L94&gt;M94,0,(YEAR(M94)-YEAR(L94))*12+MONTH(M94)-MONTH(L94)+1))</f>
         <v/>
@@ -3355,8 +3509,8 @@
         <f>IF(OR(B94="",C94="",C94&lt;B94),0,NETWORKDAYS(B94,C94)-IF(D94&gt;0,NETWORKDAYS(L94,M94),0))</f>
         <v/>
       </c>
-      <c r="F94" s="66">
-        <f>IF(OR(B94="",C94=""),"",IF(C94&lt;B94,"日付エラー",IF(B94&lt;$J$5,"対象外",IF(B94&lt;=K93,"法定",IF(B94&lt;=WORKDAY(EDATE(DATE(YEAR(K93+1),MONTH(K93+1)+6,DAY(K93+1)-1),I93),J93),"附加","対象外")))))</f>
+      <c r="F94" s="61">
+        <f>IF(OR(B94="",C94=""),"",IF(C94&lt;B94,"日付エラー",IF(B94&lt;$J$5,"対象外",IF(B94&lt;=K93,"法定",IF(B94&lt;=WORKDAY(EDATE(K93,6+I93),J93),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G94" s="48">
@@ -3375,25 +3529,25 @@
         <f>J93+IF(F94="附加",E94,0)</f>
         <v/>
       </c>
-      <c r="K94" s="67">
+      <c r="K94" s="62">
         <f>WORKDAY(EDATE($K$85,G94),H94)</f>
         <v/>
       </c>
-      <c r="L94" s="67">
+      <c r="L94" s="62">
         <f>IF(OR(B94="",C94="",C94&lt;B94),"",IF(DAY(B94)=1,B94,EOMONTH(B94,0)+1))</f>
         <v/>
       </c>
-      <c r="M94" s="67">
+      <c r="M94" s="62">
         <f>IF(OR(B94="",C94="",C94&lt;B94),"",IF(C94=EOMONTH(C94,0),C94,EOMONTH(C94,-1)))</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="66" t="n">
+      <c r="A95" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="B95" s="68" t="n"/>
-      <c r="C95" s="68" t="n"/>
+      <c r="B95" s="63" t="n"/>
+      <c r="C95" s="63" t="n"/>
       <c r="D95" s="48">
         <f>IF(OR(L95="",M95=""),0,IF(L95&gt;M95,0,(YEAR(M95)-YEAR(L95))*12+MONTH(M95)-MONTH(L95)+1))</f>
         <v/>
@@ -3402,8 +3556,8 @@
         <f>IF(OR(B95="",C95="",C95&lt;B95),0,NETWORKDAYS(B95,C95)-IF(D95&gt;0,NETWORKDAYS(L95,M95),0))</f>
         <v/>
       </c>
-      <c r="F95" s="66">
-        <f>IF(OR(B95="",C95=""),"",IF(C95&lt;B95,"日付エラー",IF(B95&lt;$J$5,"対象外",IF(B95&lt;=K94,"法定",IF(B95&lt;=WORKDAY(EDATE(DATE(YEAR(K94+1),MONTH(K94+1)+6,DAY(K94+1)-1),I94),J94),"附加","対象外")))))</f>
+      <c r="F95" s="61">
+        <f>IF(OR(B95="",C95=""),"",IF(C95&lt;B95,"日付エラー",IF(B95&lt;$J$5,"対象外",IF(B95&lt;=K94,"法定",IF(B95&lt;=WORKDAY(EDATE(K94,6+I94),J94),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G95" s="48">
@@ -3422,15 +3576,15 @@
         <f>J94+IF(F95="附加",E95,0)</f>
         <v/>
       </c>
-      <c r="K95" s="67">
+      <c r="K95" s="62">
         <f>WORKDAY(EDATE($K$85,G95),H95)</f>
         <v/>
       </c>
-      <c r="L95" s="67">
+      <c r="L95" s="62">
         <f>IF(OR(B95="",C95="",C95&lt;B95),"",IF(DAY(B95)=1,B95,EOMONTH(B95,0)+1))</f>
         <v/>
       </c>
-      <c r="M95" s="67">
+      <c r="M95" s="62">
         <f>IF(OR(B95="",C95="",C95&lt;B95),"",IF(C95=EOMONTH(C95,0),C95,EOMONTH(C95,-1)))</f>
         <v/>
       </c>
@@ -3462,7 +3616,7 @@
           <t>請求期間（始）</t>
         </is>
       </c>
-      <c r="C100" s="68" t="n"/>
+      <c r="C100" s="63" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
@@ -3470,7 +3624,7 @@
           <t>請求期間（終）</t>
         </is>
       </c>
-      <c r="C101" s="68" t="n"/>
+      <c r="C101" s="63" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
@@ -3493,8 +3647,18 @@
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="A6:B6"/>
   </mergeCells>
+  <conditionalFormatting sqref="A37:G78">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>$A37=DATE(YEAR($J$5),MONTH($J$5),1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H37:H78">
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>$A37=DATE(YEAR($J$5),MONTH($J$5),1)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F86:F95">
-    <cfRule type="expression" priority="1" dxfId="1">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>OR($F86="日付エラー",$F86="対象外")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5275,7 +5439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S72"/>
+  <dimension ref="A1:S73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" style="39" min="1" max="1"/>
@@ -5484,7 +5648,7 @@
         <f>IF(F6="","",M6-N6)</f>
         <v/>
       </c>
-      <c r="P6" s="69">
+      <c r="P6" s="64">
         <f>IF(F6="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B6,C6,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -5562,7 +5726,7 @@
         <f>IF(F7="","",M7-N7)</f>
         <v/>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="64">
         <f>IF(F7="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B7,C7,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -5640,7 +5804,7 @@
         <f>IF(F8="","",M8-N8)</f>
         <v/>
       </c>
-      <c r="P8" s="69">
+      <c r="P8" s="64">
         <f>IF(F8="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B8,C8,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -5718,7 +5882,7 @@
         <f>IF(F9="","",M9-N9)</f>
         <v/>
       </c>
-      <c r="P9" s="69">
+      <c r="P9" s="64">
         <f>IF(F9="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B9,C9,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -5796,7 +5960,7 @@
         <f>IF(F10="","",M10-N10)</f>
         <v/>
       </c>
-      <c r="P10" s="69">
+      <c r="P10" s="64">
         <f>IF(F10="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B10,C10,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -5874,7 +6038,7 @@
         <f>IF(F11="","",M11-N11)</f>
         <v/>
       </c>
-      <c r="P11" s="69">
+      <c r="P11" s="64">
         <f>IF(F11="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B11,C11,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -5952,7 +6116,7 @@
         <f>IF(F12="","",M12-N12)</f>
         <v/>
       </c>
-      <c r="P12" s="69">
+      <c r="P12" s="64">
         <f>IF(F12="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B12,C12,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -6030,7 +6194,7 @@
         <f>IF(F13="","",M13-N13)</f>
         <v/>
       </c>
-      <c r="P13" s="69">
+      <c r="P13" s="64">
         <f>IF(F13="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B13,C13,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -6108,7 +6272,7 @@
         <f>IF(F14="","",M14-N14)</f>
         <v/>
       </c>
-      <c r="P14" s="69">
+      <c r="P14" s="64">
         <f>IF(F14="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B14,C14,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -6186,7 +6350,7 @@
         <f>IF(F15="","",M15-N15)</f>
         <v/>
       </c>
-      <c r="P15" s="69">
+      <c r="P15" s="64">
         <f>IF(F15="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B15,C15,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -6264,7 +6428,7 @@
         <f>IF(F16="","",M16-N16)</f>
         <v/>
       </c>
-      <c r="P16" s="69">
+      <c r="P16" s="64">
         <f>IF(F16="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B16,C16,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -6342,7 +6506,7 @@
         <f>IF(F17="","",M17-N17)</f>
         <v/>
       </c>
-      <c r="P17" s="69">
+      <c r="P17" s="64">
         <f>IF(F17="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B17,C17,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -6420,7 +6584,7 @@
         <f>IF(F18="","",M18-N18)</f>
         <v/>
       </c>
-      <c r="P18" s="69">
+      <c r="P18" s="64">
         <f>IF(F18="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B18,C18,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -6498,7 +6662,7 @@
         <f>IF(F19="","",M19-N19)</f>
         <v/>
       </c>
-      <c r="P19" s="69">
+      <c r="P19" s="64">
         <f>IF(F19="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B19,C19,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -6576,7 +6740,7 @@
         <f>IF(F20="","",M20-N20)</f>
         <v/>
       </c>
-      <c r="P20" s="69">
+      <c r="P20" s="64">
         <f>IF(F20="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B20,C20,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -6654,7 +6818,7 @@
         <f>IF(F21="","",M21-N21)</f>
         <v/>
       </c>
-      <c r="P21" s="69">
+      <c r="P21" s="64">
         <f>IF(F21="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B21,C21,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -6732,7 +6896,7 @@
         <f>IF(F22="","",M22-N22)</f>
         <v/>
       </c>
-      <c r="P22" s="69">
+      <c r="P22" s="64">
         <f>IF(F22="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B22,C22,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -6810,7 +6974,7 @@
         <f>IF(F23="","",M23-N23)</f>
         <v/>
       </c>
-      <c r="P23" s="69">
+      <c r="P23" s="64">
         <f>IF(F23="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B23,C23,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -6888,7 +7052,7 @@
         <f>IF(F24="","",M24-N24)</f>
         <v/>
       </c>
-      <c r="P24" s="69">
+      <c r="P24" s="64">
         <f>IF(F24="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B24,C24,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -6966,7 +7130,7 @@
         <f>IF(F25="","",M25-N25)</f>
         <v/>
       </c>
-      <c r="P25" s="69">
+      <c r="P25" s="64">
         <f>IF(F25="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B25,C25,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -7044,7 +7208,7 @@
         <f>IF(F26="","",M26-N26)</f>
         <v/>
       </c>
-      <c r="P26" s="69">
+      <c r="P26" s="64">
         <f>IF(F26="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B26,C26,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -7122,7 +7286,7 @@
         <f>IF(F27="","",M27-N27)</f>
         <v/>
       </c>
-      <c r="P27" s="69">
+      <c r="P27" s="64">
         <f>IF(F27="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B27,C27,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -7200,7 +7364,7 @@
         <f>IF(F28="","",M28-N28)</f>
         <v/>
       </c>
-      <c r="P28" s="69">
+      <c r="P28" s="64">
         <f>IF(F28="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B28,C28,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -7278,7 +7442,7 @@
         <f>IF(F29="","",M29-N29)</f>
         <v/>
       </c>
-      <c r="P29" s="69">
+      <c r="P29" s="64">
         <f>IF(F29="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B29,C29,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -7356,7 +7520,7 @@
         <f>IF(F30="","",M30-N30)</f>
         <v/>
       </c>
-      <c r="P30" s="69">
+      <c r="P30" s="64">
         <f>IF(F30="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B30,C30,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -7434,7 +7598,7 @@
         <f>IF(F31="","",M31-N31)</f>
         <v/>
       </c>
-      <c r="P31" s="69">
+      <c r="P31" s="64">
         <f>IF(F31="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B31,C31,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -7512,7 +7676,7 @@
         <f>IF(F32="","",M32-N32)</f>
         <v/>
       </c>
-      <c r="P32" s="69">
+      <c r="P32" s="64">
         <f>IF(F32="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B32,C32,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -7590,7 +7754,7 @@
         <f>IF(F33="","",M33-N33)</f>
         <v/>
       </c>
-      <c r="P33" s="69">
+      <c r="P33" s="64">
         <f>IF(F33="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B33,C33,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -7668,7 +7832,7 @@
         <f>IF(F34="","",M34-N34)</f>
         <v/>
       </c>
-      <c r="P34" s="69">
+      <c r="P34" s="64">
         <f>IF(F34="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B34,C34,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -7746,7 +7910,7 @@
         <f>IF(F35="","",M35-N35)</f>
         <v/>
       </c>
-      <c r="P35" s="69">
+      <c r="P35" s="64">
         <f>IF(F35="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B35,C35,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -7824,7 +7988,7 @@
         <f>IF(F36="","",M36-N36)</f>
         <v/>
       </c>
-      <c r="P36" s="69">
+      <c r="P36" s="64">
         <f>IF(F36="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B36,C36,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -7902,7 +8066,7 @@
         <f>IF(F37="","",M37-N37)</f>
         <v/>
       </c>
-      <c r="P37" s="69">
+      <c r="P37" s="64">
         <f>IF(F37="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B37,C37,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -7980,7 +8144,7 @@
         <f>IF(F38="","",M38-N38)</f>
         <v/>
       </c>
-      <c r="P38" s="69">
+      <c r="P38" s="64">
         <f>IF(F38="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B38,C38,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -8058,7 +8222,7 @@
         <f>IF(F39="","",M39-N39)</f>
         <v/>
       </c>
-      <c r="P39" s="69">
+      <c r="P39" s="64">
         <f>IF(F39="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B39,C39,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -8136,7 +8300,7 @@
         <f>IF(F40="","",M40-N40)</f>
         <v/>
       </c>
-      <c r="P40" s="69">
+      <c r="P40" s="64">
         <f>IF(F40="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B40,C40,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -8214,7 +8378,7 @@
         <f>IF(F41="","",M41-N41)</f>
         <v/>
       </c>
-      <c r="P41" s="69">
+      <c r="P41" s="64">
         <f>IF(F41="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B41,C41,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -8292,7 +8456,7 @@
         <f>IF(F42="","",M42-N42)</f>
         <v/>
       </c>
-      <c r="P42" s="69">
+      <c r="P42" s="64">
         <f>IF(F42="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B42,C42,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -8370,7 +8534,7 @@
         <f>IF(F43="","",M43-N43)</f>
         <v/>
       </c>
-      <c r="P43" s="69">
+      <c r="P43" s="64">
         <f>IF(F43="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B43,C43,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -8448,7 +8612,7 @@
         <f>IF(F44="","",M44-N44)</f>
         <v/>
       </c>
-      <c r="P44" s="69">
+      <c r="P44" s="64">
         <f>IF(F44="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B44,C44,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -8526,7 +8690,7 @@
         <f>IF(F45="","",M45-N45)</f>
         <v/>
       </c>
-      <c r="P45" s="69">
+      <c r="P45" s="64">
         <f>IF(F45="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B45,C45,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -8604,7 +8768,7 @@
         <f>IF(F46="","",M46-N46)</f>
         <v/>
       </c>
-      <c r="P46" s="69">
+      <c r="P46" s="64">
         <f>IF(F46="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B46,C46,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -8682,7 +8846,7 @@
         <f>IF(F47="","",M47-N47)</f>
         <v/>
       </c>
-      <c r="P47" s="69">
+      <c r="P47" s="64">
         <f>IF(F47="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B47,C47,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -8760,7 +8924,7 @@
         <f>IF(F48="","",M48-N48)</f>
         <v/>
       </c>
-      <c r="P48" s="69">
+      <c r="P48" s="64">
         <f>IF(F48="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B48,C48,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -8838,7 +9002,7 @@
         <f>IF(F49="","",M49-N49)</f>
         <v/>
       </c>
-      <c r="P49" s="69">
+      <c r="P49" s="64">
         <f>IF(F49="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B49,C49,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -8916,7 +9080,7 @@
         <f>IF(F50="","",M50-N50)</f>
         <v/>
       </c>
-      <c r="P50" s="69">
+      <c r="P50" s="64">
         <f>IF(F50="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B50,C50,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -8994,7 +9158,7 @@
         <f>IF(F51="","",M51-N51)</f>
         <v/>
       </c>
-      <c r="P51" s="69">
+      <c r="P51" s="64">
         <f>IF(F51="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B51,C51,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -9072,7 +9236,7 @@
         <f>IF(F52="","",M52-N52)</f>
         <v/>
       </c>
-      <c r="P52" s="69">
+      <c r="P52" s="64">
         <f>IF(F52="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B52,C52,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -9150,7 +9314,7 @@
         <f>IF(F53="","",M53-N53)</f>
         <v/>
       </c>
-      <c r="P53" s="69">
+      <c r="P53" s="64">
         <f>IF(F53="","",IFERROR(INDEX(入力!$G$37:$G$78,MATCH(DATE(B53,C53,1),入力!$A$37:$A$78,0)),""))</f>
         <v/>
       </c>
@@ -9362,6 +9526,13 @@
       <c r="A72" s="40" t="inlineStr">
         <is>
           <t>・P列「参考」は、その月の標準報酬月額から試算した日額です。月ごとの比較用で、算定（B列）には使いません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="40" t="inlineStr">
+        <is>
+          <t>・期間の数え方は民法第140条（初日不算入）。法定給付の末日＝支給開始日から1年6か月後の応当日、附加給付の末日＝そこからさらに6か月後の応当日です。</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9600,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="70">
+      <c r="A2" s="65">
         <f>DATE(YEAR($G$4),MONTH($G$4),1)</f>
         <v/>
       </c>
@@ -9441,7 +9612,7 @@
         <f>NETWORKDAYS(A2,EOMONTH(A2,0))</f>
         <v/>
       </c>
-      <c r="D2" s="71">
+      <c r="D2" s="66">
         <f>IF(ISNUMBER(MATCH(A2,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
@@ -9452,7 +9623,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="70">
+      <c r="A3" s="65">
         <f>EDATE(A2,1)</f>
         <v/>
       </c>
@@ -9464,7 +9635,7 @@
         <f>NETWORKDAYS(A3,EOMONTH(A3,0))</f>
         <v/>
       </c>
-      <c r="D3" s="71">
+      <c r="D3" s="66">
         <f>IF(ISNUMBER(MATCH(A3,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
@@ -9475,7 +9646,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="70">
+      <c r="A4" s="65">
         <f>EDATE(A3,1)</f>
         <v/>
       </c>
@@ -9487,7 +9658,7 @@
         <f>NETWORKDAYS(A4,EOMONTH(A4,0))</f>
         <v/>
       </c>
-      <c r="D4" s="71">
+      <c r="D4" s="66">
         <f>IF(ISNUMBER(MATCH(A4,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
@@ -9496,7 +9667,7 @@
           <t>作成の開始月</t>
         </is>
       </c>
-      <c r="G4" s="72" t="n">
+      <c r="G4" s="67" t="n">
         <v>43831</v>
       </c>
       <c r="H4" s="11" t="inlineStr">
@@ -9506,7 +9677,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="70">
+      <c r="A5" s="65">
         <f>EDATE(A4,1)</f>
         <v/>
       </c>
@@ -9518,13 +9689,13 @@
         <f>NETWORKDAYS(A5,EOMONTH(A5,0))</f>
         <v/>
       </c>
-      <c r="D5" s="71">
+      <c r="D5" s="66">
         <f>IF(ISNUMBER(MATCH(A5,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="70">
+      <c r="A6" s="65">
         <f>EDATE(A5,1)</f>
         <v/>
       </c>
@@ -9536,7 +9707,7 @@
         <f>NETWORKDAYS(A6,EOMONTH(A6,0))</f>
         <v/>
       </c>
-      <c r="D6" s="71">
+      <c r="D6" s="66">
         <f>IF(ISNUMBER(MATCH(A6,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
@@ -9547,7 +9718,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="70">
+      <c r="A7" s="65">
         <f>EDATE(A6,1)</f>
         <v/>
       </c>
@@ -9559,7 +9730,7 @@
         <f>NETWORKDAYS(A7,EOMONTH(A7,0))</f>
         <v/>
       </c>
-      <c r="D7" s="71">
+      <c r="D7" s="66">
         <f>IF(ISNUMBER(MATCH(A7,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
@@ -9575,7 +9746,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="70">
+      <c r="A8" s="65">
         <f>EDATE(A7,1)</f>
         <v/>
       </c>
@@ -9587,19 +9758,19 @@
         <f>NETWORKDAYS(A8,EOMONTH(A8,0))</f>
         <v/>
       </c>
-      <c r="D8" s="71">
+      <c r="D8" s="66">
         <f>IF(ISNUMBER(MATCH(A8,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F8" s="72" t="n">
+      <c r="F8" s="67" t="n">
         <v>44531</v>
       </c>
-      <c r="G8" s="73" t="n">
+      <c r="G8" s="68" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="70">
+      <c r="A9" s="65">
         <f>EDATE(A8,1)</f>
         <v/>
       </c>
@@ -9611,15 +9782,15 @@
         <f>NETWORKDAYS(A9,EOMONTH(A9,0))</f>
         <v/>
       </c>
-      <c r="D9" s="71">
+      <c r="D9" s="66">
         <f>IF(ISNUMBER(MATCH(A9,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F9" s="72" t="n"/>
-      <c r="G9" s="73" t="n"/>
+      <c r="F9" s="67" t="n"/>
+      <c r="G9" s="68" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="70">
+      <c r="A10" s="65">
         <f>EDATE(A9,1)</f>
         <v/>
       </c>
@@ -9631,15 +9802,15 @@
         <f>NETWORKDAYS(A10,EOMONTH(A10,0))</f>
         <v/>
       </c>
-      <c r="D10" s="71">
+      <c r="D10" s="66">
         <f>IF(ISNUMBER(MATCH(A10,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F10" s="72" t="n"/>
-      <c r="G10" s="73" t="n"/>
+      <c r="F10" s="67" t="n"/>
+      <c r="G10" s="68" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="70">
+      <c r="A11" s="65">
         <f>EDATE(A10,1)</f>
         <v/>
       </c>
@@ -9651,15 +9822,15 @@
         <f>NETWORKDAYS(A11,EOMONTH(A11,0))</f>
         <v/>
       </c>
-      <c r="D11" s="71">
+      <c r="D11" s="66">
         <f>IF(ISNUMBER(MATCH(A11,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F11" s="72" t="n"/>
-      <c r="G11" s="73" t="n"/>
+      <c r="F11" s="67" t="n"/>
+      <c r="G11" s="68" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="70">
+      <c r="A12" s="65">
         <f>EDATE(A11,1)</f>
         <v/>
       </c>
@@ -9671,15 +9842,15 @@
         <f>NETWORKDAYS(A12,EOMONTH(A12,0))</f>
         <v/>
       </c>
-      <c r="D12" s="71">
+      <c r="D12" s="66">
         <f>IF(ISNUMBER(MATCH(A12,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F12" s="72" t="n"/>
-      <c r="G12" s="73" t="n"/>
+      <c r="F12" s="67" t="n"/>
+      <c r="G12" s="68" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="70">
+      <c r="A13" s="65">
         <f>EDATE(A12,1)</f>
         <v/>
       </c>
@@ -9691,15 +9862,15 @@
         <f>NETWORKDAYS(A13,EOMONTH(A13,0))</f>
         <v/>
       </c>
-      <c r="D13" s="71">
+      <c r="D13" s="66">
         <f>IF(ISNUMBER(MATCH(A13,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F13" s="72" t="n"/>
-      <c r="G13" s="73" t="n"/>
+      <c r="F13" s="67" t="n"/>
+      <c r="G13" s="68" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="70">
+      <c r="A14" s="65">
         <f>EDATE(A13,1)</f>
         <v/>
       </c>
@@ -9711,15 +9882,15 @@
         <f>NETWORKDAYS(A14,EOMONTH(A14,0))</f>
         <v/>
       </c>
-      <c r="D14" s="71">
+      <c r="D14" s="66">
         <f>IF(ISNUMBER(MATCH(A14,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F14" s="72" t="n"/>
-      <c r="G14" s="73" t="n"/>
+      <c r="F14" s="67" t="n"/>
+      <c r="G14" s="68" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="70">
+      <c r="A15" s="65">
         <f>EDATE(A14,1)</f>
         <v/>
       </c>
@@ -9731,15 +9902,15 @@
         <f>NETWORKDAYS(A15,EOMONTH(A15,0))</f>
         <v/>
       </c>
-      <c r="D15" s="71">
+      <c r="D15" s="66">
         <f>IF(ISNUMBER(MATCH(A15,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F15" s="72" t="n"/>
-      <c r="G15" s="73" t="n"/>
+      <c r="F15" s="67" t="n"/>
+      <c r="G15" s="68" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="70">
+      <c r="A16" s="65">
         <f>EDATE(A15,1)</f>
         <v/>
       </c>
@@ -9751,15 +9922,15 @@
         <f>NETWORKDAYS(A16,EOMONTH(A16,0))</f>
         <v/>
       </c>
-      <c r="D16" s="71">
+      <c r="D16" s="66">
         <f>IF(ISNUMBER(MATCH(A16,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F16" s="72" t="n"/>
-      <c r="G16" s="73" t="n"/>
+      <c r="F16" s="67" t="n"/>
+      <c r="G16" s="68" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="70">
+      <c r="A17" s="65">
         <f>EDATE(A16,1)</f>
         <v/>
       </c>
@@ -9771,15 +9942,15 @@
         <f>NETWORKDAYS(A17,EOMONTH(A17,0))</f>
         <v/>
       </c>
-      <c r="D17" s="71">
+      <c r="D17" s="66">
         <f>IF(ISNUMBER(MATCH(A17,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F17" s="72" t="n"/>
-      <c r="G17" s="73" t="n"/>
+      <c r="F17" s="67" t="n"/>
+      <c r="G17" s="68" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="70">
+      <c r="A18" s="65">
         <f>EDATE(A17,1)</f>
         <v/>
       </c>
@@ -9791,15 +9962,15 @@
         <f>NETWORKDAYS(A18,EOMONTH(A18,0))</f>
         <v/>
       </c>
-      <c r="D18" s="71">
+      <c r="D18" s="66">
         <f>IF(ISNUMBER(MATCH(A18,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F18" s="72" t="n"/>
-      <c r="G18" s="73" t="n"/>
+      <c r="F18" s="67" t="n"/>
+      <c r="G18" s="68" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="70">
+      <c r="A19" s="65">
         <f>EDATE(A18,1)</f>
         <v/>
       </c>
@@ -9811,15 +9982,15 @@
         <f>NETWORKDAYS(A19,EOMONTH(A19,0))</f>
         <v/>
       </c>
-      <c r="D19" s="71">
+      <c r="D19" s="66">
         <f>IF(ISNUMBER(MATCH(A19,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F19" s="72" t="n"/>
-      <c r="G19" s="73" t="n"/>
+      <c r="F19" s="67" t="n"/>
+      <c r="G19" s="68" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="70">
+      <c r="A20" s="65">
         <f>EDATE(A19,1)</f>
         <v/>
       </c>
@@ -9831,15 +10002,15 @@
         <f>NETWORKDAYS(A20,EOMONTH(A20,0))</f>
         <v/>
       </c>
-      <c r="D20" s="71">
+      <c r="D20" s="66">
         <f>IF(ISNUMBER(MATCH(A20,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F20" s="72" t="n"/>
-      <c r="G20" s="73" t="n"/>
+      <c r="F20" s="67" t="n"/>
+      <c r="G20" s="68" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="70">
+      <c r="A21" s="65">
         <f>EDATE(A20,1)</f>
         <v/>
       </c>
@@ -9851,15 +10022,15 @@
         <f>NETWORKDAYS(A21,EOMONTH(A21,0))</f>
         <v/>
       </c>
-      <c r="D21" s="71">
+      <c r="D21" s="66">
         <f>IF(ISNUMBER(MATCH(A21,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F21" s="72" t="n"/>
-      <c r="G21" s="73" t="n"/>
+      <c r="F21" s="67" t="n"/>
+      <c r="G21" s="68" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="70">
+      <c r="A22" s="65">
         <f>EDATE(A21,1)</f>
         <v/>
       </c>
@@ -9871,15 +10042,15 @@
         <f>NETWORKDAYS(A22,EOMONTH(A22,0))</f>
         <v/>
       </c>
-      <c r="D22" s="71">
+      <c r="D22" s="66">
         <f>IF(ISNUMBER(MATCH(A22,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F22" s="72" t="n"/>
-      <c r="G22" s="73" t="n"/>
+      <c r="F22" s="67" t="n"/>
+      <c r="G22" s="68" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="70">
+      <c r="A23" s="65">
         <f>EDATE(A22,1)</f>
         <v/>
       </c>
@@ -9891,15 +10062,15 @@
         <f>NETWORKDAYS(A23,EOMONTH(A23,0))</f>
         <v/>
       </c>
-      <c r="D23" s="71">
+      <c r="D23" s="66">
         <f>IF(ISNUMBER(MATCH(A23,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F23" s="72" t="n"/>
-      <c r="G23" s="73" t="n"/>
+      <c r="F23" s="67" t="n"/>
+      <c r="G23" s="68" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="70">
+      <c r="A24" s="65">
         <f>EDATE(A23,1)</f>
         <v/>
       </c>
@@ -9911,15 +10082,15 @@
         <f>NETWORKDAYS(A24,EOMONTH(A24,0))</f>
         <v/>
       </c>
-      <c r="D24" s="71">
+      <c r="D24" s="66">
         <f>IF(ISNUMBER(MATCH(A24,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F24" s="72" t="n"/>
-      <c r="G24" s="73" t="n"/>
+      <c r="F24" s="67" t="n"/>
+      <c r="G24" s="68" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="70">
+      <c r="A25" s="65">
         <f>EDATE(A24,1)</f>
         <v/>
       </c>
@@ -9931,15 +10102,15 @@
         <f>NETWORKDAYS(A25,EOMONTH(A25,0))</f>
         <v/>
       </c>
-      <c r="D25" s="71">
+      <c r="D25" s="66">
         <f>IF(ISNUMBER(MATCH(A25,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F25" s="72" t="n"/>
-      <c r="G25" s="73" t="n"/>
+      <c r="F25" s="67" t="n"/>
+      <c r="G25" s="68" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="70">
+      <c r="A26" s="65">
         <f>EDATE(A25,1)</f>
         <v/>
       </c>
@@ -9951,15 +10122,15 @@
         <f>NETWORKDAYS(A26,EOMONTH(A26,0))</f>
         <v/>
       </c>
-      <c r="D26" s="71">
+      <c r="D26" s="66">
         <f>IF(ISNUMBER(MATCH(A26,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F26" s="72" t="n"/>
-      <c r="G26" s="73" t="n"/>
+      <c r="F26" s="67" t="n"/>
+      <c r="G26" s="68" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="70">
+      <c r="A27" s="65">
         <f>EDATE(A26,1)</f>
         <v/>
       </c>
@@ -9971,15 +10142,15 @@
         <f>NETWORKDAYS(A27,EOMONTH(A27,0))</f>
         <v/>
       </c>
-      <c r="D27" s="71">
+      <c r="D27" s="66">
         <f>IF(ISNUMBER(MATCH(A27,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F27" s="72" t="n"/>
-      <c r="G27" s="73" t="n"/>
+      <c r="F27" s="67" t="n"/>
+      <c r="G27" s="68" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="70">
+      <c r="A28" s="65">
         <f>EDATE(A27,1)</f>
         <v/>
       </c>
@@ -9991,15 +10162,15 @@
         <f>NETWORKDAYS(A28,EOMONTH(A28,0))</f>
         <v/>
       </c>
-      <c r="D28" s="71">
+      <c r="D28" s="66">
         <f>IF(ISNUMBER(MATCH(A28,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F28" s="72" t="n"/>
-      <c r="G28" s="73" t="n"/>
+      <c r="F28" s="67" t="n"/>
+      <c r="G28" s="68" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="70">
+      <c r="A29" s="65">
         <f>EDATE(A28,1)</f>
         <v/>
       </c>
@@ -10011,15 +10182,15 @@
         <f>NETWORKDAYS(A29,EOMONTH(A29,0))</f>
         <v/>
       </c>
-      <c r="D29" s="71">
+      <c r="D29" s="66">
         <f>IF(ISNUMBER(MATCH(A29,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F29" s="72" t="n"/>
-      <c r="G29" s="73" t="n"/>
+      <c r="F29" s="67" t="n"/>
+      <c r="G29" s="68" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="70">
+      <c r="A30" s="65">
         <f>EDATE(A29,1)</f>
         <v/>
       </c>
@@ -10031,15 +10202,15 @@
         <f>NETWORKDAYS(A30,EOMONTH(A30,0))</f>
         <v/>
       </c>
-      <c r="D30" s="71">
+      <c r="D30" s="66">
         <f>IF(ISNUMBER(MATCH(A30,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F30" s="72" t="n"/>
-      <c r="G30" s="73" t="n"/>
+      <c r="F30" s="67" t="n"/>
+      <c r="G30" s="68" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="70">
+      <c r="A31" s="65">
         <f>EDATE(A30,1)</f>
         <v/>
       </c>
@@ -10051,15 +10222,15 @@
         <f>NETWORKDAYS(A31,EOMONTH(A31,0))</f>
         <v/>
       </c>
-      <c r="D31" s="71">
+      <c r="D31" s="66">
         <f>IF(ISNUMBER(MATCH(A31,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F31" s="72" t="n"/>
-      <c r="G31" s="73" t="n"/>
+      <c r="F31" s="67" t="n"/>
+      <c r="G31" s="68" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="70">
+      <c r="A32" s="65">
         <f>EDATE(A31,1)</f>
         <v/>
       </c>
@@ -10071,15 +10242,15 @@
         <f>NETWORKDAYS(A32,EOMONTH(A32,0))</f>
         <v/>
       </c>
-      <c r="D32" s="71">
+      <c r="D32" s="66">
         <f>IF(ISNUMBER(MATCH(A32,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F32" s="72" t="n"/>
-      <c r="G32" s="73" t="n"/>
+      <c r="F32" s="67" t="n"/>
+      <c r="G32" s="68" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="70">
+      <c r="A33" s="65">
         <f>EDATE(A32,1)</f>
         <v/>
       </c>
@@ -10091,15 +10262,15 @@
         <f>NETWORKDAYS(A33,EOMONTH(A33,0))</f>
         <v/>
       </c>
-      <c r="D33" s="71">
+      <c r="D33" s="66">
         <f>IF(ISNUMBER(MATCH(A33,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F33" s="72" t="n"/>
-      <c r="G33" s="73" t="n"/>
+      <c r="F33" s="67" t="n"/>
+      <c r="G33" s="68" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="70">
+      <c r="A34" s="65">
         <f>EDATE(A33,1)</f>
         <v/>
       </c>
@@ -10111,15 +10282,15 @@
         <f>NETWORKDAYS(A34,EOMONTH(A34,0))</f>
         <v/>
       </c>
-      <c r="D34" s="71">
+      <c r="D34" s="66">
         <f>IF(ISNUMBER(MATCH(A34,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F34" s="72" t="n"/>
-      <c r="G34" s="73" t="n"/>
+      <c r="F34" s="67" t="n"/>
+      <c r="G34" s="68" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="70">
+      <c r="A35" s="65">
         <f>EDATE(A34,1)</f>
         <v/>
       </c>
@@ -10131,15 +10302,15 @@
         <f>NETWORKDAYS(A35,EOMONTH(A35,0))</f>
         <v/>
       </c>
-      <c r="D35" s="71">
+      <c r="D35" s="66">
         <f>IF(ISNUMBER(MATCH(A35,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F35" s="72" t="n"/>
-      <c r="G35" s="73" t="n"/>
+      <c r="F35" s="67" t="n"/>
+      <c r="G35" s="68" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="70">
+      <c r="A36" s="65">
         <f>EDATE(A35,1)</f>
         <v/>
       </c>
@@ -10151,15 +10322,15 @@
         <f>NETWORKDAYS(A36,EOMONTH(A36,0))</f>
         <v/>
       </c>
-      <c r="D36" s="71">
+      <c r="D36" s="66">
         <f>IF(ISNUMBER(MATCH(A36,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F36" s="72" t="n"/>
-      <c r="G36" s="73" t="n"/>
+      <c r="F36" s="67" t="n"/>
+      <c r="G36" s="68" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="70">
+      <c r="A37" s="65">
         <f>EDATE(A36,1)</f>
         <v/>
       </c>
@@ -10171,15 +10342,15 @@
         <f>NETWORKDAYS(A37,EOMONTH(A37,0))</f>
         <v/>
       </c>
-      <c r="D37" s="71">
+      <c r="D37" s="66">
         <f>IF(ISNUMBER(MATCH(A37,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
-      <c r="F37" s="72" t="n"/>
-      <c r="G37" s="73" t="n"/>
+      <c r="F37" s="67" t="n"/>
+      <c r="G37" s="68" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="70">
+      <c r="A38" s="65">
         <f>EDATE(A37,1)</f>
         <v/>
       </c>
@@ -10191,13 +10362,13 @@
         <f>NETWORKDAYS(A38,EOMONTH(A38,0))</f>
         <v/>
       </c>
-      <c r="D38" s="71">
+      <c r="D38" s="66">
         <f>IF(ISNUMBER(MATCH(A38,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="70">
+      <c r="A39" s="65">
         <f>EDATE(A38,1)</f>
         <v/>
       </c>
@@ -10209,13 +10380,13 @@
         <f>NETWORKDAYS(A39,EOMONTH(A39,0))</f>
         <v/>
       </c>
-      <c r="D39" s="71">
+      <c r="D39" s="66">
         <f>IF(ISNUMBER(MATCH(A39,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="70">
+      <c r="A40" s="65">
         <f>EDATE(A39,1)</f>
         <v/>
       </c>
@@ -10227,13 +10398,13 @@
         <f>NETWORKDAYS(A40,EOMONTH(A40,0))</f>
         <v/>
       </c>
-      <c r="D40" s="71">
+      <c r="D40" s="66">
         <f>IF(ISNUMBER(MATCH(A40,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="70">
+      <c r="A41" s="65">
         <f>EDATE(A40,1)</f>
         <v/>
       </c>
@@ -10245,13 +10416,13 @@
         <f>NETWORKDAYS(A41,EOMONTH(A41,0))</f>
         <v/>
       </c>
-      <c r="D41" s="71">
+      <c r="D41" s="66">
         <f>IF(ISNUMBER(MATCH(A41,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="70">
+      <c r="A42" s="65">
         <f>EDATE(A41,1)</f>
         <v/>
       </c>
@@ -10263,13 +10434,13 @@
         <f>NETWORKDAYS(A42,EOMONTH(A42,0))</f>
         <v/>
       </c>
-      <c r="D42" s="71">
+      <c r="D42" s="66">
         <f>IF(ISNUMBER(MATCH(A42,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="70">
+      <c r="A43" s="65">
         <f>EDATE(A42,1)</f>
         <v/>
       </c>
@@ -10281,13 +10452,13 @@
         <f>NETWORKDAYS(A43,EOMONTH(A43,0))</f>
         <v/>
       </c>
-      <c r="D43" s="71">
+      <c r="D43" s="66">
         <f>IF(ISNUMBER(MATCH(A43,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="70">
+      <c r="A44" s="65">
         <f>EDATE(A43,1)</f>
         <v/>
       </c>
@@ -10299,13 +10470,13 @@
         <f>NETWORKDAYS(A44,EOMONTH(A44,0))</f>
         <v/>
       </c>
-      <c r="D44" s="71">
+      <c r="D44" s="66">
         <f>IF(ISNUMBER(MATCH(A44,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="70">
+      <c r="A45" s="65">
         <f>EDATE(A44,1)</f>
         <v/>
       </c>
@@ -10317,13 +10488,13 @@
         <f>NETWORKDAYS(A45,EOMONTH(A45,0))</f>
         <v/>
       </c>
-      <c r="D45" s="71">
+      <c r="D45" s="66">
         <f>IF(ISNUMBER(MATCH(A45,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="70">
+      <c r="A46" s="65">
         <f>EDATE(A45,1)</f>
         <v/>
       </c>
@@ -10335,13 +10506,13 @@
         <f>NETWORKDAYS(A46,EOMONTH(A46,0))</f>
         <v/>
       </c>
-      <c r="D46" s="71">
+      <c r="D46" s="66">
         <f>IF(ISNUMBER(MATCH(A46,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="70">
+      <c r="A47" s="65">
         <f>EDATE(A46,1)</f>
         <v/>
       </c>
@@ -10353,13 +10524,13 @@
         <f>NETWORKDAYS(A47,EOMONTH(A47,0))</f>
         <v/>
       </c>
-      <c r="D47" s="71">
+      <c r="D47" s="66">
         <f>IF(ISNUMBER(MATCH(A47,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="70">
+      <c r="A48" s="65">
         <f>EDATE(A47,1)</f>
         <v/>
       </c>
@@ -10371,13 +10542,13 @@
         <f>NETWORKDAYS(A48,EOMONTH(A48,0))</f>
         <v/>
       </c>
-      <c r="D48" s="71">
+      <c r="D48" s="66">
         <f>IF(ISNUMBER(MATCH(A48,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="70">
+      <c r="A49" s="65">
         <f>EDATE(A48,1)</f>
         <v/>
       </c>
@@ -10389,13 +10560,13 @@
         <f>NETWORKDAYS(A49,EOMONTH(A49,0))</f>
         <v/>
       </c>
-      <c r="D49" s="71">
+      <c r="D49" s="66">
         <f>IF(ISNUMBER(MATCH(A49,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="70">
+      <c r="A50" s="65">
         <f>EDATE(A49,1)</f>
         <v/>
       </c>
@@ -10407,13 +10578,13 @@
         <f>NETWORKDAYS(A50,EOMONTH(A50,0))</f>
         <v/>
       </c>
-      <c r="D50" s="71">
+      <c r="D50" s="66">
         <f>IF(ISNUMBER(MATCH(A50,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="70">
+      <c r="A51" s="65">
         <f>EDATE(A50,1)</f>
         <v/>
       </c>
@@ -10425,13 +10596,13 @@
         <f>NETWORKDAYS(A51,EOMONTH(A51,0))</f>
         <v/>
       </c>
-      <c r="D51" s="71">
+      <c r="D51" s="66">
         <f>IF(ISNUMBER(MATCH(A51,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="70">
+      <c r="A52" s="65">
         <f>EDATE(A51,1)</f>
         <v/>
       </c>
@@ -10443,13 +10614,13 @@
         <f>NETWORKDAYS(A52,EOMONTH(A52,0))</f>
         <v/>
       </c>
-      <c r="D52" s="71">
+      <c r="D52" s="66">
         <f>IF(ISNUMBER(MATCH(A52,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="70">
+      <c r="A53" s="65">
         <f>EDATE(A52,1)</f>
         <v/>
       </c>
@@ -10461,13 +10632,13 @@
         <f>NETWORKDAYS(A53,EOMONTH(A53,0))</f>
         <v/>
       </c>
-      <c r="D53" s="71">
+      <c r="D53" s="66">
         <f>IF(ISNUMBER(MATCH(A53,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="70">
+      <c r="A54" s="65">
         <f>EDATE(A53,1)</f>
         <v/>
       </c>
@@ -10479,13 +10650,13 @@
         <f>NETWORKDAYS(A54,EOMONTH(A54,0))</f>
         <v/>
       </c>
-      <c r="D54" s="71">
+      <c r="D54" s="66">
         <f>IF(ISNUMBER(MATCH(A54,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="70">
+      <c r="A55" s="65">
         <f>EDATE(A54,1)</f>
         <v/>
       </c>
@@ -10497,13 +10668,13 @@
         <f>NETWORKDAYS(A55,EOMONTH(A55,0))</f>
         <v/>
       </c>
-      <c r="D55" s="71">
+      <c r="D55" s="66">
         <f>IF(ISNUMBER(MATCH(A55,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="70">
+      <c r="A56" s="65">
         <f>EDATE(A55,1)</f>
         <v/>
       </c>
@@ -10515,13 +10686,13 @@
         <f>NETWORKDAYS(A56,EOMONTH(A56,0))</f>
         <v/>
       </c>
-      <c r="D56" s="71">
+      <c r="D56" s="66">
         <f>IF(ISNUMBER(MATCH(A56,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="70">
+      <c r="A57" s="65">
         <f>EDATE(A56,1)</f>
         <v/>
       </c>
@@ -10533,13 +10704,13 @@
         <f>NETWORKDAYS(A57,EOMONTH(A57,0))</f>
         <v/>
       </c>
-      <c r="D57" s="71">
+      <c r="D57" s="66">
         <f>IF(ISNUMBER(MATCH(A57,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="70">
+      <c r="A58" s="65">
         <f>EDATE(A57,1)</f>
         <v/>
       </c>
@@ -10551,13 +10722,13 @@
         <f>NETWORKDAYS(A58,EOMONTH(A58,0))</f>
         <v/>
       </c>
-      <c r="D58" s="71">
+      <c r="D58" s="66">
         <f>IF(ISNUMBER(MATCH(A58,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="70">
+      <c r="A59" s="65">
         <f>EDATE(A58,1)</f>
         <v/>
       </c>
@@ -10569,13 +10740,13 @@
         <f>NETWORKDAYS(A59,EOMONTH(A59,0))</f>
         <v/>
       </c>
-      <c r="D59" s="71">
+      <c r="D59" s="66">
         <f>IF(ISNUMBER(MATCH(A59,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="70">
+      <c r="A60" s="65">
         <f>EDATE(A59,1)</f>
         <v/>
       </c>
@@ -10587,13 +10758,13 @@
         <f>NETWORKDAYS(A60,EOMONTH(A60,0))</f>
         <v/>
       </c>
-      <c r="D60" s="71">
+      <c r="D60" s="66">
         <f>IF(ISNUMBER(MATCH(A60,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="70">
+      <c r="A61" s="65">
         <f>EDATE(A60,1)</f>
         <v/>
       </c>
@@ -10605,13 +10776,13 @@
         <f>NETWORKDAYS(A61,EOMONTH(A61,0))</f>
         <v/>
       </c>
-      <c r="D61" s="71">
+      <c r="D61" s="66">
         <f>IF(ISNUMBER(MATCH(A61,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="70">
+      <c r="A62" s="65">
         <f>EDATE(A61,1)</f>
         <v/>
       </c>
@@ -10623,13 +10794,13 @@
         <f>NETWORKDAYS(A62,EOMONTH(A62,0))</f>
         <v/>
       </c>
-      <c r="D62" s="71">
+      <c r="D62" s="66">
         <f>IF(ISNUMBER(MATCH(A62,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="70">
+      <c r="A63" s="65">
         <f>EDATE(A62,1)</f>
         <v/>
       </c>
@@ -10641,13 +10812,13 @@
         <f>NETWORKDAYS(A63,EOMONTH(A63,0))</f>
         <v/>
       </c>
-      <c r="D63" s="71">
+      <c r="D63" s="66">
         <f>IF(ISNUMBER(MATCH(A63,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="70">
+      <c r="A64" s="65">
         <f>EDATE(A63,1)</f>
         <v/>
       </c>
@@ -10659,13 +10830,13 @@
         <f>NETWORKDAYS(A64,EOMONTH(A64,0))</f>
         <v/>
       </c>
-      <c r="D64" s="71">
+      <c r="D64" s="66">
         <f>IF(ISNUMBER(MATCH(A64,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="70">
+      <c r="A65" s="65">
         <f>EDATE(A64,1)</f>
         <v/>
       </c>
@@ -10677,13 +10848,13 @@
         <f>NETWORKDAYS(A65,EOMONTH(A65,0))</f>
         <v/>
       </c>
-      <c r="D65" s="71">
+      <c r="D65" s="66">
         <f>IF(ISNUMBER(MATCH(A65,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="70">
+      <c r="A66" s="65">
         <f>EDATE(A65,1)</f>
         <v/>
       </c>
@@ -10695,13 +10866,13 @@
         <f>NETWORKDAYS(A66,EOMONTH(A66,0))</f>
         <v/>
       </c>
-      <c r="D66" s="71">
+      <c r="D66" s="66">
         <f>IF(ISNUMBER(MATCH(A66,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="70">
+      <c r="A67" s="65">
         <f>EDATE(A66,1)</f>
         <v/>
       </c>
@@ -10713,13 +10884,13 @@
         <f>NETWORKDAYS(A67,EOMONTH(A67,0))</f>
         <v/>
       </c>
-      <c r="D67" s="71">
+      <c r="D67" s="66">
         <f>IF(ISNUMBER(MATCH(A67,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="70">
+      <c r="A68" s="65">
         <f>EDATE(A67,1)</f>
         <v/>
       </c>
@@ -10731,13 +10902,13 @@
         <f>NETWORKDAYS(A68,EOMONTH(A68,0))</f>
         <v/>
       </c>
-      <c r="D68" s="71">
+      <c r="D68" s="66">
         <f>IF(ISNUMBER(MATCH(A68,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="70">
+      <c r="A69" s="65">
         <f>EDATE(A68,1)</f>
         <v/>
       </c>
@@ -10749,13 +10920,13 @@
         <f>NETWORKDAYS(A69,EOMONTH(A69,0))</f>
         <v/>
       </c>
-      <c r="D69" s="71">
+      <c r="D69" s="66">
         <f>IF(ISNUMBER(MATCH(A69,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="70">
+      <c r="A70" s="65">
         <f>EDATE(A69,1)</f>
         <v/>
       </c>
@@ -10767,13 +10938,13 @@
         <f>NETWORKDAYS(A70,EOMONTH(A70,0))</f>
         <v/>
       </c>
-      <c r="D70" s="71">
+      <c r="D70" s="66">
         <f>IF(ISNUMBER(MATCH(A70,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="70">
+      <c r="A71" s="65">
         <f>EDATE(A70,1)</f>
         <v/>
       </c>
@@ -10785,13 +10956,13 @@
         <f>NETWORKDAYS(A71,EOMONTH(A71,0))</f>
         <v/>
       </c>
-      <c r="D71" s="71">
+      <c r="D71" s="66">
         <f>IF(ISNUMBER(MATCH(A71,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="70">
+      <c r="A72" s="65">
         <f>EDATE(A71,1)</f>
         <v/>
       </c>
@@ -10803,13 +10974,13 @@
         <f>NETWORKDAYS(A72,EOMONTH(A72,0))</f>
         <v/>
       </c>
-      <c r="D72" s="71">
+      <c r="D72" s="66">
         <f>IF(ISNUMBER(MATCH(A72,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="70">
+      <c r="A73" s="65">
         <f>EDATE(A72,1)</f>
         <v/>
       </c>
@@ -10821,13 +10992,13 @@
         <f>NETWORKDAYS(A73,EOMONTH(A73,0))</f>
         <v/>
       </c>
-      <c r="D73" s="71">
+      <c r="D73" s="66">
         <f>IF(ISNUMBER(MATCH(A73,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="70">
+      <c r="A74" s="65">
         <f>EDATE(A73,1)</f>
         <v/>
       </c>
@@ -10839,13 +11010,13 @@
         <f>NETWORKDAYS(A74,EOMONTH(A74,0))</f>
         <v/>
       </c>
-      <c r="D74" s="71">
+      <c r="D74" s="66">
         <f>IF(ISNUMBER(MATCH(A74,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="70">
+      <c r="A75" s="65">
         <f>EDATE(A74,1)</f>
         <v/>
       </c>
@@ -10857,13 +11028,13 @@
         <f>NETWORKDAYS(A75,EOMONTH(A75,0))</f>
         <v/>
       </c>
-      <c r="D75" s="71">
+      <c r="D75" s="66">
         <f>IF(ISNUMBER(MATCH(A75,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="70">
+      <c r="A76" s="65">
         <f>EDATE(A75,1)</f>
         <v/>
       </c>
@@ -10875,13 +11046,13 @@
         <f>NETWORKDAYS(A76,EOMONTH(A76,0))</f>
         <v/>
       </c>
-      <c r="D76" s="71">
+      <c r="D76" s="66">
         <f>IF(ISNUMBER(MATCH(A76,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="70">
+      <c r="A77" s="65">
         <f>EDATE(A76,1)</f>
         <v/>
       </c>
@@ -10893,13 +11064,13 @@
         <f>NETWORKDAYS(A77,EOMONTH(A77,0))</f>
         <v/>
       </c>
-      <c r="D77" s="71">
+      <c r="D77" s="66">
         <f>IF(ISNUMBER(MATCH(A77,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="70">
+      <c r="A78" s="65">
         <f>EDATE(A77,1)</f>
         <v/>
       </c>
@@ -10911,13 +11082,13 @@
         <f>NETWORKDAYS(A78,EOMONTH(A78,0))</f>
         <v/>
       </c>
-      <c r="D78" s="71">
+      <c r="D78" s="66">
         <f>IF(ISNUMBER(MATCH(A78,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="70">
+      <c r="A79" s="65">
         <f>EDATE(A78,1)</f>
         <v/>
       </c>
@@ -10929,13 +11100,13 @@
         <f>NETWORKDAYS(A79,EOMONTH(A79,0))</f>
         <v/>
       </c>
-      <c r="D79" s="71">
+      <c r="D79" s="66">
         <f>IF(ISNUMBER(MATCH(A79,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="70">
+      <c r="A80" s="65">
         <f>EDATE(A79,1)</f>
         <v/>
       </c>
@@ -10947,13 +11118,13 @@
         <f>NETWORKDAYS(A80,EOMONTH(A80,0))</f>
         <v/>
       </c>
-      <c r="D80" s="71">
+      <c r="D80" s="66">
         <f>IF(ISNUMBER(MATCH(A80,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="70">
+      <c r="A81" s="65">
         <f>EDATE(A80,1)</f>
         <v/>
       </c>
@@ -10965,13 +11136,13 @@
         <f>NETWORKDAYS(A81,EOMONTH(A81,0))</f>
         <v/>
       </c>
-      <c r="D81" s="71">
+      <c r="D81" s="66">
         <f>IF(ISNUMBER(MATCH(A81,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="70">
+      <c r="A82" s="65">
         <f>EDATE(A81,1)</f>
         <v/>
       </c>
@@ -10983,13 +11154,13 @@
         <f>NETWORKDAYS(A82,EOMONTH(A82,0))</f>
         <v/>
       </c>
-      <c r="D82" s="71">
+      <c r="D82" s="66">
         <f>IF(ISNUMBER(MATCH(A82,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="70">
+      <c r="A83" s="65">
         <f>EDATE(A82,1)</f>
         <v/>
       </c>
@@ -11001,13 +11172,13 @@
         <f>NETWORKDAYS(A83,EOMONTH(A83,0))</f>
         <v/>
       </c>
-      <c r="D83" s="71">
+      <c r="D83" s="66">
         <f>IF(ISNUMBER(MATCH(A83,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="70">
+      <c r="A84" s="65">
         <f>EDATE(A83,1)</f>
         <v/>
       </c>
@@ -11019,13 +11190,13 @@
         <f>NETWORKDAYS(A84,EOMONTH(A84,0))</f>
         <v/>
       </c>
-      <c r="D84" s="71">
+      <c r="D84" s="66">
         <f>IF(ISNUMBER(MATCH(A84,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="70">
+      <c r="A85" s="65">
         <f>EDATE(A84,1)</f>
         <v/>
       </c>
@@ -11037,13 +11208,13 @@
         <f>NETWORKDAYS(A85,EOMONTH(A85,0))</f>
         <v/>
       </c>
-      <c r="D85" s="71">
+      <c r="D85" s="66">
         <f>IF(ISNUMBER(MATCH(A85,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="70">
+      <c r="A86" s="65">
         <f>EDATE(A85,1)</f>
         <v/>
       </c>
@@ -11055,13 +11226,13 @@
         <f>NETWORKDAYS(A86,EOMONTH(A86,0))</f>
         <v/>
       </c>
-      <c r="D86" s="71">
+      <c r="D86" s="66">
         <f>IF(ISNUMBER(MATCH(A86,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="70">
+      <c r="A87" s="65">
         <f>EDATE(A86,1)</f>
         <v/>
       </c>
@@ -11073,13 +11244,13 @@
         <f>NETWORKDAYS(A87,EOMONTH(A87,0))</f>
         <v/>
       </c>
-      <c r="D87" s="71">
+      <c r="D87" s="66">
         <f>IF(ISNUMBER(MATCH(A87,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="70">
+      <c r="A88" s="65">
         <f>EDATE(A87,1)</f>
         <v/>
       </c>
@@ -11091,13 +11262,13 @@
         <f>NETWORKDAYS(A88,EOMONTH(A88,0))</f>
         <v/>
       </c>
-      <c r="D88" s="71">
+      <c r="D88" s="66">
         <f>IF(ISNUMBER(MATCH(A88,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="70">
+      <c r="A89" s="65">
         <f>EDATE(A88,1)</f>
         <v/>
       </c>
@@ -11109,13 +11280,13 @@
         <f>NETWORKDAYS(A89,EOMONTH(A89,0))</f>
         <v/>
       </c>
-      <c r="D89" s="71">
+      <c r="D89" s="66">
         <f>IF(ISNUMBER(MATCH(A89,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="70">
+      <c r="A90" s="65">
         <f>EDATE(A89,1)</f>
         <v/>
       </c>
@@ -11127,13 +11298,13 @@
         <f>NETWORKDAYS(A90,EOMONTH(A90,0))</f>
         <v/>
       </c>
-      <c r="D90" s="71">
+      <c r="D90" s="66">
         <f>IF(ISNUMBER(MATCH(A90,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="70">
+      <c r="A91" s="65">
         <f>EDATE(A90,1)</f>
         <v/>
       </c>
@@ -11145,13 +11316,13 @@
         <f>NETWORKDAYS(A91,EOMONTH(A91,0))</f>
         <v/>
       </c>
-      <c r="D91" s="71">
+      <c r="D91" s="66">
         <f>IF(ISNUMBER(MATCH(A91,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="70">
+      <c r="A92" s="65">
         <f>EDATE(A91,1)</f>
         <v/>
       </c>
@@ -11163,13 +11334,13 @@
         <f>NETWORKDAYS(A92,EOMONTH(A92,0))</f>
         <v/>
       </c>
-      <c r="D92" s="71">
+      <c r="D92" s="66">
         <f>IF(ISNUMBER(MATCH(A92,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="70">
+      <c r="A93" s="65">
         <f>EDATE(A92,1)</f>
         <v/>
       </c>
@@ -11181,13 +11352,13 @@
         <f>NETWORKDAYS(A93,EOMONTH(A93,0))</f>
         <v/>
       </c>
-      <c r="D93" s="71">
+      <c r="D93" s="66">
         <f>IF(ISNUMBER(MATCH(A93,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="70">
+      <c r="A94" s="65">
         <f>EDATE(A93,1)</f>
         <v/>
       </c>
@@ -11199,13 +11370,13 @@
         <f>NETWORKDAYS(A94,EOMONTH(A94,0))</f>
         <v/>
       </c>
-      <c r="D94" s="71">
+      <c r="D94" s="66">
         <f>IF(ISNUMBER(MATCH(A94,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="70">
+      <c r="A95" s="65">
         <f>EDATE(A94,1)</f>
         <v/>
       </c>
@@ -11217,13 +11388,13 @@
         <f>NETWORKDAYS(A95,EOMONTH(A95,0))</f>
         <v/>
       </c>
-      <c r="D95" s="71">
+      <c r="D95" s="66">
         <f>IF(ISNUMBER(MATCH(A95,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="70">
+      <c r="A96" s="65">
         <f>EDATE(A95,1)</f>
         <v/>
       </c>
@@ -11235,13 +11406,13 @@
         <f>NETWORKDAYS(A96,EOMONTH(A96,0))</f>
         <v/>
       </c>
-      <c r="D96" s="71">
+      <c r="D96" s="66">
         <f>IF(ISNUMBER(MATCH(A96,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="70">
+      <c r="A97" s="65">
         <f>EDATE(A96,1)</f>
         <v/>
       </c>
@@ -11253,13 +11424,13 @@
         <f>NETWORKDAYS(A97,EOMONTH(A97,0))</f>
         <v/>
       </c>
-      <c r="D97" s="71">
+      <c r="D97" s="66">
         <f>IF(ISNUMBER(MATCH(A97,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="70">
+      <c r="A98" s="65">
         <f>EDATE(A97,1)</f>
         <v/>
       </c>
@@ -11271,13 +11442,13 @@
         <f>NETWORKDAYS(A98,EOMONTH(A98,0))</f>
         <v/>
       </c>
-      <c r="D98" s="71">
+      <c r="D98" s="66">
         <f>IF(ISNUMBER(MATCH(A98,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="70">
+      <c r="A99" s="65">
         <f>EDATE(A98,1)</f>
         <v/>
       </c>
@@ -11289,13 +11460,13 @@
         <f>NETWORKDAYS(A99,EOMONTH(A99,0))</f>
         <v/>
       </c>
-      <c r="D99" s="71">
+      <c r="D99" s="66">
         <f>IF(ISNUMBER(MATCH(A99,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="70">
+      <c r="A100" s="65">
         <f>EDATE(A99,1)</f>
         <v/>
       </c>
@@ -11307,13 +11478,13 @@
         <f>NETWORKDAYS(A100,EOMONTH(A100,0))</f>
         <v/>
       </c>
-      <c r="D100" s="71">
+      <c r="D100" s="66">
         <f>IF(ISNUMBER(MATCH(A100,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="70">
+      <c r="A101" s="65">
         <f>EDATE(A100,1)</f>
         <v/>
       </c>
@@ -11325,13 +11496,13 @@
         <f>NETWORKDAYS(A101,EOMONTH(A101,0))</f>
         <v/>
       </c>
-      <c r="D101" s="71">
+      <c r="D101" s="66">
         <f>IF(ISNUMBER(MATCH(A101,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="70">
+      <c r="A102" s="65">
         <f>EDATE(A101,1)</f>
         <v/>
       </c>
@@ -11343,13 +11514,13 @@
         <f>NETWORKDAYS(A102,EOMONTH(A102,0))</f>
         <v/>
       </c>
-      <c r="D102" s="71">
+      <c r="D102" s="66">
         <f>IF(ISNUMBER(MATCH(A102,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="70">
+      <c r="A103" s="65">
         <f>EDATE(A102,1)</f>
         <v/>
       </c>
@@ -11361,13 +11532,13 @@
         <f>NETWORKDAYS(A103,EOMONTH(A103,0))</f>
         <v/>
       </c>
-      <c r="D103" s="71">
+      <c r="D103" s="66">
         <f>IF(ISNUMBER(MATCH(A103,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="70">
+      <c r="A104" s="65">
         <f>EDATE(A103,1)</f>
         <v/>
       </c>
@@ -11379,13 +11550,13 @@
         <f>NETWORKDAYS(A104,EOMONTH(A104,0))</f>
         <v/>
       </c>
-      <c r="D104" s="71">
+      <c r="D104" s="66">
         <f>IF(ISNUMBER(MATCH(A104,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="70">
+      <c r="A105" s="65">
         <f>EDATE(A104,1)</f>
         <v/>
       </c>
@@ -11397,13 +11568,13 @@
         <f>NETWORKDAYS(A105,EOMONTH(A105,0))</f>
         <v/>
       </c>
-      <c r="D105" s="71">
+      <c r="D105" s="66">
         <f>IF(ISNUMBER(MATCH(A105,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="70">
+      <c r="A106" s="65">
         <f>EDATE(A105,1)</f>
         <v/>
       </c>
@@ -11415,13 +11586,13 @@
         <f>NETWORKDAYS(A106,EOMONTH(A106,0))</f>
         <v/>
       </c>
-      <c r="D106" s="71">
+      <c r="D106" s="66">
         <f>IF(ISNUMBER(MATCH(A106,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="70">
+      <c r="A107" s="65">
         <f>EDATE(A106,1)</f>
         <v/>
       </c>
@@ -11433,13 +11604,13 @@
         <f>NETWORKDAYS(A107,EOMONTH(A107,0))</f>
         <v/>
       </c>
-      <c r="D107" s="71">
+      <c r="D107" s="66">
         <f>IF(ISNUMBER(MATCH(A107,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="70">
+      <c r="A108" s="65">
         <f>EDATE(A107,1)</f>
         <v/>
       </c>
@@ -11451,13 +11622,13 @@
         <f>NETWORKDAYS(A108,EOMONTH(A108,0))</f>
         <v/>
       </c>
-      <c r="D108" s="71">
+      <c r="D108" s="66">
         <f>IF(ISNUMBER(MATCH(A108,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="70">
+      <c r="A109" s="65">
         <f>EDATE(A108,1)</f>
         <v/>
       </c>
@@ -11469,13 +11640,13 @@
         <f>NETWORKDAYS(A109,EOMONTH(A109,0))</f>
         <v/>
       </c>
-      <c r="D109" s="71">
+      <c r="D109" s="66">
         <f>IF(ISNUMBER(MATCH(A109,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="70">
+      <c r="A110" s="65">
         <f>EDATE(A109,1)</f>
         <v/>
       </c>
@@ -11487,13 +11658,13 @@
         <f>NETWORKDAYS(A110,EOMONTH(A110,0))</f>
         <v/>
       </c>
-      <c r="D110" s="71">
+      <c r="D110" s="66">
         <f>IF(ISNUMBER(MATCH(A110,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="70">
+      <c r="A111" s="65">
         <f>EDATE(A110,1)</f>
         <v/>
       </c>
@@ -11505,13 +11676,13 @@
         <f>NETWORKDAYS(A111,EOMONTH(A111,0))</f>
         <v/>
       </c>
-      <c r="D111" s="71">
+      <c r="D111" s="66">
         <f>IF(ISNUMBER(MATCH(A111,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="70">
+      <c r="A112" s="65">
         <f>EDATE(A111,1)</f>
         <v/>
       </c>
@@ -11523,13 +11694,13 @@
         <f>NETWORKDAYS(A112,EOMONTH(A112,0))</f>
         <v/>
       </c>
-      <c r="D112" s="71">
+      <c r="D112" s="66">
         <f>IF(ISNUMBER(MATCH(A112,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="70">
+      <c r="A113" s="65">
         <f>EDATE(A112,1)</f>
         <v/>
       </c>
@@ -11541,13 +11712,13 @@
         <f>NETWORKDAYS(A113,EOMONTH(A113,0))</f>
         <v/>
       </c>
-      <c r="D113" s="71">
+      <c r="D113" s="66">
         <f>IF(ISNUMBER(MATCH(A113,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="70">
+      <c r="A114" s="65">
         <f>EDATE(A113,1)</f>
         <v/>
       </c>
@@ -11559,13 +11730,13 @@
         <f>NETWORKDAYS(A114,EOMONTH(A114,0))</f>
         <v/>
       </c>
-      <c r="D114" s="71">
+      <c r="D114" s="66">
         <f>IF(ISNUMBER(MATCH(A114,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="70">
+      <c r="A115" s="65">
         <f>EDATE(A114,1)</f>
         <v/>
       </c>
@@ -11577,13 +11748,13 @@
         <f>NETWORKDAYS(A115,EOMONTH(A115,0))</f>
         <v/>
       </c>
-      <c r="D115" s="71">
+      <c r="D115" s="66">
         <f>IF(ISNUMBER(MATCH(A115,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="70">
+      <c r="A116" s="65">
         <f>EDATE(A115,1)</f>
         <v/>
       </c>
@@ -11595,13 +11766,13 @@
         <f>NETWORKDAYS(A116,EOMONTH(A116,0))</f>
         <v/>
       </c>
-      <c r="D116" s="71">
+      <c r="D116" s="66">
         <f>IF(ISNUMBER(MATCH(A116,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="70">
+      <c r="A117" s="65">
         <f>EDATE(A116,1)</f>
         <v/>
       </c>
@@ -11613,13 +11784,13 @@
         <f>NETWORKDAYS(A117,EOMONTH(A117,0))</f>
         <v/>
       </c>
-      <c r="D117" s="71">
+      <c r="D117" s="66">
         <f>IF(ISNUMBER(MATCH(A117,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="70">
+      <c r="A118" s="65">
         <f>EDATE(A117,1)</f>
         <v/>
       </c>
@@ -11631,13 +11802,13 @@
         <f>NETWORKDAYS(A118,EOMONTH(A118,0))</f>
         <v/>
       </c>
-      <c r="D118" s="71">
+      <c r="D118" s="66">
         <f>IF(ISNUMBER(MATCH(A118,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="70">
+      <c r="A119" s="65">
         <f>EDATE(A118,1)</f>
         <v/>
       </c>
@@ -11649,13 +11820,13 @@
         <f>NETWORKDAYS(A119,EOMONTH(A119,0))</f>
         <v/>
       </c>
-      <c r="D119" s="71">
+      <c r="D119" s="66">
         <f>IF(ISNUMBER(MATCH(A119,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="70">
+      <c r="A120" s="65">
         <f>EDATE(A119,1)</f>
         <v/>
       </c>
@@ -11667,13 +11838,13 @@
         <f>NETWORKDAYS(A120,EOMONTH(A120,0))</f>
         <v/>
       </c>
-      <c r="D120" s="71">
+      <c r="D120" s="66">
         <f>IF(ISNUMBER(MATCH(A120,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="70">
+      <c r="A121" s="65">
         <f>EDATE(A120,1)</f>
         <v/>
       </c>
@@ -11685,64 +11856,64 @@
         <f>NETWORKDAYS(A121,EOMONTH(A121,0))</f>
         <v/>
       </c>
-      <c r="D121" s="71">
+      <c r="D121" s="66">
         <f>IF(ISNUMBER(MATCH(A121,$F$8:$F$37,0)),"修正あり","")</f>
         <v/>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="74" t="n"/>
-      <c r="B122" s="74" t="n"/>
-      <c r="C122" s="74" t="n"/>
-      <c r="D122" s="74" t="n"/>
+      <c r="A122" s="69" t="n"/>
+      <c r="B122" s="69" t="n"/>
+      <c r="C122" s="69" t="n"/>
+      <c r="D122" s="69" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="74" t="n"/>
-      <c r="B123" s="74" t="n"/>
-      <c r="C123" s="74" t="n"/>
-      <c r="D123" s="74" t="n"/>
+      <c r="A123" s="69" t="n"/>
+      <c r="B123" s="69" t="n"/>
+      <c r="C123" s="69" t="n"/>
+      <c r="D123" s="69" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="74" t="n"/>
-      <c r="B124" s="74" t="n"/>
-      <c r="C124" s="74" t="n"/>
-      <c r="D124" s="74" t="n"/>
+      <c r="A124" s="69" t="n"/>
+      <c r="B124" s="69" t="n"/>
+      <c r="C124" s="69" t="n"/>
+      <c r="D124" s="69" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="74" t="n"/>
-      <c r="B125" s="74" t="n"/>
-      <c r="C125" s="74" t="n"/>
-      <c r="D125" s="74" t="n"/>
+      <c r="A125" s="69" t="n"/>
+      <c r="B125" s="69" t="n"/>
+      <c r="C125" s="69" t="n"/>
+      <c r="D125" s="69" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="74" t="n"/>
-      <c r="B126" s="74" t="n"/>
-      <c r="C126" s="74" t="n"/>
-      <c r="D126" s="74" t="n"/>
+      <c r="A126" s="69" t="n"/>
+      <c r="B126" s="69" t="n"/>
+      <c r="C126" s="69" t="n"/>
+      <c r="D126" s="69" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="74" t="n"/>
-      <c r="B127" s="74" t="n"/>
-      <c r="C127" s="74" t="n"/>
-      <c r="D127" s="74" t="n"/>
+      <c r="A127" s="69" t="n"/>
+      <c r="B127" s="69" t="n"/>
+      <c r="C127" s="69" t="n"/>
+      <c r="D127" s="69" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="74" t="n"/>
-      <c r="B128" s="74" t="n"/>
-      <c r="C128" s="74" t="n"/>
-      <c r="D128" s="74" t="n"/>
+      <c r="A128" s="69" t="n"/>
+      <c r="B128" s="69" t="n"/>
+      <c r="C128" s="69" t="n"/>
+      <c r="D128" s="69" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="74" t="n"/>
-      <c r="B129" s="74" t="n"/>
-      <c r="C129" s="74" t="n"/>
-      <c r="D129" s="74" t="n"/>
+      <c r="A129" s="69" t="n"/>
+      <c r="B129" s="69" t="n"/>
+      <c r="C129" s="69" t="n"/>
+      <c r="D129" s="69" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="74" t="n"/>
-      <c r="B130" s="74" t="n"/>
-      <c r="C130" s="74" t="n"/>
-      <c r="D130" s="74" t="n"/>
+      <c r="A130" s="69" t="n"/>
+      <c r="B130" s="69" t="n"/>
+      <c r="C130" s="69" t="n"/>
+      <c r="D130" s="69" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11791,13 +11962,19 @@
           <t>職員番号</t>
         </is>
       </c>
-      <c r="F3" s="75" t="n"/>
+      <c r="F3" s="70">
+        <f>EMP_ID</f>
+        <v/>
+      </c>
       <c r="J3" s="12" t="inlineStr">
         <is>
           <t>支給開始日（待機3日後）</t>
         </is>
       </c>
-      <c r="N3" s="76" t="n"/>
+      <c r="N3" s="71">
+        <f>P_START</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -11805,13 +11982,19 @@
           <t>氏名</t>
         </is>
       </c>
-      <c r="F4" s="77" t="n"/>
+      <c r="F4" s="72">
+        <f>EMP_NAME</f>
+        <v/>
+      </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
           <t>法定給付の末日（1年6月＋出勤）</t>
         </is>
       </c>
-      <c r="N4" s="76" t="n"/>
+      <c r="N4" s="71">
+        <f>P_LEGAL_END</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -11819,19 +12002,28 @@
           <t>請求期間</t>
         </is>
       </c>
-      <c r="F5" s="76" t="n"/>
-      <c r="G5" s="78" t="inlineStr">
+      <c r="F5" s="71">
+        <f>IF(CLAIM_FROM="","",CLAIM_FROM)</f>
+        <v/>
+      </c>
+      <c r="G5" s="73" t="inlineStr">
         <is>
           <t>～</t>
         </is>
       </c>
-      <c r="H5" s="76" t="n"/>
+      <c r="H5" s="71">
+        <f>IF(CLAIM_TO="","",CLAIM_TO)</f>
+        <v/>
+      </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
           <t>附加給付の開始日</t>
         </is>
       </c>
-      <c r="N5" s="76" t="n"/>
+      <c r="N5" s="71">
+        <f>P_ADD_START</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -11839,13 +12031,19 @@
           <t>傷病手当日額（支給開始月で固定）</t>
         </is>
       </c>
-      <c r="F6" s="79" t="n"/>
+      <c r="F6" s="74">
+        <f>DAILY_RATE</f>
+        <v/>
+      </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
           <t>附加給付の末日（+6月＋出勤）</t>
         </is>
       </c>
-      <c r="N6" s="76" t="n"/>
+      <c r="N6" s="71">
+        <f>P_ADD_END</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -11853,13 +12051,19 @@
           <t>作成日</t>
         </is>
       </c>
-      <c r="F7" s="76" t="n"/>
+      <c r="F7" s="71">
+        <f>TODAY()</f>
+        <v/>
+      </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
           <t>算定の最終日</t>
         </is>
       </c>
-      <c r="N7" s="76" t="n"/>
+      <c r="N7" s="71">
+        <f>P_FINAL</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="J8" s="12" t="inlineStr">
@@ -11867,8 +12071,14 @@
           <t>出勤による延長（月数／土日を除く日数）</t>
         </is>
       </c>
-      <c r="N8" s="80" t="n"/>
-      <c r="O8" s="81" t="n"/>
+      <c r="N8" s="75">
+        <f>EXT_MONTHS</f>
+        <v/>
+      </c>
+      <c r="O8" s="76">
+        <f>EXT_DAYS</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="42" customHeight="1" s="39">
       <c r="A9" s="18" t="inlineStr">
@@ -13345,7 +13555,7 @@
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="A10:O39">
-    <cfRule type="expression" priority="1" dxfId="2">
+    <cfRule type="expression" priority="1" dxfId="3">
       <formula>$L10="×"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13369,7 +13579,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="82" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>マクロ用の設定（シート名の文字と、メッセージの文言です。必要なときだけ直してください）</t>
         </is>
@@ -13381,7 +13591,7 @@
           <t>請求シート名の先頭</t>
         </is>
       </c>
-      <c r="B3" s="83" t="inlineStr">
+      <c r="B3" s="78" t="inlineStr">
         <is>
           <t>請求_</t>
         </is>
@@ -13393,7 +13603,7 @@
           <t>同名があるときに付ける文字</t>
         </is>
       </c>
-      <c r="B4" s="83" t="inlineStr">
+      <c r="B4" s="78" t="inlineStr">
         <is>
           <t>_</t>
         </is>
@@ -13405,7 +13615,7 @@
           <t>メッセージ：請求期間が未入力</t>
         </is>
       </c>
-      <c r="B5" s="83" t="inlineStr">
+      <c r="B5" s="78" t="inlineStr">
         <is>
           <t>請求期間の開始日と終了日を、入力シートの「請求期間（始）」「請求期間（終）」に入力してください。</t>
         </is>
@@ -13417,7 +13627,7 @@
           <t>メッセージ：開始日が終了日より後</t>
         </is>
       </c>
-      <c r="B6" s="83" t="inlineStr">
+      <c r="B6" s="78" t="inlineStr">
         <is>
           <t>請求期間の開始日が終了日より後になっています。</t>
         </is>
@@ -13429,7 +13639,7 @@
           <t>メッセージ：該当する行がない</t>
         </is>
       </c>
-      <c r="B7" s="83" t="inlineStr">
+      <c r="B7" s="78" t="inlineStr">
         <is>
           <t>この請求期間に該当する算定表の行がありません。入力シートと算定表を確認してください。</t>
         </is>
@@ -13441,7 +13651,7 @@
           <t>メッセージ：行が多すぎる</t>
         </is>
       </c>
-      <c r="B8" s="83" t="inlineStr">
+      <c r="B8" s="78" t="inlineStr">
         <is>
           <t>行数が雛形に入りきりません。請求期間を短くしてください。</t>
         </is>
@@ -13453,7 +13663,7 @@
           <t>メッセージ：完了</t>
         </is>
       </c>
-      <c r="B9" s="83" t="inlineStr">
+      <c r="B9" s="78" t="inlineStr">
         <is>
           <t>請求シートを追加しました。</t>
         </is>
@@ -13465,7 +13675,7 @@
           <t>シート名の期間の区切り</t>
         </is>
       </c>
-      <c r="B10" s="83" t="inlineStr">
+      <c r="B10" s="78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -13477,7 +13687,7 @@
           <t>雛形のシート名（コピー元）</t>
         </is>
       </c>
-      <c r="B11" s="83" t="inlineStr">
+      <c r="B11" s="78" t="inlineStr">
         <is>
           <t>請求シート雛形</t>
         </is>
@@ -13489,7 +13699,7 @@
           <t>雛形：明細の先頭行</t>
         </is>
       </c>
-      <c r="B12" s="84" t="n">
+      <c r="B12" s="79" t="n">
         <v>10</v>
       </c>
     </row>
@@ -13499,7 +13709,7 @@
           <t>雛形：明細の行数</t>
         </is>
       </c>
-      <c r="B13" s="84" t="n">
+      <c r="B13" s="79" t="n">
         <v>30</v>
       </c>
     </row>

--- a/傷病手当金算定表_v2.xlsx
+++ b/傷病手当金算定表_v2.xlsx
@@ -917,7 +917,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>・給付期間：待機3日の後に支給開始、法定給付は1年6か月、附加給付は続く6か月（傷病手当金・附加金マニュアルによる）。月の数え方は民法第140条（初日不算入）で、末日は応当日です。出勤期間があれば、丸ごと1か月は1か月、残りは土日を除く日数だけ延びます。</t>
+          <t>・給付期間：待機3日の後に支給開始、法定給付は1年6か月、附加給付は続く6か月（傷病手当金・附加金マニュアルによる）。月の数え方は民法第140条（初日不算入）で、末日は応当日です。出勤期間があれば、民法第140条で数えた月数（例：1/3〜3/3は2か月）と、残りの土日を除く日数だけ延びます。</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>※出勤した期間の開始日・終了日を、古い順に入力（10件まで）。期間のうち、丸ごと1か月ある月は「1か月」、残りは「土日を除く日数」だけ後ろにずれます。例：2/1〜3/15 → 1か月＋3/1〜3/15の土日を除く日数。</t>
+          <t>※出勤した期間の開始日・終了日を、古い順に入力（10件まで）。月は民法第140条（初日不算入）で数え、開始日の応当日までを「月数」、残りは「土日を除く日数」だけ後ろにずれます。例：1/3〜3/3 → 2か月。2/1〜3/15 → 1か月＋3/2〜3/15の土日を除く日数。</t>
         </is>
       </c>
     </row>
@@ -3072,13 +3072,13 @@
       </c>
       <c r="L84" s="18" t="inlineStr">
         <is>
-          <t>全月の始め
+          <t>月で数えた終わり
 （途中経過）</t>
         </is>
       </c>
       <c r="M84" s="18" t="inlineStr">
         <is>
-          <t>全月の終わり
+          <t>残りの始め
 （途中経過）</t>
         </is>
       </c>
@@ -3126,11 +3126,11 @@
       <c r="B86" s="63" t="n"/>
       <c r="C86" s="63" t="n"/>
       <c r="D86" s="48">
-        <f>IF(OR(L86="",M86=""),0,IF(L86&gt;M86,0,(YEAR(M86)-YEAR(L86))*12+MONTH(M86)-MONTH(L86)+1))</f>
+        <f>IF(OR(B86="",C86="",C86&lt;B86),0,MAX(0,(YEAR(C86)-YEAR(B86))*12+MONTH(C86)-MONTH(B86)-IF(EDATE(B86,(YEAR(C86)-YEAR(B86))*12+MONTH(C86)-MONTH(B86))&gt;C86,1,0)))</f>
         <v/>
       </c>
       <c r="E86" s="48">
-        <f>IF(OR(B86="",C86="",C86&lt;B86),0,NETWORKDAYS(B86,C86)-IF(D86&gt;0,NETWORKDAYS(L86,M86),0))</f>
+        <f>IF(OR(OR(B86="",C86="",C86&lt;B86),M86=""),0,NETWORKDAYS(M86,C86))</f>
         <v/>
       </c>
       <c r="F86" s="61">
@@ -3158,11 +3158,11 @@
         <v/>
       </c>
       <c r="L86" s="62">
-        <f>IF(OR(B86="",C86="",C86&lt;B86),"",IF(DAY(B86)=1,B86,EOMONTH(B86,0)+1))</f>
+        <f>IF(OR(B86="",C86="",C86&lt;B86),"",EDATE(B86,D86))</f>
         <v/>
       </c>
       <c r="M86" s="62">
-        <f>IF(OR(B86="",C86="",C86&lt;B86),"",IF(C86=EOMONTH(C86,0),C86,EOMONTH(C86,-1)))</f>
+        <f>IF(L86="","",IF(L86&gt;=C86,"",L86+1))</f>
         <v/>
       </c>
     </row>
@@ -3173,11 +3173,11 @@
       <c r="B87" s="63" t="n"/>
       <c r="C87" s="63" t="n"/>
       <c r="D87" s="48">
-        <f>IF(OR(L87="",M87=""),0,IF(L87&gt;M87,0,(YEAR(M87)-YEAR(L87))*12+MONTH(M87)-MONTH(L87)+1))</f>
+        <f>IF(OR(B87="",C87="",C87&lt;B87),0,MAX(0,(YEAR(C87)-YEAR(B87))*12+MONTH(C87)-MONTH(B87)-IF(EDATE(B87,(YEAR(C87)-YEAR(B87))*12+MONTH(C87)-MONTH(B87))&gt;C87,1,0)))</f>
         <v/>
       </c>
       <c r="E87" s="48">
-        <f>IF(OR(B87="",C87="",C87&lt;B87),0,NETWORKDAYS(B87,C87)-IF(D87&gt;0,NETWORKDAYS(L87,M87),0))</f>
+        <f>IF(OR(OR(B87="",C87="",C87&lt;B87),M87=""),0,NETWORKDAYS(M87,C87))</f>
         <v/>
       </c>
       <c r="F87" s="61">
@@ -3205,11 +3205,11 @@
         <v/>
       </c>
       <c r="L87" s="62">
-        <f>IF(OR(B87="",C87="",C87&lt;B87),"",IF(DAY(B87)=1,B87,EOMONTH(B87,0)+1))</f>
+        <f>IF(OR(B87="",C87="",C87&lt;B87),"",EDATE(B87,D87))</f>
         <v/>
       </c>
       <c r="M87" s="62">
-        <f>IF(OR(B87="",C87="",C87&lt;B87),"",IF(C87=EOMONTH(C87,0),C87,EOMONTH(C87,-1)))</f>
+        <f>IF(L87="","",IF(L87&gt;=C87,"",L87+1))</f>
         <v/>
       </c>
     </row>
@@ -3220,11 +3220,11 @@
       <c r="B88" s="63" t="n"/>
       <c r="C88" s="63" t="n"/>
       <c r="D88" s="48">
-        <f>IF(OR(L88="",M88=""),0,IF(L88&gt;M88,0,(YEAR(M88)-YEAR(L88))*12+MONTH(M88)-MONTH(L88)+1))</f>
+        <f>IF(OR(B88="",C88="",C88&lt;B88),0,MAX(0,(YEAR(C88)-YEAR(B88))*12+MONTH(C88)-MONTH(B88)-IF(EDATE(B88,(YEAR(C88)-YEAR(B88))*12+MONTH(C88)-MONTH(B88))&gt;C88,1,0)))</f>
         <v/>
       </c>
       <c r="E88" s="48">
-        <f>IF(OR(B88="",C88="",C88&lt;B88),0,NETWORKDAYS(B88,C88)-IF(D88&gt;0,NETWORKDAYS(L88,M88),0))</f>
+        <f>IF(OR(OR(B88="",C88="",C88&lt;B88),M88=""),0,NETWORKDAYS(M88,C88))</f>
         <v/>
       </c>
       <c r="F88" s="61">
@@ -3252,11 +3252,11 @@
         <v/>
       </c>
       <c r="L88" s="62">
-        <f>IF(OR(B88="",C88="",C88&lt;B88),"",IF(DAY(B88)=1,B88,EOMONTH(B88,0)+1))</f>
+        <f>IF(OR(B88="",C88="",C88&lt;B88),"",EDATE(B88,D88))</f>
         <v/>
       </c>
       <c r="M88" s="62">
-        <f>IF(OR(B88="",C88="",C88&lt;B88),"",IF(C88=EOMONTH(C88,0),C88,EOMONTH(C88,-1)))</f>
+        <f>IF(L88="","",IF(L88&gt;=C88,"",L88+1))</f>
         <v/>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
       <c r="B89" s="63" t="n"/>
       <c r="C89" s="63" t="n"/>
       <c r="D89" s="48">
-        <f>IF(OR(L89="",M89=""),0,IF(L89&gt;M89,0,(YEAR(M89)-YEAR(L89))*12+MONTH(M89)-MONTH(L89)+1))</f>
+        <f>IF(OR(B89="",C89="",C89&lt;B89),0,MAX(0,(YEAR(C89)-YEAR(B89))*12+MONTH(C89)-MONTH(B89)-IF(EDATE(B89,(YEAR(C89)-YEAR(B89))*12+MONTH(C89)-MONTH(B89))&gt;C89,1,0)))</f>
         <v/>
       </c>
       <c r="E89" s="48">
-        <f>IF(OR(B89="",C89="",C89&lt;B89),0,NETWORKDAYS(B89,C89)-IF(D89&gt;0,NETWORKDAYS(L89,M89),0))</f>
+        <f>IF(OR(OR(B89="",C89="",C89&lt;B89),M89=""),0,NETWORKDAYS(M89,C89))</f>
         <v/>
       </c>
       <c r="F89" s="61">
@@ -3299,11 +3299,11 @@
         <v/>
       </c>
       <c r="L89" s="62">
-        <f>IF(OR(B89="",C89="",C89&lt;B89),"",IF(DAY(B89)=1,B89,EOMONTH(B89,0)+1))</f>
+        <f>IF(OR(B89="",C89="",C89&lt;B89),"",EDATE(B89,D89))</f>
         <v/>
       </c>
       <c r="M89" s="62">
-        <f>IF(OR(B89="",C89="",C89&lt;B89),"",IF(C89=EOMONTH(C89,0),C89,EOMONTH(C89,-1)))</f>
+        <f>IF(L89="","",IF(L89&gt;=C89,"",L89+1))</f>
         <v/>
       </c>
     </row>
@@ -3314,11 +3314,11 @@
       <c r="B90" s="63" t="n"/>
       <c r="C90" s="63" t="n"/>
       <c r="D90" s="48">
-        <f>IF(OR(L90="",M90=""),0,IF(L90&gt;M90,0,(YEAR(M90)-YEAR(L90))*12+MONTH(M90)-MONTH(L90)+1))</f>
+        <f>IF(OR(B90="",C90="",C90&lt;B90),0,MAX(0,(YEAR(C90)-YEAR(B90))*12+MONTH(C90)-MONTH(B90)-IF(EDATE(B90,(YEAR(C90)-YEAR(B90))*12+MONTH(C90)-MONTH(B90))&gt;C90,1,0)))</f>
         <v/>
       </c>
       <c r="E90" s="48">
-        <f>IF(OR(B90="",C90="",C90&lt;B90),0,NETWORKDAYS(B90,C90)-IF(D90&gt;0,NETWORKDAYS(L90,M90),0))</f>
+        <f>IF(OR(OR(B90="",C90="",C90&lt;B90),M90=""),0,NETWORKDAYS(M90,C90))</f>
         <v/>
       </c>
       <c r="F90" s="61">
@@ -3346,11 +3346,11 @@
         <v/>
       </c>
       <c r="L90" s="62">
-        <f>IF(OR(B90="",C90="",C90&lt;B90),"",IF(DAY(B90)=1,B90,EOMONTH(B90,0)+1))</f>
+        <f>IF(OR(B90="",C90="",C90&lt;B90),"",EDATE(B90,D90))</f>
         <v/>
       </c>
       <c r="M90" s="62">
-        <f>IF(OR(B90="",C90="",C90&lt;B90),"",IF(C90=EOMONTH(C90,0),C90,EOMONTH(C90,-1)))</f>
+        <f>IF(L90="","",IF(L90&gt;=C90,"",L90+1))</f>
         <v/>
       </c>
     </row>
@@ -3361,11 +3361,11 @@
       <c r="B91" s="63" t="n"/>
       <c r="C91" s="63" t="n"/>
       <c r="D91" s="48">
-        <f>IF(OR(L91="",M91=""),0,IF(L91&gt;M91,0,(YEAR(M91)-YEAR(L91))*12+MONTH(M91)-MONTH(L91)+1))</f>
+        <f>IF(OR(B91="",C91="",C91&lt;B91),0,MAX(0,(YEAR(C91)-YEAR(B91))*12+MONTH(C91)-MONTH(B91)-IF(EDATE(B91,(YEAR(C91)-YEAR(B91))*12+MONTH(C91)-MONTH(B91))&gt;C91,1,0)))</f>
         <v/>
       </c>
       <c r="E91" s="48">
-        <f>IF(OR(B91="",C91="",C91&lt;B91),0,NETWORKDAYS(B91,C91)-IF(D91&gt;0,NETWORKDAYS(L91,M91),0))</f>
+        <f>IF(OR(OR(B91="",C91="",C91&lt;B91),M91=""),0,NETWORKDAYS(M91,C91))</f>
         <v/>
       </c>
       <c r="F91" s="61">
@@ -3393,11 +3393,11 @@
         <v/>
       </c>
       <c r="L91" s="62">
-        <f>IF(OR(B91="",C91="",C91&lt;B91),"",IF(DAY(B91)=1,B91,EOMONTH(B91,0)+1))</f>
+        <f>IF(OR(B91="",C91="",C91&lt;B91),"",EDATE(B91,D91))</f>
         <v/>
       </c>
       <c r="M91" s="62">
-        <f>IF(OR(B91="",C91="",C91&lt;B91),"",IF(C91=EOMONTH(C91,0),C91,EOMONTH(C91,-1)))</f>
+        <f>IF(L91="","",IF(L91&gt;=C91,"",L91+1))</f>
         <v/>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
       <c r="B92" s="63" t="n"/>
       <c r="C92" s="63" t="n"/>
       <c r="D92" s="48">
-        <f>IF(OR(L92="",M92=""),0,IF(L92&gt;M92,0,(YEAR(M92)-YEAR(L92))*12+MONTH(M92)-MONTH(L92)+1))</f>
+        <f>IF(OR(B92="",C92="",C92&lt;B92),0,MAX(0,(YEAR(C92)-YEAR(B92))*12+MONTH(C92)-MONTH(B92)-IF(EDATE(B92,(YEAR(C92)-YEAR(B92))*12+MONTH(C92)-MONTH(B92))&gt;C92,1,0)))</f>
         <v/>
       </c>
       <c r="E92" s="48">
-        <f>IF(OR(B92="",C92="",C92&lt;B92),0,NETWORKDAYS(B92,C92)-IF(D92&gt;0,NETWORKDAYS(L92,M92),0))</f>
+        <f>IF(OR(OR(B92="",C92="",C92&lt;B92),M92=""),0,NETWORKDAYS(M92,C92))</f>
         <v/>
       </c>
       <c r="F92" s="61">
@@ -3440,11 +3440,11 @@
         <v/>
       </c>
       <c r="L92" s="62">
-        <f>IF(OR(B92="",C92="",C92&lt;B92),"",IF(DAY(B92)=1,B92,EOMONTH(B92,0)+1))</f>
+        <f>IF(OR(B92="",C92="",C92&lt;B92),"",EDATE(B92,D92))</f>
         <v/>
       </c>
       <c r="M92" s="62">
-        <f>IF(OR(B92="",C92="",C92&lt;B92),"",IF(C92=EOMONTH(C92,0),C92,EOMONTH(C92,-1)))</f>
+        <f>IF(L92="","",IF(L92&gt;=C92,"",L92+1))</f>
         <v/>
       </c>
     </row>
@@ -3455,11 +3455,11 @@
       <c r="B93" s="63" t="n"/>
       <c r="C93" s="63" t="n"/>
       <c r="D93" s="48">
-        <f>IF(OR(L93="",M93=""),0,IF(L93&gt;M93,0,(YEAR(M93)-YEAR(L93))*12+MONTH(M93)-MONTH(L93)+1))</f>
+        <f>IF(OR(B93="",C93="",C93&lt;B93),0,MAX(0,(YEAR(C93)-YEAR(B93))*12+MONTH(C93)-MONTH(B93)-IF(EDATE(B93,(YEAR(C93)-YEAR(B93))*12+MONTH(C93)-MONTH(B93))&gt;C93,1,0)))</f>
         <v/>
       </c>
       <c r="E93" s="48">
-        <f>IF(OR(B93="",C93="",C93&lt;B93),0,NETWORKDAYS(B93,C93)-IF(D93&gt;0,NETWORKDAYS(L93,M93),0))</f>
+        <f>IF(OR(OR(B93="",C93="",C93&lt;B93),M93=""),0,NETWORKDAYS(M93,C93))</f>
         <v/>
       </c>
       <c r="F93" s="61">
@@ -3487,11 +3487,11 @@
         <v/>
       </c>
       <c r="L93" s="62">
-        <f>IF(OR(B93="",C93="",C93&lt;B93),"",IF(DAY(B93)=1,B93,EOMONTH(B93,0)+1))</f>
+        <f>IF(OR(B93="",C93="",C93&lt;B93),"",EDATE(B93,D93))</f>
         <v/>
       </c>
       <c r="M93" s="62">
-        <f>IF(OR(B93="",C93="",C93&lt;B93),"",IF(C93=EOMONTH(C93,0),C93,EOMONTH(C93,-1)))</f>
+        <f>IF(L93="","",IF(L93&gt;=C93,"",L93+1))</f>
         <v/>
       </c>
     </row>
@@ -3502,11 +3502,11 @@
       <c r="B94" s="63" t="n"/>
       <c r="C94" s="63" t="n"/>
       <c r="D94" s="48">
-        <f>IF(OR(L94="",M94=""),0,IF(L94&gt;M94,0,(YEAR(M94)-YEAR(L94))*12+MONTH(M94)-MONTH(L94)+1))</f>
+        <f>IF(OR(B94="",C94="",C94&lt;B94),0,MAX(0,(YEAR(C94)-YEAR(B94))*12+MONTH(C94)-MONTH(B94)-IF(EDATE(B94,(YEAR(C94)-YEAR(B94))*12+MONTH(C94)-MONTH(B94))&gt;C94,1,0)))</f>
         <v/>
       </c>
       <c r="E94" s="48">
-        <f>IF(OR(B94="",C94="",C94&lt;B94),0,NETWORKDAYS(B94,C94)-IF(D94&gt;0,NETWORKDAYS(L94,M94),0))</f>
+        <f>IF(OR(OR(B94="",C94="",C94&lt;B94),M94=""),0,NETWORKDAYS(M94,C94))</f>
         <v/>
       </c>
       <c r="F94" s="61">
@@ -3534,11 +3534,11 @@
         <v/>
       </c>
       <c r="L94" s="62">
-        <f>IF(OR(B94="",C94="",C94&lt;B94),"",IF(DAY(B94)=1,B94,EOMONTH(B94,0)+1))</f>
+        <f>IF(OR(B94="",C94="",C94&lt;B94),"",EDATE(B94,D94))</f>
         <v/>
       </c>
       <c r="M94" s="62">
-        <f>IF(OR(B94="",C94="",C94&lt;B94),"",IF(C94=EOMONTH(C94,0),C94,EOMONTH(C94,-1)))</f>
+        <f>IF(L94="","",IF(L94&gt;=C94,"",L94+1))</f>
         <v/>
       </c>
     </row>
@@ -3549,11 +3549,11 @@
       <c r="B95" s="63" t="n"/>
       <c r="C95" s="63" t="n"/>
       <c r="D95" s="48">
-        <f>IF(OR(L95="",M95=""),0,IF(L95&gt;M95,0,(YEAR(M95)-YEAR(L95))*12+MONTH(M95)-MONTH(L95)+1))</f>
+        <f>IF(OR(B95="",C95="",C95&lt;B95),0,MAX(0,(YEAR(C95)-YEAR(B95))*12+MONTH(C95)-MONTH(B95)-IF(EDATE(B95,(YEAR(C95)-YEAR(B95))*12+MONTH(C95)-MONTH(B95))&gt;C95,1,0)))</f>
         <v/>
       </c>
       <c r="E95" s="48">
-        <f>IF(OR(B95="",C95="",C95&lt;B95),0,NETWORKDAYS(B95,C95)-IF(D95&gt;0,NETWORKDAYS(L95,M95),0))</f>
+        <f>IF(OR(OR(B95="",C95="",C95&lt;B95),M95=""),0,NETWORKDAYS(M95,C95))</f>
         <v/>
       </c>
       <c r="F95" s="61">
@@ -3581,11 +3581,11 @@
         <v/>
       </c>
       <c r="L95" s="62">
-        <f>IF(OR(B95="",C95="",C95&lt;B95),"",IF(DAY(B95)=1,B95,EOMONTH(B95,0)+1))</f>
+        <f>IF(OR(B95="",C95="",C95&lt;B95),"",EDATE(B95,D95))</f>
         <v/>
       </c>
       <c r="M95" s="62">
-        <f>IF(OR(B95="",C95="",C95&lt;B95),"",IF(C95=EOMONTH(C95,0),C95,EOMONTH(C95,-1)))</f>
+        <f>IF(L95="","",IF(L95&gt;=C95,"",L95+1))</f>
         <v/>
       </c>
     </row>
@@ -9518,7 +9518,7 @@
     <row r="71">
       <c r="A71" s="40" t="inlineStr">
         <is>
-          <t>・出勤期間（入力シート）がある場合は、その期間を算定から除き、法定末日・附加開始日・附加末日・最終日を、出勤した分（丸ごと1か月は1か月、残りは土日を除く日数）だけ後ろにずらします。</t>
+          <t>・出勤期間（入力シート）がある場合は、その期間を算定から除き、法定末日・附加開始日・附加末日・最終日を、出勤した分（開始日の応当日で数えた月数、残りは土日を除く日数）だけ後ろにずらします。</t>
         </is>
       </c>
     </row>

--- a/傷病手当金算定表_v2.xlsx
+++ b/傷病手当金算定表_v2.xlsx
@@ -853,7 +853,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>7．請求期間ごとの内訳が必要なとき：「請求シート雛形」を複写（右クリック →「移動またはコピー」）し、複写したシートの黄色に請求期間（始・終）を入れる。マクロ AddClaimSheet でも複写できます。</t>
+          <t>7．請求期間ごとの内訳が必要なとき：「請求シート雛形」の黄色に請求期間（始・終）を入れる。マクロを取り込んだ .xlsm なら、自動で請求シートが追加される。</t>
         </is>
       </c>
     </row>
@@ -17580,7 +17580,7 @@
     <row r="49">
       <c r="A49" s="40" t="inlineStr">
         <is>
-          <t>・使い方：このシートを右クリック →「移動またはコピー」→「コピーを作成する」で複写し、複写したシートに請求期間を入れます（マクロ AddClaimSheet でも同じことができます）。</t>
+          <t>・マクロを取り込んだ .xlsm では、黄色に請求期間（始・終）を入れると、自動で新しい請求シートが追加されます（この雛形は空に戻る）。マクロがないときは、このシートを複写（右クリック →「移動またはコピー」）して、複写したシートに期間を入れます。</t>
         </is>
       </c>
       <c r="R49">

--- a/傷病手当金算定表_v2.xlsx
+++ b/傷病手当金算定表_v2.xlsx
@@ -3640,8 +3640,8 @@
     <col width="7" customWidth="1" style="39" min="2" max="2"/>
     <col width="5" customWidth="1" style="39" min="3" max="3"/>
     <col width="7" customWidth="1" style="39" min="4" max="4"/>
-    <col width="12" customWidth="1" style="39" min="5" max="5"/>
-    <col width="12" customWidth="1" style="39" min="6" max="6"/>
+    <col width="13" customWidth="1" style="39" min="5" max="5"/>
+    <col width="13" customWidth="1" style="39" min="6" max="6"/>
     <col width="9" customWidth="1" style="39" min="7" max="7"/>
     <col width="13" customWidth="1" style="39" min="8" max="8"/>
     <col width="12" customWidth="1" style="39" min="9" max="9"/>
@@ -5388,7 +5388,7 @@
     <col width="7" customWidth="1" style="39" min="2" max="2"/>
     <col width="5" customWidth="1" style="39" min="3" max="3"/>
     <col width="7" customWidth="1" style="39" min="4" max="5"/>
-    <col width="11" customWidth="1" style="39" min="6" max="7"/>
+    <col width="13" customWidth="1" style="39" min="6" max="7"/>
     <col width="9" customWidth="1" style="39" min="8" max="9"/>
     <col width="11" customWidth="1" style="39" min="10" max="10"/>
     <col width="10" customWidth="1" style="39" min="11" max="11"/>
@@ -14922,9 +14922,9 @@
     <col width="5" customWidth="1" style="39" min="3" max="3"/>
     <col width="7" customWidth="1" style="39" min="4" max="4"/>
     <col width="7" customWidth="1" style="39" min="5" max="5"/>
-    <col width="11" customWidth="1" style="39" min="6" max="6"/>
-    <col width="11" customWidth="1" style="39" min="7" max="7"/>
-    <col width="11" customWidth="1" style="39" min="8" max="8"/>
+    <col width="13" customWidth="1" style="39" min="6" max="6"/>
+    <col width="13" customWidth="1" style="39" min="7" max="7"/>
+    <col width="13" customWidth="1" style="39" min="8" max="8"/>
     <col width="9" customWidth="1" style="39" min="9" max="9"/>
     <col width="11" customWidth="1" style="39" min="10" max="10"/>
     <col width="10" customWidth="1" style="39" min="11" max="11"/>
@@ -15010,7 +15010,7 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>傷病手当日額（支給開始月で固定）</t>
+          <t>傷病手当日額（固定）</t>
         </is>
       </c>
       <c r="F6" s="73">

--- a/傷病手当金算定表_v2.xlsx
+++ b/傷病手当金算定表_v2.xlsx
@@ -1306,7 +1306,7 @@
       <c r="L5" s="63" t="n"/>
       <c r="M5" s="63" t="n"/>
     </row>
-    <row r="6" ht="27.75" customHeight="1" s="39">
+    <row r="6" ht="22" customHeight="1" s="39">
       <c r="A6" s="66" t="inlineStr">
         <is>
           <t>病気休暇の開始日</t>
@@ -1338,7 +1338,7 @@
       <c r="L6" s="63" t="n"/>
       <c r="M6" s="63" t="n"/>
     </row>
-    <row r="7" ht="27.75" customHeight="1" s="39">
+    <row r="7" ht="34" customHeight="1" s="39">
       <c r="A7" s="66" t="inlineStr">
         <is>
           <t>退職日（任意）</t>
@@ -1348,7 +1348,7 @@
       <c r="C7" s="72" t="n"/>
       <c r="D7" s="73" t="inlineStr">
         <is>
-          <t>※退職者のみ入力（在職中は空欄）。法定給付は退職後も末日まで算定</t>
+          <t>※退職者のみ入力（在職中は空欄）。法定給付は退職後も算定</t>
         </is>
       </c>
       <c r="E7" s="63" t="n"/>
@@ -1364,11 +1364,14 @@
         <f>J6+1</f>
         <v/>
       </c>
-      <c r="K7" s="63" t="n"/>
+      <c r="K7" s="71">
+        <f>IF(J9&lt;J7,"※退職のため附加給付は算定しません","")</f>
+        <v/>
+      </c>
       <c r="L7" s="63" t="n"/>
       <c r="M7" s="63" t="n"/>
     </row>
-    <row r="8" ht="54" customHeight="1" s="39">
+    <row r="8" ht="50" customHeight="1" s="39">
       <c r="A8" s="66" t="inlineStr">
         <is>
           <t>傷病手当日額の確認値（任意）</t>
@@ -1378,7 +1381,7 @@
       <c r="C8" s="74" t="n"/>
       <c r="D8" s="73" t="inlineStr">
         <is>
-          <t>※基幹の仮入力で確認した日額。入力すると全期間この額で算定。空欄なら標準報酬月額から試算（算定表で初めて〇になった月の額で固定）</t>
+          <t>※基幹で確認した日額。入力すると全期間この額で算定。空欄なら標準報酬から試算</t>
         </is>
       </c>
       <c r="E8" s="63" t="n"/>
@@ -1398,7 +1401,7 @@
       <c r="L8" s="63" t="n"/>
       <c r="M8" s="63" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="34" customHeight="1" s="39">
       <c r="A9" s="66" t="inlineStr">
         <is>
           <t>退職時附加金の受給（退職者のみ）</t>
@@ -1408,7 +1411,7 @@
       <c r="C9" s="75" t="n"/>
       <c r="D9" s="73" t="inlineStr">
         <is>
-          <t>※退職日を入力した場合のみ。「有」なら附加は退職日まで、空欄・「無」なら法定のみ</t>
+          <t>※退職日を入力した人のみ。有なら附加は退職日まで、無・空欄なら法定のみ</t>
         </is>
       </c>
       <c r="E9" s="63" t="n"/>

--- a/傷病手当金算定表_v2.xlsx
+++ b/傷病手当金算定表_v2.xlsx
@@ -1082,7 +1082,7 @@
     <row r="21">
       <c r="A21" s="62" t="inlineStr">
         <is>
-          <t>・給付期間：待機3日の後から〇×を判定し、初めて〇になった日が支給開始日です。法定給付は支給開始日から1年6か月、附加給付は続く6か月で、月は応当日の前日までです（傷病手当金・附加金マニュアルによる）。出勤期間があれば、その分だけ延びます。</t>
+          <t>・給付期間：待機3日の後から〇×を判定し、初めて〇になった日が支給開始日です。法定給付は待機後の初日から1年6か月、附加給付は続く6か月で、月は応当日の前日までです（傷病手当金・附加金マニュアルによる）。出勤期間があれば、その分だけ延びます。</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
     <row r="3">
       <c r="A3" s="65" t="inlineStr">
         <is>
-          <t>※月の数え方は応当日の前日まで（例：7/25から1年6か月 → 翌々年1/24）。支給開始日は、算定表で初めて〇になった日です。</t>
+          <t>※月の数え方は応当日の前日まで（例：待機後の初日7/25から1年6か月 → 翌々年1/24）。1年6か月は待機後の初日から数え、傷病手当日額は算定表で初めて〇になった月の額で固定します。</t>
         </is>
       </c>
       <c r="B3" s="63" t="n"/>
@@ -1290,7 +1290,7 @@
       <c r="F5" s="63" t="n"/>
       <c r="G5" s="65" t="inlineStr">
         <is>
-          <t>支給開始日（初めて〇になった日）</t>
+          <t>初めて〇になった日（日額の基準）</t>
         </is>
       </c>
       <c r="H5" s="63" t="n"/>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="68">
-        <f>EDATE($J$5,18)-1</f>
+        <f>EDATE($J$4,18)-1</f>
         <v/>
       </c>
       <c r="L85" s="87" t="n"/>
@@ -3904,7 +3904,7 @@
         <v/>
       </c>
       <c r="F86" s="90">
-        <f>IF(OR(B86="",C86=""),"",IF(C86&lt;B86,"日付エラー",IF(B86&lt;$J$5,"対象外",IF(B86&lt;=K85,"法定",IF(B86&lt;=WORKDAY(EDATE(K85+1,6+I85)-1,J85),"附加","対象外")))))</f>
+        <f>IF(OR(B86="",C86=""),"",IF(C86&lt;B86,"日付エラー",IF(B86&lt;$J$4,"対象外",IF(B86&lt;=K85,"法定",IF(B86&lt;=WORKDAY(EDATE(K85+1,6+I85)-1,J85),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G86" s="81">
@@ -3924,7 +3924,7 @@
         <v/>
       </c>
       <c r="K86" s="68">
-        <f>WORKDAY(EDATE($J$5,18+G86)-1,H86)</f>
+        <f>WORKDAY(EDATE($J$4,18+G86)-1,H86)</f>
         <v/>
       </c>
       <c r="L86" s="68">
@@ -3951,7 +3951,7 @@
         <v/>
       </c>
       <c r="F87" s="90">
-        <f>IF(OR(B87="",C87=""),"",IF(C87&lt;B87,"日付エラー",IF(B87&lt;$J$5,"対象外",IF(B87&lt;=K86,"法定",IF(B87&lt;=WORKDAY(EDATE(K86+1,6+I86)-1,J86),"附加","対象外")))))</f>
+        <f>IF(OR(B87="",C87=""),"",IF(C87&lt;B87,"日付エラー",IF(B87&lt;$J$4,"対象外",IF(B87&lt;=K86,"法定",IF(B87&lt;=WORKDAY(EDATE(K86+1,6+I86)-1,J86),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G87" s="81">
@@ -3971,7 +3971,7 @@
         <v/>
       </c>
       <c r="K87" s="68">
-        <f>WORKDAY(EDATE($J$5,18+G87)-1,H87)</f>
+        <f>WORKDAY(EDATE($J$4,18+G87)-1,H87)</f>
         <v/>
       </c>
       <c r="L87" s="68">
@@ -3998,7 +3998,7 @@
         <v/>
       </c>
       <c r="F88" s="90">
-        <f>IF(OR(B88="",C88=""),"",IF(C88&lt;B88,"日付エラー",IF(B88&lt;$J$5,"対象外",IF(B88&lt;=K87,"法定",IF(B88&lt;=WORKDAY(EDATE(K87+1,6+I87)-1,J87),"附加","対象外")))))</f>
+        <f>IF(OR(B88="",C88=""),"",IF(C88&lt;B88,"日付エラー",IF(B88&lt;$J$4,"対象外",IF(B88&lt;=K87,"法定",IF(B88&lt;=WORKDAY(EDATE(K87+1,6+I87)-1,J87),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G88" s="81">
@@ -4018,7 +4018,7 @@
         <v/>
       </c>
       <c r="K88" s="68">
-        <f>WORKDAY(EDATE($J$5,18+G88)-1,H88)</f>
+        <f>WORKDAY(EDATE($J$4,18+G88)-1,H88)</f>
         <v/>
       </c>
       <c r="L88" s="68">
@@ -4045,7 +4045,7 @@
         <v/>
       </c>
       <c r="F89" s="90">
-        <f>IF(OR(B89="",C89=""),"",IF(C89&lt;B89,"日付エラー",IF(B89&lt;$J$5,"対象外",IF(B89&lt;=K88,"法定",IF(B89&lt;=WORKDAY(EDATE(K88+1,6+I88)-1,J88),"附加","対象外")))))</f>
+        <f>IF(OR(B89="",C89=""),"",IF(C89&lt;B89,"日付エラー",IF(B89&lt;$J$4,"対象外",IF(B89&lt;=K88,"法定",IF(B89&lt;=WORKDAY(EDATE(K88+1,6+I88)-1,J88),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G89" s="81">
@@ -4065,7 +4065,7 @@
         <v/>
       </c>
       <c r="K89" s="68">
-        <f>WORKDAY(EDATE($J$5,18+G89)-1,H89)</f>
+        <f>WORKDAY(EDATE($J$4,18+G89)-1,H89)</f>
         <v/>
       </c>
       <c r="L89" s="68">
@@ -4092,7 +4092,7 @@
         <v/>
       </c>
       <c r="F90" s="90">
-        <f>IF(OR(B90="",C90=""),"",IF(C90&lt;B90,"日付エラー",IF(B90&lt;$J$5,"対象外",IF(B90&lt;=K89,"法定",IF(B90&lt;=WORKDAY(EDATE(K89+1,6+I89)-1,J89),"附加","対象外")))))</f>
+        <f>IF(OR(B90="",C90=""),"",IF(C90&lt;B90,"日付エラー",IF(B90&lt;$J$4,"対象外",IF(B90&lt;=K89,"法定",IF(B90&lt;=WORKDAY(EDATE(K89+1,6+I89)-1,J89),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G90" s="81">
@@ -4112,7 +4112,7 @@
         <v/>
       </c>
       <c r="K90" s="68">
-        <f>WORKDAY(EDATE($J$5,18+G90)-1,H90)</f>
+        <f>WORKDAY(EDATE($J$4,18+G90)-1,H90)</f>
         <v/>
       </c>
       <c r="L90" s="68">
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F91" s="90">
-        <f>IF(OR(B91="",C91=""),"",IF(C91&lt;B91,"日付エラー",IF(B91&lt;$J$5,"対象外",IF(B91&lt;=K90,"法定",IF(B91&lt;=WORKDAY(EDATE(K90+1,6+I90)-1,J90),"附加","対象外")))))</f>
+        <f>IF(OR(B91="",C91=""),"",IF(C91&lt;B91,"日付エラー",IF(B91&lt;$J$4,"対象外",IF(B91&lt;=K90,"法定",IF(B91&lt;=WORKDAY(EDATE(K90+1,6+I90)-1,J90),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G91" s="81">
@@ -4159,7 +4159,7 @@
         <v/>
       </c>
       <c r="K91" s="68">
-        <f>WORKDAY(EDATE($J$5,18+G91)-1,H91)</f>
+        <f>WORKDAY(EDATE($J$4,18+G91)-1,H91)</f>
         <v/>
       </c>
       <c r="L91" s="68">
@@ -4186,7 +4186,7 @@
         <v/>
       </c>
       <c r="F92" s="90">
-        <f>IF(OR(B92="",C92=""),"",IF(C92&lt;B92,"日付エラー",IF(B92&lt;$J$5,"対象外",IF(B92&lt;=K91,"法定",IF(B92&lt;=WORKDAY(EDATE(K91+1,6+I91)-1,J91),"附加","対象外")))))</f>
+        <f>IF(OR(B92="",C92=""),"",IF(C92&lt;B92,"日付エラー",IF(B92&lt;$J$4,"対象外",IF(B92&lt;=K91,"法定",IF(B92&lt;=WORKDAY(EDATE(K91+1,6+I91)-1,J91),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G92" s="81">
@@ -4206,7 +4206,7 @@
         <v/>
       </c>
       <c r="K92" s="68">
-        <f>WORKDAY(EDATE($J$5,18+G92)-1,H92)</f>
+        <f>WORKDAY(EDATE($J$4,18+G92)-1,H92)</f>
         <v/>
       </c>
       <c r="L92" s="68">
@@ -4233,7 +4233,7 @@
         <v/>
       </c>
       <c r="F93" s="90">
-        <f>IF(OR(B93="",C93=""),"",IF(C93&lt;B93,"日付エラー",IF(B93&lt;$J$5,"対象外",IF(B93&lt;=K92,"法定",IF(B93&lt;=WORKDAY(EDATE(K92+1,6+I92)-1,J92),"附加","対象外")))))</f>
+        <f>IF(OR(B93="",C93=""),"",IF(C93&lt;B93,"日付エラー",IF(B93&lt;$J$4,"対象外",IF(B93&lt;=K92,"法定",IF(B93&lt;=WORKDAY(EDATE(K92+1,6+I92)-1,J92),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G93" s="81">
@@ -4253,7 +4253,7 @@
         <v/>
       </c>
       <c r="K93" s="68">
-        <f>WORKDAY(EDATE($J$5,18+G93)-1,H93)</f>
+        <f>WORKDAY(EDATE($J$4,18+G93)-1,H93)</f>
         <v/>
       </c>
       <c r="L93" s="68">
@@ -4280,7 +4280,7 @@
         <v/>
       </c>
       <c r="F94" s="90">
-        <f>IF(OR(B94="",C94=""),"",IF(C94&lt;B94,"日付エラー",IF(B94&lt;$J$5,"対象外",IF(B94&lt;=K93,"法定",IF(B94&lt;=WORKDAY(EDATE(K93+1,6+I93)-1,J93),"附加","対象外")))))</f>
+        <f>IF(OR(B94="",C94=""),"",IF(C94&lt;B94,"日付エラー",IF(B94&lt;$J$4,"対象外",IF(B94&lt;=K93,"法定",IF(B94&lt;=WORKDAY(EDATE(K93+1,6+I93)-1,J93),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G94" s="81">
@@ -4300,7 +4300,7 @@
         <v/>
       </c>
       <c r="K94" s="68">
-        <f>WORKDAY(EDATE($J$5,18+G94)-1,H94)</f>
+        <f>WORKDAY(EDATE($J$4,18+G94)-1,H94)</f>
         <v/>
       </c>
       <c r="L94" s="68">
@@ -4327,7 +4327,7 @@
         <v/>
       </c>
       <c r="F95" s="90">
-        <f>IF(OR(B95="",C95=""),"",IF(C95&lt;B95,"日付エラー",IF(B95&lt;$J$5,"対象外",IF(B95&lt;=K94,"法定",IF(B95&lt;=WORKDAY(EDATE(K94+1,6+I94)-1,J94),"附加","対象外")))))</f>
+        <f>IF(OR(B95="",C95=""),"",IF(C95&lt;B95,"日付エラー",IF(B95&lt;$J$4,"対象外",IF(B95&lt;=K94,"法定",IF(B95&lt;=WORKDAY(EDATE(K94+1,6+I94)-1,J94),"附加","対象外")))))</f>
         <v/>
       </c>
       <c r="G95" s="81">
@@ -4347,7 +4347,7 @@
         <v/>
       </c>
       <c r="K95" s="68">
-        <f>WORKDAY(EDATE($J$5,18+G95)-1,H95)</f>
+        <f>WORKDAY(EDATE($J$4,18+G95)-1,H95)</f>
         <v/>
       </c>
       <c r="L95" s="68">
@@ -13780,7 +13780,7 @@
     <row r="73">
       <c r="A73" s="105" t="inlineStr">
         <is>
-          <t>・月の数え方は応当日の前日までです。法定給付の末日＝支給開始日から1年6か月後の応当日の前日、附加給付の末日＝その翌日から6か月後の応当日の前日。支給開始日は、算定表で初めて〇になった日です。</t>
+          <t>・月の数え方は応当日の前日までです。法定給付の末日＝待機後の初日から1年6か月後の応当日の前日、附加給付の末日＝その翌日から6か月後の応当日の前日。傷病手当日額は、算定表で初めて〇になった月の額で固定します。</t>
         </is>
       </c>
       <c r="B73" s="63" t="n"/>
